--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\zlaatanew\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\zlaata\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15995E10-E53C-4A35-8FC4-31702BC990F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AD519D-BC4E-43CE-A5E3-68DC2309AE84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4780" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5411" uniqueCount="628">
   <si>
     <t>S.No</t>
   </si>
@@ -1841,13 +1841,82 @@
   </si>
   <si>
     <t>Verify Accessories, Recently Viewed, and Top Selling buttons on Checkout page</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_ADM_01</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_ADM_01</t>
+  </si>
+  <si>
+    <t>Verify banner upload on home page section</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/home-page-banner</t>
+  </si>
+  <si>
+    <t>Sort by</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_ADM_02</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/product</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_ADM_02</t>
+  </si>
+  <si>
+    <t>Verify Top Selling Section Product Display on Homepage.</t>
+  </si>
+  <si>
+    <t>ProductListingName</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_ADM_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_ADM_03</t>
+  </si>
+  <si>
+    <t>Verify New Arrivals Section Product Display on Homepage.</t>
+  </si>
+  <si>
+    <t>Admin Page</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_ADM_04</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_ADM_04</t>
+  </si>
+  <si>
+    <t>Verify Category Section Display on Website.</t>
+  </si>
+  <si>
+    <t>Banner Title</t>
+  </si>
+  <si>
+    <t>Home Page Test</t>
+  </si>
+  <si>
+    <t>Saroj Test</t>
+  </si>
+  <si>
+    <t>sun flower</t>
+  </si>
+  <si>
+    <t>Flower Red Test</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1945,6 +2014,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -2008,7 +2083,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -2224,12 +2299,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2424,6 +2538,18 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2438,6 +2564,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2457,8 +2586,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3262,21 +3391,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z167"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Z172"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="118.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+    <col min="4" max="4" width="118.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3308,7 +3437,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="28">
         <v>1</v>
       </c>
@@ -3340,7 +3469,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="28">
         <v>2</v>
       </c>
@@ -3372,7 +3501,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="28">
         <v>3</v>
       </c>
@@ -3404,7 +3533,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="28">
         <v>4</v>
       </c>
@@ -3436,7 +3565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="28">
         <v>5</v>
       </c>
@@ -3468,7 +3597,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="28">
         <v>6</v>
       </c>
@@ -3500,7 +3629,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="28">
         <v>7</v>
       </c>
@@ -3532,7 +3661,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="28">
         <v>8</v>
       </c>
@@ -3564,7 +3693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="28">
         <v>9</v>
       </c>
@@ -3596,7 +3725,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="28">
         <v>10</v>
       </c>
@@ -3628,7 +3757,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="28">
         <v>11</v>
       </c>
@@ -3660,7 +3789,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="28">
         <v>12</v>
       </c>
@@ -3692,7 +3821,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="28">
         <v>13</v>
       </c>
@@ -3724,7 +3853,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="28">
         <v>14</v>
       </c>
@@ -3756,7 +3885,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="28">
         <v>15</v>
       </c>
@@ -3788,7 +3917,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="28">
         <v>16</v>
       </c>
@@ -3820,7 +3949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="28">
         <v>17</v>
       </c>
@@ -3852,7 +3981,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="28">
         <v>18</v>
       </c>
@@ -3884,7 +4013,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="28">
         <v>19</v>
       </c>
@@ -3916,7 +4045,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="28">
         <v>20</v>
       </c>
@@ -3948,7 +4077,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="28">
         <v>21</v>
       </c>
@@ -3980,7 +4109,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="45">
         <v>22</v>
       </c>
@@ -4012,21 +4141,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="83" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="88" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="84"/>
-      <c r="C24" s="84"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="85"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="90"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>1</v>
       </c>
@@ -4058,7 +4187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>2</v>
       </c>
@@ -4090,7 +4219,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>3</v>
       </c>
@@ -4122,7 +4251,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>4</v>
       </c>
@@ -4154,7 +4283,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>5</v>
       </c>
@@ -4186,7 +4315,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>6</v>
       </c>
@@ -4218,7 +4347,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>7</v>
       </c>
@@ -4250,7 +4379,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>8</v>
       </c>
@@ -4282,7 +4411,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>9</v>
       </c>
@@ -4314,7 +4443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>10</v>
       </c>
@@ -4346,7 +4475,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>11</v>
       </c>
@@ -4378,7 +4507,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>12</v>
       </c>
@@ -4410,21 +4539,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="86" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="91" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="87"/>
-      <c r="C37" s="87"/>
-      <c r="D37" s="87"/>
-      <c r="E37" s="87"/>
-      <c r="F37" s="87"/>
-      <c r="G37" s="87"/>
-      <c r="H37" s="87"/>
-      <c r="I37" s="87"/>
-      <c r="J37" s="88"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="92"/>
+      <c r="C37" s="92"/>
+      <c r="D37" s="92"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="92"/>
+      <c r="H37" s="92"/>
+      <c r="I37" s="92"/>
+      <c r="J37" s="93"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>1</v>
       </c>
@@ -4456,7 +4585,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>2</v>
       </c>
@@ -4488,7 +4617,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>3</v>
       </c>
@@ -4520,7 +4649,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>4</v>
       </c>
@@ -4552,7 +4681,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>5</v>
       </c>
@@ -4584,7 +4713,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>6</v>
       </c>
@@ -4616,7 +4745,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>7</v>
       </c>
@@ -4648,7 +4777,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>8</v>
       </c>
@@ -4680,7 +4809,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>9</v>
       </c>
@@ -4712,7 +4841,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>10</v>
       </c>
@@ -4744,7 +4873,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>11</v>
       </c>
@@ -4776,7 +4905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
         <v>12</v>
       </c>
@@ -4808,7 +4937,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>13</v>
       </c>
@@ -4840,21 +4969,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="86" t="s">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="91" t="s">
         <v>245</v>
       </c>
-      <c r="B51" s="87"/>
-      <c r="C51" s="87"/>
-      <c r="D51" s="87"/>
-      <c r="E51" s="87"/>
-      <c r="F51" s="87"/>
-      <c r="G51" s="87"/>
-      <c r="H51" s="87"/>
-      <c r="I51" s="87"/>
-      <c r="J51" s="88"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="92"/>
+      <c r="C51" s="92"/>
+      <c r="D51" s="92"/>
+      <c r="E51" s="92"/>
+      <c r="F51" s="92"/>
+      <c r="G51" s="92"/>
+      <c r="H51" s="92"/>
+      <c r="I51" s="92"/>
+      <c r="J51" s="93"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="25">
         <v>1</v>
       </c>
@@ -4886,7 +5015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="25">
         <v>2</v>
       </c>
@@ -4918,7 +5047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="25">
         <v>3</v>
       </c>
@@ -4950,7 +5079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="25">
         <v>4</v>
       </c>
@@ -4982,7 +5111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="25">
         <v>5</v>
       </c>
@@ -5014,7 +5143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="25">
         <v>6</v>
       </c>
@@ -5046,7 +5175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="25">
         <v>7</v>
       </c>
@@ -5078,7 +5207,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="25">
         <v>8</v>
       </c>
@@ -5110,7 +5239,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="25">
         <v>9</v>
       </c>
@@ -5142,7 +5271,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="25">
         <v>10</v>
       </c>
@@ -5174,21 +5303,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="86" t="s">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="91" t="s">
         <v>247</v>
       </c>
-      <c r="B62" s="87"/>
-      <c r="C62" s="87"/>
-      <c r="D62" s="87"/>
-      <c r="E62" s="87"/>
-      <c r="F62" s="87"/>
-      <c r="G62" s="87"/>
-      <c r="H62" s="87"/>
-      <c r="I62" s="87"/>
-      <c r="J62" s="88"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="92"/>
+      <c r="C62" s="92"/>
+      <c r="D62" s="92"/>
+      <c r="E62" s="92"/>
+      <c r="F62" s="92"/>
+      <c r="G62" s="92"/>
+      <c r="H62" s="92"/>
+      <c r="I62" s="92"/>
+      <c r="J62" s="93"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="25">
         <v>1</v>
       </c>
@@ -5220,7 +5349,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="25">
         <v>2</v>
       </c>
@@ -5252,7 +5381,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="25">
         <v>3</v>
       </c>
@@ -5284,7 +5413,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="25">
         <v>4</v>
       </c>
@@ -5316,7 +5445,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="25">
         <v>5</v>
       </c>
@@ -5348,7 +5477,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="25">
         <v>6</v>
       </c>
@@ -5380,7 +5509,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="25">
         <v>7</v>
       </c>
@@ -5412,7 +5541,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="25">
         <v>8</v>
       </c>
@@ -5444,7 +5573,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="25">
         <v>9</v>
       </c>
@@ -5476,7 +5605,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="25">
         <v>10</v>
       </c>
@@ -5508,7 +5637,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="25">
         <v>11</v>
       </c>
@@ -5540,21 +5669,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="86" t="s">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="91" t="s">
         <v>346</v>
       </c>
-      <c r="B74" s="87"/>
-      <c r="C74" s="87"/>
-      <c r="D74" s="87"/>
-      <c r="E74" s="87"/>
-      <c r="F74" s="87"/>
-      <c r="G74" s="87"/>
-      <c r="H74" s="87"/>
-      <c r="I74" s="87"/>
-      <c r="J74" s="88"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B74" s="92"/>
+      <c r="C74" s="92"/>
+      <c r="D74" s="92"/>
+      <c r="E74" s="92"/>
+      <c r="F74" s="92"/>
+      <c r="G74" s="92"/>
+      <c r="H74" s="92"/>
+      <c r="I74" s="92"/>
+      <c r="J74" s="93"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="25">
         <v>1</v>
       </c>
@@ -5586,7 +5715,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="25">
         <v>2</v>
       </c>
@@ -5618,7 +5747,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="25">
         <v>3</v>
       </c>
@@ -5650,7 +5779,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="25">
         <v>4</v>
       </c>
@@ -5682,7 +5811,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="25">
         <v>5</v>
       </c>
@@ -5714,7 +5843,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="25">
         <v>6</v>
       </c>
@@ -5746,7 +5875,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="25">
         <v>7</v>
       </c>
@@ -5778,7 +5907,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="25">
         <v>8</v>
       </c>
@@ -5810,7 +5939,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="25">
         <v>9</v>
       </c>
@@ -5842,7 +5971,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="25">
         <v>10</v>
       </c>
@@ -5874,7 +6003,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="25">
         <v>11</v>
       </c>
@@ -5906,7 +6035,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="25">
         <v>12</v>
       </c>
@@ -5938,7 +6067,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="25">
         <v>13</v>
       </c>
@@ -5970,7 +6099,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="25">
         <v>14</v>
       </c>
@@ -6002,7 +6131,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="25">
         <v>15</v>
       </c>
@@ -6034,7 +6163,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="25">
         <v>16</v>
       </c>
@@ -6066,7 +6195,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="25">
         <v>17</v>
       </c>
@@ -6098,7 +6227,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="25">
         <v>18</v>
       </c>
@@ -6130,7 +6259,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="25">
         <v>19</v>
       </c>
@@ -6162,7 +6291,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="25">
         <v>20</v>
       </c>
@@ -6194,7 +6323,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="25">
         <v>21</v>
       </c>
@@ -6226,7 +6355,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="25">
         <v>22</v>
       </c>
@@ -6258,7 +6387,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="25">
         <v>23</v>
       </c>
@@ -6290,7 +6419,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="25">
         <v>24</v>
       </c>
@@ -6322,7 +6451,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="25">
         <v>25</v>
       </c>
@@ -6354,7 +6483,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="25">
         <v>27</v>
       </c>
@@ -6386,7 +6515,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="25">
         <v>28</v>
       </c>
@@ -6418,21 +6547,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A102" s="89" t="s">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102" s="87" t="s">
         <v>376</v>
       </c>
-      <c r="B102" s="89"/>
-      <c r="C102" s="89"/>
-      <c r="D102" s="89"/>
-      <c r="E102" s="89"/>
-      <c r="F102" s="89"/>
-      <c r="G102" s="89"/>
-      <c r="H102" s="89"/>
-      <c r="I102" s="89"/>
-      <c r="J102" s="89"/>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B102" s="87"/>
+      <c r="C102" s="87"/>
+      <c r="D102" s="87"/>
+      <c r="E102" s="87"/>
+      <c r="F102" s="87"/>
+      <c r="G102" s="87"/>
+      <c r="H102" s="87"/>
+      <c r="I102" s="87"/>
+      <c r="J102" s="87"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="25">
         <v>1</v>
       </c>
@@ -6464,7 +6593,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="25">
         <v>2</v>
       </c>
@@ -6496,7 +6625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="25">
         <v>3</v>
       </c>
@@ -6528,7 +6657,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="25">
         <v>4</v>
       </c>
@@ -6560,7 +6689,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
         <v>5</v>
       </c>
@@ -6592,7 +6721,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="25">
         <v>6</v>
       </c>
@@ -6624,7 +6753,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="25">
         <v>7</v>
       </c>
@@ -6656,7 +6785,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="25">
         <v>8</v>
       </c>
@@ -6688,7 +6817,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="25">
         <v>9</v>
       </c>
@@ -6720,7 +6849,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="25">
         <v>9</v>
       </c>
@@ -6752,21 +6881,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A113" s="78" t="s">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A113" s="82" t="s">
         <v>378</v>
       </c>
-      <c r="B113" s="78"/>
-      <c r="C113" s="78"/>
-      <c r="D113" s="78"/>
-      <c r="E113" s="78"/>
-      <c r="F113" s="78"/>
-      <c r="G113" s="78"/>
-      <c r="H113" s="78"/>
-      <c r="I113" s="78"/>
-      <c r="J113" s="78"/>
-    </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B113" s="82"/>
+      <c r="C113" s="82"/>
+      <c r="D113" s="82"/>
+      <c r="E113" s="82"/>
+      <c r="F113" s="82"/>
+      <c r="G113" s="82"/>
+      <c r="H113" s="82"/>
+      <c r="I113" s="82"/>
+      <c r="J113" s="82"/>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="25">
         <v>1</v>
       </c>
@@ -6798,21 +6927,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="78" t="s">
+    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="82" t="s">
         <v>383</v>
       </c>
-      <c r="B115" s="78"/>
-      <c r="C115" s="78"/>
-      <c r="D115" s="78"/>
-      <c r="E115" s="78"/>
-      <c r="F115" s="78"/>
-      <c r="G115" s="78"/>
-      <c r="H115" s="78"/>
-      <c r="I115" s="78"/>
-      <c r="J115" s="78"/>
-    </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B115" s="82"/>
+      <c r="C115" s="82"/>
+      <c r="D115" s="82"/>
+      <c r="E115" s="82"/>
+      <c r="F115" s="82"/>
+      <c r="G115" s="82"/>
+      <c r="H115" s="82"/>
+      <c r="I115" s="82"/>
+      <c r="J115" s="82"/>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" s="25">
         <v>1</v>
       </c>
@@ -6844,21 +6973,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="78" t="s">
+    <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="82" t="s">
         <v>396</v>
       </c>
-      <c r="B117" s="78"/>
-      <c r="C117" s="78"/>
-      <c r="D117" s="78"/>
-      <c r="E117" s="78"/>
-      <c r="F117" s="78"/>
-      <c r="G117" s="78"/>
-      <c r="H117" s="78"/>
-      <c r="I117" s="78"/>
-      <c r="J117" s="78"/>
-    </row>
-    <row r="118" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B117" s="82"/>
+      <c r="C117" s="82"/>
+      <c r="D117" s="82"/>
+      <c r="E117" s="82"/>
+      <c r="F117" s="82"/>
+      <c r="G117" s="82"/>
+      <c r="H117" s="82"/>
+      <c r="I117" s="82"/>
+      <c r="J117" s="82"/>
+    </row>
+    <row r="118" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="25">
         <v>1</v>
       </c>
@@ -6904,7 +7033,7 @@
       <c r="W118" s="58"/>
       <c r="X118" s="58"/>
     </row>
-    <row r="119" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="25">
         <v>2</v>
       </c>
@@ -6950,7 +7079,7 @@
       <c r="W119" s="58"/>
       <c r="X119" s="58"/>
     </row>
-    <row r="120" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="25">
         <v>3</v>
       </c>
@@ -6996,7 +7125,7 @@
       <c r="W120" s="58"/>
       <c r="X120" s="58"/>
     </row>
-    <row r="121" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="25">
         <v>4</v>
       </c>
@@ -7042,7 +7171,7 @@
       <c r="W121" s="58"/>
       <c r="X121" s="58"/>
     </row>
-    <row r="122" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="25">
         <v>5</v>
       </c>
@@ -7088,7 +7217,7 @@
       <c r="W122" s="58"/>
       <c r="X122" s="58"/>
     </row>
-    <row r="123" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="25">
         <v>6</v>
       </c>
@@ -7134,7 +7263,7 @@
       <c r="W123" s="58"/>
       <c r="X123" s="58"/>
     </row>
-    <row r="124" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="25">
         <v>7</v>
       </c>
@@ -7180,21 +7309,21 @@
       <c r="W124" s="58"/>
       <c r="X124" s="58"/>
     </row>
-    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="78" t="s">
+    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="82" t="s">
         <v>413</v>
       </c>
-      <c r="B125" s="78"/>
-      <c r="C125" s="78"/>
-      <c r="D125" s="79"/>
-      <c r="E125" s="79"/>
-      <c r="F125" s="79"/>
-      <c r="G125" s="79"/>
-      <c r="H125" s="79"/>
-      <c r="I125" s="79"/>
-      <c r="J125" s="79"/>
-    </row>
-    <row r="126" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="82"/>
+      <c r="C125" s="82"/>
+      <c r="D125" s="83"/>
+      <c r="E125" s="83"/>
+      <c r="F125" s="83"/>
+      <c r="G125" s="83"/>
+      <c r="H125" s="83"/>
+      <c r="I125" s="83"/>
+      <c r="J125" s="83"/>
+    </row>
+    <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="59">
         <v>11</v>
       </c>
@@ -7240,7 +7369,7 @@
       <c r="W126" s="61"/>
       <c r="X126" s="61"/>
     </row>
-    <row r="127" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="26">
         <v>2</v>
       </c>
@@ -7286,7 +7415,7 @@
       <c r="W127" s="58"/>
       <c r="X127" s="58"/>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A128" s="26">
         <v>3</v>
       </c>
@@ -7332,7 +7461,7 @@
       <c r="W128" s="58"/>
       <c r="X128" s="58"/>
     </row>
-    <row r="129" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="26">
         <v>4</v>
       </c>
@@ -7378,7 +7507,7 @@
       <c r="W129" s="58"/>
       <c r="X129" s="58"/>
     </row>
-    <row r="130" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="26">
         <v>5</v>
       </c>
@@ -7424,7 +7553,7 @@
       <c r="W130" s="58"/>
       <c r="X130" s="58"/>
     </row>
-    <row r="131" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="26">
         <v>6</v>
       </c>
@@ -7470,7 +7599,7 @@
       <c r="W131" s="58"/>
       <c r="X131" s="58"/>
     </row>
-    <row r="132" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="26">
         <v>7</v>
       </c>
@@ -7516,7 +7645,7 @@
       <c r="W132" s="58"/>
       <c r="X132" s="58"/>
     </row>
-    <row r="133" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="26">
         <v>8</v>
       </c>
@@ -7562,7 +7691,7 @@
       <c r="W133" s="58"/>
       <c r="X133" s="58"/>
     </row>
-    <row r="134" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="26">
         <v>9</v>
       </c>
@@ -7608,7 +7737,7 @@
       <c r="W134" s="58"/>
       <c r="X134" s="58"/>
     </row>
-    <row r="135" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="26">
         <v>10</v>
       </c>
@@ -7654,21 +7783,21 @@
       <c r="W135" s="58"/>
       <c r="X135" s="58"/>
     </row>
-    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="80" t="s">
+    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="84" t="s">
         <v>442</v>
       </c>
-      <c r="B136" s="81"/>
-      <c r="C136" s="81"/>
-      <c r="D136" s="81"/>
-      <c r="E136" s="81"/>
-      <c r="F136" s="81"/>
-      <c r="G136" s="81"/>
-      <c r="H136" s="81"/>
-      <c r="I136" s="81"/>
-      <c r="J136" s="82"/>
-    </row>
-    <row r="137" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B136" s="85"/>
+      <c r="C136" s="85"/>
+      <c r="D136" s="85"/>
+      <c r="E136" s="85"/>
+      <c r="F136" s="85"/>
+      <c r="G136" s="85"/>
+      <c r="H136" s="85"/>
+      <c r="I136" s="85"/>
+      <c r="J136" s="86"/>
+    </row>
+    <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="25">
         <v>1</v>
       </c>
@@ -7714,7 +7843,7 @@
       <c r="W137" s="58"/>
       <c r="X137" s="58"/>
     </row>
-    <row r="138" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="25">
         <v>2</v>
       </c>
@@ -7760,7 +7889,7 @@
       <c r="W138" s="58"/>
       <c r="X138" s="58"/>
     </row>
-    <row r="139" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="25">
         <v>3</v>
       </c>
@@ -7806,7 +7935,7 @@
       <c r="W139" s="58"/>
       <c r="X139" s="58"/>
     </row>
-    <row r="140" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="25">
         <v>4</v>
       </c>
@@ -7838,7 +7967,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="25">
         <v>5</v>
       </c>
@@ -7884,7 +8013,7 @@
       <c r="W141" s="58"/>
       <c r="X141" s="58"/>
     </row>
-    <row r="142" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="25">
         <v>6</v>
       </c>
@@ -7930,7 +8059,7 @@
       <c r="W142" s="58"/>
       <c r="X142" s="58"/>
     </row>
-    <row r="143" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="25">
         <v>7</v>
       </c>
@@ -7976,7 +8105,7 @@
       <c r="W143" s="58"/>
       <c r="X143" s="58"/>
     </row>
-    <row r="144" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="25">
         <v>8</v>
       </c>
@@ -8022,7 +8151,7 @@
       <c r="W144" s="58"/>
       <c r="X144" s="58"/>
     </row>
-    <row r="145" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="25">
         <v>9</v>
       </c>
@@ -8068,7 +8197,7 @@
       <c r="W145" s="58"/>
       <c r="X145" s="58"/>
     </row>
-    <row r="146" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="25">
         <v>10</v>
       </c>
@@ -8114,21 +8243,21 @@
       <c r="W146" s="58"/>
       <c r="X146" s="58"/>
     </row>
-    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A147" s="78" t="s">
+    <row r="147" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A147" s="82" t="s">
         <v>514</v>
       </c>
-      <c r="B147" s="78"/>
-      <c r="C147" s="78"/>
-      <c r="D147" s="78"/>
-      <c r="E147" s="78"/>
-      <c r="F147" s="78"/>
-      <c r="G147" s="78"/>
-      <c r="H147" s="78"/>
-      <c r="I147" s="78"/>
-      <c r="J147" s="78"/>
-    </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B147" s="82"/>
+      <c r="C147" s="82"/>
+      <c r="D147" s="82"/>
+      <c r="E147" s="82"/>
+      <c r="F147" s="82"/>
+      <c r="G147" s="82"/>
+      <c r="H147" s="82"/>
+      <c r="I147" s="82"/>
+      <c r="J147" s="82"/>
+    </row>
+    <row r="148" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A148" s="25">
         <v>1</v>
       </c>
@@ -8160,21 +8289,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="78" t="s">
+    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="82" t="s">
         <v>540</v>
       </c>
-      <c r="B149" s="78"/>
-      <c r="C149" s="78"/>
-      <c r="D149" s="78"/>
-      <c r="E149" s="78"/>
-      <c r="F149" s="78"/>
-      <c r="G149" s="78"/>
-      <c r="H149" s="78"/>
-      <c r="I149" s="78"/>
-      <c r="J149" s="78"/>
-    </row>
-    <row r="150" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B149" s="82"/>
+      <c r="C149" s="82"/>
+      <c r="D149" s="82"/>
+      <c r="E149" s="82"/>
+      <c r="F149" s="82"/>
+      <c r="G149" s="82"/>
+      <c r="H149" s="82"/>
+      <c r="I149" s="82"/>
+      <c r="J149" s="82"/>
+    </row>
+    <row r="150" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="65">
         <v>1</v>
       </c>
@@ -8222,7 +8351,7 @@
       <c r="Y150" s="58"/>
       <c r="Z150" s="58"/>
     </row>
-    <row r="151" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="68">
         <v>2</v>
       </c>
@@ -8270,7 +8399,7 @@
       <c r="Y151" s="58"/>
       <c r="Z151" s="58"/>
     </row>
-    <row r="152" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="68">
         <v>3</v>
       </c>
@@ -8318,7 +8447,7 @@
       <c r="Y152" s="58"/>
       <c r="Z152" s="58"/>
     </row>
-    <row r="153" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="68">
         <v>4</v>
       </c>
@@ -8366,7 +8495,7 @@
       <c r="Y153" s="58"/>
       <c r="Z153" s="58"/>
     </row>
-    <row r="154" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="68">
         <v>5</v>
       </c>
@@ -8414,7 +8543,7 @@
       <c r="Y154" s="58"/>
       <c r="Z154" s="58"/>
     </row>
-    <row r="155" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="68">
         <v>6</v>
       </c>
@@ -8462,7 +8591,7 @@
       <c r="Y155" s="58"/>
       <c r="Z155" s="58"/>
     </row>
-    <row r="156" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="68">
         <v>7</v>
       </c>
@@ -8510,7 +8639,7 @@
       <c r="Y156" s="58"/>
       <c r="Z156" s="58"/>
     </row>
-    <row r="157" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="68">
         <v>8</v>
       </c>
@@ -8558,7 +8687,7 @@
       <c r="Y157" s="58"/>
       <c r="Z157" s="58"/>
     </row>
-    <row r="158" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="72">
         <v>9</v>
       </c>
@@ -8606,7 +8735,7 @@
       <c r="Y158" s="58"/>
       <c r="Z158" s="58"/>
     </row>
-    <row r="159" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="73">
         <v>10</v>
       </c>
@@ -8654,7 +8783,7 @@
       <c r="Y159" s="58"/>
       <c r="Z159" s="58"/>
     </row>
-    <row r="160" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="72">
         <v>11</v>
       </c>
@@ -8702,7 +8831,7 @@
       <c r="Y160" s="58"/>
       <c r="Z160" s="58"/>
     </row>
-    <row r="161" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="73">
         <v>12</v>
       </c>
@@ -8750,7 +8879,7 @@
       <c r="Y161" s="58"/>
       <c r="Z161" s="58"/>
     </row>
-    <row r="162" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="72">
         <v>13</v>
       </c>
@@ -8798,7 +8927,7 @@
       <c r="Y162" s="58"/>
       <c r="Z162" s="58"/>
     </row>
-    <row r="163" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="73">
         <v>14</v>
       </c>
@@ -8846,7 +8975,7 @@
       <c r="Y163" s="58"/>
       <c r="Z163" s="58"/>
     </row>
-    <row r="164" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="72">
         <v>15</v>
       </c>
@@ -8894,7 +9023,7 @@
       <c r="Y164" s="58"/>
       <c r="Z164" s="58"/>
     </row>
-    <row r="165" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="73">
         <v>16</v>
       </c>
@@ -8942,7 +9071,7 @@
       <c r="Y165" s="58"/>
       <c r="Z165" s="58"/>
     </row>
-    <row r="166" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="72">
         <v>17</v>
       </c>
@@ -8990,7 +9119,7 @@
       <c r="Y166" s="58"/>
       <c r="Z166" s="58"/>
     </row>
-    <row r="167" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="73">
         <v>18</v>
       </c>
@@ -9038,21 +9167,164 @@
       <c r="Y167" s="58"/>
       <c r="Z167" s="58"/>
     </row>
+    <row r="168" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="82" t="s">
+        <v>619</v>
+      </c>
+      <c r="B168" s="82"/>
+      <c r="C168" s="82"/>
+      <c r="D168" s="82"/>
+      <c r="E168" s="82"/>
+      <c r="F168" s="82"/>
+      <c r="G168" s="82"/>
+      <c r="H168" s="82"/>
+      <c r="I168" s="82"/>
+      <c r="J168" s="82"/>
+    </row>
+    <row r="169" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="73">
+        <v>1</v>
+      </c>
+      <c r="B169" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C169" s="75" t="s">
+        <v>605</v>
+      </c>
+      <c r="D169" s="77" t="s">
+        <v>607</v>
+      </c>
+      <c r="E169" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F169" s="75" t="s">
+        <v>606</v>
+      </c>
+      <c r="G169" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H169" s="74" t="s">
+        <v>544</v>
+      </c>
+      <c r="I169" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J169" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="73">
+        <v>2</v>
+      </c>
+      <c r="B170" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C170" s="75" t="s">
+        <v>613</v>
+      </c>
+      <c r="D170" s="77" t="s">
+        <v>614</v>
+      </c>
+      <c r="E170" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F170" s="75" t="s">
+        <v>611</v>
+      </c>
+      <c r="G170" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H170" s="74" t="s">
+        <v>544</v>
+      </c>
+      <c r="I170" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J170" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="171" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="73">
+        <v>3</v>
+      </c>
+      <c r="B171" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C171" s="75" t="s">
+        <v>617</v>
+      </c>
+      <c r="D171" s="81" t="s">
+        <v>618</v>
+      </c>
+      <c r="E171" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F171" s="75" t="s">
+        <v>616</v>
+      </c>
+      <c r="G171" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H171" s="74" t="s">
+        <v>544</v>
+      </c>
+      <c r="I171" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J171" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="73">
+        <v>4</v>
+      </c>
+      <c r="B172" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C172" s="79" t="s">
+        <v>621</v>
+      </c>
+      <c r="D172" s="64" t="s">
+        <v>622</v>
+      </c>
+      <c r="E172" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="F172" s="75" t="s">
+        <v>620</v>
+      </c>
+      <c r="G172" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H172" s="74" t="s">
+        <v>544</v>
+      </c>
+      <c r="I172" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J172" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A149:J149"/>
-    <mergeCell ref="A147:J147"/>
-    <mergeCell ref="A125:J125"/>
-    <mergeCell ref="A136:J136"/>
+  <mergeCells count="14">
+    <mergeCell ref="A117:J117"/>
+    <mergeCell ref="A115:J115"/>
+    <mergeCell ref="A113:J113"/>
+    <mergeCell ref="A102:J102"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A37:J37"/>
     <mergeCell ref="A51:J51"/>
     <mergeCell ref="A62:J62"/>
     <mergeCell ref="A74:J74"/>
-    <mergeCell ref="A117:J117"/>
-    <mergeCell ref="A115:J115"/>
-    <mergeCell ref="A113:J113"/>
-    <mergeCell ref="A102:J102"/>
+    <mergeCell ref="A168:J168"/>
+    <mergeCell ref="A149:J149"/>
+    <mergeCell ref="A147:J147"/>
+    <mergeCell ref="A125:J125"/>
+    <mergeCell ref="A136:J136"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -9150,28 +9422,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:U166"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:X170"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="45.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="54.28515625" customWidth="1"/>
+    <col min="2" max="2" width="45.6640625" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="54.33203125" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.42578125" customWidth="1"/>
-    <col min="12" max="12" width="53.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.44140625" customWidth="1"/>
+    <col min="12" max="12" width="53.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="71.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" customWidth="1"/>
-    <col min="21" max="21" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="71.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.109375" customWidth="1"/>
+    <col min="21" max="21" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="27" customWidth="1"/>
+    <col min="24" max="24" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>5</v>
       </c>
@@ -9235,8 +9509,17 @@
       <c r="U1" s="31" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V1" s="31" t="s">
+        <v>623</v>
+      </c>
+      <c r="W1" s="31" t="s">
+        <v>609</v>
+      </c>
+      <c r="X1" s="31" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>23</v>
       </c>
@@ -9296,8 +9579,17 @@
       <c r="U2" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V2" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W2" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X2" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
         <v>25</v>
       </c>
@@ -9357,8 +9649,17 @@
       <c r="U3" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V3" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W3" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X3" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
         <v>28</v>
       </c>
@@ -9418,8 +9719,17 @@
       <c r="U4" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V4" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W4" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X4" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
         <v>58</v>
       </c>
@@ -9479,8 +9789,17 @@
       <c r="U5" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V5" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W5" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X5" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>69</v>
       </c>
@@ -9540,8 +9859,17 @@
       <c r="U6" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V6" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W6" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X6" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="s">
         <v>73</v>
       </c>
@@ -9601,8 +9929,17 @@
       <c r="U7" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="V7" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W7" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X7" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38" t="s">
         <v>77</v>
       </c>
@@ -9662,8 +9999,17 @@
       <c r="U8" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V8" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W8" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X8" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="38" t="s">
         <v>79</v>
       </c>
@@ -9723,8 +10069,17 @@
       <c r="U9" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V9" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W9" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X9" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="38" t="s">
         <v>80</v>
       </c>
@@ -9784,8 +10139,17 @@
       <c r="U10" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V10" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W10" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X10" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="38" t="s">
         <v>81</v>
       </c>
@@ -9845,8 +10209,17 @@
       <c r="U11" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V11" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W11" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X11" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="38" t="s">
         <v>83</v>
       </c>
@@ -9906,8 +10279,17 @@
       <c r="U12" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V12" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W12" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X12" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="38" t="s">
         <v>84</v>
       </c>
@@ -9967,8 +10349,17 @@
       <c r="U13" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V13" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W13" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X13" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="38" t="s">
         <v>85</v>
       </c>
@@ -10028,8 +10419,17 @@
       <c r="U14" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V14" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W14" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X14" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" s="38" t="s">
         <v>86</v>
       </c>
@@ -10089,8 +10489,17 @@
       <c r="U15" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V15" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W15" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X15" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="38" t="s">
         <v>87</v>
       </c>
@@ -10150,8 +10559,17 @@
       <c r="U16" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V16" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W16" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X16" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="38" t="s">
         <v>88</v>
       </c>
@@ -10211,8 +10629,17 @@
       <c r="U17" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V17" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W17" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X17" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="38" t="s">
         <v>89</v>
       </c>
@@ -10272,8 +10699,17 @@
       <c r="U18" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V18" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W18" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X18" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="38" t="s">
         <v>91</v>
       </c>
@@ -10333,8 +10769,17 @@
       <c r="U19" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V19" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W19" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X19" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="38" t="s">
         <v>93</v>
       </c>
@@ -10394,8 +10839,17 @@
       <c r="U20" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V20" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W20" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X20" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="38" t="s">
         <v>94</v>
       </c>
@@ -10455,8 +10909,17 @@
       <c r="U21" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V21" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W21" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X21" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="38" t="s">
         <v>135</v>
       </c>
@@ -10516,8 +10979,17 @@
       <c r="U22" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V22" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W22" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X22" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="42" t="s">
         <v>140</v>
       </c>
@@ -10577,8 +11049,17 @@
       <c r="U23" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V23" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W23" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X23" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="53" t="s">
         <v>63</v>
       </c>
@@ -10638,8 +11119,17 @@
       <c r="U24" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V24" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W24" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X24" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="46" t="s">
         <v>144</v>
       </c>
@@ -10699,8 +11189,17 @@
       <c r="U25" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V25" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W25" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X25" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="46" t="s">
         <v>145</v>
       </c>
@@ -10760,8 +11259,17 @@
       <c r="U26" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V26" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W26" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X26" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" s="46" t="s">
         <v>146</v>
       </c>
@@ -10821,8 +11329,17 @@
       <c r="U27" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V27" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W27" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X27" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" s="46" t="s">
         <v>147</v>
       </c>
@@ -10882,8 +11399,17 @@
       <c r="U28" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V28" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W28" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X28" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="46" t="s">
         <v>148</v>
       </c>
@@ -10943,8 +11469,17 @@
       <c r="U29" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V29" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W29" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X29" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="46" t="s">
         <v>150</v>
       </c>
@@ -11004,8 +11539,17 @@
       <c r="U30" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V30" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W30" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X30" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="46" t="s">
         <v>151</v>
       </c>
@@ -11065,8 +11609,17 @@
       <c r="U31" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V31" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W31" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X31" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" s="46" t="s">
         <v>152</v>
       </c>
@@ -11126,8 +11679,17 @@
       <c r="U32" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V32" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W32" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X32" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33" s="46" t="s">
         <v>153</v>
       </c>
@@ -11187,8 +11749,17 @@
       <c r="U33" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V33" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W33" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X33" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34" s="46" t="s">
         <v>154</v>
       </c>
@@ -11248,8 +11819,17 @@
       <c r="U34" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V34" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W34" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X34" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" s="46" t="s">
         <v>155</v>
       </c>
@@ -11309,8 +11889,17 @@
       <c r="U35" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V35" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W35" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X35" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" s="33" t="s">
         <v>64</v>
       </c>
@@ -11370,8 +11959,17 @@
       <c r="U36" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V36" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W36" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X36" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37" s="54" t="s">
         <v>175</v>
       </c>
@@ -11433,8 +12031,17 @@
       <c r="U37" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V37" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W37" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X37" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38" s="47" t="s">
         <v>179</v>
       </c>
@@ -11496,8 +12103,17 @@
       <c r="U38" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V38" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W38" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X38" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="47" t="s">
         <v>182</v>
       </c>
@@ -11559,8 +12175,17 @@
       <c r="U39" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V39" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W39" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X39" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40" s="47" t="s">
         <v>185</v>
       </c>
@@ -11622,8 +12247,17 @@
       <c r="U40" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V40" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W40" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X40" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41" s="47" t="s">
         <v>188</v>
       </c>
@@ -11685,8 +12319,17 @@
       <c r="U41" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V41" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W41" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X41" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42" s="47" t="s">
         <v>190</v>
       </c>
@@ -11748,8 +12391,17 @@
       <c r="U42" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V42" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W42" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X42" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43" s="47" t="s">
         <v>193</v>
       </c>
@@ -11811,8 +12463,17 @@
       <c r="U43" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V43" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W43" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X43" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44" s="47" t="s">
         <v>196</v>
       </c>
@@ -11874,8 +12535,17 @@
       <c r="U44" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V44" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W44" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X44" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45" s="47" t="s">
         <v>199</v>
       </c>
@@ -11937,8 +12607,17 @@
       <c r="U45" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V45" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W45" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X45" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46" s="47" t="s">
         <v>201</v>
       </c>
@@ -12000,8 +12679,17 @@
       <c r="U46" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V46" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W46" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X46" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47" s="47" t="s">
         <v>203</v>
       </c>
@@ -12063,8 +12751,17 @@
       <c r="U47" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V47" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W47" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X47" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48" s="47" t="s">
         <v>205</v>
       </c>
@@ -12126,8 +12823,17 @@
       <c r="U48" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V48" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W48" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X48" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49" s="47" t="s">
         <v>207</v>
       </c>
@@ -12189,8 +12895,17 @@
       <c r="U49" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V49" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W49" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X49" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50" s="47" t="s">
         <v>209</v>
       </c>
@@ -12252,8 +12967,17 @@
       <c r="U50" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V50" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W50" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X50" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51" s="47" t="s">
         <v>211</v>
       </c>
@@ -12315,8 +13039,17 @@
       <c r="U51" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V51" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W51" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X51" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52" s="47" t="s">
         <v>213</v>
       </c>
@@ -12378,8 +13111,17 @@
       <c r="U52" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V52" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W52" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X52" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53" s="55" t="s">
         <v>214</v>
       </c>
@@ -12441,8 +13183,17 @@
       <c r="U53" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V53" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W53" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X53" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54" s="48" t="s">
         <v>215</v>
       </c>
@@ -12504,8 +13255,17 @@
       <c r="U54" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V54" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W54" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X54" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55" s="48" t="s">
         <v>216</v>
       </c>
@@ -12567,8 +13327,17 @@
       <c r="U55" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V55" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W55" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X55" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56" s="48" t="s">
         <v>217</v>
       </c>
@@ -12630,8 +13399,17 @@
       <c r="U56" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V56" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W56" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X56" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57" s="48" t="s">
         <v>218</v>
       </c>
@@ -12693,8 +13471,17 @@
       <c r="U57" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V57" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W57" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X57" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58" s="48" t="s">
         <v>219</v>
       </c>
@@ -12756,8 +13543,17 @@
       <c r="U58" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V58" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W58" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X58" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59" s="48" t="s">
         <v>220</v>
       </c>
@@ -12819,8 +13615,17 @@
       <c r="U59" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V59" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W59" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X59" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60" s="48" t="s">
         <v>221</v>
       </c>
@@ -12882,8 +13687,17 @@
       <c r="U60" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V60" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W60" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X60" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61" s="48" t="s">
         <v>222</v>
       </c>
@@ -12945,8 +13759,17 @@
       <c r="U61" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V61" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W61" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X61" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62" s="51" t="s">
         <v>223</v>
       </c>
@@ -13008,8 +13831,17 @@
       <c r="U62" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V62" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W62" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X62" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63" s="56" t="s">
         <v>250</v>
       </c>
@@ -13071,8 +13903,17 @@
       <c r="U63" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V63" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W63" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X63" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64" s="48" t="s">
         <v>254</v>
       </c>
@@ -13134,8 +13975,17 @@
       <c r="U64" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V64" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W64" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X64" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A65" s="48" t="s">
         <v>257</v>
       </c>
@@ -13197,8 +14047,17 @@
       <c r="U65" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V65" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W65" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X65" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A66" s="48" t="s">
         <v>260</v>
       </c>
@@ -13260,8 +14119,17 @@
       <c r="U66" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V66" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W66" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X66" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A67" s="48" t="s">
         <v>263</v>
       </c>
@@ -13323,8 +14191,17 @@
       <c r="U67" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V67" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W67" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X67" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A68" s="48" t="s">
         <v>266</v>
       </c>
@@ -13386,8 +14263,17 @@
       <c r="U68" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V68" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W68" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X68" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A69" s="48" t="s">
         <v>269</v>
       </c>
@@ -13449,8 +14335,17 @@
       <c r="U69" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V69" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W69" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X69" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A70" s="48" t="s">
         <v>272</v>
       </c>
@@ -13512,8 +14407,17 @@
       <c r="U70" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V70" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W70" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X70" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A71" s="48" t="s">
         <v>275</v>
       </c>
@@ -13575,8 +14479,17 @@
       <c r="U71" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V71" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W71" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X71" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A72" s="48" t="s">
         <v>278</v>
       </c>
@@ -13638,8 +14551,17 @@
       <c r="U72" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V72" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W72" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X72" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A73" s="51" t="s">
         <v>281</v>
       </c>
@@ -13703,8 +14625,17 @@
       <c r="U73" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V73" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W73" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X73" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A74" s="62" t="s">
         <v>283</v>
       </c>
@@ -13768,8 +14699,17 @@
       <c r="U74" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V74" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W74" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X74" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A75" s="48" t="s">
         <v>286</v>
       </c>
@@ -13833,8 +14773,17 @@
       <c r="U75" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V75" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W75" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X75" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A76" s="48" t="s">
         <v>288</v>
       </c>
@@ -13898,8 +14847,17 @@
       <c r="U76" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V76" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W76" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X76" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A77" s="48" t="s">
         <v>290</v>
       </c>
@@ -13963,8 +14921,17 @@
       <c r="U77" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V77" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W77" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X77" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A78" s="48" t="s">
         <v>293</v>
       </c>
@@ -14028,8 +14995,17 @@
       <c r="U78" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V78" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W78" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X78" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A79" s="48" t="s">
         <v>296</v>
       </c>
@@ -14093,8 +15069,17 @@
       <c r="U79" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V79" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W79" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X79" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A80" s="48" t="s">
         <v>299</v>
       </c>
@@ -14158,8 +15143,17 @@
       <c r="U80" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V80" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W80" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X80" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A81" s="48" t="s">
         <v>302</v>
       </c>
@@ -14223,8 +15217,17 @@
       <c r="U81" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V81" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W81" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X81" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A82" s="48" t="s">
         <v>305</v>
       </c>
@@ -14288,8 +15291,17 @@
       <c r="U82" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V82" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W82" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X82" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A83" s="48" t="s">
         <v>307</v>
       </c>
@@ -14353,8 +15365,17 @@
       <c r="U83" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V83" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W83" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X83" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A84" s="48" t="s">
         <v>309</v>
       </c>
@@ -14418,8 +15439,17 @@
       <c r="U84" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V84" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W84" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X84" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A85" s="48" t="s">
         <v>311</v>
       </c>
@@ -14483,8 +15513,17 @@
       <c r="U85" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V85" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W85" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X85" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A86" s="48" t="s">
         <v>314</v>
       </c>
@@ -14548,8 +15587,17 @@
       <c r="U86" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V86" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W86" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X86" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A87" s="48" t="s">
         <v>317</v>
       </c>
@@ -14613,8 +15661,17 @@
       <c r="U87" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V87" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W87" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X87" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A88" s="48" t="s">
         <v>320</v>
       </c>
@@ -14678,8 +15735,17 @@
       <c r="U88" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V88" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W88" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X88" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A89" s="48" t="s">
         <v>323</v>
       </c>
@@ -14743,8 +15809,17 @@
       <c r="U89" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V89" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W89" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X89" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A90" s="48" t="s">
         <v>325</v>
       </c>
@@ -14808,8 +15883,17 @@
       <c r="U90" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V90" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W90" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X90" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A91" s="48" t="s">
         <v>328</v>
       </c>
@@ -14873,8 +15957,17 @@
       <c r="U91" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V91" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W91" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X91" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A92" s="48" t="s">
         <v>331</v>
       </c>
@@ -14938,8 +16031,17 @@
       <c r="U92" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V92" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W92" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X92" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A93" s="48" t="s">
         <v>333</v>
       </c>
@@ -15003,8 +16105,17 @@
       <c r="U93" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V93" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W93" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X93" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A94" s="48" t="s">
         <v>335</v>
       </c>
@@ -15068,8 +16179,17 @@
       <c r="U94" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V94" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W94" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X94" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A95" s="48" t="s">
         <v>337</v>
       </c>
@@ -15133,8 +16253,17 @@
       <c r="U95" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V95" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W95" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X95" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A96" s="48" t="s">
         <v>339</v>
       </c>
@@ -15198,8 +16327,17 @@
       <c r="U96" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V96" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W96" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X96" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A97" s="48" t="s">
         <v>341</v>
       </c>
@@ -15263,8 +16401,17 @@
       <c r="U97" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V97" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W97" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X97" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A98" s="48" t="s">
         <v>343</v>
       </c>
@@ -15328,8 +16475,17 @@
       <c r="U98" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V98" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W98" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X98" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A99" s="48" t="s">
         <v>345</v>
       </c>
@@ -15393,8 +16549,17 @@
       <c r="U99" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V99" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W99" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X99" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A100" s="48" t="s">
         <v>601</v>
       </c>
@@ -15458,8 +16623,17 @@
       <c r="U100" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V100" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W100" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X100" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A101" s="48" t="s">
         <v>349</v>
       </c>
@@ -15523,8 +16697,17 @@
       <c r="U101" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V101" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W101" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X101" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A102" s="48" t="s">
         <v>353</v>
       </c>
@@ -15588,8 +16771,17 @@
       <c r="U102" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V102" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W102" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X102" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103" s="48" t="s">
         <v>356</v>
       </c>
@@ -15653,8 +16845,17 @@
       <c r="U103" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V103" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W103" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X103" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A104" s="48" t="s">
         <v>359</v>
       </c>
@@ -15718,8 +16919,17 @@
       <c r="U104" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V104" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W104" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X104" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A105" s="48" t="s">
         <v>362</v>
       </c>
@@ -15783,8 +16993,17 @@
       <c r="U105" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V105" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W105" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X105" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106" s="48" t="s">
         <v>365</v>
       </c>
@@ -15848,8 +17067,17 @@
       <c r="U106" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V106" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W106" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X106" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A107" s="48" t="s">
         <v>368</v>
       </c>
@@ -15913,8 +17141,17 @@
       <c r="U107" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V107" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W107" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X107" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A108" s="48" t="s">
         <v>370</v>
       </c>
@@ -15978,8 +17215,17 @@
       <c r="U108" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V108" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W108" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X108" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A109" s="48" t="s">
         <v>372</v>
       </c>
@@ -16043,8 +17289,17 @@
       <c r="U109" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V109" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W109" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X109" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A110" s="48" t="s">
         <v>602</v>
       </c>
@@ -16108,8 +17363,17 @@
       <c r="U110" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V110" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W110" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X110" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111" s="48" t="s">
         <v>380</v>
       </c>
@@ -16173,8 +17437,17 @@
       <c r="U111" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V111" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W111" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X111" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A112" s="48" t="s">
         <v>385</v>
       </c>
@@ -16238,8 +17511,17 @@
       <c r="U112" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V112" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W112" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X112" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113" s="48" t="s">
         <v>399</v>
       </c>
@@ -16303,8 +17585,17 @@
       <c r="U113" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V113" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W113" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X113" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="48" t="s">
         <v>401</v>
       </c>
@@ -16368,8 +17659,17 @@
       <c r="U114" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V114" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W114" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X114" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A115" s="48" t="s">
         <v>402</v>
       </c>
@@ -16433,8 +17733,17 @@
       <c r="U115" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V115" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W115" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X115" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" s="48" t="s">
         <v>403</v>
       </c>
@@ -16498,8 +17807,17 @@
       <c r="U116" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V116" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W116" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X116" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A117" s="48" t="s">
         <v>404</v>
       </c>
@@ -16563,8 +17881,17 @@
       <c r="U117" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V117" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W117" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X117" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118" s="48" t="s">
         <v>405</v>
       </c>
@@ -16628,8 +17955,17 @@
       <c r="U118" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V118" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W118" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X118" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A119" s="48" t="s">
         <v>407</v>
       </c>
@@ -16693,8 +18029,17 @@
       <c r="U119" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V119" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W119" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X119" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A120" s="48" t="s">
         <v>409</v>
       </c>
@@ -16758,8 +18103,17 @@
       <c r="U120" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="121" spans="1:21" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="V120" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W120" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X120" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A121" s="62" t="s">
         <v>415</v>
       </c>
@@ -16823,8 +18177,17 @@
       <c r="U121" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V121" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W121" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X121" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A122" s="48" t="s">
         <v>419</v>
       </c>
@@ -16888,8 +18251,17 @@
       <c r="U122" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V122" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W122" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X122" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A123" s="48" t="s">
         <v>422</v>
       </c>
@@ -16953,8 +18325,17 @@
       <c r="U123" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="124" spans="1:21" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="V123" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W123" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X123" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A124" s="48" t="s">
         <v>424</v>
       </c>
@@ -17018,8 +18399,17 @@
       <c r="U124" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="125" spans="1:21" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="V124" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W124" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X124" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="125" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A125" s="48" t="s">
         <v>426</v>
       </c>
@@ -17083,8 +18473,17 @@
       <c r="U125" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V125" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W125" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X125" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A126" s="48" t="s">
         <v>429</v>
       </c>
@@ -17148,8 +18547,17 @@
       <c r="U126" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V126" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W126" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X126" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A127" s="48" t="s">
         <v>432</v>
       </c>
@@ -17213,8 +18621,17 @@
       <c r="U127" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V127" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W127" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X127" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A128" s="48" t="s">
         <v>435</v>
       </c>
@@ -17278,8 +18695,17 @@
       <c r="U128" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="129" spans="1:21" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="V128" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W128" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X128" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A129" s="48" t="s">
         <v>438</v>
       </c>
@@ -17343,8 +18769,17 @@
       <c r="U129" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V129" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W129" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X129" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A130" s="48" t="s">
         <v>441</v>
       </c>
@@ -17408,8 +18843,17 @@
       <c r="U130" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V130" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W130" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X130" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A131" s="48" t="s">
         <v>399</v>
       </c>
@@ -17473,8 +18917,17 @@
       <c r="U131" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V131" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W131" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X131" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A132" s="48" t="s">
         <v>401</v>
       </c>
@@ -17538,8 +18991,17 @@
       <c r="U132" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V132" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W132" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X132" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A133" s="48" t="s">
         <v>402</v>
       </c>
@@ -17603,8 +19065,17 @@
       <c r="U133" s="48" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V133" s="48" t="s">
+        <v>493</v>
+      </c>
+      <c r="W133" s="48" t="s">
+        <v>493</v>
+      </c>
+      <c r="X133" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A134" s="48" t="s">
         <v>403</v>
       </c>
@@ -17668,8 +19139,17 @@
       <c r="U134" s="48" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V134" s="48" t="s">
+        <v>487</v>
+      </c>
+      <c r="W134" s="48" t="s">
+        <v>487</v>
+      </c>
+      <c r="X134" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A135" s="48" t="s">
         <v>404</v>
       </c>
@@ -17733,8 +19213,17 @@
       <c r="U135" s="48" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V135" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="W135" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="X135" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A136" s="48" t="s">
         <v>405</v>
       </c>
@@ -17798,8 +19287,17 @@
       <c r="U136" s="48" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V136" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="W136" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="X136" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A137" s="48" t="s">
         <v>407</v>
       </c>
@@ -17863,8 +19361,17 @@
       <c r="U137" s="48" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V137" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="W137" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="X137" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A138" s="48" t="s">
         <v>445</v>
       </c>
@@ -17928,8 +19435,17 @@
       <c r="U138" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V138" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W138" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X138" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A139" s="48" t="s">
         <v>449</v>
       </c>
@@ -17993,8 +19509,17 @@
       <c r="U139" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V139" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W139" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X139" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A140" s="48" t="s">
         <v>452</v>
       </c>
@@ -18058,8 +19583,17 @@
       <c r="U140" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V140" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W140" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X140" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A141" s="48" t="s">
         <v>454</v>
       </c>
@@ -18123,8 +19657,17 @@
       <c r="U141" s="48" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V141" s="48" t="s">
+        <v>535</v>
+      </c>
+      <c r="W141" s="48" t="s">
+        <v>535</v>
+      </c>
+      <c r="X141" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A142" s="48" t="s">
         <v>457</v>
       </c>
@@ -18188,8 +19731,17 @@
       <c r="U142" s="48" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V142" s="48" t="s">
+        <v>487</v>
+      </c>
+      <c r="W142" s="48" t="s">
+        <v>487</v>
+      </c>
+      <c r="X142" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="143" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A143" s="48" t="s">
         <v>460</v>
       </c>
@@ -18253,8 +19805,17 @@
       <c r="U143" s="48" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V143" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="W143" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="X143" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A144" s="48" t="s">
         <v>463</v>
       </c>
@@ -18318,8 +19879,17 @@
       <c r="U144" s="48" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V144" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="W144" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="X144" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="145" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A145" s="48" t="s">
         <v>466</v>
       </c>
@@ -18383,8 +19953,17 @@
       <c r="U145" s="48" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="146" spans="1:21" ht="64.5" x14ac:dyDescent="0.25">
+      <c r="V145" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="W145" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="X145" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="146" spans="1:24" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A146" s="48" t="s">
         <v>469</v>
       </c>
@@ -18448,8 +20027,17 @@
       <c r="U146" s="48" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="147" spans="1:21" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="V146" s="48" t="s">
+        <v>491</v>
+      </c>
+      <c r="W146" s="48" t="s">
+        <v>491</v>
+      </c>
+      <c r="X146" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="147" spans="1:24" ht="53.4" x14ac:dyDescent="0.3">
       <c r="A147" s="48" t="s">
         <v>472</v>
       </c>
@@ -18513,8 +20101,17 @@
       <c r="U147" s="48" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="148" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V147" s="48" t="s">
+        <v>492</v>
+      </c>
+      <c r="W147" s="48" t="s">
+        <v>492</v>
+      </c>
+      <c r="X147" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="148" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="48" t="s">
         <v>513</v>
       </c>
@@ -18578,8 +20175,17 @@
       <c r="U148" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="149" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V148" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W148" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X148" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="149" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="67" t="s">
         <v>543</v>
       </c>
@@ -18643,8 +20249,17 @@
       <c r="U149" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="150" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V149" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W149" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X149" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="150" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="70" t="s">
         <v>547</v>
       </c>
@@ -18708,8 +20323,17 @@
       <c r="U150" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="151" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V150" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W150" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X150" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="151" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="67" t="s">
         <v>550</v>
       </c>
@@ -18773,8 +20397,17 @@
       <c r="U151" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="152" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V151" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W151" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X151" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="152" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="70" t="s">
         <v>553</v>
       </c>
@@ -18838,8 +20471,17 @@
       <c r="U152" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="153" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V152" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W152" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X152" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="67" t="s">
         <v>555</v>
       </c>
@@ -18903,8 +20545,17 @@
       <c r="U153" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="154" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V153" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W153" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X153" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="70" t="s">
         <v>557</v>
       </c>
@@ -18968,8 +20619,17 @@
       <c r="U154" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="155" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V154" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W154" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X154" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="155" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="67" t="s">
         <v>559</v>
       </c>
@@ -19033,8 +20693,17 @@
       <c r="U155" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="156" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V155" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W155" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X155" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="156" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="70" t="s">
         <v>561</v>
       </c>
@@ -19098,8 +20767,17 @@
       <c r="U156" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="157" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V156" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W156" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X156" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="157" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="67" t="s">
         <v>563</v>
       </c>
@@ -19163,8 +20841,17 @@
       <c r="U157" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="158" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V157" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W157" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X157" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="158" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="70" t="s">
         <v>566</v>
       </c>
@@ -19228,8 +20915,17 @@
       <c r="U158" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="159" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V158" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W158" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X158" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="159" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="67" t="s">
         <v>569</v>
       </c>
@@ -19293,8 +20989,17 @@
       <c r="U159" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="160" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V159" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W159" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X159" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="70" t="s">
         <v>572</v>
       </c>
@@ -19358,8 +21063,17 @@
       <c r="U160" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="161" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V160" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W160" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X160" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="161" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="67" t="s">
         <v>575</v>
       </c>
@@ -19423,8 +21137,17 @@
       <c r="U161" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="162" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V161" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W161" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X161" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="162" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="70" t="s">
         <v>578</v>
       </c>
@@ -19488,8 +21211,17 @@
       <c r="U162" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="163" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V162" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W162" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X162" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="163" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="67" t="s">
         <v>581</v>
       </c>
@@ -19553,8 +21285,17 @@
       <c r="U163" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="164" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X163" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="164" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="67" t="s">
         <v>583</v>
       </c>
@@ -19618,8 +21359,17 @@
       <c r="U164" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="165" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X164" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="165" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="67" t="s">
         <v>585</v>
       </c>
@@ -19683,8 +21433,17 @@
       <c r="U165" s="48" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="166" spans="1:21" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X165" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="166" spans="1:24" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="67" t="s">
         <v>588</v>
       </c>
@@ -19746,6 +21505,311 @@
         <v>22</v>
       </c>
       <c r="U166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X166" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="167" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="75" t="s">
+        <v>606</v>
+      </c>
+      <c r="B167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S167" s="49" t="s">
+        <v>608</v>
+      </c>
+      <c r="T167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V167" s="48" t="s">
+        <v>624</v>
+      </c>
+      <c r="W167" s="36" t="s">
+        <v>610</v>
+      </c>
+      <c r="X167" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="168" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="75" t="s">
+        <v>611</v>
+      </c>
+      <c r="B168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S168" s="49" t="s">
+        <v>612</v>
+      </c>
+      <c r="T168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W168" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X168" s="78" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="169" spans="1:24" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="75" t="s">
+        <v>616</v>
+      </c>
+      <c r="B169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S169" s="49" t="s">
+        <v>612</v>
+      </c>
+      <c r="T169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W169" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X169" s="94" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="170" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="75" t="s">
+        <v>620</v>
+      </c>
+      <c r="B170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S170" s="49" t="s">
+        <v>608</v>
+      </c>
+      <c r="T170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V170" s="48" t="s">
+        <v>625</v>
+      </c>
+      <c r="W170" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X170" s="48" t="s">
         <v>22</v>
       </c>
     </row>
@@ -19873,8 +21937,12 @@
     <hyperlink ref="G126" r:id="rId15" xr:uid="{FEC9AB2B-6FD0-4D08-96BB-5634F117BFB0}"/>
     <hyperlink ref="D136" r:id="rId16" xr:uid="{EAE526E7-10C0-4EC9-846A-D81343ACBEC4}"/>
     <hyperlink ref="G166" r:id="rId17" xr:uid="{0A52F660-ABF2-41CF-BD4C-5E55458D590D}"/>
+    <hyperlink ref="S167" r:id="rId18" xr:uid="{13FB8A07-5562-4AAB-9E83-934C01965617}"/>
+    <hyperlink ref="S169" r:id="rId19" xr:uid="{23F160B7-D3CD-415D-B0D6-1EECB7AFE96F}"/>
+    <hyperlink ref="S170" r:id="rId20" xr:uid="{7206C778-989C-4587-83FA-C09C20DA42BD}"/>
+    <hyperlink ref="X168" r:id="rId21" tooltip="sun flower" display="https://qa.zlta.testingserver8.com/product-detail/pink-sun-flower" xr:uid="{CFFC3DF8-4F00-4B09-AF68-A4EB71080BA6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId18"/>
+  <pageSetup orientation="portrait" r:id="rId22"/>
 </worksheet>
 </file>
--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\zlaata\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AD519D-BC4E-43CE-A5E3-68DC2309AE84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D1B537-ACC1-4AED-97B8-5BA63B47E338}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="3240" yWindow="3240" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5411" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5477" uniqueCount="635">
   <si>
     <t>S.No</t>
   </si>
@@ -1903,13 +1903,34 @@
     <t>Home Page Test</t>
   </si>
   <si>
-    <t>Saroj Test</t>
-  </si>
-  <si>
     <t>sun flower</t>
   </si>
   <si>
-    <t>Flower Red Test</t>
+    <t>Test demo</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_ADM_05</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_ADM_05</t>
+  </si>
+  <si>
+    <t>Verify bulk product upload and visibility.</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_ADM_06</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_ADM_06</t>
+  </si>
+  <si>
+    <t>Remove product SKU from Top Selling and verify on User App.</t>
+  </si>
+  <si>
+    <t>pink real heaven</t>
+  </si>
+  <si>
+    <t>sadsdasad</t>
   </si>
 </sst>
 </file>
@@ -2083,7 +2104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -2338,12 +2359,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2550,19 +2584,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2585,6 +2611,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3391,7 +3429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z172"/>
+  <dimension ref="A1:Z174"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -4142,18 +4180,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="88" t="s">
+      <c r="A24" s="86" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="90"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="87"/>
+      <c r="H24" s="87"/>
+      <c r="I24" s="87"/>
+      <c r="J24" s="88"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
@@ -4540,18 +4578,18 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="91" t="s">
+      <c r="A37" s="89" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="92"/>
-      <c r="C37" s="92"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="92"/>
-      <c r="G37" s="92"/>
-      <c r="H37" s="92"/>
-      <c r="I37" s="92"/>
-      <c r="J37" s="93"/>
+      <c r="B37" s="90"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="90"/>
+      <c r="F37" s="90"/>
+      <c r="G37" s="90"/>
+      <c r="H37" s="90"/>
+      <c r="I37" s="90"/>
+      <c r="J37" s="91"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
@@ -4970,18 +5008,18 @@
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="91" t="s">
+      <c r="A51" s="89" t="s">
         <v>245</v>
       </c>
-      <c r="B51" s="92"/>
-      <c r="C51" s="92"/>
-      <c r="D51" s="92"/>
-      <c r="E51" s="92"/>
-      <c r="F51" s="92"/>
-      <c r="G51" s="92"/>
-      <c r="H51" s="92"/>
-      <c r="I51" s="92"/>
-      <c r="J51" s="93"/>
+      <c r="B51" s="90"/>
+      <c r="C51" s="90"/>
+      <c r="D51" s="90"/>
+      <c r="E51" s="90"/>
+      <c r="F51" s="90"/>
+      <c r="G51" s="90"/>
+      <c r="H51" s="90"/>
+      <c r="I51" s="90"/>
+      <c r="J51" s="91"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="25">
@@ -5304,18 +5342,18 @@
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="91" t="s">
+      <c r="A62" s="89" t="s">
         <v>247</v>
       </c>
-      <c r="B62" s="92"/>
-      <c r="C62" s="92"/>
-      <c r="D62" s="92"/>
-      <c r="E62" s="92"/>
-      <c r="F62" s="92"/>
-      <c r="G62" s="92"/>
-      <c r="H62" s="92"/>
-      <c r="I62" s="92"/>
-      <c r="J62" s="93"/>
+      <c r="B62" s="90"/>
+      <c r="C62" s="90"/>
+      <c r="D62" s="90"/>
+      <c r="E62" s="90"/>
+      <c r="F62" s="90"/>
+      <c r="G62" s="90"/>
+      <c r="H62" s="90"/>
+      <c r="I62" s="90"/>
+      <c r="J62" s="91"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="25">
@@ -5670,18 +5708,18 @@
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="91" t="s">
+      <c r="A74" s="89" t="s">
         <v>346</v>
       </c>
-      <c r="B74" s="92"/>
-      <c r="C74" s="92"/>
-      <c r="D74" s="92"/>
-      <c r="E74" s="92"/>
-      <c r="F74" s="92"/>
-      <c r="G74" s="92"/>
-      <c r="H74" s="92"/>
-      <c r="I74" s="92"/>
-      <c r="J74" s="93"/>
+      <c r="B74" s="90"/>
+      <c r="C74" s="90"/>
+      <c r="D74" s="90"/>
+      <c r="E74" s="90"/>
+      <c r="F74" s="90"/>
+      <c r="G74" s="90"/>
+      <c r="H74" s="90"/>
+      <c r="I74" s="90"/>
+      <c r="J74" s="91"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="25">
@@ -6548,18 +6586,18 @@
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A102" s="87" t="s">
+      <c r="A102" s="85" t="s">
         <v>376</v>
       </c>
-      <c r="B102" s="87"/>
-      <c r="C102" s="87"/>
-      <c r="D102" s="87"/>
-      <c r="E102" s="87"/>
-      <c r="F102" s="87"/>
-      <c r="G102" s="87"/>
-      <c r="H102" s="87"/>
-      <c r="I102" s="87"/>
-      <c r="J102" s="87"/>
+      <c r="B102" s="85"/>
+      <c r="C102" s="85"/>
+      <c r="D102" s="85"/>
+      <c r="E102" s="85"/>
+      <c r="F102" s="85"/>
+      <c r="G102" s="85"/>
+      <c r="H102" s="85"/>
+      <c r="I102" s="85"/>
+      <c r="J102" s="85"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="25">
@@ -6882,18 +6920,18 @@
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A113" s="82" t="s">
+      <c r="A113" s="84" t="s">
         <v>378</v>
       </c>
-      <c r="B113" s="82"/>
-      <c r="C113" s="82"/>
-      <c r="D113" s="82"/>
-      <c r="E113" s="82"/>
-      <c r="F113" s="82"/>
-      <c r="G113" s="82"/>
-      <c r="H113" s="82"/>
-      <c r="I113" s="82"/>
-      <c r="J113" s="82"/>
+      <c r="B113" s="84"/>
+      <c r="C113" s="84"/>
+      <c r="D113" s="84"/>
+      <c r="E113" s="84"/>
+      <c r="F113" s="84"/>
+      <c r="G113" s="84"/>
+      <c r="H113" s="84"/>
+      <c r="I113" s="84"/>
+      <c r="J113" s="84"/>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="25">
@@ -6928,18 +6966,18 @@
       </c>
     </row>
     <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="82" t="s">
+      <c r="A115" s="84" t="s">
         <v>383</v>
       </c>
-      <c r="B115" s="82"/>
-      <c r="C115" s="82"/>
-      <c r="D115" s="82"/>
-      <c r="E115" s="82"/>
-      <c r="F115" s="82"/>
-      <c r="G115" s="82"/>
-      <c r="H115" s="82"/>
-      <c r="I115" s="82"/>
-      <c r="J115" s="82"/>
+      <c r="B115" s="84"/>
+      <c r="C115" s="84"/>
+      <c r="D115" s="84"/>
+      <c r="E115" s="84"/>
+      <c r="F115" s="84"/>
+      <c r="G115" s="84"/>
+      <c r="H115" s="84"/>
+      <c r="I115" s="84"/>
+      <c r="J115" s="84"/>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" s="25">
@@ -6974,18 +7012,18 @@
       </c>
     </row>
     <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="82" t="s">
+      <c r="A117" s="84" t="s">
         <v>396</v>
       </c>
-      <c r="B117" s="82"/>
-      <c r="C117" s="82"/>
-      <c r="D117" s="82"/>
-      <c r="E117" s="82"/>
-      <c r="F117" s="82"/>
-      <c r="G117" s="82"/>
-      <c r="H117" s="82"/>
-      <c r="I117" s="82"/>
-      <c r="J117" s="82"/>
+      <c r="B117" s="84"/>
+      <c r="C117" s="84"/>
+      <c r="D117" s="84"/>
+      <c r="E117" s="84"/>
+      <c r="F117" s="84"/>
+      <c r="G117" s="84"/>
+      <c r="H117" s="84"/>
+      <c r="I117" s="84"/>
+      <c r="J117" s="84"/>
     </row>
     <row r="118" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="25">
@@ -7310,18 +7348,18 @@
       <c r="X124" s="58"/>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="82" t="s">
+      <c r="A125" s="84" t="s">
         <v>413</v>
       </c>
-      <c r="B125" s="82"/>
-      <c r="C125" s="82"/>
-      <c r="D125" s="83"/>
-      <c r="E125" s="83"/>
-      <c r="F125" s="83"/>
-      <c r="G125" s="83"/>
-      <c r="H125" s="83"/>
-      <c r="I125" s="83"/>
-      <c r="J125" s="83"/>
+      <c r="B125" s="84"/>
+      <c r="C125" s="84"/>
+      <c r="D125" s="92"/>
+      <c r="E125" s="92"/>
+      <c r="F125" s="92"/>
+      <c r="G125" s="92"/>
+      <c r="H125" s="92"/>
+      <c r="I125" s="92"/>
+      <c r="J125" s="92"/>
     </row>
     <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="59">
@@ -7784,18 +7822,18 @@
       <c r="X135" s="58"/>
     </row>
     <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="84" t="s">
+      <c r="A136" s="93" t="s">
         <v>442</v>
       </c>
-      <c r="B136" s="85"/>
-      <c r="C136" s="85"/>
-      <c r="D136" s="85"/>
-      <c r="E136" s="85"/>
-      <c r="F136" s="85"/>
-      <c r="G136" s="85"/>
-      <c r="H136" s="85"/>
-      <c r="I136" s="85"/>
-      <c r="J136" s="86"/>
+      <c r="B136" s="94"/>
+      <c r="C136" s="94"/>
+      <c r="D136" s="94"/>
+      <c r="E136" s="94"/>
+      <c r="F136" s="94"/>
+      <c r="G136" s="94"/>
+      <c r="H136" s="94"/>
+      <c r="I136" s="94"/>
+      <c r="J136" s="95"/>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="25">
@@ -8244,18 +8282,18 @@
       <c r="X146" s="58"/>
     </row>
     <row r="147" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A147" s="82" t="s">
+      <c r="A147" s="84" t="s">
         <v>514</v>
       </c>
-      <c r="B147" s="82"/>
-      <c r="C147" s="82"/>
-      <c r="D147" s="82"/>
-      <c r="E147" s="82"/>
-      <c r="F147" s="82"/>
-      <c r="G147" s="82"/>
-      <c r="H147" s="82"/>
-      <c r="I147" s="82"/>
-      <c r="J147" s="82"/>
+      <c r="B147" s="84"/>
+      <c r="C147" s="84"/>
+      <c r="D147" s="84"/>
+      <c r="E147" s="84"/>
+      <c r="F147" s="84"/>
+      <c r="G147" s="84"/>
+      <c r="H147" s="84"/>
+      <c r="I147" s="84"/>
+      <c r="J147" s="84"/>
     </row>
     <row r="148" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A148" s="25">
@@ -8290,18 +8328,18 @@
       </c>
     </row>
     <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="82" t="s">
+      <c r="A149" s="84" t="s">
         <v>540</v>
       </c>
-      <c r="B149" s="82"/>
-      <c r="C149" s="82"/>
-      <c r="D149" s="82"/>
-      <c r="E149" s="82"/>
-      <c r="F149" s="82"/>
-      <c r="G149" s="82"/>
-      <c r="H149" s="82"/>
-      <c r="I149" s="82"/>
-      <c r="J149" s="82"/>
+      <c r="B149" s="84"/>
+      <c r="C149" s="84"/>
+      <c r="D149" s="84"/>
+      <c r="E149" s="84"/>
+      <c r="F149" s="84"/>
+      <c r="G149" s="84"/>
+      <c r="H149" s="84"/>
+      <c r="I149" s="84"/>
+      <c r="J149" s="84"/>
     </row>
     <row r="150" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="65">
@@ -9168,18 +9206,18 @@
       <c r="Z167" s="58"/>
     </row>
     <row r="168" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="82" t="s">
+      <c r="A168" s="84" t="s">
         <v>619</v>
       </c>
-      <c r="B168" s="82"/>
-      <c r="C168" s="82"/>
-      <c r="D168" s="82"/>
-      <c r="E168" s="82"/>
-      <c r="F168" s="82"/>
-      <c r="G168" s="82"/>
-      <c r="H168" s="82"/>
-      <c r="I168" s="82"/>
-      <c r="J168" s="82"/>
+      <c r="B168" s="84"/>
+      <c r="C168" s="84"/>
+      <c r="D168" s="84"/>
+      <c r="E168" s="84"/>
+      <c r="F168" s="84"/>
+      <c r="G168" s="84"/>
+      <c r="H168" s="84"/>
+      <c r="I168" s="84"/>
+      <c r="J168" s="84"/>
     </row>
     <row r="169" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="73">
@@ -9309,8 +9347,77 @@
         <v>13</v>
       </c>
     </row>
+    <row r="173" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="73">
+        <v>5</v>
+      </c>
+      <c r="B173" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C173" s="79" t="s">
+        <v>628</v>
+      </c>
+      <c r="D173" s="83" t="s">
+        <v>629</v>
+      </c>
+      <c r="E173" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="F173" s="75" t="s">
+        <v>627</v>
+      </c>
+      <c r="G173" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H173" s="74" t="s">
+        <v>544</v>
+      </c>
+      <c r="I173" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J173" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="174" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="73">
+        <v>2</v>
+      </c>
+      <c r="B174" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C174" s="75" t="s">
+        <v>630</v>
+      </c>
+      <c r="D174" s="77" t="s">
+        <v>632</v>
+      </c>
+      <c r="E174" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F174" s="75" t="s">
+        <v>631</v>
+      </c>
+      <c r="G174" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H174" s="74" t="s">
+        <v>544</v>
+      </c>
+      <c r="I174" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J174" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A168:J168"/>
+    <mergeCell ref="A149:J149"/>
+    <mergeCell ref="A147:J147"/>
+    <mergeCell ref="A125:J125"/>
+    <mergeCell ref="A136:J136"/>
     <mergeCell ref="A117:J117"/>
     <mergeCell ref="A115:J115"/>
     <mergeCell ref="A113:J113"/>
@@ -9320,11 +9427,6 @@
     <mergeCell ref="A51:J51"/>
     <mergeCell ref="A62:J62"/>
     <mergeCell ref="A74:J74"/>
-    <mergeCell ref="A168:J168"/>
-    <mergeCell ref="A149:J149"/>
-    <mergeCell ref="A147:J147"/>
-    <mergeCell ref="A125:J125"/>
-    <mergeCell ref="A136:J136"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -9422,7 +9524,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:X170"/>
+  <dimension ref="A1:X173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -21518,156 +21620,108 @@
       </c>
     </row>
     <row r="167" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="75" t="s">
-        <v>606</v>
-      </c>
-      <c r="B167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S167" s="49" t="s">
-        <v>608</v>
-      </c>
-      <c r="T167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V167" s="48" t="s">
-        <v>624</v>
-      </c>
-      <c r="W167" s="36" t="s">
-        <v>610</v>
-      </c>
-      <c r="X167" s="48" t="s">
-        <v>22</v>
-      </c>
+      <c r="A167" s="82"/>
+      <c r="B167" s="48"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="48"/>
+      <c r="E167" s="48"/>
+      <c r="F167" s="48"/>
+      <c r="G167" s="49"/>
+      <c r="H167" s="48"/>
+      <c r="I167" s="48"/>
+      <c r="J167" s="36"/>
+      <c r="K167" s="48"/>
+      <c r="L167" s="48"/>
+      <c r="M167" s="48"/>
+      <c r="N167" s="48"/>
+      <c r="O167" s="48"/>
+      <c r="P167" s="48"/>
+      <c r="Q167" s="48"/>
+      <c r="R167" s="48"/>
+      <c r="S167" s="48"/>
+      <c r="T167" s="48"/>
+      <c r="U167" s="48"/>
+      <c r="V167" s="48"/>
+      <c r="W167" s="48"/>
+      <c r="X167" s="48"/>
     </row>
     <row r="168" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="75" t="s">
+        <v>606</v>
+      </c>
+      <c r="B168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S168" s="49" t="s">
+        <v>608</v>
+      </c>
+      <c r="T168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V168" s="48" t="s">
+        <v>624</v>
+      </c>
+      <c r="W168" s="36" t="s">
+        <v>610</v>
+      </c>
+      <c r="X168" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="169" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="75" t="s">
         <v>611</v>
-      </c>
-      <c r="B168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S168" s="49" t="s">
-        <v>612</v>
-      </c>
-      <c r="T168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W168" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X168" s="78" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="169" spans="1:24" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="75" t="s">
-        <v>616</v>
       </c>
       <c r="B169" s="48" t="s">
         <v>22</v>
@@ -21735,82 +21789,304 @@
       <c r="W169" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="X169" s="94" t="s">
+      <c r="X169" s="78" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="170" spans="1:24" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="75" t="s">
+        <v>616</v>
+      </c>
+      <c r="B170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S170" s="49" t="s">
+        <v>612</v>
+      </c>
+      <c r="T170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W170" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X170" s="96" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="171" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="75" t="s">
+        <v>620</v>
+      </c>
+      <c r="B171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S171" s="49" t="s">
+        <v>608</v>
+      </c>
+      <c r="T171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V171" s="48" t="s">
+        <v>626</v>
+      </c>
+      <c r="W171" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X171" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="172" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="75" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="170" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="75" t="s">
-        <v>620</v>
-      </c>
-      <c r="B170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S170" s="49" t="s">
-        <v>608</v>
-      </c>
-      <c r="T170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V170" s="48" t="s">
+      <c r="B172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S172" s="49" t="s">
+        <v>612</v>
+      </c>
+      <c r="T172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W172" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X172" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="173" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="75" t="s">
+        <v>631</v>
+      </c>
+      <c r="B173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S173" s="49" t="s">
+        <v>612</v>
+      </c>
+      <c r="T173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W173" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X173" s="78" t="s">
         <v>625</v>
-      </c>
-      <c r="W170" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X170" s="48" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -21937,12 +22213,14 @@
     <hyperlink ref="G126" r:id="rId15" xr:uid="{FEC9AB2B-6FD0-4D08-96BB-5634F117BFB0}"/>
     <hyperlink ref="D136" r:id="rId16" xr:uid="{EAE526E7-10C0-4EC9-846A-D81343ACBEC4}"/>
     <hyperlink ref="G166" r:id="rId17" xr:uid="{0A52F660-ABF2-41CF-BD4C-5E55458D590D}"/>
-    <hyperlink ref="S167" r:id="rId18" xr:uid="{13FB8A07-5562-4AAB-9E83-934C01965617}"/>
-    <hyperlink ref="S169" r:id="rId19" xr:uid="{23F160B7-D3CD-415D-B0D6-1EECB7AFE96F}"/>
-    <hyperlink ref="S170" r:id="rId20" xr:uid="{7206C778-989C-4587-83FA-C09C20DA42BD}"/>
-    <hyperlink ref="X168" r:id="rId21" tooltip="sun flower" display="https://qa.zlta.testingserver8.com/product-detail/pink-sun-flower" xr:uid="{CFFC3DF8-4F00-4B09-AF68-A4EB71080BA6}"/>
+    <hyperlink ref="S168" r:id="rId18" xr:uid="{13FB8A07-5562-4AAB-9E83-934C01965617}"/>
+    <hyperlink ref="S170" r:id="rId19" xr:uid="{23F160B7-D3CD-415D-B0D6-1EECB7AFE96F}"/>
+    <hyperlink ref="S171" r:id="rId20" xr:uid="{7206C778-989C-4587-83FA-C09C20DA42BD}"/>
+    <hyperlink ref="S172" r:id="rId21" xr:uid="{3B0D666D-626C-490D-A9B6-B9643B9EDF8A}"/>
+    <hyperlink ref="X173" r:id="rId22" tooltip="sun flower" display="https://qa.zlta.testingserver8.com/product-detail/pink-sun-flower" xr:uid="{8DF4456C-34CD-4BEB-9600-CDFCBBC5E3F1}"/>
+    <hyperlink ref="X169" r:id="rId23" tooltip="pink real heaven" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{7AB2CC85-055B-4B62-B758-A407CA7BD409}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId22"/>
+  <pageSetup orientation="portrait" r:id="rId24"/>
 </worksheet>
 </file>
--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\zlaata\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\repository\ZlaataProduction\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D1B537-ACC1-4AED-97B8-5BA63B47E338}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9998249F-6F60-4A79-BB66-4F67AFC08533}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3240" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5477" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5510" uniqueCount="638">
   <si>
     <t>S.No</t>
   </si>
@@ -1903,9 +1903,6 @@
     <t>Home Page Test</t>
   </si>
   <si>
-    <t>sun flower</t>
-  </si>
-  <si>
     <t>Test demo</t>
   </si>
   <si>
@@ -1931,6 +1928,18 @@
   </si>
   <si>
     <t>sadsdasad</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_ADM_07</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/special-timer-event</t>
+  </si>
+  <si>
+    <t>Verify all uploaded Special Timer products appear in Admin and User App.</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_ADM_07</t>
   </si>
 </sst>
 </file>
@@ -2377,7 +2386,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2588,7 +2597,25 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2611,21 +2638,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3429,7 +3441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z174"/>
+  <dimension ref="A1:Z175"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -4180,18 +4192,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="86" t="s">
+      <c r="A24" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="87"/>
-      <c r="C24" s="87"/>
-      <c r="D24" s="87"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="87"/>
-      <c r="G24" s="87"/>
-      <c r="H24" s="87"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="88"/>
+      <c r="B24" s="93"/>
+      <c r="C24" s="93"/>
+      <c r="D24" s="93"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="94"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
@@ -4578,18 +4590,18 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="89" t="s">
+      <c r="A37" s="95" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="90"/>
-      <c r="C37" s="90"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="90"/>
-      <c r="F37" s="90"/>
-      <c r="G37" s="90"/>
-      <c r="H37" s="90"/>
-      <c r="I37" s="90"/>
-      <c r="J37" s="91"/>
+      <c r="B37" s="96"/>
+      <c r="C37" s="96"/>
+      <c r="D37" s="96"/>
+      <c r="E37" s="96"/>
+      <c r="F37" s="96"/>
+      <c r="G37" s="96"/>
+      <c r="H37" s="96"/>
+      <c r="I37" s="96"/>
+      <c r="J37" s="97"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
@@ -5008,18 +5020,18 @@
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="89" t="s">
+      <c r="A51" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="B51" s="90"/>
-      <c r="C51" s="90"/>
-      <c r="D51" s="90"/>
-      <c r="E51" s="90"/>
-      <c r="F51" s="90"/>
-      <c r="G51" s="90"/>
-      <c r="H51" s="90"/>
-      <c r="I51" s="90"/>
-      <c r="J51" s="91"/>
+      <c r="B51" s="96"/>
+      <c r="C51" s="96"/>
+      <c r="D51" s="96"/>
+      <c r="E51" s="96"/>
+      <c r="F51" s="96"/>
+      <c r="G51" s="96"/>
+      <c r="H51" s="96"/>
+      <c r="I51" s="96"/>
+      <c r="J51" s="97"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="25">
@@ -5342,18 +5354,18 @@
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="89" t="s">
+      <c r="A62" s="95" t="s">
         <v>247</v>
       </c>
-      <c r="B62" s="90"/>
-      <c r="C62" s="90"/>
-      <c r="D62" s="90"/>
-      <c r="E62" s="90"/>
-      <c r="F62" s="90"/>
-      <c r="G62" s="90"/>
-      <c r="H62" s="90"/>
-      <c r="I62" s="90"/>
-      <c r="J62" s="91"/>
+      <c r="B62" s="96"/>
+      <c r="C62" s="96"/>
+      <c r="D62" s="96"/>
+      <c r="E62" s="96"/>
+      <c r="F62" s="96"/>
+      <c r="G62" s="96"/>
+      <c r="H62" s="96"/>
+      <c r="I62" s="96"/>
+      <c r="J62" s="97"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="25">
@@ -5708,18 +5720,18 @@
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="89" t="s">
+      <c r="A74" s="95" t="s">
         <v>346</v>
       </c>
-      <c r="B74" s="90"/>
-      <c r="C74" s="90"/>
-      <c r="D74" s="90"/>
-      <c r="E74" s="90"/>
-      <c r="F74" s="90"/>
-      <c r="G74" s="90"/>
-      <c r="H74" s="90"/>
-      <c r="I74" s="90"/>
-      <c r="J74" s="91"/>
+      <c r="B74" s="96"/>
+      <c r="C74" s="96"/>
+      <c r="D74" s="96"/>
+      <c r="E74" s="96"/>
+      <c r="F74" s="96"/>
+      <c r="G74" s="96"/>
+      <c r="H74" s="96"/>
+      <c r="I74" s="96"/>
+      <c r="J74" s="97"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="25">
@@ -6586,18 +6598,18 @@
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A102" s="85" t="s">
+      <c r="A102" s="91" t="s">
         <v>376</v>
       </c>
-      <c r="B102" s="85"/>
-      <c r="C102" s="85"/>
-      <c r="D102" s="85"/>
-      <c r="E102" s="85"/>
-      <c r="F102" s="85"/>
-      <c r="G102" s="85"/>
-      <c r="H102" s="85"/>
-      <c r="I102" s="85"/>
-      <c r="J102" s="85"/>
+      <c r="B102" s="91"/>
+      <c r="C102" s="91"/>
+      <c r="D102" s="91"/>
+      <c r="E102" s="91"/>
+      <c r="F102" s="91"/>
+      <c r="G102" s="91"/>
+      <c r="H102" s="91"/>
+      <c r="I102" s="91"/>
+      <c r="J102" s="91"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="25">
@@ -6920,18 +6932,18 @@
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A113" s="84" t="s">
+      <c r="A113" s="86" t="s">
         <v>378</v>
       </c>
-      <c r="B113" s="84"/>
-      <c r="C113" s="84"/>
-      <c r="D113" s="84"/>
-      <c r="E113" s="84"/>
-      <c r="F113" s="84"/>
-      <c r="G113" s="84"/>
-      <c r="H113" s="84"/>
-      <c r="I113" s="84"/>
-      <c r="J113" s="84"/>
+      <c r="B113" s="86"/>
+      <c r="C113" s="86"/>
+      <c r="D113" s="86"/>
+      <c r="E113" s="86"/>
+      <c r="F113" s="86"/>
+      <c r="G113" s="86"/>
+      <c r="H113" s="86"/>
+      <c r="I113" s="86"/>
+      <c r="J113" s="86"/>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="25">
@@ -6966,18 +6978,18 @@
       </c>
     </row>
     <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="84" t="s">
+      <c r="A115" s="86" t="s">
         <v>383</v>
       </c>
-      <c r="B115" s="84"/>
-      <c r="C115" s="84"/>
-      <c r="D115" s="84"/>
-      <c r="E115" s="84"/>
-      <c r="F115" s="84"/>
-      <c r="G115" s="84"/>
-      <c r="H115" s="84"/>
-      <c r="I115" s="84"/>
-      <c r="J115" s="84"/>
+      <c r="B115" s="86"/>
+      <c r="C115" s="86"/>
+      <c r="D115" s="86"/>
+      <c r="E115" s="86"/>
+      <c r="F115" s="86"/>
+      <c r="G115" s="86"/>
+      <c r="H115" s="86"/>
+      <c r="I115" s="86"/>
+      <c r="J115" s="86"/>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" s="25">
@@ -7012,18 +7024,18 @@
       </c>
     </row>
     <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="84" t="s">
+      <c r="A117" s="86" t="s">
         <v>396</v>
       </c>
-      <c r="B117" s="84"/>
-      <c r="C117" s="84"/>
-      <c r="D117" s="84"/>
-      <c r="E117" s="84"/>
-      <c r="F117" s="84"/>
-      <c r="G117" s="84"/>
-      <c r="H117" s="84"/>
-      <c r="I117" s="84"/>
-      <c r="J117" s="84"/>
+      <c r="B117" s="86"/>
+      <c r="C117" s="86"/>
+      <c r="D117" s="86"/>
+      <c r="E117" s="86"/>
+      <c r="F117" s="86"/>
+      <c r="G117" s="86"/>
+      <c r="H117" s="86"/>
+      <c r="I117" s="86"/>
+      <c r="J117" s="86"/>
     </row>
     <row r="118" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="25">
@@ -7348,18 +7360,18 @@
       <c r="X124" s="58"/>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="84" t="s">
+      <c r="A125" s="86" t="s">
         <v>413</v>
       </c>
-      <c r="B125" s="84"/>
-      <c r="C125" s="84"/>
-      <c r="D125" s="92"/>
-      <c r="E125" s="92"/>
-      <c r="F125" s="92"/>
-      <c r="G125" s="92"/>
-      <c r="H125" s="92"/>
-      <c r="I125" s="92"/>
-      <c r="J125" s="92"/>
+      <c r="B125" s="86"/>
+      <c r="C125" s="86"/>
+      <c r="D125" s="87"/>
+      <c r="E125" s="87"/>
+      <c r="F125" s="87"/>
+      <c r="G125" s="87"/>
+      <c r="H125" s="87"/>
+      <c r="I125" s="87"/>
+      <c r="J125" s="87"/>
     </row>
     <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="59">
@@ -7822,18 +7834,18 @@
       <c r="X135" s="58"/>
     </row>
     <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="93" t="s">
+      <c r="A136" s="88" t="s">
         <v>442</v>
       </c>
-      <c r="B136" s="94"/>
-      <c r="C136" s="94"/>
-      <c r="D136" s="94"/>
-      <c r="E136" s="94"/>
-      <c r="F136" s="94"/>
-      <c r="G136" s="94"/>
-      <c r="H136" s="94"/>
-      <c r="I136" s="94"/>
-      <c r="J136" s="95"/>
+      <c r="B136" s="89"/>
+      <c r="C136" s="89"/>
+      <c r="D136" s="89"/>
+      <c r="E136" s="89"/>
+      <c r="F136" s="89"/>
+      <c r="G136" s="89"/>
+      <c r="H136" s="89"/>
+      <c r="I136" s="89"/>
+      <c r="J136" s="90"/>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="25">
@@ -8282,18 +8294,18 @@
       <c r="X146" s="58"/>
     </row>
     <row r="147" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A147" s="84" t="s">
+      <c r="A147" s="86" t="s">
         <v>514</v>
       </c>
-      <c r="B147" s="84"/>
-      <c r="C147" s="84"/>
-      <c r="D147" s="84"/>
-      <c r="E147" s="84"/>
-      <c r="F147" s="84"/>
-      <c r="G147" s="84"/>
-      <c r="H147" s="84"/>
-      <c r="I147" s="84"/>
-      <c r="J147" s="84"/>
+      <c r="B147" s="86"/>
+      <c r="C147" s="86"/>
+      <c r="D147" s="86"/>
+      <c r="E147" s="86"/>
+      <c r="F147" s="86"/>
+      <c r="G147" s="86"/>
+      <c r="H147" s="86"/>
+      <c r="I147" s="86"/>
+      <c r="J147" s="86"/>
     </row>
     <row r="148" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A148" s="25">
@@ -8328,18 +8340,18 @@
       </c>
     </row>
     <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="84" t="s">
+      <c r="A149" s="86" t="s">
         <v>540</v>
       </c>
-      <c r="B149" s="84"/>
-      <c r="C149" s="84"/>
-      <c r="D149" s="84"/>
-      <c r="E149" s="84"/>
-      <c r="F149" s="84"/>
-      <c r="G149" s="84"/>
-      <c r="H149" s="84"/>
-      <c r="I149" s="84"/>
-      <c r="J149" s="84"/>
+      <c r="B149" s="86"/>
+      <c r="C149" s="86"/>
+      <c r="D149" s="86"/>
+      <c r="E149" s="86"/>
+      <c r="F149" s="86"/>
+      <c r="G149" s="86"/>
+      <c r="H149" s="86"/>
+      <c r="I149" s="86"/>
+      <c r="J149" s="86"/>
     </row>
     <row r="150" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="65">
@@ -9206,18 +9218,18 @@
       <c r="Z167" s="58"/>
     </row>
     <row r="168" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="84" t="s">
+      <c r="A168" s="86" t="s">
         <v>619</v>
       </c>
-      <c r="B168" s="84"/>
-      <c r="C168" s="84"/>
-      <c r="D168" s="84"/>
-      <c r="E168" s="84"/>
-      <c r="F168" s="84"/>
-      <c r="G168" s="84"/>
-      <c r="H168" s="84"/>
-      <c r="I168" s="84"/>
-      <c r="J168" s="84"/>
+      <c r="B168" s="86"/>
+      <c r="C168" s="86"/>
+      <c r="D168" s="86"/>
+      <c r="E168" s="86"/>
+      <c r="F168" s="86"/>
+      <c r="G168" s="86"/>
+      <c r="H168" s="86"/>
+      <c r="I168" s="86"/>
+      <c r="J168" s="86"/>
     </row>
     <row r="169" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="73">
@@ -9355,16 +9367,16 @@
         <v>10</v>
       </c>
       <c r="C173" s="79" t="s">
+        <v>627</v>
+      </c>
+      <c r="D173" s="83" t="s">
         <v>628</v>
-      </c>
-      <c r="D173" s="83" t="s">
-        <v>629</v>
       </c>
       <c r="E173" s="80" t="s">
         <v>14</v>
       </c>
       <c r="F173" s="75" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G173" s="74" t="s">
         <v>11</v>
@@ -9381,22 +9393,22 @@
     </row>
     <row r="174" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="73">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B174" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C174" s="75" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D174" s="77" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E174" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F174" s="75" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G174" s="74" t="s">
         <v>11</v>
@@ -9411,13 +9423,40 @@
         <v>13</v>
       </c>
     </row>
+    <row r="175" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="73">
+        <v>7</v>
+      </c>
+      <c r="B175" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C175" s="75" t="s">
+        <v>637</v>
+      </c>
+      <c r="D175" s="83" t="s">
+        <v>636</v>
+      </c>
+      <c r="E175" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F175" s="75" t="s">
+        <v>634</v>
+      </c>
+      <c r="G175" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H175" s="74" t="s">
+        <v>544</v>
+      </c>
+      <c r="I175" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J175" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A168:J168"/>
-    <mergeCell ref="A149:J149"/>
-    <mergeCell ref="A147:J147"/>
-    <mergeCell ref="A125:J125"/>
-    <mergeCell ref="A136:J136"/>
     <mergeCell ref="A117:J117"/>
     <mergeCell ref="A115:J115"/>
     <mergeCell ref="A113:J113"/>
@@ -9427,6 +9466,11 @@
     <mergeCell ref="A51:J51"/>
     <mergeCell ref="A62:J62"/>
     <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A168:J168"/>
+    <mergeCell ref="A149:J149"/>
+    <mergeCell ref="A147:J147"/>
+    <mergeCell ref="A125:J125"/>
+    <mergeCell ref="A136:J136"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -9524,7 +9568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:X173"/>
+  <dimension ref="A1:X174"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -21790,7 +21834,7 @@
         <v>22</v>
       </c>
       <c r="X169" s="78" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="170" spans="1:24" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -21863,8 +21907,8 @@
       <c r="W170" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="X170" s="96" t="s">
-        <v>634</v>
+      <c r="X170" s="84" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="171" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -21932,7 +21976,7 @@
         <v>22</v>
       </c>
       <c r="V171" s="48" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="W171" s="36" t="s">
         <v>22</v>
@@ -21943,7 +21987,7 @@
     </row>
     <row r="172" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="75" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B172" s="48" t="s">
         <v>22</v>
@@ -22017,7 +22061,7 @@
     </row>
     <row r="173" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="75" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B173" s="48" t="s">
         <v>22</v>
@@ -22085,8 +22129,82 @@
       <c r="W173" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="X173" s="78" t="s">
-        <v>625</v>
+      <c r="X173" s="85" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="174" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="75" t="s">
+        <v>634</v>
+      </c>
+      <c r="B174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S174" s="49" t="s">
+        <v>635</v>
+      </c>
+      <c r="T174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W174" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X174" s="48" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -22217,8 +22335,8 @@
     <hyperlink ref="S170" r:id="rId19" xr:uid="{23F160B7-D3CD-415D-B0D6-1EECB7AFE96F}"/>
     <hyperlink ref="S171" r:id="rId20" xr:uid="{7206C778-989C-4587-83FA-C09C20DA42BD}"/>
     <hyperlink ref="S172" r:id="rId21" xr:uid="{3B0D666D-626C-490D-A9B6-B9643B9EDF8A}"/>
-    <hyperlink ref="X173" r:id="rId22" tooltip="sun flower" display="https://qa.zlta.testingserver8.com/product-detail/pink-sun-flower" xr:uid="{8DF4456C-34CD-4BEB-9600-CDFCBBC5E3F1}"/>
-    <hyperlink ref="X169" r:id="rId23" tooltip="pink real heaven" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{7AB2CC85-055B-4B62-B758-A407CA7BD409}"/>
+    <hyperlink ref="X169" r:id="rId22" tooltip="pink real heaven" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{7AB2CC85-055B-4B62-B758-A407CA7BD409}"/>
+    <hyperlink ref="X173" r:id="rId23" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{E6426F17-2EE7-4F4A-80B0-E58B87C35EDA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId24"/>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\repository\ZlaataProduction\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlataaProduction\ZlaataProduction\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9998249F-6F60-4A79-BB66-4F67AFC08533}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D01CEEE-6A89-415C-B453-5BB9012117FD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5510" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5510" uniqueCount="637">
   <si>
     <t>S.No</t>
   </si>
@@ -154,9 +154,6 @@
     <t>Login</t>
   </si>
   <si>
-    <t>User Login Scenario</t>
-  </si>
-  <si>
     <t>Exchange Link</t>
   </si>
   <si>
@@ -502,9 +499,6 @@
     <t>TC_UI_Zlaata_Login_02</t>
   </si>
   <si>
-    <t>FirstBuy200 Coupon is displaying</t>
-  </si>
-  <si>
     <t>TC_UI_Zlaata_Login_03</t>
   </si>
   <si>
@@ -550,9 +544,6 @@
     <t>TC_UI_Zlaata_Home_01</t>
   </si>
   <si>
-    <t>Verify if the user is able to click on the homepage banner.</t>
-  </si>
-  <si>
     <t>TD_UI_Zlaata_Home_01</t>
   </si>
   <si>
@@ -571,9 +562,6 @@
     <t>TC_UI_Zlaata_Home_03</t>
   </si>
   <si>
-    <t>Verify if the user is able to click on the banner pause button.</t>
-  </si>
-  <si>
     <t>TD_UI_Zlaata_Home_03</t>
   </si>
   <si>
@@ -703,30 +691,18 @@
     <t>TC_UI_Zlaata_Menus_01</t>
   </si>
   <si>
-    <t>Verify that the user is able to click the Homepage header menu.</t>
-  </si>
-  <si>
     <t>Menus</t>
   </si>
   <si>
     <t>TC_UI_Zlaata_Menus_02</t>
   </si>
   <si>
-    <t>Verify that the user is able to click the "New Arrival" page header menu.</t>
-  </si>
-  <si>
     <t>TC_UI_Zlaata_Menus_03</t>
   </si>
   <si>
-    <t>Verify that the user is able to click the "New Arrival" hover image.</t>
-  </si>
-  <si>
     <t>TC_UI_Zlaata_Menus_04</t>
   </si>
   <si>
-    <t>Verify that the user is able to click the "Sale" header menu.</t>
-  </si>
-  <si>
     <t>TC_UI_Zlaata_Menus_05</t>
   </si>
   <si>
@@ -904,9 +880,6 @@
     <t>TC_UI_Zlaata_PDP_05</t>
   </si>
   <si>
-    <t>Verify "Best Price" Functionality</t>
-  </si>
-  <si>
     <t>TD_UI_Zlaata_PDP_05</t>
   </si>
   <si>
@@ -1940,6 +1913,30 @@
   </si>
   <si>
     <t>TC_UI_Zlaata_ADM_07</t>
+  </si>
+  <si>
+    <t>Verify if the user is able to launch URL and click Logo and banner on the homepage banner.</t>
+  </si>
+  <si>
+    <t>Verify that the user is able to click All  Header menu.</t>
+  </si>
+  <si>
+    <t>Verify that the user is able to click the "New Arrival" page header menu All Suggestion products.</t>
+  </si>
+  <si>
+    <t>Verify that the user is able to click any all category in the "Shop" dropdown.</t>
+  </si>
+  <si>
+    <t>Verify that the user is able to click the "Bss-Lady" header menu All Suggestions.</t>
+  </si>
+  <si>
+    <t>User Login Negative Scenario</t>
+  </si>
+  <si>
+    <t>User Login Valid Scenario</t>
+  </si>
+  <si>
+    <t>Verify Color item Selection Functionality</t>
   </si>
 </sst>
 </file>
@@ -3498,7 +3495,7 @@
         <v>15</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>14</v>
@@ -3530,7 +3527,7 @@
         <v>24</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>14</v>
@@ -3562,7 +3559,7 @@
         <v>27</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
@@ -3591,16 +3588,16 @@
         <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>11</v>
@@ -3623,16 +3620,16 @@
         <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>11</v>
@@ -3655,16 +3652,16 @@
         <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>11</v>
@@ -3687,16 +3684,16 @@
         <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>97</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>98</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>11</v>
@@ -3719,16 +3716,16 @@
         <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>11</v>
@@ -3751,16 +3748,16 @@
         <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>101</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>102</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>11</v>
@@ -3783,16 +3780,16 @@
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>11</v>
@@ -3815,16 +3812,16 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>11</v>
@@ -3847,16 +3844,16 @@
         <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>108</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>11</v>
@@ -3879,16 +3876,16 @@
         <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>11</v>
@@ -3911,16 +3908,16 @@
         <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>110</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>111</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>11</v>
@@ -3943,16 +3940,16 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>112</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>113</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>11</v>
@@ -3975,16 +3972,16 @@
         <v>10</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>114</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>115</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>11</v>
@@ -4007,16 +4004,16 @@
         <v>10</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>116</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>117</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>11</v>
@@ -4039,16 +4036,16 @@
         <v>10</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>118</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>119</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>11</v>
@@ -4071,16 +4068,16 @@
         <v>10</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>11</v>
@@ -4103,16 +4100,16 @@
         <v>10</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>11</v>
@@ -4135,16 +4132,16 @@
         <v>10</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>11</v>
@@ -4167,16 +4164,16 @@
         <v>10</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E23" s="16" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>11</v>
@@ -4193,7 +4190,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="92" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B24" s="93"/>
       <c r="C24" s="93"/>
@@ -4213,16 +4210,16 @@
         <v>10</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>42</v>
+        <v>634</v>
       </c>
       <c r="E25" s="22" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G25" s="22" t="s">
         <v>11</v>
@@ -4245,16 +4242,16 @@
         <v>10</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>158</v>
+        <v>635</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>11</v>
@@ -4277,16 +4274,16 @@
         <v>10</v>
       </c>
       <c r="C27" s="47" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D27" s="47" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F27" s="46" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>11</v>
@@ -4309,16 +4306,16 @@
         <v>10</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>11</v>
@@ -4341,16 +4338,16 @@
         <v>10</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>11</v>
@@ -4373,16 +4370,16 @@
         <v>10</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D30" s="47" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F30" s="46" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>11</v>
@@ -4405,16 +4402,16 @@
         <v>10</v>
       </c>
       <c r="C31" s="47" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D31" s="47" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="E31" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F31" s="46" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>11</v>
@@ -4437,16 +4434,16 @@
         <v>10</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F32" s="46" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>11</v>
@@ -4469,16 +4466,16 @@
         <v>10</v>
       </c>
       <c r="C33" s="47" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D33" s="47" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F33" s="46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>11</v>
@@ -4501,16 +4498,16 @@
         <v>10</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D34" s="47" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E34" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F34" s="46" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G34" s="13" t="s">
         <v>11</v>
@@ -4533,16 +4530,16 @@
         <v>10</v>
       </c>
       <c r="C35" s="47" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D35" s="47" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E35" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F35" s="46" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>11</v>
@@ -4565,16 +4562,16 @@
         <v>10</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D36" s="47" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F36" s="46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>11</v>
@@ -4591,7 +4588,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="95" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B37" s="96"/>
       <c r="C37" s="96"/>
@@ -4611,22 +4608,22 @@
         <v>10</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D38" s="48" t="s">
-        <v>174</v>
+        <v>629</v>
       </c>
       <c r="E38" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F38" s="47" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I38" s="13" t="s">
         <v>12</v>
@@ -4643,22 +4640,22 @@
         <v>10</v>
       </c>
       <c r="C39" s="47" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D39" s="48" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E39" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F39" s="47" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I39" s="13" t="s">
         <v>12</v>
@@ -4675,22 +4672,22 @@
         <v>10</v>
       </c>
       <c r="C40" s="47" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D40" s="48" t="s">
-        <v>181</v>
+        <v>632</v>
       </c>
       <c r="E40" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F40" s="47" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G40" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I40" s="13" t="s">
         <v>12</v>
@@ -4707,22 +4704,22 @@
         <v>10</v>
       </c>
       <c r="C41" s="47" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D41" s="48" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E41" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F41" s="47" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>12</v>
@@ -4739,22 +4736,22 @@
         <v>10</v>
       </c>
       <c r="C42" s="47" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D42" s="48" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E42" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F42" s="47" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I42" s="13" t="s">
         <v>12</v>
@@ -4771,22 +4768,22 @@
         <v>10</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D43" s="48" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="E43" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F43" s="47" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>12</v>
@@ -4803,22 +4800,22 @@
         <v>10</v>
       </c>
       <c r="C44" s="47" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D44" s="48" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E44" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F44" s="47" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G44" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I44" s="13" t="s">
         <v>12</v>
@@ -4835,22 +4832,22 @@
         <v>10</v>
       </c>
       <c r="C45" s="47" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D45" s="48" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E45" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F45" s="47" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G45" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I45" s="13" t="s">
         <v>12</v>
@@ -4867,22 +4864,22 @@
         <v>10</v>
       </c>
       <c r="C46" s="47" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D46" s="48" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E46" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F46" s="47" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G46" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I46" s="13" t="s">
         <v>12</v>
@@ -4899,22 +4896,22 @@
         <v>10</v>
       </c>
       <c r="C47" s="47" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D47" s="48" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="E47" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F47" s="47" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G47" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I47" s="13" t="s">
         <v>12</v>
@@ -4931,22 +4928,22 @@
         <v>10</v>
       </c>
       <c r="C48" s="47" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D48" s="48" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E48" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F48" s="47" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G48" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I48" s="13" t="s">
         <v>12</v>
@@ -4963,22 +4960,22 @@
         <v>10</v>
       </c>
       <c r="C49" s="47" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D49" s="48" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E49" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F49" s="47" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G49" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I49" s="13" t="s">
         <v>12</v>
@@ -4995,22 +4992,22 @@
         <v>10</v>
       </c>
       <c r="C50" s="47" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D50" s="48" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E50" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F50" s="47" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G50" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I50" s="13" t="s">
         <v>12</v>
@@ -5021,7 +5018,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="95" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B51" s="96"/>
       <c r="C51" s="96"/>
@@ -5041,22 +5038,22 @@
         <v>10</v>
       </c>
       <c r="C52" s="48" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D52" s="48" t="s">
-        <v>225</v>
+        <v>630</v>
       </c>
       <c r="E52" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F52" s="48" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="G52" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I52" s="13" t="s">
         <v>12</v>
@@ -5073,22 +5070,22 @@
         <v>10</v>
       </c>
       <c r="C53" s="48" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D53" s="48" t="s">
-        <v>228</v>
+        <v>631</v>
       </c>
       <c r="E53" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F53" s="48" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G53" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I53" s="13" t="s">
         <v>12</v>
@@ -5105,22 +5102,22 @@
         <v>10</v>
       </c>
       <c r="C54" s="48" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D54" s="48" t="s">
-        <v>230</v>
+        <v>632</v>
       </c>
       <c r="E54" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F54" s="48" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="G54" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I54" s="13" t="s">
         <v>12</v>
@@ -5137,22 +5134,22 @@
         <v>10</v>
       </c>
       <c r="C55" s="48" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D55" s="48" t="s">
-        <v>232</v>
+        <v>633</v>
       </c>
       <c r="E55" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F55" s="48" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I55" s="13" t="s">
         <v>12</v>
@@ -5169,22 +5166,22 @@
         <v>10</v>
       </c>
       <c r="C56" s="48" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="D56" s="48" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="E56" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F56" s="48" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I56" s="13" t="s">
         <v>12</v>
@@ -5201,22 +5198,22 @@
         <v>10</v>
       </c>
       <c r="C57" s="48" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D57" s="48" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="E57" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F57" s="48" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>12</v>
@@ -5233,22 +5230,22 @@
         <v>10</v>
       </c>
       <c r="C58" s="48" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D58" s="48" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="E58" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F58" s="48" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I58" s="13" t="s">
         <v>12</v>
@@ -5265,22 +5262,22 @@
         <v>10</v>
       </c>
       <c r="C59" s="48" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="D59" s="48" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E59" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F59" s="48" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>12</v>
@@ -5297,22 +5294,22 @@
         <v>10</v>
       </c>
       <c r="C60" s="48" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D60" s="48" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E60" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F60" s="48" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I60" s="13" t="s">
         <v>12</v>
@@ -5329,22 +5326,22 @@
         <v>10</v>
       </c>
       <c r="C61" s="48" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D61" s="48" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E61" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F61" s="48" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I61" s="13" t="s">
         <v>12</v>
@@ -5355,7 +5352,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="95" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B62" s="96"/>
       <c r="C62" s="96"/>
@@ -5375,22 +5372,22 @@
         <v>10</v>
       </c>
       <c r="C63" s="48" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D63" s="48" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E63" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F63" s="48" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="G63" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H63" s="48" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I63" s="48" t="s">
         <v>12</v>
@@ -5407,22 +5404,22 @@
         <v>10</v>
       </c>
       <c r="C64" s="48" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D64" s="48" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E64" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F64" s="48" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="G64" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H64" s="48" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I64" s="48" t="s">
         <v>12</v>
@@ -5439,22 +5436,22 @@
         <v>10</v>
       </c>
       <c r="C65" s="48" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="D65" s="48" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="E65" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F65" s="48" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="G65" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H65" s="48" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I65" s="48" t="s">
         <v>12</v>
@@ -5471,22 +5468,22 @@
         <v>10</v>
       </c>
       <c r="C66" s="48" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D66" s="48" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E66" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F66" s="48" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G66" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H66" s="48" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I66" s="48" t="s">
         <v>12</v>
@@ -5503,22 +5500,22 @@
         <v>10</v>
       </c>
       <c r="C67" s="48" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D67" s="48" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="E67" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F67" s="48" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="G67" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H67" s="48" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I67" s="48" t="s">
         <v>12</v>
@@ -5535,22 +5532,22 @@
         <v>10</v>
       </c>
       <c r="C68" s="48" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="D68" s="48" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="E68" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F68" s="48" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="G68" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H68" s="48" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I68" s="48" t="s">
         <v>12</v>
@@ -5567,22 +5564,22 @@
         <v>10</v>
       </c>
       <c r="C69" s="48" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D69" s="48" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="E69" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F69" s="48" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="G69" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H69" s="48" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I69" s="48" t="s">
         <v>12</v>
@@ -5599,22 +5596,22 @@
         <v>10</v>
       </c>
       <c r="C70" s="48" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D70" s="48" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E70" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F70" s="48" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="G70" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H70" s="48" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I70" s="48" t="s">
         <v>12</v>
@@ -5631,22 +5628,22 @@
         <v>10</v>
       </c>
       <c r="C71" s="48" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D71" s="48" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E71" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F71" s="48" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="G71" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H71" s="48" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I71" s="48" t="s">
         <v>12</v>
@@ -5663,22 +5660,22 @@
         <v>10</v>
       </c>
       <c r="C72" s="48" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="D72" s="48" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="E72" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F72" s="48" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G72" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H72" s="48" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I72" s="48" t="s">
         <v>12</v>
@@ -5695,22 +5692,22 @@
         <v>10</v>
       </c>
       <c r="C73" s="48" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D73" s="48" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E73" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F73" s="48" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="G73" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H73" s="48" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I73" s="48" t="s">
         <v>12</v>
@@ -5721,7 +5718,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="95" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="B74" s="96"/>
       <c r="C74" s="96"/>
@@ -5741,22 +5738,22 @@
         <v>10</v>
       </c>
       <c r="C75" s="48" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D75" s="48" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="E75" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F75" s="48" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="G75" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H75" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I75" s="48" t="s">
         <v>12</v>
@@ -5773,22 +5770,22 @@
         <v>10</v>
       </c>
       <c r="C76" s="48" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D76" s="48" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="E76" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F76" s="48" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="G76" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H76" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I76" s="48" t="s">
         <v>12</v>
@@ -5805,22 +5802,22 @@
         <v>10</v>
       </c>
       <c r="C77" s="48" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="D77" s="48" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="E77" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F77" s="48" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="G77" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H77" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I77" s="48" t="s">
         <v>12</v>
@@ -5837,22 +5834,22 @@
         <v>10</v>
       </c>
       <c r="C78" s="48" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="D78" s="48" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="E78" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F78" s="48" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="G78" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H78" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I78" s="48" t="s">
         <v>12</v>
@@ -5869,22 +5866,22 @@
         <v>10</v>
       </c>
       <c r="C79" s="48" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="D79" s="48" t="s">
-        <v>292</v>
+        <v>636</v>
       </c>
       <c r="E79" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F79" s="48" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="G79" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H79" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I79" s="48" t="s">
         <v>12</v>
@@ -5901,22 +5898,22 @@
         <v>10</v>
       </c>
       <c r="C80" s="48" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D80" s="48" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="E80" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F80" s="48" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="G80" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H80" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I80" s="48" t="s">
         <v>12</v>
@@ -5933,22 +5930,22 @@
         <v>10</v>
       </c>
       <c r="C81" s="48" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D81" s="48" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E81" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F81" s="48" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="G81" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H81" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I81" s="48" t="s">
         <v>12</v>
@@ -5965,22 +5962,22 @@
         <v>10</v>
       </c>
       <c r="C82" s="48" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D82" s="48" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="E82" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F82" s="48" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="G82" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H82" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I82" s="48" t="s">
         <v>12</v>
@@ -5997,22 +5994,22 @@
         <v>10</v>
       </c>
       <c r="C83" s="48" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="D83" s="48" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="E83" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F83" s="48" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="G83" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H83" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I83" s="48" t="s">
         <v>12</v>
@@ -6029,22 +6026,22 @@
         <v>10</v>
       </c>
       <c r="C84" s="48" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="D84" s="48" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="E84" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F84" s="48" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="G84" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H84" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I84" s="48" t="s">
         <v>12</v>
@@ -6061,22 +6058,22 @@
         <v>10</v>
       </c>
       <c r="C85" s="48" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="D85" s="48" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="E85" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F85" s="48" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="G85" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H85" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I85" s="48" t="s">
         <v>12</v>
@@ -6093,22 +6090,22 @@
         <v>10</v>
       </c>
       <c r="C86" s="48" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="D86" s="48" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="E86" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F86" s="48" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="G86" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H86" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I86" s="48" t="s">
         <v>12</v>
@@ -6125,22 +6122,22 @@
         <v>10</v>
       </c>
       <c r="C87" s="48" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="D87" s="48" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="E87" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F87" s="48" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="G87" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H87" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I87" s="48" t="s">
         <v>12</v>
@@ -6157,22 +6154,22 @@
         <v>10</v>
       </c>
       <c r="C88" s="48" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="D88" s="48" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="E88" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F88" s="48" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="G88" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H88" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I88" s="48" t="s">
         <v>12</v>
@@ -6189,22 +6186,22 @@
         <v>10</v>
       </c>
       <c r="C89" s="48" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="D89" s="48" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="E89" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F89" s="48" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="G89" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H89" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I89" s="48" t="s">
         <v>12</v>
@@ -6221,22 +6218,22 @@
         <v>10</v>
       </c>
       <c r="C90" s="48" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D90" s="48" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="E90" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F90" s="48" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="G90" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H90" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I90" s="48" t="s">
         <v>12</v>
@@ -6253,22 +6250,22 @@
         <v>10</v>
       </c>
       <c r="C91" s="48" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="D91" s="48" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="E91" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F91" s="48" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="G91" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H91" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I91" s="48" t="s">
         <v>12</v>
@@ -6285,22 +6282,22 @@
         <v>10</v>
       </c>
       <c r="C92" s="48" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D92" s="48" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E92" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F92" s="48" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="G92" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H92" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I92" s="48" t="s">
         <v>12</v>
@@ -6317,22 +6314,22 @@
         <v>10</v>
       </c>
       <c r="C93" s="48" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D93" s="48" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="E93" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F93" s="48" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="G93" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H93" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I93" s="48" t="s">
         <v>12</v>
@@ -6349,22 +6346,22 @@
         <v>10</v>
       </c>
       <c r="C94" s="48" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D94" s="48" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="E94" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F94" s="48" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="G94" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H94" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I94" s="48" t="s">
         <v>12</v>
@@ -6381,22 +6378,22 @@
         <v>10</v>
       </c>
       <c r="C95" s="48" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="D95" s="48" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="E95" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F95" s="48" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="G95" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H95" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I95" s="48" t="s">
         <v>12</v>
@@ -6413,22 +6410,22 @@
         <v>10</v>
       </c>
       <c r="C96" s="48" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="D96" s="48" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="E96" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F96" s="48" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="G96" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H96" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I96" s="48" t="s">
         <v>12</v>
@@ -6445,22 +6442,22 @@
         <v>10</v>
       </c>
       <c r="C97" s="48" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="D97" s="48" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="E97" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F97" s="48" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="G97" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H97" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I97" s="48" t="s">
         <v>12</v>
@@ -6477,22 +6474,22 @@
         <v>10</v>
       </c>
       <c r="C98" s="48" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="D98" s="48" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="E98" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F98" s="48" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G98" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H98" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I98" s="48" t="s">
         <v>12</v>
@@ -6509,22 +6506,22 @@
         <v>10</v>
       </c>
       <c r="C99" s="48" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="D99" s="48" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="E99" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F99" s="48" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G99" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H99" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I99" s="48" t="s">
         <v>12</v>
@@ -6541,22 +6538,22 @@
         <v>10</v>
       </c>
       <c r="C100" s="48" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D100" s="48" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="E100" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F100" s="48" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="G100" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H100" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I100" s="48" t="s">
         <v>26</v>
@@ -6573,22 +6570,22 @@
         <v>10</v>
       </c>
       <c r="C101" s="48" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="D101" s="48" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="E101" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F101" s="48" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="G101" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H101" s="48" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I101" s="48" t="s">
         <v>26</v>
@@ -6599,7 +6596,7 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="91" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B102" s="91"/>
       <c r="C102" s="91"/>
@@ -6619,22 +6616,22 @@
         <v>10</v>
       </c>
       <c r="C103" s="48" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="D103" s="48" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="E103" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F103" s="48" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="G103" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H103" s="48" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="I103" s="48" t="s">
         <v>12</v>
@@ -6651,22 +6648,22 @@
         <v>10</v>
       </c>
       <c r="C104" s="48" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="D104" s="48" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="E104" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F104" s="48" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="G104" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H104" s="48" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="I104" s="48" t="s">
         <v>12</v>
@@ -6683,22 +6680,22 @@
         <v>10</v>
       </c>
       <c r="C105" s="48" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D105" s="48" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="E105" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F105" s="48" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="G105" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H105" s="48" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="I105" s="48" t="s">
         <v>12</v>
@@ -6715,22 +6712,22 @@
         <v>10</v>
       </c>
       <c r="C106" s="48" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D106" s="48" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="E106" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F106" s="48" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="G106" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H106" s="48" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="I106" s="48" t="s">
         <v>12</v>
@@ -6747,22 +6744,22 @@
         <v>10</v>
       </c>
       <c r="C107" s="48" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="D107" s="48" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="E107" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F107" s="48" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="G107" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H107" s="48" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="I107" s="48" t="s">
         <v>12</v>
@@ -6779,22 +6776,22 @@
         <v>10</v>
       </c>
       <c r="C108" s="48" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="D108" s="48" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="E108" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F108" s="48" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="G108" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H108" s="48" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="I108" s="48" t="s">
         <v>12</v>
@@ -6811,22 +6808,22 @@
         <v>10</v>
       </c>
       <c r="C109" s="48" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="D109" s="48" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="E109" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F109" s="48" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="G109" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H109" s="48" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="I109" s="48" t="s">
         <v>12</v>
@@ -6843,22 +6840,22 @@
         <v>10</v>
       </c>
       <c r="C110" s="48" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="D110" s="48" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="E110" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F110" s="48" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="G110" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H110" s="48" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="I110" s="48" t="s">
         <v>12</v>
@@ -6875,22 +6872,22 @@
         <v>10</v>
       </c>
       <c r="C111" s="48" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="D111" s="48" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="E111" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F111" s="48" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="G111" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H111" s="48" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="I111" s="48" t="s">
         <v>12</v>
@@ -6907,22 +6904,22 @@
         <v>10</v>
       </c>
       <c r="C112" s="48" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="D112" s="48" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="E112" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F112" s="48" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="G112" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H112" s="48" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="I112" s="48" t="s">
         <v>12</v>
@@ -6933,7 +6930,7 @@
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113" s="86" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B113" s="86"/>
       <c r="C113" s="86"/>
@@ -6953,22 +6950,22 @@
         <v>10</v>
       </c>
       <c r="C114" s="48" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="D114" s="24" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="E114" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F114" s="48" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="G114" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H114" s="48" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="I114" s="48" t="s">
         <v>12</v>
@@ -6979,7 +6976,7 @@
     </row>
     <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="86" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="B115" s="86"/>
       <c r="C115" s="86"/>
@@ -6999,22 +6996,22 @@
         <v>10</v>
       </c>
       <c r="C116" s="48" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="D116" s="24" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="E116" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F116" s="48" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="G116" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H116" s="48" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="I116" s="48" t="s">
         <v>12</v>
@@ -7025,7 +7022,7 @@
     </row>
     <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="86" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B117" s="86"/>
       <c r="C117" s="86"/>
@@ -7045,22 +7042,22 @@
         <v>10</v>
       </c>
       <c r="C118" s="48" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="D118" s="51" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="E118" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F118" s="51" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="G118" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H118" s="51" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="I118" s="51" t="s">
         <v>12</v>
@@ -7091,22 +7088,22 @@
         <v>10</v>
       </c>
       <c r="C119" s="48" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="D119" s="63" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="E119" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F119" s="48" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="G119" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H119" s="48" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="I119" s="48" t="s">
         <v>12</v>
@@ -7137,22 +7134,22 @@
         <v>10</v>
       </c>
       <c r="C120" s="48" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="D120" s="64" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="E120" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F120" s="48" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="G120" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H120" s="48" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="I120" s="48" t="s">
         <v>12</v>
@@ -7183,22 +7180,22 @@
         <v>10</v>
       </c>
       <c r="C121" s="48" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="D121" s="64" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="E121" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F121" s="48" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="G121" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H121" s="48" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="I121" s="48" t="s">
         <v>12</v>
@@ -7229,22 +7226,22 @@
         <v>10</v>
       </c>
       <c r="C122" s="48" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="D122" s="64" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="E122" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F122" s="48" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="G122" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H122" s="48" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="I122" s="48" t="s">
         <v>12</v>
@@ -7275,22 +7272,22 @@
         <v>10</v>
       </c>
       <c r="C123" s="48" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="D123" s="64" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="E123" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F123" s="48" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="G123" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H123" s="48" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="I123" s="48" t="s">
         <v>12</v>
@@ -7321,22 +7318,22 @@
         <v>10</v>
       </c>
       <c r="C124" s="48" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="D124" s="64" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="E124" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F124" s="48" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="G124" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H124" s="48" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="I124" s="48" t="s">
         <v>12</v>
@@ -7361,7 +7358,7 @@
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="86" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="B125" s="86"/>
       <c r="C125" s="86"/>
@@ -7381,22 +7378,22 @@
         <v>10</v>
       </c>
       <c r="C126" s="48" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="D126" s="60" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="E126" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F126" s="48" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="G126" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H126" s="27" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="I126" s="27" t="s">
         <v>12</v>
@@ -7427,22 +7424,22 @@
         <v>10</v>
       </c>
       <c r="C127" s="48" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="D127" s="27" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="E127" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F127" s="48" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="G127" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H127" s="27" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="I127" s="27" t="s">
         <v>26</v>
@@ -7473,22 +7470,22 @@
         <v>10</v>
       </c>
       <c r="C128" s="48" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D128" s="27" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="E128" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F128" s="48" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="G128" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H128" s="27" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="I128" s="27" t="s">
         <v>12</v>
@@ -7519,22 +7516,22 @@
         <v>10</v>
       </c>
       <c r="C129" s="48" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="D129" s="27" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="E129" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F129" s="48" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="G129" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H129" s="27" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="I129" s="27" t="s">
         <v>12</v>
@@ -7565,22 +7562,22 @@
         <v>10</v>
       </c>
       <c r="C130" s="48" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="D130" s="27" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="E130" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F130" s="48" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="G130" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H130" s="27" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="I130" s="27" t="s">
         <v>12</v>
@@ -7611,22 +7608,22 @@
         <v>10</v>
       </c>
       <c r="C131" s="48" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="D131" s="27" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="E131" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F131" s="48" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="G131" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H131" s="27" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="I131" s="27" t="s">
         <v>12</v>
@@ -7657,22 +7654,22 @@
         <v>10</v>
       </c>
       <c r="C132" s="48" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="D132" s="27" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="E132" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F132" s="48" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="G132" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H132" s="27" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="I132" s="27" t="s">
         <v>12</v>
@@ -7703,22 +7700,22 @@
         <v>10</v>
       </c>
       <c r="C133" s="48" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="D133" s="27" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="E133" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F133" s="48" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="G133" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H133" s="27" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="I133" s="27" t="s">
         <v>12</v>
@@ -7749,22 +7746,22 @@
         <v>10</v>
       </c>
       <c r="C134" s="48" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="D134" s="27" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="E134" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F134" s="48" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="G134" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H134" s="27" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="I134" s="27" t="s">
         <v>12</v>
@@ -7795,22 +7792,22 @@
         <v>10</v>
       </c>
       <c r="C135" s="48" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="D135" s="27" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="E135" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F135" s="48" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="G135" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H135" s="27" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="I135" s="27" t="s">
         <v>12</v>
@@ -7835,7 +7832,7 @@
     </row>
     <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="88" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="B136" s="89"/>
       <c r="C136" s="89"/>
@@ -7855,22 +7852,22 @@
         <v>10</v>
       </c>
       <c r="C137" s="48" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="D137" s="48" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="E137" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F137" s="48" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="G137" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H137" s="48" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="I137" s="48" t="s">
         <v>12</v>
@@ -7901,22 +7898,22 @@
         <v>10</v>
       </c>
       <c r="C138" s="48" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="D138" s="48" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="E138" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F138" s="48" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G138" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H138" s="48" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="I138" s="48" t="s">
         <v>12</v>
@@ -7947,22 +7944,22 @@
         <v>10</v>
       </c>
       <c r="C139" s="48" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D139" s="48" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="E139" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F139" s="48" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="G139" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H139" s="48" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="I139" s="48" t="s">
         <v>12</v>
@@ -7993,22 +7990,22 @@
         <v>10</v>
       </c>
       <c r="C140" s="48" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="D140" s="48" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="E140" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F140" s="48" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="G140" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H140" s="48" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="I140" s="48" t="s">
         <v>12</v>
@@ -8025,22 +8022,22 @@
         <v>10</v>
       </c>
       <c r="C141" s="48" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="D141" s="48" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="E141" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F141" s="48" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="G141" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H141" s="48" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="I141" s="48" t="s">
         <v>12</v>
@@ -8071,22 +8068,22 @@
         <v>10</v>
       </c>
       <c r="C142" s="48" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="D142" s="48" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="E142" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F142" s="48" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="G142" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H142" s="48" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="I142" s="48" t="s">
         <v>12</v>
@@ -8117,22 +8114,22 @@
         <v>10</v>
       </c>
       <c r="C143" s="48" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D143" s="48" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="E143" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F143" s="48" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="G143" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H143" s="48" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="I143" s="48" t="s">
         <v>12</v>
@@ -8163,22 +8160,22 @@
         <v>10</v>
       </c>
       <c r="C144" s="48" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="D144" s="48" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="E144" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F144" s="48" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="G144" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H144" s="48" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="I144" s="48" t="s">
         <v>12</v>
@@ -8209,22 +8206,22 @@
         <v>10</v>
       </c>
       <c r="C145" s="48" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="D145" s="48" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="E145" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F145" s="48" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="G145" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H145" s="48" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="I145" s="48" t="s">
         <v>12</v>
@@ -8255,22 +8252,22 @@
         <v>10</v>
       </c>
       <c r="C146" s="48" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D146" s="48" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="E146" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F146" s="48" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="G146" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H146" s="48" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="I146" s="48" t="s">
         <v>12</v>
@@ -8295,7 +8292,7 @@
     </row>
     <row r="147" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A147" s="86" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="B147" s="86"/>
       <c r="C147" s="86"/>
@@ -8315,22 +8312,22 @@
         <v>10</v>
       </c>
       <c r="C148" s="48" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="D148" s="24" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="E148" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F148" s="48" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="G148" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H148" s="48" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="I148" s="48" t="s">
         <v>12</v>
@@ -8341,7 +8338,7 @@
     </row>
     <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="86" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="B149" s="86"/>
       <c r="C149" s="86"/>
@@ -8361,22 +8358,22 @@
         <v>10</v>
       </c>
       <c r="C150" s="67" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="D150" s="66" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="E150" s="66" t="s">
         <v>14</v>
       </c>
       <c r="F150" s="67" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="G150" s="66" t="s">
         <v>11</v>
       </c>
       <c r="H150" s="66" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I150" s="66" t="s">
         <v>12</v>
@@ -8409,22 +8406,22 @@
         <v>10</v>
       </c>
       <c r="C151" s="70" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="D151" s="69" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="E151" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F151" s="70" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="G151" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H151" s="69" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I151" s="69" t="s">
         <v>12</v>
@@ -8457,22 +8454,22 @@
         <v>10</v>
       </c>
       <c r="C152" s="70" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="D152" s="71" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="E152" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F152" s="70" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="G152" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H152" s="69" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I152" s="69" t="s">
         <v>12</v>
@@ -8505,22 +8502,22 @@
         <v>10</v>
       </c>
       <c r="C153" s="70" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="D153" s="69" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="E153" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F153" s="70" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="G153" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H153" s="69" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I153" s="69" t="s">
         <v>12</v>
@@ -8553,22 +8550,22 @@
         <v>10</v>
       </c>
       <c r="C154" s="70" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="D154" s="69" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="E154" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F154" s="70" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="G154" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H154" s="69" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I154" s="69" t="s">
         <v>12</v>
@@ -8601,22 +8598,22 @@
         <v>10</v>
       </c>
       <c r="C155" s="70" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="D155" s="71" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="E155" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F155" s="70" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="G155" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H155" s="69" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I155" s="69" t="s">
         <v>12</v>
@@ -8649,22 +8646,22 @@
         <v>10</v>
       </c>
       <c r="C156" s="70" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="D156" s="69" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="E156" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F156" s="70" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="G156" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H156" s="69" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I156" s="69" t="s">
         <v>12</v>
@@ -8697,22 +8694,22 @@
         <v>10</v>
       </c>
       <c r="C157" s="70" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="D157" s="69" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="E157" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F157" s="70" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="G157" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H157" s="69" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I157" s="69" t="s">
         <v>12</v>
@@ -8745,22 +8742,22 @@
         <v>10</v>
       </c>
       <c r="C158" s="75" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="D158" s="74" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="E158" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F158" s="75" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="G158" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H158" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I158" s="74" t="s">
         <v>12</v>
@@ -8793,22 +8790,22 @@
         <v>10</v>
       </c>
       <c r="C159" s="75" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="D159" s="74" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="E159" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F159" s="75" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="G159" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H159" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I159" s="74" t="s">
         <v>12</v>
@@ -8841,22 +8838,22 @@
         <v>10</v>
       </c>
       <c r="C160" s="75" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="D160" s="74" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="E160" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F160" s="75" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="G160" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H160" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I160" s="74" t="s">
         <v>12</v>
@@ -8889,22 +8886,22 @@
         <v>10</v>
       </c>
       <c r="C161" s="75" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="D161" s="74" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="E161" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F161" s="75" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="G161" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H161" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I161" s="74" t="s">
         <v>12</v>
@@ -8937,22 +8934,22 @@
         <v>10</v>
       </c>
       <c r="C162" s="75" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="D162" s="74" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="E162" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F162" s="75" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="G162" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H162" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I162" s="74" t="s">
         <v>12</v>
@@ -8985,22 +8982,22 @@
         <v>10</v>
       </c>
       <c r="C163" s="75" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="D163" s="76" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="E163" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F163" s="75" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="G163" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H163" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I163" s="74" t="s">
         <v>12</v>
@@ -9033,22 +9030,22 @@
         <v>10</v>
       </c>
       <c r="C164" s="75" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="D164" s="76" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="E164" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F164" s="75" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="G164" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H164" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I164" s="74" t="s">
         <v>12</v>
@@ -9081,22 +9078,22 @@
         <v>10</v>
       </c>
       <c r="C165" s="75" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="D165" s="76" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E165" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F165" s="75" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="G165" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H165" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I165" s="74" t="s">
         <v>12</v>
@@ -9129,22 +9126,22 @@
         <v>10</v>
       </c>
       <c r="C166" s="75" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="D166" s="76" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="E166" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F166" s="75" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="G166" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H166" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I166" s="74" t="s">
         <v>12</v>
@@ -9177,22 +9174,22 @@
         <v>10</v>
       </c>
       <c r="C167" s="75" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="D167" s="77" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="E167" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F167" s="75" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="G167" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H167" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I167" s="74" t="s">
         <v>12</v>
@@ -9219,7 +9216,7 @@
     </row>
     <row r="168" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="86" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="B168" s="86"/>
       <c r="C168" s="86"/>
@@ -9239,22 +9236,22 @@
         <v>10</v>
       </c>
       <c r="C169" s="75" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="D169" s="77" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="E169" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F169" s="75" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="G169" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H169" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I169" s="74" t="s">
         <v>12</v>
@@ -9271,22 +9268,22 @@
         <v>10</v>
       </c>
       <c r="C170" s="75" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="D170" s="77" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="E170" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F170" s="75" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="G170" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H170" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I170" s="74" t="s">
         <v>12</v>
@@ -9303,22 +9300,22 @@
         <v>10</v>
       </c>
       <c r="C171" s="75" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="D171" s="81" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="E171" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F171" s="75" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="G171" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H171" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I171" s="74" t="s">
         <v>12</v>
@@ -9335,22 +9332,22 @@
         <v>10</v>
       </c>
       <c r="C172" s="79" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="D172" s="64" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E172" s="80" t="s">
         <v>14</v>
       </c>
       <c r="F172" s="75" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="G172" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H172" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I172" s="74" t="s">
         <v>12</v>
@@ -9367,22 +9364,22 @@
         <v>10</v>
       </c>
       <c r="C173" s="79" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="D173" s="83" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="E173" s="80" t="s">
         <v>14</v>
       </c>
       <c r="F173" s="75" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="G173" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H173" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I173" s="74" t="s">
         <v>12</v>
@@ -9399,22 +9396,22 @@
         <v>10</v>
       </c>
       <c r="C174" s="75" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="D174" s="77" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="E174" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F174" s="75" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="G174" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H174" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I174" s="74" t="s">
         <v>12</v>
@@ -9431,22 +9428,22 @@
         <v>10</v>
       </c>
       <c r="C175" s="75" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="D175" s="83" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="E175" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F175" s="75" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="G175" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H175" s="74" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="I175" s="74" t="s">
         <v>12</v>
@@ -9605,7 +9602,7 @@
         <v>19</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F1" s="31" t="s">
         <v>30</v>
@@ -9626,43 +9623,43 @@
         <v>35</v>
       </c>
       <c r="L1" s="30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M1" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="31" t="s">
+      <c r="O1" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="31" t="s">
+      <c r="P1" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="P1" s="31" t="s">
+      <c r="Q1" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="31" t="s">
-        <v>50</v>
-      </c>
       <c r="R1" s="31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S1" s="30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="T1" s="30" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="U1" s="31" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="V1" s="31" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="W1" s="31" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="X1" s="31" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -9700,7 +9697,7 @@
         <v>22</v>
       </c>
       <c r="L2" s="34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M2" s="34" t="s">
         <v>22</v>
@@ -9770,7 +9767,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M3" s="34" t="s">
         <v>22</v>
@@ -9810,10 +9807,10 @@
         <v>28</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D4" s="34" t="s">
         <v>22</v>
@@ -9840,7 +9837,7 @@
         <v>22</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M4" s="34" t="s">
         <v>22</v>
@@ -9877,10 +9874,10 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="34" t="s">
         <v>58</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>59</v>
       </c>
       <c r="C5" s="34" t="s">
         <v>21</v>
@@ -9910,25 +9907,25 @@
         <v>37</v>
       </c>
       <c r="L5" s="34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M5" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="N5" s="36" t="s">
+      <c r="O5" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="P5" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="O5" s="36" t="s">
+      <c r="Q5" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="P5" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q5" s="36" t="s">
-        <v>55</v>
-      </c>
       <c r="R5" s="37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S5" s="28"/>
       <c r="T5" s="28"/>
@@ -9947,13 +9944,13 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6" s="34" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D6" s="39" t="s">
         <v>22</v>
@@ -9986,7 +9983,7 @@
         <v>22</v>
       </c>
       <c r="N6" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O6" s="39" t="s">
         <v>22</v>
@@ -10017,16 +10014,16 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" s="39" t="s">
         <v>22</v>
@@ -10056,7 +10053,7 @@
         <v>22</v>
       </c>
       <c r="N7" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O7" s="39" t="s">
         <v>22</v>
@@ -10087,11 +10084,11 @@
     </row>
     <row r="8" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="40" t="s">
-        <v>78</v>
-      </c>
       <c r="C8" s="39" t="s">
         <v>22</v>
       </c>
@@ -10120,7 +10117,7 @@
         <v>22</v>
       </c>
       <c r="L8" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M8" s="39" t="s">
         <v>22</v>
@@ -10157,13 +10154,13 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B9" s="39" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D9" s="39" t="s">
         <v>22</v>
@@ -10190,7 +10187,7 @@
         <v>22</v>
       </c>
       <c r="L9" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M9" s="39" t="s">
         <v>22</v>
@@ -10227,7 +10224,7 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B10" s="39" t="s">
         <v>29</v>
@@ -10236,7 +10233,7 @@
         <v>21</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" s="39" t="s">
         <v>22</v>
@@ -10260,7 +10257,7 @@
         <v>22</v>
       </c>
       <c r="L10" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M10" s="39" t="s">
         <v>22</v>
@@ -10297,16 +10294,16 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="38" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" s="39" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" s="39" t="s">
         <v>22</v>
@@ -10330,7 +10327,7 @@
         <v>22</v>
       </c>
       <c r="L11" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M11" s="39" t="s">
         <v>22</v>
@@ -10367,13 +10364,13 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D12" s="39" t="s">
         <v>22</v>
@@ -10403,7 +10400,7 @@
         <v>22</v>
       </c>
       <c r="M12" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N12" s="39" t="s">
         <v>22</v>
@@ -10437,10 +10434,10 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="39" t="s">
         <v>22</v>
@@ -10470,7 +10467,7 @@
         <v>22</v>
       </c>
       <c r="L13" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M13" s="39" t="s">
         <v>22</v>
@@ -10507,13 +10504,13 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B14" s="39" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D14" s="39" t="s">
         <v>22</v>
@@ -10540,7 +10537,7 @@
         <v>22</v>
       </c>
       <c r="L14" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M14" s="39" t="s">
         <v>22</v>
@@ -10577,13 +10574,13 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" s="38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B15" s="39" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D15" s="39" t="s">
         <v>22</v>
@@ -10610,7 +10607,7 @@
         <v>22</v>
       </c>
       <c r="L15" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M15" s="39" t="s">
         <v>22</v>
@@ -10647,14 +10644,14 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="C16" s="36" t="s">
-        <v>132</v>
-      </c>
       <c r="D16" s="39" t="s">
         <v>22</v>
       </c>
@@ -10680,7 +10677,7 @@
         <v>22</v>
       </c>
       <c r="L16" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M16" s="39" t="s">
         <v>22</v>
@@ -10717,13 +10714,13 @@
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B17" s="39" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>22</v>
@@ -10750,7 +10747,7 @@
         <v>22</v>
       </c>
       <c r="L17" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M17" s="39" t="s">
         <v>22</v>
@@ -10787,16 +10784,16 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B18" s="39" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D18" s="41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E18" s="39" t="s">
         <v>22</v>
@@ -10820,7 +10817,7 @@
         <v>22</v>
       </c>
       <c r="L18" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M18" s="39" t="s">
         <v>22</v>
@@ -10857,16 +10854,16 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B19" s="39" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E19" s="39" t="s">
         <v>22</v>
@@ -10890,7 +10887,7 @@
         <v>22</v>
       </c>
       <c r="L19" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M19" s="39" t="s">
         <v>22</v>
@@ -10927,13 +10924,13 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="38" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D20" s="39" t="s">
         <v>22</v>
@@ -10957,7 +10954,7 @@
         <v>22</v>
       </c>
       <c r="K20" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L20" s="39" t="s">
         <v>22</v>
@@ -10978,7 +10975,7 @@
         <v>22</v>
       </c>
       <c r="R20" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S20" s="28"/>
       <c r="T20" s="28"/>
@@ -10997,16 +10994,16 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E21" s="39" t="s">
         <v>22</v>
@@ -11030,7 +11027,7 @@
         <v>22</v>
       </c>
       <c r="L21" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M21" s="39" t="s">
         <v>22</v>
@@ -11067,19 +11064,19 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B22" s="39" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F22" s="39" t="s">
         <v>22</v>
@@ -11100,7 +11097,7 @@
         <v>22</v>
       </c>
       <c r="L22" s="39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M22" s="39" t="s">
         <v>22</v>
@@ -11137,7 +11134,7 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B23" s="43" t="s">
         <v>20</v>
@@ -11146,10 +11143,10 @@
         <v>21</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E23" s="43" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F23" s="43" t="s">
         <v>22</v>
@@ -11170,7 +11167,7 @@
         <v>22</v>
       </c>
       <c r="L23" s="43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M23" s="43" t="s">
         <v>22</v>
@@ -11207,7 +11204,7 @@
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B24" s="47" t="s">
         <v>40</v>
@@ -11277,7 +11274,7 @@
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B25" s="47" t="s">
         <v>22</v>
@@ -11347,7 +11344,7 @@
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="46" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B26" s="47" t="s">
         <v>22</v>
@@ -11417,13 +11414,13 @@
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" s="46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B27" s="47" t="s">
         <v>22</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D27" s="47" t="s">
         <v>22</v>
@@ -11487,13 +11484,13 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" s="46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B28" s="47" t="s">
         <v>22</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D28" s="47" t="s">
         <v>22</v>
@@ -11557,13 +11554,13 @@
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="50" t="s">
         <v>148</v>
-      </c>
-      <c r="B29" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="50" t="s">
-        <v>149</v>
       </c>
       <c r="D29" s="47" t="s">
         <v>22</v>
@@ -11627,7 +11624,7 @@
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="46" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B30" s="47" t="s">
         <v>22</v>
@@ -11697,13 +11694,13 @@
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="46" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B31" s="47" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D31" s="47" t="s">
         <v>22</v>
@@ -11767,13 +11764,13 @@
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" s="46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B32" s="47" t="s">
         <v>22</v>
       </c>
       <c r="C32" s="49" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D32" s="47" t="s">
         <v>22</v>
@@ -11837,13 +11834,13 @@
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33" s="46" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B33" s="47" t="s">
         <v>22</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D33" s="47" t="s">
         <v>22</v>
@@ -11907,7 +11904,7 @@
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34" s="46" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B34" s="47" t="s">
         <v>22</v>
@@ -11977,7 +11974,7 @@
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" s="46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B35" s="47" t="s">
         <v>22</v>
@@ -12047,7 +12044,7 @@
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" s="33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B36" s="34" t="s">
         <v>20</v>
@@ -12080,25 +12077,25 @@
         <v>37</v>
       </c>
       <c r="L36" s="34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M36" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="N36" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="N36" s="36" t="s">
+      <c r="O36" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="P36" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="O36" s="36" t="s">
+      <c r="Q36" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="P36" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q36" s="36" t="s">
-        <v>55</v>
-      </c>
       <c r="R36" s="37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S36" s="28"/>
       <c r="T36" s="28"/>
@@ -12117,7 +12114,7 @@
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37" s="54" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B37" s="47" t="s">
         <v>22</v>
@@ -12189,7 +12186,7 @@
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38" s="47" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B38" s="48" t="s">
         <v>22</v>
@@ -12261,7 +12258,7 @@
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="47" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B39" s="48" t="s">
         <v>22</v>
@@ -12333,7 +12330,7 @@
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40" s="47" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B40" s="48" t="s">
         <v>22</v>
@@ -12405,7 +12402,7 @@
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41" s="47" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B41" s="48" t="s">
         <v>22</v>
@@ -12477,7 +12474,7 @@
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42" s="47" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B42" s="48" t="s">
         <v>22</v>
@@ -12549,7 +12546,7 @@
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43" s="47" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B43" s="48" t="s">
         <v>22</v>
@@ -12621,7 +12618,7 @@
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44" s="47" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B44" s="48" t="s">
         <v>22</v>
@@ -12693,7 +12690,7 @@
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45" s="47" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B45" s="48" t="s">
         <v>22</v>
@@ -12765,7 +12762,7 @@
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46" s="47" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B46" s="48" t="s">
         <v>22</v>
@@ -12837,7 +12834,7 @@
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47" s="47" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B47" s="48" t="s">
         <v>22</v>
@@ -12909,7 +12906,7 @@
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48" s="47" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B48" s="48" t="s">
         <v>22</v>
@@ -12981,7 +12978,7 @@
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49" s="47" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B49" s="48" t="s">
         <v>22</v>
@@ -13053,7 +13050,7 @@
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50" s="47" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B50" s="48" t="s">
         <v>22</v>
@@ -13125,7 +13122,7 @@
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51" s="47" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B51" s="48" t="s">
         <v>22</v>
@@ -13197,7 +13194,7 @@
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52" s="47" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B52" s="48" t="s">
         <v>22</v>
@@ -13269,7 +13266,7 @@
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53" s="55" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B53" s="48" t="s">
         <v>22</v>
@@ -13341,7 +13338,7 @@
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54" s="48" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B54" s="48" t="s">
         <v>22</v>
@@ -13413,7 +13410,7 @@
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55" s="48" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B55" s="48" t="s">
         <v>22</v>
@@ -13485,7 +13482,7 @@
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56" s="48" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B56" s="48" t="s">
         <v>22</v>
@@ -13557,7 +13554,7 @@
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57" s="48" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B57" s="48" t="s">
         <v>22</v>
@@ -13629,7 +13626,7 @@
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58" s="48" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B58" s="48" t="s">
         <v>22</v>
@@ -13701,7 +13698,7 @@
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59" s="48" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B59" s="48" t="s">
         <v>22</v>
@@ -13773,7 +13770,7 @@
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60" s="48" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B60" s="48" t="s">
         <v>22</v>
@@ -13845,7 +13842,7 @@
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61" s="48" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B61" s="48" t="s">
         <v>22</v>
@@ -13917,7 +13914,7 @@
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62" s="51" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B62" s="51" t="s">
         <v>22</v>
@@ -13989,7 +13986,7 @@
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63" s="56" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B63" s="48" t="s">
         <v>22</v>
@@ -14061,7 +14058,7 @@
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64" s="48" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B64" s="48" t="s">
         <v>22</v>
@@ -14133,7 +14130,7 @@
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A65" s="48" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B65" s="48" t="s">
         <v>22</v>
@@ -14205,7 +14202,7 @@
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A66" s="48" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B66" s="48" t="s">
         <v>22</v>
@@ -14277,7 +14274,7 @@
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A67" s="48" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B67" s="48" t="s">
         <v>22</v>
@@ -14349,7 +14346,7 @@
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A68" s="48" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B68" s="48" t="s">
         <v>22</v>
@@ -14421,7 +14418,7 @@
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A69" s="48" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B69" s="48" t="s">
         <v>22</v>
@@ -14493,13 +14490,13 @@
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A70" s="48" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B70" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C70" s="36" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="D70" s="48" t="s">
         <v>22</v>
@@ -14565,7 +14562,7 @@
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A71" s="48" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B71" s="48" t="s">
         <v>22</v>
@@ -14637,7 +14634,7 @@
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A72" s="48" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B72" s="48" t="s">
         <v>22</v>
@@ -14709,7 +14706,7 @@
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A73" s="51" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B73" s="51" t="s">
         <v>22</v>
@@ -14783,7 +14780,7 @@
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A74" s="62" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B74" s="48" t="s">
         <v>22</v>
@@ -14857,7 +14854,7 @@
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A75" s="48" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B75" s="48" t="s">
         <v>22</v>
@@ -14931,7 +14928,7 @@
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A76" s="48" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B76" s="48" t="s">
         <v>22</v>
@@ -15005,7 +15002,7 @@
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A77" s="48" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B77" s="48" t="s">
         <v>22</v>
@@ -15079,7 +15076,7 @@
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A78" s="48" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B78" s="48" t="s">
         <v>22</v>
@@ -15153,7 +15150,7 @@
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A79" s="48" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B79" s="48" t="s">
         <v>22</v>
@@ -15227,7 +15224,7 @@
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A80" s="48" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B80" s="48" t="s">
         <v>22</v>
@@ -15301,7 +15298,7 @@
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A81" s="48" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B81" s="48" t="s">
         <v>22</v>
@@ -15375,7 +15372,7 @@
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A82" s="48" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B82" s="48" t="s">
         <v>22</v>
@@ -15449,7 +15446,7 @@
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A83" s="48" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B83" s="48" t="s">
         <v>22</v>
@@ -15523,7 +15520,7 @@
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A84" s="48" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B84" s="48" t="s">
         <v>22</v>
@@ -15597,7 +15594,7 @@
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A85" s="48" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B85" s="48" t="s">
         <v>22</v>
@@ -15671,7 +15668,7 @@
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A86" s="48" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B86" s="48" t="s">
         <v>22</v>
@@ -15745,7 +15742,7 @@
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A87" s="48" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B87" s="48" t="s">
         <v>22</v>
@@ -15819,7 +15816,7 @@
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A88" s="48" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="B88" s="48" t="s">
         <v>22</v>
@@ -15893,7 +15890,7 @@
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A89" s="48" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="B89" s="48" t="s">
         <v>22</v>
@@ -15967,7 +15964,7 @@
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A90" s="48" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B90" s="48" t="s">
         <v>22</v>
@@ -16041,7 +16038,7 @@
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A91" s="48" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B91" s="48" t="s">
         <v>22</v>
@@ -16115,7 +16112,7 @@
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A92" s="48" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="B92" s="48" t="s">
         <v>22</v>
@@ -16189,7 +16186,7 @@
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A93" s="48" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="B93" s="48" t="s">
         <v>22</v>
@@ -16263,7 +16260,7 @@
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A94" s="48" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="B94" s="48" t="s">
         <v>22</v>
@@ -16337,7 +16334,7 @@
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A95" s="48" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B95" s="48" t="s">
         <v>22</v>
@@ -16411,7 +16408,7 @@
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A96" s="48" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B96" s="48" t="s">
         <v>22</v>
@@ -16485,7 +16482,7 @@
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A97" s="48" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B97" s="48" t="s">
         <v>22</v>
@@ -16559,7 +16556,7 @@
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A98" s="48" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="B98" s="48" t="s">
         <v>22</v>
@@ -16633,7 +16630,7 @@
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A99" s="48" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B99" s="51" t="s">
         <v>22</v>
@@ -16707,7 +16704,7 @@
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A100" s="48" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="B100" s="51" t="s">
         <v>22</v>
@@ -16781,7 +16778,7 @@
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A101" s="48" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B101" s="48" t="s">
         <v>22</v>
@@ -16855,7 +16852,7 @@
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A102" s="48" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B102" s="48" t="s">
         <v>22</v>
@@ -16929,7 +16926,7 @@
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103" s="48" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B103" s="48" t="s">
         <v>22</v>
@@ -17003,7 +17000,7 @@
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A104" s="48" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B104" s="48" t="s">
         <v>22</v>
@@ -17077,7 +17074,7 @@
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A105" s="48" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="B105" s="48" t="s">
         <v>22</v>
@@ -17151,7 +17148,7 @@
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106" s="48" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B106" s="48" t="s">
         <v>22</v>
@@ -17225,7 +17222,7 @@
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A107" s="48" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B107" s="48" t="s">
         <v>22</v>
@@ -17299,7 +17296,7 @@
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A108" s="48" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B108" s="48" t="s">
         <v>22</v>
@@ -17373,7 +17370,7 @@
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A109" s="48" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B109" s="48" t="s">
         <v>22</v>
@@ -17447,7 +17444,7 @@
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A110" s="48" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="B110" s="48" t="s">
         <v>22</v>
@@ -17521,7 +17518,7 @@
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111" s="48" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B111" s="48" t="s">
         <v>22</v>
@@ -17595,7 +17592,7 @@
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A112" s="48" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="B112" s="48" t="s">
         <v>22</v>
@@ -17669,7 +17666,7 @@
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113" s="48" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B113" s="48" t="s">
         <v>22</v>
@@ -17743,7 +17740,7 @@
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="48" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B114" s="48" t="s">
         <v>22</v>
@@ -17817,7 +17814,7 @@
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A115" s="48" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="B115" s="48" t="s">
         <v>22</v>
@@ -17891,7 +17888,7 @@
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" s="48" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B116" s="48" t="s">
         <v>22</v>
@@ -17965,7 +17962,7 @@
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A117" s="48" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B117" s="48" t="s">
         <v>22</v>
@@ -18039,7 +18036,7 @@
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118" s="48" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="B118" s="48" t="s">
         <v>22</v>
@@ -18113,7 +18110,7 @@
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A119" s="48" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="B119" s="48" t="s">
         <v>22</v>
@@ -18187,7 +18184,7 @@
     </row>
     <row r="120" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A120" s="48" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="B120" s="48" t="s">
         <v>22</v>
@@ -18261,13 +18258,13 @@
     </row>
     <row r="121" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A121" s="62" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B121" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C121" s="36" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="D121" s="48" t="s">
         <v>22</v>
@@ -18276,22 +18273,22 @@
         <v>22</v>
       </c>
       <c r="F121" s="48" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="G121" s="49" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="H121" s="48" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="I121" s="48" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="J121" s="36" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="K121" s="48" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="L121" s="48" t="s">
         <v>22</v>
@@ -18335,7 +18332,7 @@
     </row>
     <row r="122" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A122" s="48" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B122" s="48" t="s">
         <v>22</v>
@@ -18409,13 +18406,13 @@
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A123" s="48" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="B123" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C123" s="36" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="D123" s="48" t="s">
         <v>22</v>
@@ -18424,22 +18421,22 @@
         <v>22</v>
       </c>
       <c r="F123" s="48" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="G123" s="49" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="H123" s="48" t="s">
         <v>37</v>
       </c>
       <c r="I123" s="48" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="J123" s="36" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="K123" s="48" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="L123" s="48" t="s">
         <v>22</v>
@@ -18483,13 +18480,13 @@
     </row>
     <row r="124" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A124" s="48" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="B124" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C124" s="36" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="D124" s="48" t="s">
         <v>22</v>
@@ -18498,22 +18495,22 @@
         <v>22</v>
       </c>
       <c r="F124" s="48" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="G124" s="49" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="H124" s="48" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="I124" s="48" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="J124" s="36" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="K124" s="48" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="L124" s="48" t="s">
         <v>22</v>
@@ -18557,13 +18554,13 @@
     </row>
     <row r="125" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A125" s="48" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="B125" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C125" s="36" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="D125" s="48" t="s">
         <v>22</v>
@@ -18575,19 +18572,19 @@
         <v>29</v>
       </c>
       <c r="G125" s="49" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="H125" s="48" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="I125" s="48" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="J125" s="36" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="K125" s="48" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="L125" s="48" t="s">
         <v>22</v>
@@ -18631,13 +18628,13 @@
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A126" s="48" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="B126" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C126" s="36" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="D126" s="48" t="s">
         <v>22</v>
@@ -18646,22 +18643,22 @@
         <v>22</v>
       </c>
       <c r="F126" s="48" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="G126" s="49" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="H126" s="48" t="s">
         <v>38</v>
       </c>
       <c r="I126" s="48" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="J126" s="36" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K126" s="48" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="L126" s="48" t="s">
         <v>22</v>
@@ -18705,7 +18702,7 @@
     </row>
     <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A127" s="48" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="B127" s="48" t="s">
         <v>22</v>
@@ -18779,7 +18776,7 @@
     </row>
     <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A128" s="48" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="B128" s="48" t="s">
         <v>22</v>
@@ -18853,13 +18850,13 @@
     </row>
     <row r="129" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A129" s="48" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B129" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C129" s="36" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="D129" s="48" t="s">
         <v>22</v>
@@ -18871,19 +18868,19 @@
         <v>29</v>
       </c>
       <c r="G129" s="49" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="H129" s="48" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="I129" s="48" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="J129" s="36" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="K129" s="48" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="L129" s="48" t="s">
         <v>22</v>
@@ -18927,7 +18924,7 @@
     </row>
     <row r="130" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A130" s="48" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="B130" s="48" t="s">
         <v>22</v>
@@ -19001,7 +18998,7 @@
     </row>
     <row r="131" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A131" s="48" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B131" s="48" t="s">
         <v>22</v>
@@ -19075,7 +19072,7 @@
     </row>
     <row r="132" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A132" s="48" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B132" s="48" t="s">
         <v>22</v>
@@ -19149,7 +19146,7 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A133" s="48" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="B133" s="48" t="s">
         <v>22</v>
@@ -19209,13 +19206,13 @@
         <v>22</v>
       </c>
       <c r="U133" s="48" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="V133" s="48" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="W133" s="48" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="X133" s="48" t="s">
         <v>22</v>
@@ -19223,7 +19220,7 @@
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A134" s="48" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B134" s="48" t="s">
         <v>22</v>
@@ -19283,13 +19280,13 @@
         <v>22</v>
       </c>
       <c r="U134" s="48" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="V134" s="48" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="W134" s="48" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="X134" s="48" t="s">
         <v>22</v>
@@ -19297,7 +19294,7 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A135" s="48" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B135" s="48" t="s">
         <v>22</v>
@@ -19357,13 +19354,13 @@
         <v>22</v>
       </c>
       <c r="U135" s="48" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="V135" s="48" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="W135" s="48" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="X135" s="48" t="s">
         <v>22</v>
@@ -19371,7 +19368,7 @@
     </row>
     <row r="136" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A136" s="48" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="B136" s="48" t="s">
         <v>22</v>
@@ -19380,7 +19377,7 @@
         <v>22</v>
       </c>
       <c r="D136" s="49" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E136" s="48" t="s">
         <v>22</v>
@@ -19431,13 +19428,13 @@
         <v>22</v>
       </c>
       <c r="U136" s="48" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="V136" s="48" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="W136" s="48" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="X136" s="48" t="s">
         <v>22</v>
@@ -19445,7 +19442,7 @@
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A137" s="48" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="B137" s="48" t="s">
         <v>22</v>
@@ -19505,13 +19502,13 @@
         <v>22</v>
       </c>
       <c r="U137" s="48" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="V137" s="48" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="W137" s="48" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="X137" s="48" t="s">
         <v>22</v>
@@ -19519,7 +19516,7 @@
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A138" s="48" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="B138" s="48" t="s">
         <v>22</v>
@@ -19593,7 +19590,7 @@
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A139" s="48" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="B139" s="48" t="s">
         <v>22</v>
@@ -19667,7 +19664,7 @@
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A140" s="48" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="B140" s="48" t="s">
         <v>22</v>
@@ -19741,7 +19738,7 @@
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A141" s="48" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="B141" s="48" t="s">
         <v>22</v>
@@ -19801,13 +19798,13 @@
         <v>22</v>
       </c>
       <c r="U141" s="48" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="V141" s="48" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="W141" s="48" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="X141" s="48" t="s">
         <v>22</v>
@@ -19815,7 +19812,7 @@
     </row>
     <row r="142" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A142" s="48" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="B142" s="48" t="s">
         <v>22</v>
@@ -19875,13 +19872,13 @@
         <v>22</v>
       </c>
       <c r="U142" s="48" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="V142" s="48" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="W142" s="48" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="X142" s="48" t="s">
         <v>22</v>
@@ -19889,7 +19886,7 @@
     </row>
     <row r="143" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A143" s="48" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="B143" s="48" t="s">
         <v>22</v>
@@ -19949,13 +19946,13 @@
         <v>22</v>
       </c>
       <c r="U143" s="48" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="V143" s="48" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="W143" s="48" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="X143" s="48" t="s">
         <v>22</v>
@@ -19963,7 +19960,7 @@
     </row>
     <row r="144" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A144" s="48" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B144" s="48" t="s">
         <v>22</v>
@@ -20023,13 +20020,13 @@
         <v>22</v>
       </c>
       <c r="U144" s="48" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="V144" s="48" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="W144" s="48" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="X144" s="48" t="s">
         <v>22</v>
@@ -20037,7 +20034,7 @@
     </row>
     <row r="145" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A145" s="48" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="B145" s="48" t="s">
         <v>22</v>
@@ -20097,13 +20094,13 @@
         <v>22</v>
       </c>
       <c r="U145" s="48" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="V145" s="48" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="W145" s="48" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="X145" s="48" t="s">
         <v>22</v>
@@ -20111,7 +20108,7 @@
     </row>
     <row r="146" spans="1:24" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A146" s="48" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="B146" s="48" t="s">
         <v>22</v>
@@ -20171,13 +20168,13 @@
         <v>22</v>
       </c>
       <c r="U146" s="48" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="V146" s="48" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="W146" s="48" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="X146" s="48" t="s">
         <v>22</v>
@@ -20185,7 +20182,7 @@
     </row>
     <row r="147" spans="1:24" ht="53.4" x14ac:dyDescent="0.3">
       <c r="A147" s="48" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="B147" s="48" t="s">
         <v>22</v>
@@ -20245,13 +20242,13 @@
         <v>22</v>
       </c>
       <c r="U147" s="48" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="V147" s="48" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="W147" s="48" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="X147" s="48" t="s">
         <v>22</v>
@@ -20259,7 +20256,7 @@
     </row>
     <row r="148" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="48" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="B148" s="48" t="s">
         <v>22</v>
@@ -20333,7 +20330,7 @@
     </row>
     <row r="149" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="67" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="B149" s="48" t="s">
         <v>22</v>
@@ -20407,7 +20404,7 @@
     </row>
     <row r="150" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="70" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="B150" s="48" t="s">
         <v>22</v>
@@ -20481,7 +20478,7 @@
     </row>
     <row r="151" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="67" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="B151" s="48" t="s">
         <v>22</v>
@@ -20555,7 +20552,7 @@
     </row>
     <row r="152" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="70" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="B152" s="48" t="s">
         <v>22</v>
@@ -20629,7 +20626,7 @@
     </row>
     <row r="153" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="67" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="B153" s="48" t="s">
         <v>22</v>
@@ -20703,7 +20700,7 @@
     </row>
     <row r="154" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="70" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="B154" s="48" t="s">
         <v>22</v>
@@ -20777,7 +20774,7 @@
     </row>
     <row r="155" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="67" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="B155" s="48" t="s">
         <v>22</v>
@@ -20851,7 +20848,7 @@
     </row>
     <row r="156" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="70" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="B156" s="48" t="s">
         <v>22</v>
@@ -20925,7 +20922,7 @@
     </row>
     <row r="157" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="67" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="B157" s="48" t="s">
         <v>22</v>
@@ -20999,7 +20996,7 @@
     </row>
     <row r="158" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="70" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="B158" s="48" t="s">
         <v>22</v>
@@ -21073,7 +21070,7 @@
     </row>
     <row r="159" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="67" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="B159" s="48" t="s">
         <v>22</v>
@@ -21147,7 +21144,7 @@
     </row>
     <row r="160" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="70" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="B160" s="48" t="s">
         <v>22</v>
@@ -21221,7 +21218,7 @@
     </row>
     <row r="161" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="67" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="B161" s="48" t="s">
         <v>22</v>
@@ -21295,7 +21292,7 @@
     </row>
     <row r="162" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="70" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="B162" s="48" t="s">
         <v>22</v>
@@ -21369,7 +21366,7 @@
     </row>
     <row r="163" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="67" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B163" s="48" t="s">
         <v>22</v>
@@ -21443,7 +21440,7 @@
     </row>
     <row r="164" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="67" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B164" s="48" t="s">
         <v>22</v>
@@ -21517,7 +21514,7 @@
     </row>
     <row r="165" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="67" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="B165" s="48" t="s">
         <v>22</v>
@@ -21591,13 +21588,13 @@
     </row>
     <row r="166" spans="1:24" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="67" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="B166" s="48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C166" s="36" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="D166" s="48" t="s">
         <v>22</v>
@@ -21606,22 +21603,22 @@
         <v>22</v>
       </c>
       <c r="F166" s="48" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="G166" s="49" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="H166" s="48" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="I166" s="48" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="J166" s="36" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="K166" s="48" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="L166" s="48" t="s">
         <v>22</v>
@@ -21691,7 +21688,7 @@
     </row>
     <row r="168" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="75" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="B168" s="48" t="s">
         <v>22</v>
@@ -21745,7 +21742,7 @@
         <v>22</v>
       </c>
       <c r="S168" s="49" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="T168" s="48" t="s">
         <v>22</v>
@@ -21754,10 +21751,10 @@
         <v>22</v>
       </c>
       <c r="V168" s="48" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="W168" s="36" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="X168" s="48" t="s">
         <v>22</v>
@@ -21765,7 +21762,7 @@
     </row>
     <row r="169" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="75" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B169" s="48" t="s">
         <v>22</v>
@@ -21819,7 +21816,7 @@
         <v>22</v>
       </c>
       <c r="S169" s="49" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="T169" s="48" t="s">
         <v>22</v>
@@ -21834,12 +21831,12 @@
         <v>22</v>
       </c>
       <c r="X169" s="78" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
     </row>
     <row r="170" spans="1:24" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="75" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="B170" s="48" t="s">
         <v>22</v>
@@ -21893,7 +21890,7 @@
         <v>22</v>
       </c>
       <c r="S170" s="49" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="T170" s="48" t="s">
         <v>22</v>
@@ -21908,12 +21905,12 @@
         <v>22</v>
       </c>
       <c r="X170" s="84" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
     </row>
     <row r="171" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="75" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="B171" s="48" t="s">
         <v>22</v>
@@ -21967,7 +21964,7 @@
         <v>22</v>
       </c>
       <c r="S171" s="49" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="T171" s="48" t="s">
         <v>22</v>
@@ -21976,7 +21973,7 @@
         <v>22</v>
       </c>
       <c r="V171" s="48" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="W171" s="36" t="s">
         <v>22</v>
@@ -21987,7 +21984,7 @@
     </row>
     <row r="172" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="75" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="B172" s="48" t="s">
         <v>22</v>
@@ -22041,7 +22038,7 @@
         <v>22</v>
       </c>
       <c r="S172" s="49" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="T172" s="48" t="s">
         <v>22</v>
@@ -22061,7 +22058,7 @@
     </row>
     <row r="173" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="75" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="B173" s="48" t="s">
         <v>22</v>
@@ -22115,7 +22112,7 @@
         <v>22</v>
       </c>
       <c r="S173" s="49" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="T173" s="48" t="s">
         <v>22</v>
@@ -22130,12 +22127,12 @@
         <v>22</v>
       </c>
       <c r="X173" s="85" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
     </row>
     <row r="174" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="75" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="B174" s="48" t="s">
         <v>22</v>
@@ -22189,7 +22186,7 @@
         <v>22</v>
       </c>
       <c r="S174" s="49" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="T174" s="48" t="s">
         <v>22</v>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlataaProduction\ZlaataProduction\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D01CEEE-6A89-415C-B453-5BB9012117FD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954C3298-C4D9-483E-9E0B-B3302E4F7F26}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -2603,18 +2603,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2635,6 +2623,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4189,18 +4189,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="92" t="s">
+      <c r="A24" s="88" t="s">
         <v>155</v>
       </c>
-      <c r="B24" s="93"/>
-      <c r="C24" s="93"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="93"/>
-      <c r="G24" s="93"/>
-      <c r="H24" s="93"/>
-      <c r="I24" s="93"/>
-      <c r="J24" s="94"/>
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="90"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
@@ -4587,18 +4587,18 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="95" t="s">
+      <c r="A37" s="91" t="s">
         <v>170</v>
       </c>
-      <c r="B37" s="96"/>
-      <c r="C37" s="96"/>
-      <c r="D37" s="96"/>
-      <c r="E37" s="96"/>
-      <c r="F37" s="96"/>
-      <c r="G37" s="96"/>
-      <c r="H37" s="96"/>
-      <c r="I37" s="96"/>
-      <c r="J37" s="97"/>
+      <c r="B37" s="92"/>
+      <c r="C37" s="92"/>
+      <c r="D37" s="92"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="92"/>
+      <c r="H37" s="92"/>
+      <c r="I37" s="92"/>
+      <c r="J37" s="93"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
@@ -5017,18 +5017,18 @@
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="95" t="s">
+      <c r="A51" s="91" t="s">
         <v>237</v>
       </c>
-      <c r="B51" s="96"/>
-      <c r="C51" s="96"/>
-      <c r="D51" s="96"/>
-      <c r="E51" s="96"/>
-      <c r="F51" s="96"/>
-      <c r="G51" s="96"/>
-      <c r="H51" s="96"/>
-      <c r="I51" s="96"/>
-      <c r="J51" s="97"/>
+      <c r="B51" s="92"/>
+      <c r="C51" s="92"/>
+      <c r="D51" s="92"/>
+      <c r="E51" s="92"/>
+      <c r="F51" s="92"/>
+      <c r="G51" s="92"/>
+      <c r="H51" s="92"/>
+      <c r="I51" s="92"/>
+      <c r="J51" s="93"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="25">
@@ -5351,18 +5351,18 @@
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="95" t="s">
+      <c r="A62" s="91" t="s">
         <v>239</v>
       </c>
-      <c r="B62" s="96"/>
-      <c r="C62" s="96"/>
-      <c r="D62" s="96"/>
-      <c r="E62" s="96"/>
-      <c r="F62" s="96"/>
-      <c r="G62" s="96"/>
-      <c r="H62" s="96"/>
-      <c r="I62" s="96"/>
-      <c r="J62" s="97"/>
+      <c r="B62" s="92"/>
+      <c r="C62" s="92"/>
+      <c r="D62" s="92"/>
+      <c r="E62" s="92"/>
+      <c r="F62" s="92"/>
+      <c r="G62" s="92"/>
+      <c r="H62" s="92"/>
+      <c r="I62" s="92"/>
+      <c r="J62" s="93"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="25">
@@ -5717,18 +5717,18 @@
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="95" t="s">
+      <c r="A74" s="91" t="s">
         <v>337</v>
       </c>
-      <c r="B74" s="96"/>
-      <c r="C74" s="96"/>
-      <c r="D74" s="96"/>
-      <c r="E74" s="96"/>
-      <c r="F74" s="96"/>
-      <c r="G74" s="96"/>
-      <c r="H74" s="96"/>
-      <c r="I74" s="96"/>
-      <c r="J74" s="97"/>
+      <c r="B74" s="92"/>
+      <c r="C74" s="92"/>
+      <c r="D74" s="92"/>
+      <c r="E74" s="92"/>
+      <c r="F74" s="92"/>
+      <c r="G74" s="92"/>
+      <c r="H74" s="92"/>
+      <c r="I74" s="92"/>
+      <c r="J74" s="93"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="25">
@@ -6595,18 +6595,18 @@
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A102" s="91" t="s">
+      <c r="A102" s="87" t="s">
         <v>367</v>
       </c>
-      <c r="B102" s="91"/>
-      <c r="C102" s="91"/>
-      <c r="D102" s="91"/>
-      <c r="E102" s="91"/>
-      <c r="F102" s="91"/>
-      <c r="G102" s="91"/>
-      <c r="H102" s="91"/>
-      <c r="I102" s="91"/>
-      <c r="J102" s="91"/>
+      <c r="B102" s="87"/>
+      <c r="C102" s="87"/>
+      <c r="D102" s="87"/>
+      <c r="E102" s="87"/>
+      <c r="F102" s="87"/>
+      <c r="G102" s="87"/>
+      <c r="H102" s="87"/>
+      <c r="I102" s="87"/>
+      <c r="J102" s="87"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="25">
@@ -7362,13 +7362,13 @@
       </c>
       <c r="B125" s="86"/>
       <c r="C125" s="86"/>
-      <c r="D125" s="87"/>
-      <c r="E125" s="87"/>
-      <c r="F125" s="87"/>
-      <c r="G125" s="87"/>
-      <c r="H125" s="87"/>
-      <c r="I125" s="87"/>
-      <c r="J125" s="87"/>
+      <c r="D125" s="94"/>
+      <c r="E125" s="94"/>
+      <c r="F125" s="94"/>
+      <c r="G125" s="94"/>
+      <c r="H125" s="94"/>
+      <c r="I125" s="94"/>
+      <c r="J125" s="94"/>
     </row>
     <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="59">
@@ -7831,18 +7831,18 @@
       <c r="X135" s="58"/>
     </row>
     <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="88" t="s">
+      <c r="A136" s="95" t="s">
         <v>433</v>
       </c>
-      <c r="B136" s="89"/>
-      <c r="C136" s="89"/>
-      <c r="D136" s="89"/>
-      <c r="E136" s="89"/>
-      <c r="F136" s="89"/>
-      <c r="G136" s="89"/>
-      <c r="H136" s="89"/>
-      <c r="I136" s="89"/>
-      <c r="J136" s="90"/>
+      <c r="B136" s="96"/>
+      <c r="C136" s="96"/>
+      <c r="D136" s="96"/>
+      <c r="E136" s="96"/>
+      <c r="F136" s="96"/>
+      <c r="G136" s="96"/>
+      <c r="H136" s="96"/>
+      <c r="I136" s="96"/>
+      <c r="J136" s="97"/>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="25">
@@ -9454,6 +9454,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A168:J168"/>
+    <mergeCell ref="A149:J149"/>
+    <mergeCell ref="A147:J147"/>
+    <mergeCell ref="A125:J125"/>
+    <mergeCell ref="A136:J136"/>
     <mergeCell ref="A117:J117"/>
     <mergeCell ref="A115:J115"/>
     <mergeCell ref="A113:J113"/>
@@ -9463,11 +9468,6 @@
     <mergeCell ref="A51:J51"/>
     <mergeCell ref="A62:J62"/>
     <mergeCell ref="A74:J74"/>
-    <mergeCell ref="A168:J168"/>
-    <mergeCell ref="A149:J149"/>
-    <mergeCell ref="A147:J147"/>
-    <mergeCell ref="A125:J125"/>
-    <mergeCell ref="A136:J136"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlataaProduction\ZlaataProduction\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954C3298-C4D9-483E-9E0B-B3302E4F7F26}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49427BA3-C5E2-4047-B033-04C16049078E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5510" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5543" uniqueCount="640">
   <si>
     <t>S.No</t>
   </si>
@@ -706,9 +706,6 @@
     <t>TC_UI_Zlaata_Menus_05</t>
   </si>
   <si>
-    <t>Verify that the user is able to click the "Boss Lady" hover image.</t>
-  </si>
-  <si>
     <t>TC_UI_Zlaata_Menus_06</t>
   </si>
   <si>
@@ -1937,6 +1934,18 @@
   </si>
   <si>
     <t>Verify Color item Selection Functionality</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Orders_02</t>
+  </si>
+  <si>
+    <t>Verify user Cancelling order and all labels.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Orders_02</t>
+  </si>
+  <si>
+    <t>Verify that the user is able to Mouse hover any all category in the "Shop" dropdown.</t>
   </si>
 </sst>
 </file>
@@ -3438,7 +3447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z175"/>
+  <dimension ref="A1:Z176"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -3495,7 +3504,7 @@
         <v>15</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>14</v>
@@ -4213,7 +4222,7 @@
         <v>61</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E25" s="22" t="s">
         <v>14</v>
@@ -4245,7 +4254,7 @@
         <v>156</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>14</v>
@@ -4277,7 +4286,7 @@
         <v>157</v>
       </c>
       <c r="D27" s="47" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>14</v>
@@ -4309,7 +4318,7 @@
         <v>158</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>14</v>
@@ -4341,7 +4350,7 @@
         <v>159</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>14</v>
@@ -4373,7 +4382,7 @@
         <v>160</v>
       </c>
       <c r="D30" s="47" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>14</v>
@@ -4405,7 +4414,7 @@
         <v>161</v>
       </c>
       <c r="D31" s="47" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E31" s="13" t="s">
         <v>14</v>
@@ -4437,7 +4446,7 @@
         <v>162</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>14</v>
@@ -4469,7 +4478,7 @@
         <v>163</v>
       </c>
       <c r="D33" s="47" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>14</v>
@@ -4501,7 +4510,7 @@
         <v>164</v>
       </c>
       <c r="D34" s="47" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E34" s="13" t="s">
         <v>14</v>
@@ -4611,7 +4620,7 @@
         <v>171</v>
       </c>
       <c r="D38" s="48" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E38" s="47" t="s">
         <v>14</v>
@@ -4675,7 +4684,7 @@
         <v>177</v>
       </c>
       <c r="D40" s="48" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E40" s="47" t="s">
         <v>14</v>
@@ -4771,7 +4780,7 @@
         <v>185</v>
       </c>
       <c r="D43" s="48" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E43" s="47" t="s">
         <v>14</v>
@@ -4899,7 +4908,7 @@
         <v>196</v>
       </c>
       <c r="D47" s="48" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E47" s="47" t="s">
         <v>14</v>
@@ -5018,7 +5027,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="91" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B51" s="92"/>
       <c r="C51" s="92"/>
@@ -5041,7 +5050,7 @@
         <v>220</v>
       </c>
       <c r="D52" s="48" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E52" s="48" t="s">
         <v>14</v>
@@ -5073,7 +5082,7 @@
         <v>222</v>
       </c>
       <c r="D53" s="48" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E53" s="48" t="s">
         <v>14</v>
@@ -5105,7 +5114,7 @@
         <v>223</v>
       </c>
       <c r="D54" s="48" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E54" s="48" t="s">
         <v>14</v>
@@ -5137,7 +5146,7 @@
         <v>224</v>
       </c>
       <c r="D55" s="48" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E55" s="48" t="s">
         <v>14</v>
@@ -5169,7 +5178,7 @@
         <v>225</v>
       </c>
       <c r="D56" s="48" t="s">
-        <v>226</v>
+        <v>639</v>
       </c>
       <c r="E56" s="48" t="s">
         <v>14</v>
@@ -5198,10 +5207,10 @@
         <v>10</v>
       </c>
       <c r="C57" s="48" t="s">
+        <v>226</v>
+      </c>
+      <c r="D57" s="48" t="s">
         <v>227</v>
-      </c>
-      <c r="D57" s="48" t="s">
-        <v>228</v>
       </c>
       <c r="E57" s="48" t="s">
         <v>14</v>
@@ -5230,10 +5239,10 @@
         <v>10</v>
       </c>
       <c r="C58" s="48" t="s">
+        <v>228</v>
+      </c>
+      <c r="D58" s="48" t="s">
         <v>229</v>
-      </c>
-      <c r="D58" s="48" t="s">
-        <v>230</v>
       </c>
       <c r="E58" s="48" t="s">
         <v>14</v>
@@ -5262,10 +5271,10 @@
         <v>10</v>
       </c>
       <c r="C59" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="D59" s="48" t="s">
         <v>231</v>
-      </c>
-      <c r="D59" s="48" t="s">
-        <v>232</v>
       </c>
       <c r="E59" s="48" t="s">
         <v>14</v>
@@ -5294,10 +5303,10 @@
         <v>10</v>
       </c>
       <c r="C60" s="48" t="s">
+        <v>232</v>
+      </c>
+      <c r="D60" s="48" t="s">
         <v>233</v>
-      </c>
-      <c r="D60" s="48" t="s">
-        <v>234</v>
       </c>
       <c r="E60" s="48" t="s">
         <v>14</v>
@@ -5326,10 +5335,10 @@
         <v>10</v>
       </c>
       <c r="C61" s="48" t="s">
+        <v>234</v>
+      </c>
+      <c r="D61" s="48" t="s">
         <v>235</v>
-      </c>
-      <c r="D61" s="48" t="s">
-        <v>236</v>
       </c>
       <c r="E61" s="48" t="s">
         <v>14</v>
@@ -5352,7 +5361,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="91" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B62" s="92"/>
       <c r="C62" s="92"/>
@@ -5372,22 +5381,22 @@
         <v>10</v>
       </c>
       <c r="C63" s="48" t="s">
+        <v>239</v>
+      </c>
+      <c r="D63" s="48" t="s">
         <v>240</v>
-      </c>
-      <c r="D63" s="48" t="s">
-        <v>241</v>
       </c>
       <c r="E63" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F63" s="48" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G63" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H63" s="48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I63" s="48" t="s">
         <v>12</v>
@@ -5404,22 +5413,22 @@
         <v>10</v>
       </c>
       <c r="C64" s="48" t="s">
+        <v>243</v>
+      </c>
+      <c r="D64" s="48" t="s">
         <v>244</v>
-      </c>
-      <c r="D64" s="48" t="s">
-        <v>245</v>
       </c>
       <c r="E64" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F64" s="48" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G64" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H64" s="48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I64" s="48" t="s">
         <v>12</v>
@@ -5436,22 +5445,22 @@
         <v>10</v>
       </c>
       <c r="C65" s="48" t="s">
+        <v>246</v>
+      </c>
+      <c r="D65" s="48" t="s">
         <v>247</v>
-      </c>
-      <c r="D65" s="48" t="s">
-        <v>248</v>
       </c>
       <c r="E65" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F65" s="48" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G65" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H65" s="48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I65" s="48" t="s">
         <v>12</v>
@@ -5468,22 +5477,22 @@
         <v>10</v>
       </c>
       <c r="C66" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="D66" s="48" t="s">
         <v>250</v>
-      </c>
-      <c r="D66" s="48" t="s">
-        <v>251</v>
       </c>
       <c r="E66" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F66" s="48" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G66" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H66" s="48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I66" s="48" t="s">
         <v>12</v>
@@ -5500,22 +5509,22 @@
         <v>10</v>
       </c>
       <c r="C67" s="48" t="s">
+        <v>252</v>
+      </c>
+      <c r="D67" s="48" t="s">
         <v>253</v>
-      </c>
-      <c r="D67" s="48" t="s">
-        <v>254</v>
       </c>
       <c r="E67" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F67" s="48" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G67" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H67" s="48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I67" s="48" t="s">
         <v>12</v>
@@ -5532,22 +5541,22 @@
         <v>10</v>
       </c>
       <c r="C68" s="48" t="s">
+        <v>255</v>
+      </c>
+      <c r="D68" s="48" t="s">
         <v>256</v>
-      </c>
-      <c r="D68" s="48" t="s">
-        <v>257</v>
       </c>
       <c r="E68" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F68" s="48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G68" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H68" s="48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I68" s="48" t="s">
         <v>12</v>
@@ -5564,22 +5573,22 @@
         <v>10</v>
       </c>
       <c r="C69" s="48" t="s">
+        <v>258</v>
+      </c>
+      <c r="D69" s="48" t="s">
         <v>259</v>
-      </c>
-      <c r="D69" s="48" t="s">
-        <v>260</v>
       </c>
       <c r="E69" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F69" s="48" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G69" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H69" s="48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I69" s="48" t="s">
         <v>12</v>
@@ -5596,22 +5605,22 @@
         <v>10</v>
       </c>
       <c r="C70" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="D70" s="48" t="s">
         <v>262</v>
-      </c>
-      <c r="D70" s="48" t="s">
-        <v>263</v>
       </c>
       <c r="E70" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F70" s="48" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G70" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H70" s="48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I70" s="48" t="s">
         <v>12</v>
@@ -5628,22 +5637,22 @@
         <v>10</v>
       </c>
       <c r="C71" s="48" t="s">
+        <v>264</v>
+      </c>
+      <c r="D71" s="48" t="s">
         <v>265</v>
-      </c>
-      <c r="D71" s="48" t="s">
-        <v>266</v>
       </c>
       <c r="E71" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F71" s="48" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G71" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H71" s="48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I71" s="48" t="s">
         <v>12</v>
@@ -5660,22 +5669,22 @@
         <v>10</v>
       </c>
       <c r="C72" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="D72" s="48" t="s">
         <v>268</v>
-      </c>
-      <c r="D72" s="48" t="s">
-        <v>269</v>
       </c>
       <c r="E72" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F72" s="48" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G72" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H72" s="48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I72" s="48" t="s">
         <v>12</v>
@@ -5692,22 +5701,22 @@
         <v>10</v>
       </c>
       <c r="C73" s="48" t="s">
+        <v>270</v>
+      </c>
+      <c r="D73" s="48" t="s">
         <v>271</v>
-      </c>
-      <c r="D73" s="48" t="s">
-        <v>272</v>
       </c>
       <c r="E73" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F73" s="48" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G73" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H73" s="48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I73" s="48" t="s">
         <v>12</v>
@@ -5718,7 +5727,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="91" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B74" s="92"/>
       <c r="C74" s="92"/>
@@ -5738,22 +5747,22 @@
         <v>10</v>
       </c>
       <c r="C75" s="48" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D75" s="48" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E75" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F75" s="48" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G75" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H75" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I75" s="48" t="s">
         <v>12</v>
@@ -5770,22 +5779,22 @@
         <v>10</v>
       </c>
       <c r="C76" s="48" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D76" s="48" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E76" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F76" s="48" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G76" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H76" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I76" s="48" t="s">
         <v>12</v>
@@ -5802,22 +5811,22 @@
         <v>10</v>
       </c>
       <c r="C77" s="48" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D77" s="48" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E77" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F77" s="48" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G77" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H77" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I77" s="48" t="s">
         <v>12</v>
@@ -5834,22 +5843,22 @@
         <v>10</v>
       </c>
       <c r="C78" s="48" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D78" s="48" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E78" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F78" s="48" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G78" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H78" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I78" s="48" t="s">
         <v>12</v>
@@ -5866,22 +5875,22 @@
         <v>10</v>
       </c>
       <c r="C79" s="48" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D79" s="48" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E79" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F79" s="48" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G79" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H79" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I79" s="48" t="s">
         <v>12</v>
@@ -5898,22 +5907,22 @@
         <v>10</v>
       </c>
       <c r="C80" s="48" t="s">
+        <v>284</v>
+      </c>
+      <c r="D80" s="48" t="s">
         <v>285</v>
-      </c>
-      <c r="D80" s="48" t="s">
-        <v>286</v>
       </c>
       <c r="E80" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F80" s="48" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G80" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H80" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I80" s="48" t="s">
         <v>12</v>
@@ -5930,22 +5939,22 @@
         <v>10</v>
       </c>
       <c r="C81" s="48" t="s">
+        <v>287</v>
+      </c>
+      <c r="D81" s="48" t="s">
         <v>288</v>
-      </c>
-      <c r="D81" s="48" t="s">
-        <v>289</v>
       </c>
       <c r="E81" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F81" s="48" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G81" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H81" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I81" s="48" t="s">
         <v>12</v>
@@ -5962,22 +5971,22 @@
         <v>10</v>
       </c>
       <c r="C82" s="48" t="s">
+        <v>290</v>
+      </c>
+      <c r="D82" s="48" t="s">
         <v>291</v>
-      </c>
-      <c r="D82" s="48" t="s">
-        <v>292</v>
       </c>
       <c r="E82" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F82" s="48" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G82" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H82" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I82" s="48" t="s">
         <v>12</v>
@@ -5994,22 +6003,22 @@
         <v>10</v>
       </c>
       <c r="C83" s="48" t="s">
+        <v>293</v>
+      </c>
+      <c r="D83" s="48" t="s">
         <v>294</v>
-      </c>
-      <c r="D83" s="48" t="s">
-        <v>295</v>
       </c>
       <c r="E83" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F83" s="48" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G83" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H83" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I83" s="48" t="s">
         <v>12</v>
@@ -6026,22 +6035,22 @@
         <v>10</v>
       </c>
       <c r="C84" s="48" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D84" s="48" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E84" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F84" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G84" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H84" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I84" s="48" t="s">
         <v>12</v>
@@ -6058,22 +6067,22 @@
         <v>10</v>
       </c>
       <c r="C85" s="48" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D85" s="48" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E85" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F85" s="48" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G85" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H85" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I85" s="48" t="s">
         <v>12</v>
@@ -6090,22 +6099,22 @@
         <v>10</v>
       </c>
       <c r="C86" s="48" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D86" s="48" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E86" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F86" s="48" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G86" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H86" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I86" s="48" t="s">
         <v>12</v>
@@ -6122,22 +6131,22 @@
         <v>10</v>
       </c>
       <c r="C87" s="48" t="s">
+        <v>302</v>
+      </c>
+      <c r="D87" s="48" t="s">
         <v>303</v>
-      </c>
-      <c r="D87" s="48" t="s">
-        <v>304</v>
       </c>
       <c r="E87" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F87" s="48" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G87" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H87" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I87" s="48" t="s">
         <v>12</v>
@@ -6154,22 +6163,22 @@
         <v>10</v>
       </c>
       <c r="C88" s="48" t="s">
+        <v>305</v>
+      </c>
+      <c r="D88" s="48" t="s">
         <v>306</v>
-      </c>
-      <c r="D88" s="48" t="s">
-        <v>307</v>
       </c>
       <c r="E88" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F88" s="48" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G88" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H88" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I88" s="48" t="s">
         <v>12</v>
@@ -6186,22 +6195,22 @@
         <v>10</v>
       </c>
       <c r="C89" s="48" t="s">
+        <v>308</v>
+      </c>
+      <c r="D89" s="48" t="s">
         <v>309</v>
-      </c>
-      <c r="D89" s="48" t="s">
-        <v>310</v>
       </c>
       <c r="E89" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F89" s="48" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G89" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H89" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I89" s="48" t="s">
         <v>12</v>
@@ -6218,22 +6227,22 @@
         <v>10</v>
       </c>
       <c r="C90" s="48" t="s">
+        <v>311</v>
+      </c>
+      <c r="D90" s="48" t="s">
         <v>312</v>
-      </c>
-      <c r="D90" s="48" t="s">
-        <v>313</v>
       </c>
       <c r="E90" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F90" s="48" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G90" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H90" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I90" s="48" t="s">
         <v>12</v>
@@ -6250,22 +6259,22 @@
         <v>10</v>
       </c>
       <c r="C91" s="48" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D91" s="48" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E91" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F91" s="48" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G91" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H91" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I91" s="48" t="s">
         <v>12</v>
@@ -6282,22 +6291,22 @@
         <v>10</v>
       </c>
       <c r="C92" s="48" t="s">
+        <v>316</v>
+      </c>
+      <c r="D92" s="48" t="s">
         <v>317</v>
-      </c>
-      <c r="D92" s="48" t="s">
-        <v>318</v>
       </c>
       <c r="E92" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F92" s="48" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G92" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H92" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I92" s="48" t="s">
         <v>12</v>
@@ -6314,22 +6323,22 @@
         <v>10</v>
       </c>
       <c r="C93" s="48" t="s">
+        <v>319</v>
+      </c>
+      <c r="D93" s="48" t="s">
         <v>320</v>
-      </c>
-      <c r="D93" s="48" t="s">
-        <v>321</v>
       </c>
       <c r="E93" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F93" s="48" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G93" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H93" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I93" s="48" t="s">
         <v>12</v>
@@ -6346,22 +6355,22 @@
         <v>10</v>
       </c>
       <c r="C94" s="48" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D94" s="48" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E94" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F94" s="48" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G94" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H94" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I94" s="48" t="s">
         <v>12</v>
@@ -6378,22 +6387,22 @@
         <v>10</v>
       </c>
       <c r="C95" s="48" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D95" s="48" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E95" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F95" s="48" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G95" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H95" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I95" s="48" t="s">
         <v>12</v>
@@ -6410,22 +6419,22 @@
         <v>10</v>
       </c>
       <c r="C96" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D96" s="48" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E96" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F96" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G96" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H96" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I96" s="48" t="s">
         <v>12</v>
@@ -6442,22 +6451,22 @@
         <v>10</v>
       </c>
       <c r="C97" s="48" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D97" s="48" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E97" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F97" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G97" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H97" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I97" s="48" t="s">
         <v>12</v>
@@ -6474,22 +6483,22 @@
         <v>10</v>
       </c>
       <c r="C98" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D98" s="48" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E98" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F98" s="48" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G98" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H98" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I98" s="48" t="s">
         <v>12</v>
@@ -6506,22 +6515,22 @@
         <v>10</v>
       </c>
       <c r="C99" s="48" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D99" s="48" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E99" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F99" s="48" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G99" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H99" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I99" s="48" t="s">
         <v>12</v>
@@ -6538,22 +6547,22 @@
         <v>10</v>
       </c>
       <c r="C100" s="48" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D100" s="48" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E100" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F100" s="48" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G100" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H100" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I100" s="48" t="s">
         <v>26</v>
@@ -6570,22 +6579,22 @@
         <v>10</v>
       </c>
       <c r="C101" s="48" t="s">
+        <v>589</v>
+      </c>
+      <c r="D101" s="48" t="s">
         <v>590</v>
-      </c>
-      <c r="D101" s="48" t="s">
-        <v>591</v>
       </c>
       <c r="E101" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F101" s="48" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G101" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H101" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I101" s="48" t="s">
         <v>26</v>
@@ -6596,7 +6605,7 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="87" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B102" s="87"/>
       <c r="C102" s="87"/>
@@ -6616,22 +6625,22 @@
         <v>10</v>
       </c>
       <c r="C103" s="48" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D103" s="48" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E103" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F103" s="48" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G103" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H103" s="48" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I103" s="48" t="s">
         <v>12</v>
@@ -6648,22 +6657,22 @@
         <v>10</v>
       </c>
       <c r="C104" s="48" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D104" s="48" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E104" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F104" s="48" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G104" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H104" s="48" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I104" s="48" t="s">
         <v>12</v>
@@ -6680,22 +6689,22 @@
         <v>10</v>
       </c>
       <c r="C105" s="48" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D105" s="48" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E105" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F105" s="48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G105" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H105" s="48" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I105" s="48" t="s">
         <v>12</v>
@@ -6712,22 +6721,22 @@
         <v>10</v>
       </c>
       <c r="C106" s="48" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D106" s="48" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E106" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F106" s="48" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G106" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H106" s="48" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I106" s="48" t="s">
         <v>12</v>
@@ -6744,22 +6753,22 @@
         <v>10</v>
       </c>
       <c r="C107" s="48" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D107" s="48" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E107" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F107" s="48" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G107" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H107" s="48" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I107" s="48" t="s">
         <v>12</v>
@@ -6776,22 +6785,22 @@
         <v>10</v>
       </c>
       <c r="C108" s="48" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D108" s="48" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E108" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F108" s="48" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G108" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H108" s="48" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I108" s="48" t="s">
         <v>12</v>
@@ -6808,22 +6817,22 @@
         <v>10</v>
       </c>
       <c r="C109" s="48" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D109" s="48" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E109" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F109" s="48" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G109" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H109" s="48" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I109" s="48" t="s">
         <v>12</v>
@@ -6840,22 +6849,22 @@
         <v>10</v>
       </c>
       <c r="C110" s="48" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D110" s="48" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E110" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F110" s="48" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G110" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H110" s="48" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I110" s="48" t="s">
         <v>12</v>
@@ -6872,22 +6881,22 @@
         <v>10</v>
       </c>
       <c r="C111" s="48" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D111" s="48" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E111" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F111" s="48" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G111" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H111" s="48" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I111" s="48" t="s">
         <v>12</v>
@@ -6904,22 +6913,22 @@
         <v>10</v>
       </c>
       <c r="C112" s="48" t="s">
+        <v>593</v>
+      </c>
+      <c r="D112" s="48" t="s">
         <v>594</v>
-      </c>
-      <c r="D112" s="48" t="s">
-        <v>595</v>
       </c>
       <c r="E112" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F112" s="48" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G112" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H112" s="48" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I112" s="48" t="s">
         <v>12</v>
@@ -6930,7 +6939,7 @@
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113" s="86" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B113" s="86"/>
       <c r="C113" s="86"/>
@@ -6950,22 +6959,22 @@
         <v>10</v>
       </c>
       <c r="C114" s="48" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D114" s="24" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E114" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F114" s="48" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G114" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H114" s="48" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I114" s="48" t="s">
         <v>12</v>
@@ -6976,7 +6985,7 @@
     </row>
     <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="86" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B115" s="86"/>
       <c r="C115" s="86"/>
@@ -6996,22 +7005,22 @@
         <v>10</v>
       </c>
       <c r="C116" s="48" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D116" s="24" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E116" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F116" s="48" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G116" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H116" s="48" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I116" s="48" t="s">
         <v>12</v>
@@ -7022,7 +7031,7 @@
     </row>
     <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="86" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B117" s="86"/>
       <c r="C117" s="86"/>
@@ -7042,22 +7051,22 @@
         <v>10</v>
       </c>
       <c r="C118" s="48" t="s">
+        <v>387</v>
+      </c>
+      <c r="D118" s="51" t="s">
         <v>388</v>
-      </c>
-      <c r="D118" s="51" t="s">
-        <v>389</v>
       </c>
       <c r="E118" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F118" s="51" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G118" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H118" s="51" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I118" s="51" t="s">
         <v>12</v>
@@ -7088,22 +7097,22 @@
         <v>10</v>
       </c>
       <c r="C119" s="48" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D119" s="63" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E119" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F119" s="48" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G119" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H119" s="48" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I119" s="48" t="s">
         <v>12</v>
@@ -7134,22 +7143,22 @@
         <v>10</v>
       </c>
       <c r="C120" s="48" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D120" s="64" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E120" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F120" s="48" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G120" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H120" s="48" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I120" s="48" t="s">
         <v>12</v>
@@ -7180,22 +7189,22 @@
         <v>10</v>
       </c>
       <c r="C121" s="48" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D121" s="64" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E121" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F121" s="48" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G121" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H121" s="48" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I121" s="48" t="s">
         <v>12</v>
@@ -7226,22 +7235,22 @@
         <v>10</v>
       </c>
       <c r="C122" s="48" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D122" s="64" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E122" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F122" s="48" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G122" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H122" s="48" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I122" s="48" t="s">
         <v>12</v>
@@ -7272,22 +7281,22 @@
         <v>10</v>
       </c>
       <c r="C123" s="48" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D123" s="64" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E123" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F123" s="48" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G123" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H123" s="48" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I123" s="48" t="s">
         <v>12</v>
@@ -7318,22 +7327,22 @@
         <v>10</v>
       </c>
       <c r="C124" s="48" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D124" s="64" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E124" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F124" s="48" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G124" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H124" s="48" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I124" s="48" t="s">
         <v>12</v>
@@ -7358,7 +7367,7 @@
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="86" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B125" s="86"/>
       <c r="C125" s="86"/>
@@ -7378,22 +7387,22 @@
         <v>10</v>
       </c>
       <c r="C126" s="48" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D126" s="60" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E126" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F126" s="48" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G126" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H126" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I126" s="27" t="s">
         <v>12</v>
@@ -7424,22 +7433,22 @@
         <v>10</v>
       </c>
       <c r="C127" s="48" t="s">
+        <v>407</v>
+      </c>
+      <c r="D127" s="27" t="s">
         <v>408</v>
-      </c>
-      <c r="D127" s="27" t="s">
-        <v>409</v>
       </c>
       <c r="E127" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F127" s="48" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G127" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H127" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I127" s="27" t="s">
         <v>26</v>
@@ -7470,22 +7479,22 @@
         <v>10</v>
       </c>
       <c r="C128" s="48" t="s">
+        <v>410</v>
+      </c>
+      <c r="D128" s="27" t="s">
         <v>411</v>
-      </c>
-      <c r="D128" s="27" t="s">
-        <v>412</v>
       </c>
       <c r="E128" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F128" s="48" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G128" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H128" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I128" s="27" t="s">
         <v>12</v>
@@ -7516,22 +7525,22 @@
         <v>10</v>
       </c>
       <c r="C129" s="48" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D129" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E129" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F129" s="48" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G129" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H129" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I129" s="27" t="s">
         <v>12</v>
@@ -7562,22 +7571,22 @@
         <v>10</v>
       </c>
       <c r="C130" s="48" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D130" s="27" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E130" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F130" s="48" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G130" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H130" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I130" s="27" t="s">
         <v>12</v>
@@ -7608,22 +7617,22 @@
         <v>10</v>
       </c>
       <c r="C131" s="48" t="s">
+        <v>417</v>
+      </c>
+      <c r="D131" s="27" t="s">
         <v>418</v>
-      </c>
-      <c r="D131" s="27" t="s">
-        <v>419</v>
       </c>
       <c r="E131" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F131" s="48" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G131" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H131" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I131" s="27" t="s">
         <v>12</v>
@@ -7654,22 +7663,22 @@
         <v>10</v>
       </c>
       <c r="C132" s="48" t="s">
+        <v>420</v>
+      </c>
+      <c r="D132" s="27" t="s">
         <v>421</v>
-      </c>
-      <c r="D132" s="27" t="s">
-        <v>422</v>
       </c>
       <c r="E132" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F132" s="48" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G132" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H132" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I132" s="27" t="s">
         <v>12</v>
@@ -7700,22 +7709,22 @@
         <v>10</v>
       </c>
       <c r="C133" s="48" t="s">
+        <v>423</v>
+      </c>
+      <c r="D133" s="27" t="s">
         <v>424</v>
-      </c>
-      <c r="D133" s="27" t="s">
-        <v>425</v>
       </c>
       <c r="E133" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F133" s="48" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G133" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H133" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I133" s="27" t="s">
         <v>12</v>
@@ -7746,22 +7755,22 @@
         <v>10</v>
       </c>
       <c r="C134" s="48" t="s">
+        <v>426</v>
+      </c>
+      <c r="D134" s="27" t="s">
         <v>427</v>
-      </c>
-      <c r="D134" s="27" t="s">
-        <v>428</v>
       </c>
       <c r="E134" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F134" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G134" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H134" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I134" s="27" t="s">
         <v>12</v>
@@ -7792,22 +7801,22 @@
         <v>10</v>
       </c>
       <c r="C135" s="48" t="s">
+        <v>429</v>
+      </c>
+      <c r="D135" s="27" t="s">
         <v>430</v>
-      </c>
-      <c r="D135" s="27" t="s">
-        <v>431</v>
       </c>
       <c r="E135" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F135" s="48" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G135" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H135" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I135" s="27" t="s">
         <v>12</v>
@@ -7832,7 +7841,7 @@
     </row>
     <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="95" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B136" s="96"/>
       <c r="C136" s="96"/>
@@ -7852,22 +7861,22 @@
         <v>10</v>
       </c>
       <c r="C137" s="48" t="s">
+        <v>433</v>
+      </c>
+      <c r="D137" s="48" t="s">
         <v>434</v>
-      </c>
-      <c r="D137" s="48" t="s">
-        <v>435</v>
       </c>
       <c r="E137" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F137" s="48" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G137" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H137" s="48" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I137" s="48" t="s">
         <v>12</v>
@@ -7898,22 +7907,22 @@
         <v>10</v>
       </c>
       <c r="C138" s="48" t="s">
+        <v>437</v>
+      </c>
+      <c r="D138" s="48" t="s">
         <v>438</v>
-      </c>
-      <c r="D138" s="48" t="s">
-        <v>439</v>
       </c>
       <c r="E138" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F138" s="48" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G138" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H138" s="48" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I138" s="48" t="s">
         <v>12</v>
@@ -7944,22 +7953,22 @@
         <v>10</v>
       </c>
       <c r="C139" s="48" t="s">
+        <v>440</v>
+      </c>
+      <c r="D139" s="48" t="s">
         <v>441</v>
-      </c>
-      <c r="D139" s="48" t="s">
-        <v>442</v>
       </c>
       <c r="E139" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F139" s="48" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G139" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H139" s="48" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I139" s="48" t="s">
         <v>12</v>
@@ -7990,22 +7999,22 @@
         <v>10</v>
       </c>
       <c r="C140" s="48" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D140" s="48" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E140" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F140" s="48" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G140" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H140" s="48" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I140" s="48" t="s">
         <v>12</v>
@@ -8022,22 +8031,22 @@
         <v>10</v>
       </c>
       <c r="C141" s="48" t="s">
+        <v>445</v>
+      </c>
+      <c r="D141" s="48" t="s">
         <v>446</v>
-      </c>
-      <c r="D141" s="48" t="s">
-        <v>447</v>
       </c>
       <c r="E141" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F141" s="48" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G141" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H141" s="48" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I141" s="48" t="s">
         <v>12</v>
@@ -8068,22 +8077,22 @@
         <v>10</v>
       </c>
       <c r="C142" s="48" t="s">
+        <v>448</v>
+      </c>
+      <c r="D142" s="48" t="s">
         <v>449</v>
-      </c>
-      <c r="D142" s="48" t="s">
-        <v>450</v>
       </c>
       <c r="E142" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F142" s="48" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G142" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H142" s="48" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I142" s="48" t="s">
         <v>12</v>
@@ -8114,22 +8123,22 @@
         <v>10</v>
       </c>
       <c r="C143" s="48" t="s">
+        <v>451</v>
+      </c>
+      <c r="D143" s="48" t="s">
         <v>452</v>
-      </c>
-      <c r="D143" s="48" t="s">
-        <v>453</v>
       </c>
       <c r="E143" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F143" s="48" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G143" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H143" s="48" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I143" s="48" t="s">
         <v>12</v>
@@ -8160,22 +8169,22 @@
         <v>10</v>
       </c>
       <c r="C144" s="48" t="s">
+        <v>454</v>
+      </c>
+      <c r="D144" s="48" t="s">
         <v>455</v>
-      </c>
-      <c r="D144" s="48" t="s">
-        <v>456</v>
       </c>
       <c r="E144" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F144" s="48" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G144" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H144" s="48" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I144" s="48" t="s">
         <v>12</v>
@@ -8206,22 +8215,22 @@
         <v>10</v>
       </c>
       <c r="C145" s="48" t="s">
+        <v>457</v>
+      </c>
+      <c r="D145" s="48" t="s">
         <v>458</v>
-      </c>
-      <c r="D145" s="48" t="s">
-        <v>459</v>
       </c>
       <c r="E145" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F145" s="48" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G145" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H145" s="48" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I145" s="48" t="s">
         <v>12</v>
@@ -8252,22 +8261,22 @@
         <v>10</v>
       </c>
       <c r="C146" s="48" t="s">
+        <v>460</v>
+      </c>
+      <c r="D146" s="48" t="s">
         <v>461</v>
-      </c>
-      <c r="D146" s="48" t="s">
-        <v>462</v>
       </c>
       <c r="E146" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F146" s="48" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G146" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H146" s="48" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I146" s="48" t="s">
         <v>12</v>
@@ -8292,7 +8301,7 @@
     </row>
     <row r="147" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A147" s="86" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B147" s="86"/>
       <c r="C147" s="86"/>
@@ -8312,22 +8321,22 @@
         <v>10</v>
       </c>
       <c r="C148" s="48" t="s">
+        <v>505</v>
+      </c>
+      <c r="D148" s="24" t="s">
         <v>506</v>
-      </c>
-      <c r="D148" s="24" t="s">
-        <v>507</v>
       </c>
       <c r="E148" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F148" s="48" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G148" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H148" s="48" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I148" s="48" t="s">
         <v>12</v>
@@ -8336,97 +8345,81 @@
         <v>13</v>
       </c>
     </row>
-    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="86" t="s">
+    <row r="149" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A149" s="25">
+        <v>2</v>
+      </c>
+      <c r="B149" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C149" s="48" t="s">
+        <v>636</v>
+      </c>
+      <c r="D149" s="24" t="s">
+        <v>637</v>
+      </c>
+      <c r="E149" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F149" s="48" t="s">
+        <v>638</v>
+      </c>
+      <c r="G149" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H149" s="48" t="s">
+        <v>371</v>
+      </c>
+      <c r="I149" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J149" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="150" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="86" t="s">
+        <v>530</v>
+      </c>
+      <c r="B150" s="86"/>
+      <c r="C150" s="86"/>
+      <c r="D150" s="86"/>
+      <c r="E150" s="86"/>
+      <c r="F150" s="86"/>
+      <c r="G150" s="86"/>
+      <c r="H150" s="86"/>
+      <c r="I150" s="86"/>
+      <c r="J150" s="86"/>
+    </row>
+    <row r="151" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="65">
+        <v>1</v>
+      </c>
+      <c r="B151" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="C151" s="67" t="s">
         <v>531</v>
       </c>
-      <c r="B149" s="86"/>
-      <c r="C149" s="86"/>
-      <c r="D149" s="86"/>
-      <c r="E149" s="86"/>
-      <c r="F149" s="86"/>
-      <c r="G149" s="86"/>
-      <c r="H149" s="86"/>
-      <c r="I149" s="86"/>
-      <c r="J149" s="86"/>
-    </row>
-    <row r="150" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="65">
-        <v>1</v>
-      </c>
-      <c r="B150" s="66" t="s">
-        <v>10</v>
-      </c>
-      <c r="C150" s="67" t="s">
+      <c r="D151" s="66" t="s">
         <v>532</v>
       </c>
-      <c r="D150" s="66" t="s">
+      <c r="E151" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="F151" s="67" t="s">
         <v>533</v>
       </c>
-      <c r="E150" s="66" t="s">
-        <v>14</v>
-      </c>
-      <c r="F150" s="67" t="s">
+      <c r="G151" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="H151" s="66" t="s">
         <v>534</v>
       </c>
-      <c r="G150" s="66" t="s">
-        <v>11</v>
-      </c>
-      <c r="H150" s="66" t="s">
-        <v>535</v>
-      </c>
-      <c r="I150" s="66" t="s">
+      <c r="I151" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="J150" s="66" t="s">
-        <v>13</v>
-      </c>
-      <c r="K150" s="58"/>
-      <c r="L150" s="58"/>
-      <c r="M150" s="58"/>
-      <c r="N150" s="58"/>
-      <c r="O150" s="58"/>
-      <c r="P150" s="58"/>
-      <c r="Q150" s="58"/>
-      <c r="R150" s="58"/>
-      <c r="S150" s="58"/>
-      <c r="T150" s="58"/>
-      <c r="U150" s="58"/>
-      <c r="V150" s="58"/>
-      <c r="W150" s="58"/>
-      <c r="X150" s="58"/>
-      <c r="Y150" s="58"/>
-      <c r="Z150" s="58"/>
-    </row>
-    <row r="151" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="68">
-        <v>2</v>
-      </c>
-      <c r="B151" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="C151" s="70" t="s">
-        <v>536</v>
-      </c>
-      <c r="D151" s="69" t="s">
-        <v>537</v>
-      </c>
-      <c r="E151" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="F151" s="70" t="s">
-        <v>538</v>
-      </c>
-      <c r="G151" s="69" t="s">
-        <v>11</v>
-      </c>
-      <c r="H151" s="69" t="s">
-        <v>535</v>
-      </c>
-      <c r="I151" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="J151" s="69" t="s">
+      <c r="J151" s="66" t="s">
         <v>13</v>
       </c>
       <c r="K151" s="58"/>
@@ -8448,28 +8441,28 @@
     </row>
     <row r="152" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B152" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C152" s="70" t="s">
-        <v>539</v>
-      </c>
-      <c r="D152" s="71" t="s">
-        <v>540</v>
+        <v>535</v>
+      </c>
+      <c r="D152" s="69" t="s">
+        <v>536</v>
       </c>
       <c r="E152" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F152" s="70" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="G152" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H152" s="69" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I152" s="69" t="s">
         <v>12</v>
@@ -8496,28 +8489,28 @@
     </row>
     <row r="153" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B153" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C153" s="70" t="s">
-        <v>542</v>
-      </c>
-      <c r="D153" s="69" t="s">
-        <v>543</v>
+        <v>538</v>
+      </c>
+      <c r="D153" s="71" t="s">
+        <v>539</v>
       </c>
       <c r="E153" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F153" s="70" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="G153" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H153" s="69" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I153" s="69" t="s">
         <v>12</v>
@@ -8544,28 +8537,28 @@
     </row>
     <row r="154" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B154" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C154" s="70" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D154" s="69" t="s">
-        <v>583</v>
+        <v>542</v>
       </c>
       <c r="E154" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F154" s="70" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="G154" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H154" s="69" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I154" s="69" t="s">
         <v>12</v>
@@ -8592,28 +8585,28 @@
     </row>
     <row r="155" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B155" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C155" s="70" t="s">
-        <v>547</v>
-      </c>
-      <c r="D155" s="71" t="s">
-        <v>584</v>
+        <v>544</v>
+      </c>
+      <c r="D155" s="69" t="s">
+        <v>582</v>
       </c>
       <c r="E155" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F155" s="70" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="G155" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H155" s="69" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I155" s="69" t="s">
         <v>12</v>
@@ -8640,28 +8633,28 @@
     </row>
     <row r="156" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="68">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B156" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C156" s="70" t="s">
-        <v>549</v>
-      </c>
-      <c r="D156" s="69" t="s">
-        <v>585</v>
+        <v>546</v>
+      </c>
+      <c r="D156" s="71" t="s">
+        <v>583</v>
       </c>
       <c r="E156" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F156" s="70" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="G156" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H156" s="69" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I156" s="69" t="s">
         <v>12</v>
@@ -8688,28 +8681,28 @@
     </row>
     <row r="157" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="68">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B157" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C157" s="70" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D157" s="69" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E157" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F157" s="70" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="G157" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H157" s="69" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I157" s="69" t="s">
         <v>12</v>
@@ -8735,34 +8728,34 @@
       <c r="Z157" s="58"/>
     </row>
     <row r="158" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="72">
-        <v>9</v>
-      </c>
-      <c r="B158" s="74" t="s">
+      <c r="A158" s="68">
+        <v>8</v>
+      </c>
+      <c r="B158" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="C158" s="75" t="s">
-        <v>553</v>
-      </c>
-      <c r="D158" s="74" t="s">
-        <v>556</v>
-      </c>
-      <c r="E158" s="74" t="s">
+      <c r="C158" s="70" t="s">
+        <v>550</v>
+      </c>
+      <c r="D158" s="69" t="s">
+        <v>585</v>
+      </c>
+      <c r="E158" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="F158" s="75" t="s">
-        <v>554</v>
-      </c>
-      <c r="G158" s="74" t="s">
+      <c r="F158" s="70" t="s">
+        <v>551</v>
+      </c>
+      <c r="G158" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="H158" s="74" t="s">
-        <v>535</v>
-      </c>
-      <c r="I158" s="74" t="s">
+      <c r="H158" s="69" t="s">
+        <v>534</v>
+      </c>
+      <c r="I158" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="J158" s="74" t="s">
+      <c r="J158" s="69" t="s">
         <v>13</v>
       </c>
       <c r="K158" s="58"/>
@@ -8783,29 +8776,29 @@
       <c r="Z158" s="58"/>
     </row>
     <row r="159" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="73">
-        <v>10</v>
+      <c r="A159" s="72">
+        <v>9</v>
       </c>
       <c r="B159" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C159" s="75" t="s">
+        <v>552</v>
+      </c>
+      <c r="D159" s="74" t="s">
         <v>555</v>
-      </c>
-      <c r="D159" s="74" t="s">
-        <v>559</v>
       </c>
       <c r="E159" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F159" s="75" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="G159" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H159" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I159" s="74" t="s">
         <v>12</v>
@@ -8831,29 +8824,29 @@
       <c r="Z159" s="58"/>
     </row>
     <row r="160" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="72">
-        <v>11</v>
+      <c r="A160" s="73">
+        <v>10</v>
       </c>
       <c r="B160" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C160" s="75" t="s">
+        <v>554</v>
+      </c>
+      <c r="D160" s="74" t="s">
         <v>558</v>
-      </c>
-      <c r="D160" s="74" t="s">
-        <v>562</v>
       </c>
       <c r="E160" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F160" s="75" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="G160" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H160" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I160" s="74" t="s">
         <v>12</v>
@@ -8879,29 +8872,29 @@
       <c r="Z160" s="58"/>
     </row>
     <row r="161" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="73">
-        <v>12</v>
+      <c r="A161" s="72">
+        <v>11</v>
       </c>
       <c r="B161" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C161" s="75" t="s">
+        <v>557</v>
+      </c>
+      <c r="D161" s="74" t="s">
         <v>561</v>
-      </c>
-      <c r="D161" s="74" t="s">
-        <v>565</v>
       </c>
       <c r="E161" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F161" s="75" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="G161" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H161" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I161" s="74" t="s">
         <v>12</v>
@@ -8927,29 +8920,29 @@
       <c r="Z161" s="58"/>
     </row>
     <row r="162" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="72">
-        <v>13</v>
+      <c r="A162" s="73">
+        <v>12</v>
       </c>
       <c r="B162" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C162" s="75" t="s">
+        <v>560</v>
+      </c>
+      <c r="D162" s="74" t="s">
         <v>564</v>
-      </c>
-      <c r="D162" s="74" t="s">
-        <v>568</v>
       </c>
       <c r="E162" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F162" s="75" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="G162" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H162" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I162" s="74" t="s">
         <v>12</v>
@@ -8975,29 +8968,29 @@
       <c r="Z162" s="58"/>
     </row>
     <row r="163" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="73">
-        <v>14</v>
+      <c r="A163" s="72">
+        <v>13</v>
       </c>
       <c r="B163" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C163" s="75" t="s">
+        <v>563</v>
+      </c>
+      <c r="D163" s="74" t="s">
         <v>567</v>
-      </c>
-      <c r="D163" s="76" t="s">
-        <v>571</v>
       </c>
       <c r="E163" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F163" s="75" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="G163" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H163" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I163" s="74" t="s">
         <v>12</v>
@@ -9023,29 +9016,29 @@
       <c r="Z163" s="58"/>
     </row>
     <row r="164" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="72">
-        <v>15</v>
+      <c r="A164" s="73">
+        <v>14</v>
       </c>
       <c r="B164" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C164" s="75" t="s">
+        <v>566</v>
+      </c>
+      <c r="D164" s="76" t="s">
         <v>570</v>
-      </c>
-      <c r="D164" s="76" t="s">
-        <v>587</v>
       </c>
       <c r="E164" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F164" s="75" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="G164" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H164" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I164" s="74" t="s">
         <v>12</v>
@@ -9071,29 +9064,29 @@
       <c r="Z164" s="58"/>
     </row>
     <row r="165" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="73">
-        <v>16</v>
+      <c r="A165" s="72">
+        <v>15</v>
       </c>
       <c r="B165" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C165" s="75" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="D165" s="76" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="E165" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F165" s="75" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G165" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H165" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I165" s="74" t="s">
         <v>12</v>
@@ -9119,29 +9112,29 @@
       <c r="Z165" s="58"/>
     </row>
     <row r="166" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="72">
-        <v>17</v>
+      <c r="A166" s="73">
+        <v>16</v>
       </c>
       <c r="B166" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C166" s="75" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D166" s="76" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E166" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F166" s="75" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="G166" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H166" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I166" s="74" t="s">
         <v>12</v>
@@ -9167,29 +9160,29 @@
       <c r="Z166" s="58"/>
     </row>
     <row r="167" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="73">
-        <v>18</v>
+      <c r="A167" s="72">
+        <v>17</v>
       </c>
       <c r="B167" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C167" s="75" t="s">
-        <v>577</v>
-      </c>
-      <c r="D167" s="77" t="s">
-        <v>581</v>
+        <v>574</v>
+      </c>
+      <c r="D167" s="76" t="s">
+        <v>579</v>
       </c>
       <c r="E167" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F167" s="75" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="G167" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H167" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I167" s="74" t="s">
         <v>12</v>
@@ -9215,75 +9208,91 @@
       <c r="Z167" s="58"/>
     </row>
     <row r="168" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="86" t="s">
-        <v>610</v>
-      </c>
-      <c r="B168" s="86"/>
-      <c r="C168" s="86"/>
-      <c r="D168" s="86"/>
-      <c r="E168" s="86"/>
-      <c r="F168" s="86"/>
-      <c r="G168" s="86"/>
-      <c r="H168" s="86"/>
-      <c r="I168" s="86"/>
-      <c r="J168" s="86"/>
+      <c r="A168" s="73">
+        <v>18</v>
+      </c>
+      <c r="B168" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C168" s="75" t="s">
+        <v>576</v>
+      </c>
+      <c r="D168" s="77" t="s">
+        <v>580</v>
+      </c>
+      <c r="E168" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F168" s="75" t="s">
+        <v>578</v>
+      </c>
+      <c r="G168" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H168" s="74" t="s">
+        <v>534</v>
+      </c>
+      <c r="I168" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J168" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="K168" s="58"/>
+      <c r="L168" s="58"/>
+      <c r="M168" s="58"/>
+      <c r="N168" s="58"/>
+      <c r="O168" s="58"/>
+      <c r="P168" s="58"/>
+      <c r="Q168" s="58"/>
+      <c r="R168" s="58"/>
+      <c r="S168" s="58"/>
+      <c r="T168" s="58"/>
+      <c r="U168" s="58"/>
+      <c r="V168" s="58"/>
+      <c r="W168" s="58"/>
+      <c r="X168" s="58"/>
+      <c r="Y168" s="58"/>
+      <c r="Z168" s="58"/>
     </row>
     <row r="169" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="73">
-        <v>1</v>
-      </c>
-      <c r="B169" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="C169" s="75" t="s">
-        <v>596</v>
-      </c>
-      <c r="D169" s="77" t="s">
-        <v>598</v>
-      </c>
-      <c r="E169" s="74" t="s">
-        <v>14</v>
-      </c>
-      <c r="F169" s="75" t="s">
-        <v>597</v>
-      </c>
-      <c r="G169" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="H169" s="74" t="s">
-        <v>535</v>
-      </c>
-      <c r="I169" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="J169" s="74" t="s">
-        <v>13</v>
-      </c>
+      <c r="A169" s="86" t="s">
+        <v>609</v>
+      </c>
+      <c r="B169" s="86"/>
+      <c r="C169" s="86"/>
+      <c r="D169" s="86"/>
+      <c r="E169" s="86"/>
+      <c r="F169" s="86"/>
+      <c r="G169" s="86"/>
+      <c r="H169" s="86"/>
+      <c r="I169" s="86"/>
+      <c r="J169" s="86"/>
     </row>
     <row r="170" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B170" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C170" s="75" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="D170" s="77" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="E170" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F170" s="75" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="G170" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H170" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I170" s="74" t="s">
         <v>12</v>
@@ -9294,28 +9303,28 @@
     </row>
     <row r="171" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B171" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C171" s="75" t="s">
-        <v>608</v>
-      </c>
-      <c r="D171" s="81" t="s">
-        <v>609</v>
+        <v>603</v>
+      </c>
+      <c r="D171" s="77" t="s">
+        <v>604</v>
       </c>
       <c r="E171" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F171" s="75" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="G171" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H171" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I171" s="74" t="s">
         <v>12</v>
@@ -9326,28 +9335,28 @@
     </row>
     <row r="172" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B172" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="C172" s="79" t="s">
-        <v>612</v>
-      </c>
-      <c r="D172" s="64" t="s">
-        <v>613</v>
-      </c>
-      <c r="E172" s="80" t="s">
+      <c r="C172" s="75" t="s">
+        <v>607</v>
+      </c>
+      <c r="D172" s="81" t="s">
+        <v>608</v>
+      </c>
+      <c r="E172" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F172" s="75" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="G172" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H172" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I172" s="74" t="s">
         <v>12</v>
@@ -9358,28 +9367,28 @@
     </row>
     <row r="173" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B173" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C173" s="79" t="s">
-        <v>618</v>
-      </c>
-      <c r="D173" s="83" t="s">
-        <v>619</v>
+        <v>611</v>
+      </c>
+      <c r="D173" s="64" t="s">
+        <v>612</v>
       </c>
       <c r="E173" s="80" t="s">
         <v>14</v>
       </c>
       <c r="F173" s="75" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="G173" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H173" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I173" s="74" t="s">
         <v>12</v>
@@ -9390,28 +9399,28 @@
     </row>
     <row r="174" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B174" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="C174" s="75" t="s">
-        <v>620</v>
-      </c>
-      <c r="D174" s="77" t="s">
-        <v>622</v>
-      </c>
-      <c r="E174" s="74" t="s">
+      <c r="C174" s="79" t="s">
+        <v>617</v>
+      </c>
+      <c r="D174" s="83" t="s">
+        <v>618</v>
+      </c>
+      <c r="E174" s="80" t="s">
         <v>14</v>
       </c>
       <c r="F174" s="75" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="G174" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H174" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I174" s="74" t="s">
         <v>12</v>
@@ -9422,28 +9431,28 @@
     </row>
     <row r="175" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="73">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B175" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C175" s="75" t="s">
-        <v>628</v>
-      </c>
-      <c r="D175" s="83" t="s">
-        <v>627</v>
+        <v>619</v>
+      </c>
+      <c r="D175" s="77" t="s">
+        <v>621</v>
       </c>
       <c r="E175" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F175" s="75" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="G175" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H175" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I175" s="74" t="s">
         <v>12</v>
@@ -9452,10 +9461,42 @@
         <v>13</v>
       </c>
     </row>
+    <row r="176" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="73">
+        <v>7</v>
+      </c>
+      <c r="B176" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C176" s="75" t="s">
+        <v>627</v>
+      </c>
+      <c r="D176" s="83" t="s">
+        <v>626</v>
+      </c>
+      <c r="E176" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F176" s="75" t="s">
+        <v>624</v>
+      </c>
+      <c r="G176" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H176" s="74" t="s">
+        <v>534</v>
+      </c>
+      <c r="I176" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J176" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A168:J168"/>
-    <mergeCell ref="A149:J149"/>
+    <mergeCell ref="A169:J169"/>
+    <mergeCell ref="A150:J150"/>
     <mergeCell ref="A147:J147"/>
     <mergeCell ref="A125:J125"/>
     <mergeCell ref="A136:J136"/>
@@ -9565,7 +9606,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:X174"/>
+  <dimension ref="A1:X175"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -9647,19 +9688,19 @@
         <v>133</v>
       </c>
       <c r="T1" s="30" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="U1" s="31" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="V1" s="31" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="W1" s="31" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="X1" s="31" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -10720,7 +10761,7 @@
         <v>29</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>22</v>
@@ -11070,7 +11111,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D22" s="39" t="s">
         <v>95</v>
@@ -13986,7 +14027,7 @@
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B63" s="48" t="s">
         <v>22</v>
@@ -14058,7 +14099,7 @@
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64" s="48" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B64" s="48" t="s">
         <v>22</v>
@@ -14130,7 +14171,7 @@
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A65" s="48" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B65" s="48" t="s">
         <v>22</v>
@@ -14202,7 +14243,7 @@
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A66" s="48" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B66" s="48" t="s">
         <v>22</v>
@@ -14274,7 +14315,7 @@
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A67" s="48" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B67" s="48" t="s">
         <v>22</v>
@@ -14346,7 +14387,7 @@
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A68" s="48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B68" s="48" t="s">
         <v>22</v>
@@ -14418,7 +14459,7 @@
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A69" s="48" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B69" s="48" t="s">
         <v>22</v>
@@ -14490,13 +14531,13 @@
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A70" s="48" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B70" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C70" s="36" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D70" s="48" t="s">
         <v>22</v>
@@ -14562,7 +14603,7 @@
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A71" s="48" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B71" s="48" t="s">
         <v>22</v>
@@ -14634,7 +14675,7 @@
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A72" s="48" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B72" s="48" t="s">
         <v>22</v>
@@ -14706,7 +14747,7 @@
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A73" s="51" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B73" s="51" t="s">
         <v>22</v>
@@ -14780,7 +14821,7 @@
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A74" s="62" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B74" s="48" t="s">
         <v>22</v>
@@ -14854,7 +14895,7 @@
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A75" s="48" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B75" s="48" t="s">
         <v>22</v>
@@ -14928,7 +14969,7 @@
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A76" s="48" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B76" s="48" t="s">
         <v>22</v>
@@ -15002,7 +15043,7 @@
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A77" s="48" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B77" s="48" t="s">
         <v>22</v>
@@ -15076,7 +15117,7 @@
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A78" s="48" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B78" s="48" t="s">
         <v>22</v>
@@ -15150,7 +15191,7 @@
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A79" s="48" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B79" s="48" t="s">
         <v>22</v>
@@ -15224,7 +15265,7 @@
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A80" s="48" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B80" s="48" t="s">
         <v>22</v>
@@ -15298,7 +15339,7 @@
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A81" s="48" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B81" s="48" t="s">
         <v>22</v>
@@ -15372,7 +15413,7 @@
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A82" s="48" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B82" s="48" t="s">
         <v>22</v>
@@ -15446,7 +15487,7 @@
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A83" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B83" s="48" t="s">
         <v>22</v>
@@ -15520,7 +15561,7 @@
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A84" s="48" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B84" s="48" t="s">
         <v>22</v>
@@ -15594,7 +15635,7 @@
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A85" s="48" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B85" s="48" t="s">
         <v>22</v>
@@ -15668,7 +15709,7 @@
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A86" s="48" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B86" s="48" t="s">
         <v>22</v>
@@ -15742,7 +15783,7 @@
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A87" s="48" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B87" s="48" t="s">
         <v>22</v>
@@ -15816,7 +15857,7 @@
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A88" s="48" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B88" s="48" t="s">
         <v>22</v>
@@ -15890,7 +15931,7 @@
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A89" s="48" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B89" s="48" t="s">
         <v>22</v>
@@ -15964,7 +16005,7 @@
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A90" s="48" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B90" s="48" t="s">
         <v>22</v>
@@ -16038,7 +16079,7 @@
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A91" s="48" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B91" s="48" t="s">
         <v>22</v>
@@ -16112,7 +16153,7 @@
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A92" s="48" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B92" s="48" t="s">
         <v>22</v>
@@ -16186,7 +16227,7 @@
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A93" s="48" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B93" s="48" t="s">
         <v>22</v>
@@ -16260,7 +16301,7 @@
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A94" s="48" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B94" s="48" t="s">
         <v>22</v>
@@ -16334,7 +16375,7 @@
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A95" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B95" s="48" t="s">
         <v>22</v>
@@ -16408,7 +16449,7 @@
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A96" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B96" s="48" t="s">
         <v>22</v>
@@ -16482,7 +16523,7 @@
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A97" s="48" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B97" s="48" t="s">
         <v>22</v>
@@ -16556,7 +16597,7 @@
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A98" s="48" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B98" s="48" t="s">
         <v>22</v>
@@ -16630,7 +16671,7 @@
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A99" s="48" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B99" s="51" t="s">
         <v>22</v>
@@ -16704,7 +16745,7 @@
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A100" s="48" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B100" s="51" t="s">
         <v>22</v>
@@ -16778,7 +16819,7 @@
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A101" s="48" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B101" s="48" t="s">
         <v>22</v>
@@ -16852,7 +16893,7 @@
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A102" s="48" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B102" s="48" t="s">
         <v>22</v>
@@ -16926,7 +16967,7 @@
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103" s="48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B103" s="48" t="s">
         <v>22</v>
@@ -17000,7 +17041,7 @@
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A104" s="48" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B104" s="48" t="s">
         <v>22</v>
@@ -17074,7 +17115,7 @@
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A105" s="48" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B105" s="48" t="s">
         <v>22</v>
@@ -17148,7 +17189,7 @@
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106" s="48" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B106" s="48" t="s">
         <v>22</v>
@@ -17222,7 +17263,7 @@
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A107" s="48" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B107" s="48" t="s">
         <v>22</v>
@@ -17296,7 +17337,7 @@
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A108" s="48" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B108" s="48" t="s">
         <v>22</v>
@@ -17370,7 +17411,7 @@
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A109" s="48" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B109" s="48" t="s">
         <v>22</v>
@@ -17444,7 +17485,7 @@
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A110" s="48" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B110" s="48" t="s">
         <v>22</v>
@@ -17518,7 +17559,7 @@
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111" s="48" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B111" s="48" t="s">
         <v>22</v>
@@ -17592,7 +17633,7 @@
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A112" s="48" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B112" s="48" t="s">
         <v>22</v>
@@ -17666,7 +17707,7 @@
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113" s="48" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B113" s="48" t="s">
         <v>22</v>
@@ -17740,7 +17781,7 @@
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="48" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B114" s="48" t="s">
         <v>22</v>
@@ -17814,7 +17855,7 @@
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A115" s="48" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B115" s="48" t="s">
         <v>22</v>
@@ -17888,7 +17929,7 @@
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" s="48" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B116" s="48" t="s">
         <v>22</v>
@@ -17962,7 +18003,7 @@
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A117" s="48" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B117" s="48" t="s">
         <v>22</v>
@@ -18036,7 +18077,7 @@
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118" s="48" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B118" s="48" t="s">
         <v>22</v>
@@ -18110,7 +18151,7 @@
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A119" s="48" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B119" s="48" t="s">
         <v>22</v>
@@ -18184,7 +18225,7 @@
     </row>
     <row r="120" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A120" s="48" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B120" s="48" t="s">
         <v>22</v>
@@ -18258,13 +18299,13 @@
     </row>
     <row r="121" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A121" s="62" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B121" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C121" s="36" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D121" s="48" t="s">
         <v>22</v>
@@ -18273,22 +18314,22 @@
         <v>22</v>
       </c>
       <c r="F121" s="48" t="s">
+        <v>485</v>
+      </c>
+      <c r="G121" s="49" t="s">
         <v>486</v>
       </c>
-      <c r="G121" s="49" t="s">
+      <c r="H121" s="48" t="s">
         <v>487</v>
       </c>
-      <c r="H121" s="48" t="s">
+      <c r="I121" s="48" t="s">
         <v>488</v>
       </c>
-      <c r="I121" s="48" t="s">
+      <c r="J121" s="36" t="s">
+        <v>468</v>
+      </c>
+      <c r="K121" s="48" t="s">
         <v>489</v>
-      </c>
-      <c r="J121" s="36" t="s">
-        <v>469</v>
-      </c>
-      <c r="K121" s="48" t="s">
-        <v>490</v>
       </c>
       <c r="L121" s="48" t="s">
         <v>22</v>
@@ -18332,7 +18373,7 @@
     </row>
     <row r="122" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A122" s="48" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B122" s="48" t="s">
         <v>22</v>
@@ -18406,37 +18447,37 @@
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A123" s="48" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B123" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C123" s="36" t="s">
+        <v>464</v>
+      </c>
+      <c r="D123" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E123" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F123" s="48" t="s">
         <v>465</v>
       </c>
-      <c r="D123" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E123" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F123" s="48" t="s">
+      <c r="G123" s="49" t="s">
         <v>466</v>
-      </c>
-      <c r="G123" s="49" t="s">
-        <v>467</v>
       </c>
       <c r="H123" s="48" t="s">
         <v>37</v>
       </c>
       <c r="I123" s="48" t="s">
+        <v>467</v>
+      </c>
+      <c r="J123" s="36" t="s">
         <v>468</v>
       </c>
-      <c r="J123" s="36" t="s">
+      <c r="K123" s="48" t="s">
         <v>469</v>
-      </c>
-      <c r="K123" s="48" t="s">
-        <v>470</v>
       </c>
       <c r="L123" s="48" t="s">
         <v>22</v>
@@ -18480,13 +18521,13 @@
     </row>
     <row r="124" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A124" s="48" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B124" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C124" s="36" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D124" s="48" t="s">
         <v>22</v>
@@ -18495,22 +18536,22 @@
         <v>22</v>
       </c>
       <c r="F124" s="48" t="s">
+        <v>471</v>
+      </c>
+      <c r="G124" s="49" t="s">
         <v>472</v>
       </c>
-      <c r="G124" s="49" t="s">
+      <c r="H124" s="48" t="s">
         <v>473</v>
       </c>
-      <c r="H124" s="48" t="s">
-        <v>474</v>
-      </c>
       <c r="I124" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="J124" s="36" t="s">
         <v>491</v>
       </c>
-      <c r="J124" s="36" t="s">
+      <c r="K124" s="48" t="s">
         <v>492</v>
-      </c>
-      <c r="K124" s="48" t="s">
-        <v>493</v>
       </c>
       <c r="L124" s="48" t="s">
         <v>22</v>
@@ -18554,13 +18595,13 @@
     </row>
     <row r="125" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A125" s="48" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B125" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C125" s="36" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D125" s="48" t="s">
         <v>22</v>
@@ -18572,19 +18613,19 @@
         <v>29</v>
       </c>
       <c r="G125" s="49" t="s">
+        <v>472</v>
+      </c>
+      <c r="H125" s="48" t="s">
         <v>473</v>
       </c>
-      <c r="H125" s="48" t="s">
+      <c r="I125" s="48" t="s">
         <v>474</v>
       </c>
-      <c r="I125" s="48" t="s">
+      <c r="J125" s="36" t="s">
         <v>475</v>
       </c>
-      <c r="J125" s="36" t="s">
+      <c r="K125" s="48" t="s">
         <v>476</v>
-      </c>
-      <c r="K125" s="48" t="s">
-        <v>477</v>
       </c>
       <c r="L125" s="48" t="s">
         <v>22</v>
@@ -18628,37 +18669,37 @@
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A126" s="48" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B126" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C126" s="36" t="s">
+        <v>493</v>
+      </c>
+      <c r="D126" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E126" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F126" s="48" t="s">
         <v>494</v>
       </c>
-      <c r="D126" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E126" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F126" s="48" t="s">
+      <c r="G126" s="49" t="s">
         <v>495</v>
-      </c>
-      <c r="G126" s="49" t="s">
-        <v>496</v>
       </c>
       <c r="H126" s="48" t="s">
         <v>38</v>
       </c>
       <c r="I126" s="48" t="s">
+        <v>496</v>
+      </c>
+      <c r="J126" s="36" t="s">
         <v>497</v>
       </c>
-      <c r="J126" s="36" t="s">
-        <v>498</v>
-      </c>
       <c r="K126" s="48" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="L126" s="48" t="s">
         <v>22</v>
@@ -18702,7 +18743,7 @@
     </row>
     <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A127" s="48" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B127" s="48" t="s">
         <v>22</v>
@@ -18776,7 +18817,7 @@
     </row>
     <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A128" s="48" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B128" s="48" t="s">
         <v>22</v>
@@ -18850,13 +18891,13 @@
     </row>
     <row r="129" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A129" s="48" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B129" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C129" s="36" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D129" s="48" t="s">
         <v>22</v>
@@ -18868,19 +18909,19 @@
         <v>29</v>
       </c>
       <c r="G129" s="49" t="s">
+        <v>472</v>
+      </c>
+      <c r="H129" s="48" t="s">
         <v>473</v>
       </c>
-      <c r="H129" s="48" t="s">
+      <c r="I129" s="48" t="s">
         <v>474</v>
       </c>
-      <c r="I129" s="48" t="s">
-        <v>475</v>
-      </c>
       <c r="J129" s="36" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K129" s="48" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L129" s="48" t="s">
         <v>22</v>
@@ -18924,7 +18965,7 @@
     </row>
     <row r="130" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A130" s="48" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B130" s="48" t="s">
         <v>22</v>
@@ -18998,7 +19039,7 @@
     </row>
     <row r="131" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A131" s="48" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B131" s="48" t="s">
         <v>22</v>
@@ -19072,7 +19113,7 @@
     </row>
     <row r="132" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A132" s="48" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B132" s="48" t="s">
         <v>22</v>
@@ -19146,7 +19187,7 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A133" s="48" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B133" s="48" t="s">
         <v>22</v>
@@ -19206,13 +19247,13 @@
         <v>22</v>
       </c>
       <c r="U133" s="48" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="V133" s="48" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="W133" s="48" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="X133" s="48" t="s">
         <v>22</v>
@@ -19220,7 +19261,7 @@
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A134" s="48" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B134" s="48" t="s">
         <v>22</v>
@@ -19280,13 +19321,13 @@
         <v>22</v>
       </c>
       <c r="U134" s="48" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="V134" s="48" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="W134" s="48" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="X134" s="48" t="s">
         <v>22</v>
@@ -19294,7 +19335,7 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A135" s="48" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B135" s="48" t="s">
         <v>22</v>
@@ -19354,13 +19395,13 @@
         <v>22</v>
       </c>
       <c r="U135" s="48" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="V135" s="48" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="W135" s="48" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="X135" s="48" t="s">
         <v>22</v>
@@ -19368,7 +19409,7 @@
     </row>
     <row r="136" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A136" s="48" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B136" s="48" t="s">
         <v>22</v>
@@ -19428,13 +19469,13 @@
         <v>22</v>
       </c>
       <c r="U136" s="48" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="V136" s="48" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="W136" s="48" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="X136" s="48" t="s">
         <v>22</v>
@@ -19442,7 +19483,7 @@
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A137" s="48" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B137" s="48" t="s">
         <v>22</v>
@@ -19502,13 +19543,13 @@
         <v>22</v>
       </c>
       <c r="U137" s="48" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="V137" s="48" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="W137" s="48" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="X137" s="48" t="s">
         <v>22</v>
@@ -19516,7 +19557,7 @@
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A138" s="48" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B138" s="48" t="s">
         <v>22</v>
@@ -19590,7 +19631,7 @@
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A139" s="48" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B139" s="48" t="s">
         <v>22</v>
@@ -19664,7 +19705,7 @@
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A140" s="48" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B140" s="48" t="s">
         <v>22</v>
@@ -19738,7 +19779,7 @@
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A141" s="48" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B141" s="48" t="s">
         <v>22</v>
@@ -19798,13 +19839,13 @@
         <v>22</v>
       </c>
       <c r="U141" s="48" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="V141" s="48" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="W141" s="48" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="X141" s="48" t="s">
         <v>22</v>
@@ -19812,7 +19853,7 @@
     </row>
     <row r="142" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A142" s="48" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B142" s="48" t="s">
         <v>22</v>
@@ -19872,13 +19913,13 @@
         <v>22</v>
       </c>
       <c r="U142" s="48" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="V142" s="48" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="W142" s="48" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="X142" s="48" t="s">
         <v>22</v>
@@ -19886,7 +19927,7 @@
     </row>
     <row r="143" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A143" s="48" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B143" s="48" t="s">
         <v>22</v>
@@ -19946,13 +19987,13 @@
         <v>22</v>
       </c>
       <c r="U143" s="48" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="V143" s="48" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="W143" s="48" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="X143" s="48" t="s">
         <v>22</v>
@@ -19960,7 +20001,7 @@
     </row>
     <row r="144" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A144" s="48" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B144" s="48" t="s">
         <v>22</v>
@@ -20020,13 +20061,13 @@
         <v>22</v>
       </c>
       <c r="U144" s="48" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="V144" s="48" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="W144" s="48" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="X144" s="48" t="s">
         <v>22</v>
@@ -20034,7 +20075,7 @@
     </row>
     <row r="145" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A145" s="48" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B145" s="48" t="s">
         <v>22</v>
@@ -20094,13 +20135,13 @@
         <v>22</v>
       </c>
       <c r="U145" s="48" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="V145" s="48" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="W145" s="48" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="X145" s="48" t="s">
         <v>22</v>
@@ -20108,7 +20149,7 @@
     </row>
     <row r="146" spans="1:24" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A146" s="48" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B146" s="48" t="s">
         <v>22</v>
@@ -20168,13 +20209,13 @@
         <v>22</v>
       </c>
       <c r="U146" s="48" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="V146" s="48" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="W146" s="48" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="X146" s="48" t="s">
         <v>22</v>
@@ -20182,7 +20223,7 @@
     </row>
     <row r="147" spans="1:24" ht="53.4" x14ac:dyDescent="0.3">
       <c r="A147" s="48" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B147" s="48" t="s">
         <v>22</v>
@@ -20242,21 +20283,21 @@
         <v>22</v>
       </c>
       <c r="U147" s="48" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="V147" s="48" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="W147" s="48" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="X147" s="48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="148" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A148" s="48" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B148" s="48" t="s">
         <v>22</v>
@@ -20329,8 +20370,8 @@
       </c>
     </row>
     <row r="149" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="67" t="s">
-        <v>534</v>
+      <c r="A149" s="48" t="s">
+        <v>638</v>
       </c>
       <c r="B149" s="48" t="s">
         <v>22</v>
@@ -20403,8 +20444,8 @@
       </c>
     </row>
     <row r="150" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="70" t="s">
-        <v>538</v>
+      <c r="A150" s="67" t="s">
+        <v>533</v>
       </c>
       <c r="B150" s="48" t="s">
         <v>22</v>
@@ -20477,8 +20518,8 @@
       </c>
     </row>
     <row r="151" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="67" t="s">
-        <v>541</v>
+      <c r="A151" s="70" t="s">
+        <v>537</v>
       </c>
       <c r="B151" s="48" t="s">
         <v>22</v>
@@ -20551,8 +20592,8 @@
       </c>
     </row>
     <row r="152" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="70" t="s">
-        <v>544</v>
+      <c r="A152" s="67" t="s">
+        <v>540</v>
       </c>
       <c r="B152" s="48" t="s">
         <v>22</v>
@@ -20625,8 +20666,8 @@
       </c>
     </row>
     <row r="153" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="67" t="s">
-        <v>546</v>
+      <c r="A153" s="70" t="s">
+        <v>543</v>
       </c>
       <c r="B153" s="48" t="s">
         <v>22</v>
@@ -20699,8 +20740,8 @@
       </c>
     </row>
     <row r="154" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="70" t="s">
-        <v>548</v>
+      <c r="A154" s="67" t="s">
+        <v>545</v>
       </c>
       <c r="B154" s="48" t="s">
         <v>22</v>
@@ -20773,8 +20814,8 @@
       </c>
     </row>
     <row r="155" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="67" t="s">
-        <v>550</v>
+      <c r="A155" s="70" t="s">
+        <v>547</v>
       </c>
       <c r="B155" s="48" t="s">
         <v>22</v>
@@ -20847,8 +20888,8 @@
       </c>
     </row>
     <row r="156" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="70" t="s">
-        <v>552</v>
+      <c r="A156" s="67" t="s">
+        <v>549</v>
       </c>
       <c r="B156" s="48" t="s">
         <v>22</v>
@@ -20921,8 +20962,8 @@
       </c>
     </row>
     <row r="157" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="67" t="s">
-        <v>554</v>
+      <c r="A157" s="70" t="s">
+        <v>551</v>
       </c>
       <c r="B157" s="48" t="s">
         <v>22</v>
@@ -20995,8 +21036,8 @@
       </c>
     </row>
     <row r="158" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="70" t="s">
-        <v>557</v>
+      <c r="A158" s="67" t="s">
+        <v>553</v>
       </c>
       <c r="B158" s="48" t="s">
         <v>22</v>
@@ -21069,8 +21110,8 @@
       </c>
     </row>
     <row r="159" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="67" t="s">
-        <v>560</v>
+      <c r="A159" s="70" t="s">
+        <v>556</v>
       </c>
       <c r="B159" s="48" t="s">
         <v>22</v>
@@ -21143,8 +21184,8 @@
       </c>
     </row>
     <row r="160" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="70" t="s">
-        <v>563</v>
+      <c r="A160" s="67" t="s">
+        <v>559</v>
       </c>
       <c r="B160" s="48" t="s">
         <v>22</v>
@@ -21217,8 +21258,8 @@
       </c>
     </row>
     <row r="161" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="67" t="s">
-        <v>566</v>
+      <c r="A161" s="70" t="s">
+        <v>562</v>
       </c>
       <c r="B161" s="48" t="s">
         <v>22</v>
@@ -21291,8 +21332,8 @@
       </c>
     </row>
     <row r="162" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="70" t="s">
-        <v>569</v>
+      <c r="A162" s="67" t="s">
+        <v>565</v>
       </c>
       <c r="B162" s="48" t="s">
         <v>22</v>
@@ -21365,8 +21406,8 @@
       </c>
     </row>
     <row r="163" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="67" t="s">
-        <v>572</v>
+      <c r="A163" s="70" t="s">
+        <v>568</v>
       </c>
       <c r="B163" s="48" t="s">
         <v>22</v>
@@ -21440,7 +21481,7 @@
     </row>
     <row r="164" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="67" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B164" s="48" t="s">
         <v>22</v>
@@ -21514,7 +21555,7 @@
     </row>
     <row r="165" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="67" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B165" s="48" t="s">
         <v>22</v>
@@ -21586,405 +21627,405 @@
         <v>22</v>
       </c>
     </row>
-    <row r="166" spans="1:24" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="67" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X166" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="167" spans="1:24" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="67" t="s">
+        <v>578</v>
+      </c>
+      <c r="B167" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="C166" s="36" t="s">
+      <c r="C167" s="36" t="s">
+        <v>470</v>
+      </c>
+      <c r="D167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F167" s="48" t="s">
         <v>471</v>
       </c>
-      <c r="D166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F166" s="48" t="s">
+      <c r="G167" s="49" t="s">
         <v>472</v>
       </c>
-      <c r="G166" s="49" t="s">
+      <c r="H167" s="48" t="s">
         <v>473</v>
       </c>
-      <c r="H166" s="48" t="s">
-        <v>474</v>
-      </c>
-      <c r="I166" s="48" t="s">
+      <c r="I167" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="J167" s="36" t="s">
         <v>491</v>
       </c>
-      <c r="J166" s="36" t="s">
+      <c r="K167" s="48" t="s">
         <v>492</v>
       </c>
-      <c r="K166" s="48" t="s">
-        <v>493</v>
-      </c>
-      <c r="L166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X166" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="167" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="82"/>
-      <c r="B167" s="48"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="48"/>
-      <c r="E167" s="48"/>
-      <c r="F167" s="48"/>
-      <c r="G167" s="49"/>
-      <c r="H167" s="48"/>
-      <c r="I167" s="48"/>
-      <c r="J167" s="36"/>
-      <c r="K167" s="48"/>
-      <c r="L167" s="48"/>
-      <c r="M167" s="48"/>
-      <c r="N167" s="48"/>
-      <c r="O167" s="48"/>
-      <c r="P167" s="48"/>
-      <c r="Q167" s="48"/>
-      <c r="R167" s="48"/>
-      <c r="S167" s="48"/>
-      <c r="T167" s="48"/>
-      <c r="U167" s="48"/>
-      <c r="V167" s="48"/>
-      <c r="W167" s="48"/>
-      <c r="X167" s="48"/>
+      <c r="L167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X167" s="48" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="168" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="75" t="s">
-        <v>597</v>
-      </c>
-      <c r="B168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S168" s="49" t="s">
-        <v>599</v>
-      </c>
-      <c r="T168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V168" s="48" t="s">
-        <v>615</v>
-      </c>
-      <c r="W168" s="36" t="s">
-        <v>601</v>
-      </c>
-      <c r="X168" s="48" t="s">
-        <v>22</v>
-      </c>
+      <c r="A168" s="82"/>
+      <c r="B168" s="48"/>
+      <c r="C168" s="36"/>
+      <c r="D168" s="48"/>
+      <c r="E168" s="48"/>
+      <c r="F168" s="48"/>
+      <c r="G168" s="49"/>
+      <c r="H168" s="48"/>
+      <c r="I168" s="48"/>
+      <c r="J168" s="36"/>
+      <c r="K168" s="48"/>
+      <c r="L168" s="48"/>
+      <c r="M168" s="48"/>
+      <c r="N168" s="48"/>
+      <c r="O168" s="48"/>
+      <c r="P168" s="48"/>
+      <c r="Q168" s="48"/>
+      <c r="R168" s="48"/>
+      <c r="S168" s="48"/>
+      <c r="T168" s="48"/>
+      <c r="U168" s="48"/>
+      <c r="V168" s="48"/>
+      <c r="W168" s="48"/>
+      <c r="X168" s="48"/>
     </row>
     <row r="169" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="75" t="s">
+        <v>596</v>
+      </c>
+      <c r="B169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S169" s="49" t="s">
+        <v>598</v>
+      </c>
+      <c r="T169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V169" s="48" t="s">
+        <v>614</v>
+      </c>
+      <c r="W169" s="36" t="s">
+        <v>600</v>
+      </c>
+      <c r="X169" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="170" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="75" t="s">
+        <v>601</v>
+      </c>
+      <c r="B170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S170" s="49" t="s">
         <v>602</v>
       </c>
-      <c r="B169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S169" s="49" t="s">
-        <v>603</v>
-      </c>
-      <c r="T169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W169" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X169" s="78" t="s">
+      <c r="T170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W170" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X170" s="78" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="171" spans="1:24" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="75" t="s">
+        <v>606</v>
+      </c>
+      <c r="B171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S171" s="49" t="s">
+        <v>602</v>
+      </c>
+      <c r="T171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W171" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X171" s="84" t="s">
         <v>623</v>
-      </c>
-    </row>
-    <row r="170" spans="1:24" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="75" t="s">
-        <v>607</v>
-      </c>
-      <c r="B170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S170" s="49" t="s">
-        <v>603</v>
-      </c>
-      <c r="T170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W170" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X170" s="84" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="171" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="75" t="s">
-        <v>611</v>
-      </c>
-      <c r="B171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S171" s="49" t="s">
-        <v>599</v>
-      </c>
-      <c r="T171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V171" s="48" t="s">
-        <v>616</v>
-      </c>
-      <c r="W171" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X171" s="48" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="172" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="75" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="B172" s="48" t="s">
         <v>22</v>
@@ -22038,7 +22079,7 @@
         <v>22</v>
       </c>
       <c r="S172" s="49" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="T172" s="48" t="s">
         <v>22</v>
@@ -22047,7 +22088,7 @@
         <v>22</v>
       </c>
       <c r="V172" s="48" t="s">
-        <v>22</v>
+        <v>615</v>
       </c>
       <c r="W172" s="36" t="s">
         <v>22</v>
@@ -22058,7 +22099,7 @@
     </row>
     <row r="173" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="75" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B173" s="48" t="s">
         <v>22</v>
@@ -22112,7 +22153,7 @@
         <v>22</v>
       </c>
       <c r="S173" s="49" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="T173" s="48" t="s">
         <v>22</v>
@@ -22126,81 +22167,155 @@
       <c r="W173" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="X173" s="85" t="s">
-        <v>623</v>
+      <c r="X173" s="48" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="174" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="75" t="s">
+        <v>620</v>
+      </c>
+      <c r="B174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S174" s="49" t="s">
+        <v>602</v>
+      </c>
+      <c r="T174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W174" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X174" s="85" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="175" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="75" t="s">
+        <v>624</v>
+      </c>
+      <c r="B175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S175" s="49" t="s">
         <v>625</v>
       </c>
-      <c r="B174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S174" s="49" t="s">
-        <v>626</v>
-      </c>
-      <c r="T174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W174" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X174" s="48" t="s">
+      <c r="T175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W175" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X175" s="48" t="s">
         <v>22</v>
       </c>
     </row>
@@ -22327,13 +22442,13 @@
     <hyperlink ref="G121" r:id="rId14" xr:uid="{009DD950-489A-4511-9EE8-3302596C4B91}"/>
     <hyperlink ref="G126" r:id="rId15" xr:uid="{FEC9AB2B-6FD0-4D08-96BB-5634F117BFB0}"/>
     <hyperlink ref="D136" r:id="rId16" xr:uid="{EAE526E7-10C0-4EC9-846A-D81343ACBEC4}"/>
-    <hyperlink ref="G166" r:id="rId17" xr:uid="{0A52F660-ABF2-41CF-BD4C-5E55458D590D}"/>
-    <hyperlink ref="S168" r:id="rId18" xr:uid="{13FB8A07-5562-4AAB-9E83-934C01965617}"/>
-    <hyperlink ref="S170" r:id="rId19" xr:uid="{23F160B7-D3CD-415D-B0D6-1EECB7AFE96F}"/>
-    <hyperlink ref="S171" r:id="rId20" xr:uid="{7206C778-989C-4587-83FA-C09C20DA42BD}"/>
-    <hyperlink ref="S172" r:id="rId21" xr:uid="{3B0D666D-626C-490D-A9B6-B9643B9EDF8A}"/>
-    <hyperlink ref="X169" r:id="rId22" tooltip="pink real heaven" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{7AB2CC85-055B-4B62-B758-A407CA7BD409}"/>
-    <hyperlink ref="X173" r:id="rId23" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{E6426F17-2EE7-4F4A-80B0-E58B87C35EDA}"/>
+    <hyperlink ref="G167" r:id="rId17" xr:uid="{0A52F660-ABF2-41CF-BD4C-5E55458D590D}"/>
+    <hyperlink ref="S169" r:id="rId18" xr:uid="{13FB8A07-5562-4AAB-9E83-934C01965617}"/>
+    <hyperlink ref="S171" r:id="rId19" xr:uid="{23F160B7-D3CD-415D-B0D6-1EECB7AFE96F}"/>
+    <hyperlink ref="S172" r:id="rId20" xr:uid="{7206C778-989C-4587-83FA-C09C20DA42BD}"/>
+    <hyperlink ref="S173" r:id="rId21" xr:uid="{3B0D666D-626C-490D-A9B6-B9643B9EDF8A}"/>
+    <hyperlink ref="X170" r:id="rId22" tooltip="pink real heaven" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{7AB2CC85-055B-4B62-B758-A407CA7BD409}"/>
+    <hyperlink ref="X174" r:id="rId23" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{E6426F17-2EE7-4F4A-80B0-E58B87C35EDA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId24"/>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlataaProduction\ZlaataProduction\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\Zlaata1\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49427BA3-C5E2-4047-B033-04C16049078E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82FA3213-BC0C-48F1-8C05-CA8AB84D5C0A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5543" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5841" uniqueCount="667">
   <si>
     <t>S.No</t>
   </si>
@@ -1192,9 +1192,6 @@
     <t>TC_UI_Zlaata_FS_01</t>
   </si>
   <si>
-    <t>Verify that Shop All footer links are clickable.</t>
-  </si>
-  <si>
     <t>TD_UI_Zlaata_FS_01</t>
   </si>
   <si>
@@ -1222,21 +1219,9 @@
     <t>TD_UI_Zlaata_FS_07</t>
   </si>
   <si>
-    <t>Verify that the Zlaata email ID is displayed in the footer.</t>
-  </si>
-  <si>
     <t>TD_UI_Zlaata_FS_08</t>
   </si>
   <si>
-    <t>Verify that user can subscribe to the newsletter with a valid new email ID</t>
-  </si>
-  <si>
-    <t>Verify that user cannot subscribe to the newsletter using an already subscribed email ID</t>
-  </si>
-  <si>
-    <t>Verify that user cannot subscribe to the newsletter using an invalid email ID</t>
-  </si>
-  <si>
     <t>Address page</t>
   </si>
   <si>
@@ -1946,6 +1931,102 @@
   </si>
   <si>
     <t>Verify that the user is able to Mouse hover any all category in the "Shop" dropdown.</t>
+  </si>
+  <si>
+    <t>Verify that About Us Content details and URL are displayed in the footer.</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Link_01</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Link_01</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Verify that all application links and URLs are not broken.</t>
+  </si>
+  <si>
+    <t>Verify that Blogs Content details and URL are displayed in the footer.</t>
+  </si>
+  <si>
+    <t>Verify that Pop Shop Content details and URL are displayed in the footer.</t>
+  </si>
+  <si>
+    <t>Verify that Terms &amp; Conditions Content details and URL are displayed in the footer.</t>
+  </si>
+  <si>
+    <t>Verify that Privacy Policy Content details and URL are displayed in the footer.</t>
+  </si>
+  <si>
+    <t>Verify that Raise a query Content details and URL are displayed in the footer.</t>
+  </si>
+  <si>
+    <t>Verify that Faq Content details and URL are displayed in the footer.</t>
+  </si>
+  <si>
+    <t>Verify that Shipping &amp; Cancellation Policy Content details and URL are displayed in the footer.</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_FS_08</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_FS_09</t>
+  </si>
+  <si>
+    <t>Verify that Return, Exchange &amp; Replacement Policy Content details and URL are displayed in the footer.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_FS_09</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_FS_10</t>
+  </si>
+  <si>
+    <t>Verify that Contact Us Content details Time, Mobile, Email and Address are displayed in the footer.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_FS_10</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_FS_11</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_FS_11</t>
+  </si>
+  <si>
+    <t>Verify that Track Order are displayed in the footer.</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_FS_12</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_FS_12</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_FS_13</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_FS_13</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_FS_14</t>
+  </si>
+  <si>
+    <t>Verify that Copy Rights is displayed in the footer.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_FS_14</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_FS_15</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_FS_15</t>
+  </si>
+  <si>
+    <t>Verify that user can subscribe to the newsletter field.</t>
   </si>
 </sst>
 </file>
@@ -3447,7 +3528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z176"/>
+  <dimension ref="A1:Z186"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -3504,7 +3585,7 @@
         <v>15</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>14</v>
@@ -4222,7 +4303,7 @@
         <v>61</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="E25" s="22" t="s">
         <v>14</v>
@@ -4254,7 +4335,7 @@
         <v>156</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>14</v>
@@ -4620,7 +4701,7 @@
         <v>171</v>
       </c>
       <c r="D38" s="48" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="E38" s="47" t="s">
         <v>14</v>
@@ -4684,7 +4765,7 @@
         <v>177</v>
       </c>
       <c r="D40" s="48" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="E40" s="47" t="s">
         <v>14</v>
@@ -4780,7 +4861,7 @@
         <v>185</v>
       </c>
       <c r="D43" s="48" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="E43" s="47" t="s">
         <v>14</v>
@@ -5050,7 +5131,7 @@
         <v>220</v>
       </c>
       <c r="D52" s="48" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E52" s="48" t="s">
         <v>14</v>
@@ -5082,7 +5163,7 @@
         <v>222</v>
       </c>
       <c r="D53" s="48" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="E53" s="48" t="s">
         <v>14</v>
@@ -5114,7 +5195,7 @@
         <v>223</v>
       </c>
       <c r="D54" s="48" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="E54" s="48" t="s">
         <v>14</v>
@@ -5146,7 +5227,7 @@
         <v>224</v>
       </c>
       <c r="D55" s="48" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="E55" s="48" t="s">
         <v>14</v>
@@ -5178,7 +5259,7 @@
         <v>225</v>
       </c>
       <c r="D56" s="48" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E56" s="48" t="s">
         <v>14</v>
@@ -5750,7 +5831,7 @@
         <v>273</v>
       </c>
       <c r="D75" s="48" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="E75" s="48" t="s">
         <v>14</v>
@@ -5782,7 +5863,7 @@
         <v>276</v>
       </c>
       <c r="D76" s="48" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="E76" s="48" t="s">
         <v>14</v>
@@ -5814,7 +5895,7 @@
         <v>278</v>
       </c>
       <c r="D77" s="48" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="E77" s="48" t="s">
         <v>14</v>
@@ -5846,7 +5927,7 @@
         <v>280</v>
       </c>
       <c r="D78" s="48" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="E78" s="48" t="s">
         <v>14</v>
@@ -5878,7 +5959,7 @@
         <v>282</v>
       </c>
       <c r="D79" s="48" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="E79" s="48" t="s">
         <v>14</v>
@@ -6038,7 +6119,7 @@
         <v>296</v>
       </c>
       <c r="D84" s="48" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="E84" s="48" t="s">
         <v>14</v>
@@ -6070,7 +6151,7 @@
         <v>298</v>
       </c>
       <c r="D85" s="48" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="E85" s="48" t="s">
         <v>14</v>
@@ -6102,7 +6183,7 @@
         <v>300</v>
       </c>
       <c r="D86" s="48" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E86" s="48" t="s">
         <v>14</v>
@@ -6262,7 +6343,7 @@
         <v>314</v>
       </c>
       <c r="D91" s="48" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E91" s="48" t="s">
         <v>14</v>
@@ -6358,7 +6439,7 @@
         <v>322</v>
       </c>
       <c r="D94" s="48" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="E94" s="48" t="s">
         <v>14</v>
@@ -6390,7 +6471,7 @@
         <v>324</v>
       </c>
       <c r="D95" s="48" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E95" s="48" t="s">
         <v>14</v>
@@ -6422,7 +6503,7 @@
         <v>326</v>
       </c>
       <c r="D96" s="48" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="E96" s="48" t="s">
         <v>14</v>
@@ -6454,7 +6535,7 @@
         <v>328</v>
       </c>
       <c r="D97" s="48" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="E97" s="48" t="s">
         <v>14</v>
@@ -6486,7 +6567,7 @@
         <v>330</v>
       </c>
       <c r="D98" s="48" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="E98" s="48" t="s">
         <v>14</v>
@@ -6518,7 +6599,7 @@
         <v>332</v>
       </c>
       <c r="D99" s="48" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E99" s="48" t="s">
         <v>14</v>
@@ -6579,16 +6660,16 @@
         <v>10</v>
       </c>
       <c r="C101" s="48" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="D101" s="48" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="E101" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F101" s="48" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G101" s="48" t="s">
         <v>11</v>
@@ -6913,16 +6994,16 @@
         <v>10</v>
       </c>
       <c r="C112" s="48" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D112" s="48" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="E112" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F112" s="48" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="G112" s="48" t="s">
         <v>11</v>
@@ -7054,19 +7135,19 @@
         <v>387</v>
       </c>
       <c r="D118" s="51" t="s">
-        <v>388</v>
+        <v>635</v>
       </c>
       <c r="E118" s="51" t="s">
         <v>14</v>
       </c>
       <c r="F118" s="51" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G118" s="51" t="s">
         <v>11</v>
       </c>
       <c r="H118" s="51" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I118" s="51" t="s">
         <v>12</v>
@@ -7097,22 +7178,22 @@
         <v>10</v>
       </c>
       <c r="C119" s="48" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D119" s="63" t="s">
-        <v>527</v>
+        <v>640</v>
       </c>
       <c r="E119" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F119" s="48" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G119" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H119" s="48" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I119" s="48" t="s">
         <v>12</v>
@@ -7143,22 +7224,22 @@
         <v>10</v>
       </c>
       <c r="C120" s="48" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="D120" s="64" t="s">
-        <v>396</v>
+        <v>641</v>
       </c>
       <c r="E120" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F120" s="48" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G120" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H120" s="48" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I120" s="48" t="s">
         <v>12</v>
@@ -7189,22 +7270,22 @@
         <v>10</v>
       </c>
       <c r="C121" s="48" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="D121" s="64" t="s">
-        <v>398</v>
+        <v>642</v>
       </c>
       <c r="E121" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F121" s="48" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G121" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H121" s="48" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I121" s="48" t="s">
         <v>12</v>
@@ -7235,22 +7316,22 @@
         <v>10</v>
       </c>
       <c r="C122" s="48" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="D122" s="64" t="s">
-        <v>400</v>
+        <v>643</v>
       </c>
       <c r="E122" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F122" s="48" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G122" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H122" s="48" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I122" s="48" t="s">
         <v>12</v>
@@ -7281,22 +7362,22 @@
         <v>10</v>
       </c>
       <c r="C123" s="48" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="D123" s="64" t="s">
-        <v>401</v>
+        <v>644</v>
       </c>
       <c r="E123" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F123" s="48" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G123" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H123" s="48" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I123" s="48" t="s">
         <v>12</v>
@@ -7327,22 +7408,22 @@
         <v>10</v>
       </c>
       <c r="C124" s="48" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D124" s="64" t="s">
-        <v>402</v>
+        <v>645</v>
       </c>
       <c r="E124" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F124" s="48" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G124" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H124" s="48" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I124" s="48" t="s">
         <v>12</v>
@@ -7365,98 +7446,130 @@
       <c r="W124" s="58"/>
       <c r="X124" s="58"/>
     </row>
-    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="86" t="s">
-        <v>403</v>
-      </c>
-      <c r="B125" s="86"/>
-      <c r="C125" s="86"/>
-      <c r="D125" s="94"/>
-      <c r="E125" s="94"/>
-      <c r="F125" s="94"/>
-      <c r="G125" s="94"/>
-      <c r="H125" s="94"/>
-      <c r="I125" s="94"/>
-      <c r="J125" s="94"/>
+    <row r="125" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="25">
+        <v>8</v>
+      </c>
+      <c r="B125" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C125" s="48" t="s">
+        <v>647</v>
+      </c>
+      <c r="D125" s="63" t="s">
+        <v>646</v>
+      </c>
+      <c r="E125" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F125" s="48" t="s">
+        <v>397</v>
+      </c>
+      <c r="G125" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H125" s="48" t="s">
+        <v>389</v>
+      </c>
+      <c r="I125" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J125" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K125" s="57"/>
+      <c r="L125" s="58"/>
+      <c r="M125" s="58"/>
+      <c r="N125" s="58"/>
+      <c r="O125" s="58"/>
+      <c r="P125" s="58"/>
+      <c r="Q125" s="58"/>
+      <c r="R125" s="58"/>
+      <c r="S125" s="58"/>
+      <c r="T125" s="58"/>
+      <c r="U125" s="58"/>
+      <c r="V125" s="58"/>
+      <c r="W125" s="58"/>
+      <c r="X125" s="58"/>
     </row>
     <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="59">
+      <c r="A126" s="25">
+        <v>9</v>
+      </c>
+      <c r="B126" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C126" s="48" t="s">
+        <v>648</v>
+      </c>
+      <c r="D126" s="63" t="s">
+        <v>649</v>
+      </c>
+      <c r="E126" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F126" s="48" t="s">
+        <v>650</v>
+      </c>
+      <c r="G126" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B126" s="60" t="s">
+      <c r="H126" s="48" t="s">
+        <v>389</v>
+      </c>
+      <c r="I126" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J126" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K126" s="57"/>
+      <c r="L126" s="58"/>
+      <c r="M126" s="58"/>
+      <c r="N126" s="58"/>
+      <c r="O126" s="58"/>
+      <c r="P126" s="58"/>
+      <c r="Q126" s="58"/>
+      <c r="R126" s="58"/>
+      <c r="S126" s="58"/>
+      <c r="T126" s="58"/>
+      <c r="U126" s="58"/>
+      <c r="V126" s="58"/>
+      <c r="W126" s="58"/>
+      <c r="X126" s="58"/>
+    </row>
+    <row r="127" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="25">
         <v>10</v>
       </c>
-      <c r="C126" s="48" t="s">
-        <v>404</v>
-      </c>
-      <c r="D126" s="60" t="s">
-        <v>500</v>
-      </c>
-      <c r="E126" s="27" t="s">
+      <c r="B127" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C127" s="48" t="s">
+        <v>651</v>
+      </c>
+      <c r="D127" s="63" t="s">
+        <v>652</v>
+      </c>
+      <c r="E127" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F126" s="48" t="s">
-        <v>405</v>
-      </c>
-      <c r="G126" s="27" t="s">
+      <c r="F127" s="48" t="s">
+        <v>653</v>
+      </c>
+      <c r="G127" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H126" s="27" t="s">
-        <v>406</v>
-      </c>
-      <c r="I126" s="27" t="s">
+      <c r="H127" s="48" t="s">
+        <v>389</v>
+      </c>
+      <c r="I127" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J126" s="27" t="s">
+      <c r="J127" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="K126" s="61"/>
-      <c r="L126" s="61"/>
-      <c r="M126" s="61"/>
-      <c r="N126" s="61"/>
-      <c r="O126" s="61"/>
-      <c r="P126" s="61"/>
-      <c r="Q126" s="61"/>
-      <c r="R126" s="61"/>
-      <c r="S126" s="61"/>
-      <c r="T126" s="61"/>
-      <c r="U126" s="61"/>
-      <c r="V126" s="61"/>
-      <c r="W126" s="61"/>
-      <c r="X126" s="61"/>
-    </row>
-    <row r="127" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="26">
-        <v>2</v>
-      </c>
-      <c r="B127" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="C127" s="48" t="s">
-        <v>407</v>
-      </c>
-      <c r="D127" s="27" t="s">
-        <v>408</v>
-      </c>
-      <c r="E127" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="F127" s="48" t="s">
-        <v>409</v>
-      </c>
-      <c r="G127" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="H127" s="27" t="s">
-        <v>406</v>
-      </c>
-      <c r="I127" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="J127" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="K127" s="58"/>
+      <c r="K127" s="57"/>
       <c r="L127" s="58"/>
       <c r="M127" s="58"/>
       <c r="N127" s="58"/>
@@ -7471,38 +7584,38 @@
       <c r="W127" s="58"/>
       <c r="X127" s="58"/>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A128" s="26">
-        <v>3</v>
-      </c>
-      <c r="B128" s="27" t="s">
+    <row r="128" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="25">
+        <v>11</v>
+      </c>
+      <c r="B128" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C128" s="48" t="s">
-        <v>410</v>
-      </c>
-      <c r="D128" s="27" t="s">
-        <v>411</v>
-      </c>
-      <c r="E128" s="27" t="s">
+        <v>655</v>
+      </c>
+      <c r="D128" s="63" t="s">
+        <v>656</v>
+      </c>
+      <c r="E128" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F128" s="48" t="s">
-        <v>412</v>
-      </c>
-      <c r="G128" s="27" t="s">
+        <v>654</v>
+      </c>
+      <c r="G128" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H128" s="27" t="s">
-        <v>406</v>
-      </c>
-      <c r="I128" s="27" t="s">
+      <c r="H128" s="48" t="s">
+        <v>389</v>
+      </c>
+      <c r="I128" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J128" s="27" t="s">
+      <c r="J128" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="K128" s="58"/>
+      <c r="K128" s="57"/>
       <c r="L128" s="58"/>
       <c r="M128" s="58"/>
       <c r="N128" s="58"/>
@@ -7518,37 +7631,37 @@
       <c r="X128" s="58"/>
     </row>
     <row r="129" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="26">
-        <v>4</v>
-      </c>
-      <c r="B129" s="27" t="s">
+      <c r="A129" s="25">
+        <v>12</v>
+      </c>
+      <c r="B129" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C129" s="48" t="s">
-        <v>413</v>
-      </c>
-      <c r="D129" s="27" t="s">
-        <v>501</v>
-      </c>
-      <c r="E129" s="27" t="s">
+        <v>657</v>
+      </c>
+      <c r="D129" s="64" t="s">
+        <v>395</v>
+      </c>
+      <c r="E129" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F129" s="48" t="s">
-        <v>414</v>
-      </c>
-      <c r="G129" s="27" t="s">
+        <v>658</v>
+      </c>
+      <c r="G129" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H129" s="27" t="s">
-        <v>406</v>
-      </c>
-      <c r="I129" s="27" t="s">
+      <c r="H129" s="48" t="s">
+        <v>389</v>
+      </c>
+      <c r="I129" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J129" s="27" t="s">
+      <c r="J129" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="K129" s="58"/>
+      <c r="K129" s="57"/>
       <c r="L129" s="58"/>
       <c r="M129" s="58"/>
       <c r="N129" s="58"/>
@@ -7564,37 +7677,37 @@
       <c r="X129" s="58"/>
     </row>
     <row r="130" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="26">
-        <v>5</v>
-      </c>
-      <c r="B130" s="27" t="s">
+      <c r="A130" s="25">
+        <v>13</v>
+      </c>
+      <c r="B130" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C130" s="48" t="s">
-        <v>415</v>
-      </c>
-      <c r="D130" s="27" t="s">
-        <v>502</v>
-      </c>
-      <c r="E130" s="27" t="s">
+        <v>659</v>
+      </c>
+      <c r="D130" s="63" t="s">
+        <v>522</v>
+      </c>
+      <c r="E130" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F130" s="48" t="s">
-        <v>416</v>
-      </c>
-      <c r="G130" s="27" t="s">
+        <v>660</v>
+      </c>
+      <c r="G130" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H130" s="27" t="s">
-        <v>406</v>
-      </c>
-      <c r="I130" s="27" t="s">
+      <c r="H130" s="48" t="s">
+        <v>389</v>
+      </c>
+      <c r="I130" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J130" s="27" t="s">
+      <c r="J130" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="K130" s="58"/>
+      <c r="K130" s="57"/>
       <c r="L130" s="58"/>
       <c r="M130" s="58"/>
       <c r="N130" s="58"/>
@@ -7610,37 +7723,37 @@
       <c r="X130" s="58"/>
     </row>
     <row r="131" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="26">
-        <v>6</v>
-      </c>
-      <c r="B131" s="27" t="s">
+      <c r="A131" s="25">
+        <v>14</v>
+      </c>
+      <c r="B131" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C131" s="48" t="s">
-        <v>417</v>
-      </c>
-      <c r="D131" s="27" t="s">
-        <v>418</v>
-      </c>
-      <c r="E131" s="27" t="s">
+        <v>661</v>
+      </c>
+      <c r="D131" s="63" t="s">
+        <v>662</v>
+      </c>
+      <c r="E131" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F131" s="48" t="s">
-        <v>419</v>
-      </c>
-      <c r="G131" s="27" t="s">
+        <v>663</v>
+      </c>
+      <c r="G131" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H131" s="27" t="s">
-        <v>406</v>
-      </c>
-      <c r="I131" s="27" t="s">
+      <c r="H131" s="48" t="s">
+        <v>389</v>
+      </c>
+      <c r="I131" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J131" s="27" t="s">
+      <c r="J131" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="K131" s="58"/>
+      <c r="K131" s="57"/>
       <c r="L131" s="58"/>
       <c r="M131" s="58"/>
       <c r="N131" s="58"/>
@@ -7656,37 +7769,37 @@
       <c r="X131" s="58"/>
     </row>
     <row r="132" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="26">
-        <v>7</v>
-      </c>
-      <c r="B132" s="27" t="s">
+      <c r="A132" s="25">
+        <v>15</v>
+      </c>
+      <c r="B132" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C132" s="48" t="s">
-        <v>420</v>
-      </c>
-      <c r="D132" s="27" t="s">
-        <v>421</v>
-      </c>
-      <c r="E132" s="27" t="s">
+        <v>664</v>
+      </c>
+      <c r="D132" s="63" t="s">
+        <v>666</v>
+      </c>
+      <c r="E132" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F132" s="48" t="s">
-        <v>422</v>
-      </c>
-      <c r="G132" s="27" t="s">
+        <v>665</v>
+      </c>
+      <c r="G132" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H132" s="27" t="s">
-        <v>406</v>
-      </c>
-      <c r="I132" s="27" t="s">
+      <c r="H132" s="48" t="s">
+        <v>389</v>
+      </c>
+      <c r="I132" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J132" s="27" t="s">
+      <c r="J132" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="K132" s="58"/>
+      <c r="K132" s="57"/>
       <c r="L132" s="58"/>
       <c r="M132" s="58"/>
       <c r="N132" s="58"/>
@@ -7701,76 +7814,44 @@
       <c r="W132" s="58"/>
       <c r="X132" s="58"/>
     </row>
-    <row r="133" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="26">
-        <v>8</v>
-      </c>
-      <c r="B133" s="27" t="s">
+    <row r="133" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="86" t="s">
+        <v>398</v>
+      </c>
+      <c r="B133" s="86"/>
+      <c r="C133" s="86"/>
+      <c r="D133" s="94"/>
+      <c r="E133" s="94"/>
+      <c r="F133" s="94"/>
+      <c r="G133" s="94"/>
+      <c r="H133" s="94"/>
+      <c r="I133" s="94"/>
+      <c r="J133" s="94"/>
+    </row>
+    <row r="134" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="59">
+        <v>11</v>
+      </c>
+      <c r="B134" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="C133" s="48" t="s">
-        <v>423</v>
-      </c>
-      <c r="D133" s="27" t="s">
-        <v>424</v>
-      </c>
-      <c r="E133" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="F133" s="48" t="s">
-        <v>425</v>
-      </c>
-      <c r="G133" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="H133" s="27" t="s">
-        <v>406</v>
-      </c>
-      <c r="I133" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="J133" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="K133" s="58"/>
-      <c r="L133" s="58"/>
-      <c r="M133" s="58"/>
-      <c r="N133" s="58"/>
-      <c r="O133" s="58"/>
-      <c r="P133" s="58"/>
-      <c r="Q133" s="58"/>
-      <c r="R133" s="58"/>
-      <c r="S133" s="58"/>
-      <c r="T133" s="58"/>
-      <c r="U133" s="58"/>
-      <c r="V133" s="58"/>
-      <c r="W133" s="58"/>
-      <c r="X133" s="58"/>
-    </row>
-    <row r="134" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="26">
-        <v>9</v>
-      </c>
-      <c r="B134" s="27" t="s">
-        <v>10</v>
-      </c>
       <c r="C134" s="48" t="s">
-        <v>426</v>
-      </c>
-      <c r="D134" s="27" t="s">
-        <v>427</v>
+        <v>399</v>
+      </c>
+      <c r="D134" s="60" t="s">
+        <v>495</v>
       </c>
       <c r="E134" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F134" s="48" t="s">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="G134" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H134" s="27" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="I134" s="27" t="s">
         <v>12</v>
@@ -7778,48 +7859,48 @@
       <c r="J134" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="K134" s="58"/>
-      <c r="L134" s="58"/>
-      <c r="M134" s="58"/>
-      <c r="N134" s="58"/>
-      <c r="O134" s="58"/>
-      <c r="P134" s="58"/>
-      <c r="Q134" s="58"/>
-      <c r="R134" s="58"/>
-      <c r="S134" s="58"/>
-      <c r="T134" s="58"/>
-      <c r="U134" s="58"/>
-      <c r="V134" s="58"/>
-      <c r="W134" s="58"/>
-      <c r="X134" s="58"/>
+      <c r="K134" s="61"/>
+      <c r="L134" s="61"/>
+      <c r="M134" s="61"/>
+      <c r="N134" s="61"/>
+      <c r="O134" s="61"/>
+      <c r="P134" s="61"/>
+      <c r="Q134" s="61"/>
+      <c r="R134" s="61"/>
+      <c r="S134" s="61"/>
+      <c r="T134" s="61"/>
+      <c r="U134" s="61"/>
+      <c r="V134" s="61"/>
+      <c r="W134" s="61"/>
+      <c r="X134" s="61"/>
     </row>
     <row r="135" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="26">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B135" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C135" s="48" t="s">
-        <v>429</v>
+        <v>402</v>
       </c>
       <c r="D135" s="27" t="s">
-        <v>430</v>
+        <v>403</v>
       </c>
       <c r="E135" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F135" s="48" t="s">
-        <v>431</v>
+        <v>404</v>
       </c>
       <c r="G135" s="27" t="s">
         <v>11</v>
       </c>
       <c r="H135" s="27" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="I135" s="27" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J135" s="27" t="s">
         <v>13</v>
@@ -7839,49 +7920,81 @@
       <c r="W135" s="58"/>
       <c r="X135" s="58"/>
     </row>
-    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="95" t="s">
-        <v>432</v>
-      </c>
-      <c r="B136" s="96"/>
-      <c r="C136" s="96"/>
-      <c r="D136" s="96"/>
-      <c r="E136" s="96"/>
-      <c r="F136" s="96"/>
-      <c r="G136" s="96"/>
-      <c r="H136" s="96"/>
-      <c r="I136" s="96"/>
-      <c r="J136" s="97"/>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A136" s="26">
+        <v>3</v>
+      </c>
+      <c r="B136" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C136" s="48" t="s">
+        <v>405</v>
+      </c>
+      <c r="D136" s="27" t="s">
+        <v>406</v>
+      </c>
+      <c r="E136" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F136" s="48" t="s">
+        <v>407</v>
+      </c>
+      <c r="G136" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="H136" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="I136" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="J136" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="K136" s="58"/>
+      <c r="L136" s="58"/>
+      <c r="M136" s="58"/>
+      <c r="N136" s="58"/>
+      <c r="O136" s="58"/>
+      <c r="P136" s="58"/>
+      <c r="Q136" s="58"/>
+      <c r="R136" s="58"/>
+      <c r="S136" s="58"/>
+      <c r="T136" s="58"/>
+      <c r="U136" s="58"/>
+      <c r="V136" s="58"/>
+      <c r="W136" s="58"/>
+      <c r="X136" s="58"/>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="25">
-        <v>1</v>
-      </c>
-      <c r="B137" s="48" t="s">
+      <c r="A137" s="26">
+        <v>4</v>
+      </c>
+      <c r="B137" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C137" s="48" t="s">
-        <v>433</v>
-      </c>
-      <c r="D137" s="48" t="s">
-        <v>434</v>
-      </c>
-      <c r="E137" s="48" t="s">
+        <v>408</v>
+      </c>
+      <c r="D137" s="27" t="s">
+        <v>496</v>
+      </c>
+      <c r="E137" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F137" s="48" t="s">
-        <v>435</v>
-      </c>
-      <c r="G137" s="48" t="s">
+        <v>409</v>
+      </c>
+      <c r="G137" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="H137" s="48" t="s">
-        <v>436</v>
-      </c>
-      <c r="I137" s="48" t="s">
+      <c r="H137" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="I137" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="J137" s="48" t="s">
+      <c r="J137" s="27" t="s">
         <v>13</v>
       </c>
       <c r="K137" s="58"/>
@@ -7900,34 +8013,34 @@
       <c r="X137" s="58"/>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="25">
-        <v>2</v>
-      </c>
-      <c r="B138" s="48" t="s">
+      <c r="A138" s="26">
+        <v>5</v>
+      </c>
+      <c r="B138" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C138" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="D138" s="48" t="s">
-        <v>438</v>
-      </c>
-      <c r="E138" s="48" t="s">
+        <v>410</v>
+      </c>
+      <c r="D138" s="27" t="s">
+        <v>497</v>
+      </c>
+      <c r="E138" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F138" s="48" t="s">
-        <v>439</v>
-      </c>
-      <c r="G138" s="48" t="s">
+        <v>411</v>
+      </c>
+      <c r="G138" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="H138" s="48" t="s">
-        <v>436</v>
-      </c>
-      <c r="I138" s="48" t="s">
+      <c r="H138" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="I138" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="J138" s="48" t="s">
+      <c r="J138" s="27" t="s">
         <v>13</v>
       </c>
       <c r="K138" s="58"/>
@@ -7946,34 +8059,34 @@
       <c r="X138" s="58"/>
     </row>
     <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="25">
-        <v>3</v>
-      </c>
-      <c r="B139" s="48" t="s">
+      <c r="A139" s="26">
+        <v>6</v>
+      </c>
+      <c r="B139" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C139" s="48" t="s">
-        <v>440</v>
-      </c>
-      <c r="D139" s="48" t="s">
-        <v>441</v>
-      </c>
-      <c r="E139" s="48" t="s">
+        <v>412</v>
+      </c>
+      <c r="D139" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="E139" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F139" s="48" t="s">
-        <v>442</v>
-      </c>
-      <c r="G139" s="48" t="s">
+        <v>414</v>
+      </c>
+      <c r="G139" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="H139" s="48" t="s">
-        <v>436</v>
-      </c>
-      <c r="I139" s="48" t="s">
+      <c r="H139" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="I139" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="J139" s="48" t="s">
+      <c r="J139" s="27" t="s">
         <v>13</v>
       </c>
       <c r="K139" s="58"/>
@@ -7992,66 +8105,80 @@
       <c r="X139" s="58"/>
     </row>
     <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="25">
-        <v>4</v>
-      </c>
-      <c r="B140" s="48" t="s">
+      <c r="A140" s="26">
+        <v>7</v>
+      </c>
+      <c r="B140" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C140" s="48" t="s">
-        <v>443</v>
-      </c>
-      <c r="D140" s="48" t="s">
-        <v>463</v>
-      </c>
-      <c r="E140" s="48" t="s">
+        <v>415</v>
+      </c>
+      <c r="D140" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E140" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F140" s="48" t="s">
-        <v>444</v>
-      </c>
-      <c r="G140" s="48" t="s">
+        <v>417</v>
+      </c>
+      <c r="G140" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="H140" s="48" t="s">
-        <v>436</v>
-      </c>
-      <c r="I140" s="48" t="s">
+      <c r="H140" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="I140" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="J140" s="48" t="s">
+      <c r="J140" s="27" t="s">
         <v>13</v>
       </c>
+      <c r="K140" s="58"/>
+      <c r="L140" s="58"/>
+      <c r="M140" s="58"/>
+      <c r="N140" s="58"/>
+      <c r="O140" s="58"/>
+      <c r="P140" s="58"/>
+      <c r="Q140" s="58"/>
+      <c r="R140" s="58"/>
+      <c r="S140" s="58"/>
+      <c r="T140" s="58"/>
+      <c r="U140" s="58"/>
+      <c r="V140" s="58"/>
+      <c r="W140" s="58"/>
+      <c r="X140" s="58"/>
     </row>
     <row r="141" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="25">
-        <v>5</v>
-      </c>
-      <c r="B141" s="48" t="s">
+      <c r="A141" s="26">
+        <v>8</v>
+      </c>
+      <c r="B141" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C141" s="48" t="s">
-        <v>445</v>
-      </c>
-      <c r="D141" s="48" t="s">
-        <v>446</v>
-      </c>
-      <c r="E141" s="48" t="s">
+        <v>418</v>
+      </c>
+      <c r="D141" s="27" t="s">
+        <v>419</v>
+      </c>
+      <c r="E141" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F141" s="48" t="s">
-        <v>447</v>
-      </c>
-      <c r="G141" s="48" t="s">
+        <v>420</v>
+      </c>
+      <c r="G141" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="H141" s="48" t="s">
-        <v>436</v>
-      </c>
-      <c r="I141" s="48" t="s">
+      <c r="H141" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="I141" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="J141" s="48" t="s">
+      <c r="J141" s="27" t="s">
         <v>13</v>
       </c>
       <c r="K141" s="58"/>
@@ -8070,34 +8197,34 @@
       <c r="X141" s="58"/>
     </row>
     <row r="142" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="25">
-        <v>6</v>
-      </c>
-      <c r="B142" s="48" t="s">
+      <c r="A142" s="26">
+        <v>9</v>
+      </c>
+      <c r="B142" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C142" s="48" t="s">
-        <v>448</v>
-      </c>
-      <c r="D142" s="48" t="s">
-        <v>449</v>
-      </c>
-      <c r="E142" s="48" t="s">
+        <v>421</v>
+      </c>
+      <c r="D142" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="E142" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F142" s="48" t="s">
-        <v>450</v>
-      </c>
-      <c r="G142" s="48" t="s">
+        <v>423</v>
+      </c>
+      <c r="G142" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="H142" s="48" t="s">
-        <v>436</v>
-      </c>
-      <c r="I142" s="48" t="s">
+      <c r="H142" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="I142" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="J142" s="48" t="s">
+      <c r="J142" s="27" t="s">
         <v>13</v>
       </c>
       <c r="K142" s="58"/>
@@ -8116,34 +8243,34 @@
       <c r="X142" s="58"/>
     </row>
     <row r="143" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="25">
-        <v>7</v>
-      </c>
-      <c r="B143" s="48" t="s">
+      <c r="A143" s="26">
         <v>10</v>
       </c>
+      <c r="B143" s="27" t="s">
+        <v>10</v>
+      </c>
       <c r="C143" s="48" t="s">
-        <v>451</v>
-      </c>
-      <c r="D143" s="48" t="s">
-        <v>452</v>
-      </c>
-      <c r="E143" s="48" t="s">
+        <v>424</v>
+      </c>
+      <c r="D143" s="27" t="s">
+        <v>425</v>
+      </c>
+      <c r="E143" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F143" s="48" t="s">
-        <v>453</v>
-      </c>
-      <c r="G143" s="48" t="s">
+        <v>426</v>
+      </c>
+      <c r="G143" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="H143" s="48" t="s">
-        <v>436</v>
-      </c>
-      <c r="I143" s="48" t="s">
+      <c r="H143" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="I143" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="J143" s="48" t="s">
+      <c r="J143" s="27" t="s">
         <v>13</v>
       </c>
       <c r="K143" s="58"/>
@@ -8161,76 +8288,44 @@
       <c r="W143" s="58"/>
       <c r="X143" s="58"/>
     </row>
-    <row r="144" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="25">
-        <v>8</v>
-      </c>
-      <c r="B144" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="C144" s="48" t="s">
-        <v>454</v>
-      </c>
-      <c r="D144" s="48" t="s">
-        <v>455</v>
-      </c>
-      <c r="E144" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="F144" s="48" t="s">
-        <v>456</v>
-      </c>
-      <c r="G144" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="H144" s="48" t="s">
-        <v>436</v>
-      </c>
-      <c r="I144" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="J144" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="K144" s="58"/>
-      <c r="L144" s="58"/>
-      <c r="M144" s="58"/>
-      <c r="N144" s="58"/>
-      <c r="O144" s="58"/>
-      <c r="P144" s="58"/>
-      <c r="Q144" s="58"/>
-      <c r="R144" s="58"/>
-      <c r="S144" s="58"/>
-      <c r="T144" s="58"/>
-      <c r="U144" s="58"/>
-      <c r="V144" s="58"/>
-      <c r="W144" s="58"/>
-      <c r="X144" s="58"/>
+    <row r="144" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="95" t="s">
+        <v>427</v>
+      </c>
+      <c r="B144" s="96"/>
+      <c r="C144" s="96"/>
+      <c r="D144" s="96"/>
+      <c r="E144" s="96"/>
+      <c r="F144" s="96"/>
+      <c r="G144" s="96"/>
+      <c r="H144" s="96"/>
+      <c r="I144" s="96"/>
+      <c r="J144" s="97"/>
     </row>
     <row r="145" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="25">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B145" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C145" s="48" t="s">
-        <v>457</v>
+        <v>428</v>
       </c>
       <c r="D145" s="48" t="s">
-        <v>458</v>
+        <v>429</v>
       </c>
       <c r="E145" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F145" s="48" t="s">
-        <v>459</v>
+        <v>430</v>
       </c>
       <c r="G145" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H145" s="48" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="I145" s="48" t="s">
         <v>12</v>
@@ -8255,28 +8350,28 @@
     </row>
     <row r="146" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="25">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B146" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C146" s="48" t="s">
-        <v>460</v>
+        <v>432</v>
       </c>
       <c r="D146" s="48" t="s">
-        <v>461</v>
+        <v>433</v>
       </c>
       <c r="E146" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F146" s="48" t="s">
-        <v>462</v>
+        <v>434</v>
       </c>
       <c r="G146" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H146" s="48" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="I146" s="48" t="s">
         <v>12</v>
@@ -8299,44 +8394,76 @@
       <c r="W146" s="58"/>
       <c r="X146" s="58"/>
     </row>
-    <row r="147" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A147" s="86" t="s">
-        <v>504</v>
-      </c>
-      <c r="B147" s="86"/>
-      <c r="C147" s="86"/>
-      <c r="D147" s="86"/>
-      <c r="E147" s="86"/>
-      <c r="F147" s="86"/>
-      <c r="G147" s="86"/>
-      <c r="H147" s="86"/>
-      <c r="I147" s="86"/>
-      <c r="J147" s="86"/>
-    </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="25">
+        <v>3</v>
+      </c>
+      <c r="B147" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" s="48" t="s">
+        <v>435</v>
+      </c>
+      <c r="D147" s="48" t="s">
+        <v>436</v>
+      </c>
+      <c r="E147" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F147" s="48" t="s">
+        <v>437</v>
+      </c>
+      <c r="G147" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H147" s="48" t="s">
+        <v>431</v>
+      </c>
+      <c r="I147" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J147" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K147" s="58"/>
+      <c r="L147" s="58"/>
+      <c r="M147" s="58"/>
+      <c r="N147" s="58"/>
+      <c r="O147" s="58"/>
+      <c r="P147" s="58"/>
+      <c r="Q147" s="58"/>
+      <c r="R147" s="58"/>
+      <c r="S147" s="58"/>
+      <c r="T147" s="58"/>
+      <c r="U147" s="58"/>
+      <c r="V147" s="58"/>
+      <c r="W147" s="58"/>
+      <c r="X147" s="58"/>
+    </row>
+    <row r="148" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B148" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C148" s="48" t="s">
-        <v>505</v>
-      </c>
-      <c r="D148" s="24" t="s">
-        <v>506</v>
+        <v>438</v>
+      </c>
+      <c r="D148" s="48" t="s">
+        <v>458</v>
       </c>
       <c r="E148" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F148" s="48" t="s">
-        <v>503</v>
+        <v>439</v>
       </c>
       <c r="G148" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H148" s="48" t="s">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="I148" s="48" t="s">
         <v>12</v>
@@ -8345,30 +8472,30 @@
         <v>13</v>
       </c>
     </row>
-    <row r="149" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B149" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C149" s="48" t="s">
-        <v>636</v>
-      </c>
-      <c r="D149" s="24" t="s">
-        <v>637</v>
+        <v>440</v>
+      </c>
+      <c r="D149" s="48" t="s">
+        <v>441</v>
       </c>
       <c r="E149" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F149" s="48" t="s">
-        <v>638</v>
+        <v>442</v>
       </c>
       <c r="G149" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H149" s="48" t="s">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="I149" s="48" t="s">
         <v>12</v>
@@ -8376,50 +8503,96 @@
       <c r="J149" s="48" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="150" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="86" t="s">
-        <v>530</v>
-      </c>
-      <c r="B150" s="86"/>
-      <c r="C150" s="86"/>
-      <c r="D150" s="86"/>
-      <c r="E150" s="86"/>
-      <c r="F150" s="86"/>
-      <c r="G150" s="86"/>
-      <c r="H150" s="86"/>
-      <c r="I150" s="86"/>
-      <c r="J150" s="86"/>
+      <c r="K149" s="58"/>
+      <c r="L149" s="58"/>
+      <c r="M149" s="58"/>
+      <c r="N149" s="58"/>
+      <c r="O149" s="58"/>
+      <c r="P149" s="58"/>
+      <c r="Q149" s="58"/>
+      <c r="R149" s="58"/>
+      <c r="S149" s="58"/>
+      <c r="T149" s="58"/>
+      <c r="U149" s="58"/>
+      <c r="V149" s="58"/>
+      <c r="W149" s="58"/>
+      <c r="X149" s="58"/>
+    </row>
+    <row r="150" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="25">
+        <v>6</v>
+      </c>
+      <c r="B150" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150" s="48" t="s">
+        <v>443</v>
+      </c>
+      <c r="D150" s="48" t="s">
+        <v>444</v>
+      </c>
+      <c r="E150" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F150" s="48" t="s">
+        <v>445</v>
+      </c>
+      <c r="G150" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H150" s="48" t="s">
+        <v>431</v>
+      </c>
+      <c r="I150" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J150" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K150" s="58"/>
+      <c r="L150" s="58"/>
+      <c r="M150" s="58"/>
+      <c r="N150" s="58"/>
+      <c r="O150" s="58"/>
+      <c r="P150" s="58"/>
+      <c r="Q150" s="58"/>
+      <c r="R150" s="58"/>
+      <c r="S150" s="58"/>
+      <c r="T150" s="58"/>
+      <c r="U150" s="58"/>
+      <c r="V150" s="58"/>
+      <c r="W150" s="58"/>
+      <c r="X150" s="58"/>
     </row>
     <row r="151" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="65">
-        <v>1</v>
-      </c>
-      <c r="B151" s="66" t="s">
+      <c r="A151" s="25">
+        <v>7</v>
+      </c>
+      <c r="B151" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="C151" s="67" t="s">
-        <v>531</v>
-      </c>
-      <c r="D151" s="66" t="s">
-        <v>532</v>
-      </c>
-      <c r="E151" s="66" t="s">
+      <c r="C151" s="48" t="s">
+        <v>446</v>
+      </c>
+      <c r="D151" s="48" t="s">
+        <v>447</v>
+      </c>
+      <c r="E151" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F151" s="67" t="s">
-        <v>533</v>
-      </c>
-      <c r="G151" s="66" t="s">
+      <c r="F151" s="48" t="s">
+        <v>448</v>
+      </c>
+      <c r="G151" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H151" s="66" t="s">
-        <v>534</v>
-      </c>
-      <c r="I151" s="66" t="s">
+      <c r="H151" s="48" t="s">
+        <v>431</v>
+      </c>
+      <c r="I151" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J151" s="66" t="s">
+      <c r="J151" s="48" t="s">
         <v>13</v>
       </c>
       <c r="K151" s="58"/>
@@ -8436,38 +8609,36 @@
       <c r="V151" s="58"/>
       <c r="W151" s="58"/>
       <c r="X151" s="58"/>
-      <c r="Y151" s="58"/>
-      <c r="Z151" s="58"/>
     </row>
     <row r="152" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="68">
-        <v>2</v>
-      </c>
-      <c r="B152" s="69" t="s">
+      <c r="A152" s="25">
+        <v>8</v>
+      </c>
+      <c r="B152" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="C152" s="70" t="s">
-        <v>535</v>
-      </c>
-      <c r="D152" s="69" t="s">
-        <v>536</v>
-      </c>
-      <c r="E152" s="69" t="s">
+      <c r="C152" s="48" t="s">
+        <v>449</v>
+      </c>
+      <c r="D152" s="48" t="s">
+        <v>450</v>
+      </c>
+      <c r="E152" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F152" s="70" t="s">
-        <v>537</v>
-      </c>
-      <c r="G152" s="69" t="s">
+      <c r="F152" s="48" t="s">
+        <v>451</v>
+      </c>
+      <c r="G152" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H152" s="69" t="s">
-        <v>534</v>
-      </c>
-      <c r="I152" s="69" t="s">
+      <c r="H152" s="48" t="s">
+        <v>431</v>
+      </c>
+      <c r="I152" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J152" s="69" t="s">
+      <c r="J152" s="48" t="s">
         <v>13</v>
       </c>
       <c r="K152" s="58"/>
@@ -8484,38 +8655,36 @@
       <c r="V152" s="58"/>
       <c r="W152" s="58"/>
       <c r="X152" s="58"/>
-      <c r="Y152" s="58"/>
-      <c r="Z152" s="58"/>
     </row>
     <row r="153" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="68">
-        <v>3</v>
-      </c>
-      <c r="B153" s="69" t="s">
+      <c r="A153" s="25">
+        <v>9</v>
+      </c>
+      <c r="B153" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="C153" s="70" t="s">
-        <v>538</v>
-      </c>
-      <c r="D153" s="71" t="s">
-        <v>539</v>
-      </c>
-      <c r="E153" s="69" t="s">
+      <c r="C153" s="48" t="s">
+        <v>452</v>
+      </c>
+      <c r="D153" s="48" t="s">
+        <v>453</v>
+      </c>
+      <c r="E153" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F153" s="70" t="s">
-        <v>540</v>
-      </c>
-      <c r="G153" s="69" t="s">
+      <c r="F153" s="48" t="s">
+        <v>454</v>
+      </c>
+      <c r="G153" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H153" s="69" t="s">
-        <v>534</v>
-      </c>
-      <c r="I153" s="69" t="s">
+      <c r="H153" s="48" t="s">
+        <v>431</v>
+      </c>
+      <c r="I153" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J153" s="69" t="s">
+      <c r="J153" s="48" t="s">
         <v>13</v>
       </c>
       <c r="K153" s="58"/>
@@ -8532,38 +8701,36 @@
       <c r="V153" s="58"/>
       <c r="W153" s="58"/>
       <c r="X153" s="58"/>
-      <c r="Y153" s="58"/>
-      <c r="Z153" s="58"/>
     </row>
     <row r="154" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="68">
-        <v>4</v>
-      </c>
-      <c r="B154" s="69" t="s">
+      <c r="A154" s="25">
         <v>10</v>
       </c>
-      <c r="C154" s="70" t="s">
-        <v>541</v>
-      </c>
-      <c r="D154" s="69" t="s">
-        <v>542</v>
-      </c>
-      <c r="E154" s="69" t="s">
+      <c r="B154" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C154" s="48" t="s">
+        <v>455</v>
+      </c>
+      <c r="D154" s="48" t="s">
+        <v>456</v>
+      </c>
+      <c r="E154" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F154" s="70" t="s">
-        <v>543</v>
-      </c>
-      <c r="G154" s="69" t="s">
+      <c r="F154" s="48" t="s">
+        <v>457</v>
+      </c>
+      <c r="G154" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H154" s="69" t="s">
-        <v>534</v>
-      </c>
-      <c r="I154" s="69" t="s">
+      <c r="H154" s="48" t="s">
+        <v>431</v>
+      </c>
+      <c r="I154" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J154" s="69" t="s">
+      <c r="J154" s="48" t="s">
         <v>13</v>
       </c>
       <c r="K154" s="58"/>
@@ -8580,230 +8747,128 @@
       <c r="V154" s="58"/>
       <c r="W154" s="58"/>
       <c r="X154" s="58"/>
-      <c r="Y154" s="58"/>
-      <c r="Z154" s="58"/>
-    </row>
-    <row r="155" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="68">
-        <v>5</v>
-      </c>
-      <c r="B155" s="69" t="s">
+    </row>
+    <row r="155" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A155" s="86" t="s">
+        <v>499</v>
+      </c>
+      <c r="B155" s="86"/>
+      <c r="C155" s="86"/>
+      <c r="D155" s="86"/>
+      <c r="E155" s="86"/>
+      <c r="F155" s="86"/>
+      <c r="G155" s="86"/>
+      <c r="H155" s="86"/>
+      <c r="I155" s="86"/>
+      <c r="J155" s="86"/>
+    </row>
+    <row r="156" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A156" s="25">
+        <v>1</v>
+      </c>
+      <c r="B156" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="C155" s="70" t="s">
-        <v>544</v>
-      </c>
-      <c r="D155" s="69" t="s">
-        <v>582</v>
-      </c>
-      <c r="E155" s="69" t="s">
+      <c r="C156" s="48" t="s">
+        <v>500</v>
+      </c>
+      <c r="D156" s="24" t="s">
+        <v>501</v>
+      </c>
+      <c r="E156" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F155" s="70" t="s">
-        <v>545</v>
-      </c>
-      <c r="G155" s="69" t="s">
+      <c r="F156" s="48" t="s">
+        <v>498</v>
+      </c>
+      <c r="G156" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H155" s="69" t="s">
-        <v>534</v>
-      </c>
-      <c r="I155" s="69" t="s">
+      <c r="H156" s="48" t="s">
+        <v>371</v>
+      </c>
+      <c r="I156" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J155" s="69" t="s">
+      <c r="J156" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="K155" s="58"/>
-      <c r="L155" s="58"/>
-      <c r="M155" s="58"/>
-      <c r="N155" s="58"/>
-      <c r="O155" s="58"/>
-      <c r="P155" s="58"/>
-      <c r="Q155" s="58"/>
-      <c r="R155" s="58"/>
-      <c r="S155" s="58"/>
-      <c r="T155" s="58"/>
-      <c r="U155" s="58"/>
-      <c r="V155" s="58"/>
-      <c r="W155" s="58"/>
-      <c r="X155" s="58"/>
-      <c r="Y155" s="58"/>
-      <c r="Z155" s="58"/>
-    </row>
-    <row r="156" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="68">
-        <v>6</v>
-      </c>
-      <c r="B156" s="69" t="s">
+    </row>
+    <row r="157" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A157" s="25">
+        <v>2</v>
+      </c>
+      <c r="B157" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="C156" s="70" t="s">
-        <v>546</v>
-      </c>
-      <c r="D156" s="71" t="s">
-        <v>583</v>
-      </c>
-      <c r="E156" s="69" t="s">
+      <c r="C157" s="48" t="s">
+        <v>631</v>
+      </c>
+      <c r="D157" s="24" t="s">
+        <v>632</v>
+      </c>
+      <c r="E157" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F156" s="70" t="s">
-        <v>547</v>
-      </c>
-      <c r="G156" s="69" t="s">
+      <c r="F157" s="48" t="s">
+        <v>633</v>
+      </c>
+      <c r="G157" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H156" s="69" t="s">
-        <v>534</v>
-      </c>
-      <c r="I156" s="69" t="s">
+      <c r="H157" s="48" t="s">
+        <v>371</v>
+      </c>
+      <c r="I157" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J156" s="69" t="s">
+      <c r="J157" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="K156" s="58"/>
-      <c r="L156" s="58"/>
-      <c r="M156" s="58"/>
-      <c r="N156" s="58"/>
-      <c r="O156" s="58"/>
-      <c r="P156" s="58"/>
-      <c r="Q156" s="58"/>
-      <c r="R156" s="58"/>
-      <c r="S156" s="58"/>
-      <c r="T156" s="58"/>
-      <c r="U156" s="58"/>
-      <c r="V156" s="58"/>
-      <c r="W156" s="58"/>
-      <c r="X156" s="58"/>
-      <c r="Y156" s="58"/>
-      <c r="Z156" s="58"/>
-    </row>
-    <row r="157" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="68">
-        <v>7</v>
-      </c>
-      <c r="B157" s="69" t="s">
+    </row>
+    <row r="158" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="86" t="s">
+        <v>525</v>
+      </c>
+      <c r="B158" s="86"/>
+      <c r="C158" s="86"/>
+      <c r="D158" s="86"/>
+      <c r="E158" s="86"/>
+      <c r="F158" s="86"/>
+      <c r="G158" s="86"/>
+      <c r="H158" s="86"/>
+      <c r="I158" s="86"/>
+      <c r="J158" s="86"/>
+    </row>
+    <row r="159" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="65">
+        <v>1</v>
+      </c>
+      <c r="B159" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="C157" s="70" t="s">
-        <v>548</v>
-      </c>
-      <c r="D157" s="69" t="s">
-        <v>584</v>
-      </c>
-      <c r="E157" s="69" t="s">
+      <c r="C159" s="67" t="s">
+        <v>526</v>
+      </c>
+      <c r="D159" s="66" t="s">
+        <v>527</v>
+      </c>
+      <c r="E159" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F157" s="70" t="s">
-        <v>549</v>
-      </c>
-      <c r="G157" s="69" t="s">
+      <c r="F159" s="67" t="s">
+        <v>528</v>
+      </c>
+      <c r="G159" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="H157" s="69" t="s">
-        <v>534</v>
-      </c>
-      <c r="I157" s="69" t="s">
+      <c r="H159" s="66" t="s">
+        <v>529</v>
+      </c>
+      <c r="I159" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="J157" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="K157" s="58"/>
-      <c r="L157" s="58"/>
-      <c r="M157" s="58"/>
-      <c r="N157" s="58"/>
-      <c r="O157" s="58"/>
-      <c r="P157" s="58"/>
-      <c r="Q157" s="58"/>
-      <c r="R157" s="58"/>
-      <c r="S157" s="58"/>
-      <c r="T157" s="58"/>
-      <c r="U157" s="58"/>
-      <c r="V157" s="58"/>
-      <c r="W157" s="58"/>
-      <c r="X157" s="58"/>
-      <c r="Y157" s="58"/>
-      <c r="Z157" s="58"/>
-    </row>
-    <row r="158" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="68">
-        <v>8</v>
-      </c>
-      <c r="B158" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="C158" s="70" t="s">
-        <v>550</v>
-      </c>
-      <c r="D158" s="69" t="s">
-        <v>585</v>
-      </c>
-      <c r="E158" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="F158" s="70" t="s">
-        <v>551</v>
-      </c>
-      <c r="G158" s="69" t="s">
-        <v>11</v>
-      </c>
-      <c r="H158" s="69" t="s">
-        <v>534</v>
-      </c>
-      <c r="I158" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="J158" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="K158" s="58"/>
-      <c r="L158" s="58"/>
-      <c r="M158" s="58"/>
-      <c r="N158" s="58"/>
-      <c r="O158" s="58"/>
-      <c r="P158" s="58"/>
-      <c r="Q158" s="58"/>
-      <c r="R158" s="58"/>
-      <c r="S158" s="58"/>
-      <c r="T158" s="58"/>
-      <c r="U158" s="58"/>
-      <c r="V158" s="58"/>
-      <c r="W158" s="58"/>
-      <c r="X158" s="58"/>
-      <c r="Y158" s="58"/>
-      <c r="Z158" s="58"/>
-    </row>
-    <row r="159" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="72">
-        <v>9</v>
-      </c>
-      <c r="B159" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="C159" s="75" t="s">
-        <v>552</v>
-      </c>
-      <c r="D159" s="74" t="s">
-        <v>555</v>
-      </c>
-      <c r="E159" s="74" t="s">
-        <v>14</v>
-      </c>
-      <c r="F159" s="75" t="s">
-        <v>553</v>
-      </c>
-      <c r="G159" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="H159" s="74" t="s">
-        <v>534</v>
-      </c>
-      <c r="I159" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="J159" s="74" t="s">
+      <c r="J159" s="66" t="s">
         <v>13</v>
       </c>
       <c r="K159" s="58"/>
@@ -8824,34 +8889,34 @@
       <c r="Z159" s="58"/>
     </row>
     <row r="160" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="73">
+      <c r="A160" s="68">
+        <v>2</v>
+      </c>
+      <c r="B160" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="B160" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="C160" s="75" t="s">
-        <v>554</v>
-      </c>
-      <c r="D160" s="74" t="s">
-        <v>558</v>
-      </c>
-      <c r="E160" s="74" t="s">
+      <c r="C160" s="70" t="s">
+        <v>530</v>
+      </c>
+      <c r="D160" s="69" t="s">
+        <v>531</v>
+      </c>
+      <c r="E160" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="F160" s="75" t="s">
-        <v>556</v>
-      </c>
-      <c r="G160" s="74" t="s">
+      <c r="F160" s="70" t="s">
+        <v>532</v>
+      </c>
+      <c r="G160" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="H160" s="74" t="s">
-        <v>534</v>
-      </c>
-      <c r="I160" s="74" t="s">
+      <c r="H160" s="69" t="s">
+        <v>529</v>
+      </c>
+      <c r="I160" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="J160" s="74" t="s">
+      <c r="J160" s="69" t="s">
         <v>13</v>
       </c>
       <c r="K160" s="58"/>
@@ -8872,34 +8937,34 @@
       <c r="Z160" s="58"/>
     </row>
     <row r="161" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="72">
+      <c r="A161" s="68">
+        <v>3</v>
+      </c>
+      <c r="B161" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C161" s="70" t="s">
+        <v>533</v>
+      </c>
+      <c r="D161" s="71" t="s">
+        <v>534</v>
+      </c>
+      <c r="E161" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F161" s="70" t="s">
+        <v>535</v>
+      </c>
+      <c r="G161" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="B161" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="C161" s="75" t="s">
-        <v>557</v>
-      </c>
-      <c r="D161" s="74" t="s">
-        <v>561</v>
-      </c>
-      <c r="E161" s="74" t="s">
-        <v>14</v>
-      </c>
-      <c r="F161" s="75" t="s">
-        <v>559</v>
-      </c>
-      <c r="G161" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="H161" s="74" t="s">
-        <v>534</v>
-      </c>
-      <c r="I161" s="74" t="s">
+      <c r="H161" s="69" t="s">
+        <v>529</v>
+      </c>
+      <c r="I161" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="J161" s="74" t="s">
+      <c r="J161" s="69" t="s">
         <v>13</v>
       </c>
       <c r="K161" s="58"/>
@@ -8920,34 +8985,34 @@
       <c r="Z161" s="58"/>
     </row>
     <row r="162" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="73">
+      <c r="A162" s="68">
+        <v>4</v>
+      </c>
+      <c r="B162" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C162" s="70" t="s">
+        <v>536</v>
+      </c>
+      <c r="D162" s="69" t="s">
+        <v>537</v>
+      </c>
+      <c r="E162" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F162" s="70" t="s">
+        <v>538</v>
+      </c>
+      <c r="G162" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="H162" s="69" t="s">
+        <v>529</v>
+      </c>
+      <c r="I162" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="B162" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="C162" s="75" t="s">
-        <v>560</v>
-      </c>
-      <c r="D162" s="74" t="s">
-        <v>564</v>
-      </c>
-      <c r="E162" s="74" t="s">
-        <v>14</v>
-      </c>
-      <c r="F162" s="75" t="s">
-        <v>562</v>
-      </c>
-      <c r="G162" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="H162" s="74" t="s">
-        <v>534</v>
-      </c>
-      <c r="I162" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="J162" s="74" t="s">
+      <c r="J162" s="69" t="s">
         <v>13</v>
       </c>
       <c r="K162" s="58"/>
@@ -8968,34 +9033,34 @@
       <c r="Z162" s="58"/>
     </row>
     <row r="163" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="72">
-        <v>13</v>
-      </c>
-      <c r="B163" s="74" t="s">
+      <c r="A163" s="68">
+        <v>5</v>
+      </c>
+      <c r="B163" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="C163" s="75" t="s">
-        <v>563</v>
-      </c>
-      <c r="D163" s="74" t="s">
-        <v>567</v>
-      </c>
-      <c r="E163" s="74" t="s">
+      <c r="C163" s="70" t="s">
+        <v>539</v>
+      </c>
+      <c r="D163" s="69" t="s">
+        <v>577</v>
+      </c>
+      <c r="E163" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="F163" s="75" t="s">
-        <v>565</v>
-      </c>
-      <c r="G163" s="74" t="s">
+      <c r="F163" s="70" t="s">
+        <v>540</v>
+      </c>
+      <c r="G163" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="H163" s="74" t="s">
-        <v>534</v>
-      </c>
-      <c r="I163" s="74" t="s">
+      <c r="H163" s="69" t="s">
+        <v>529</v>
+      </c>
+      <c r="I163" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="J163" s="74" t="s">
+      <c r="J163" s="69" t="s">
         <v>13</v>
       </c>
       <c r="K163" s="58"/>
@@ -9016,34 +9081,34 @@
       <c r="Z163" s="58"/>
     </row>
     <row r="164" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="73">
+      <c r="A164" s="68">
+        <v>6</v>
+      </c>
+      <c r="B164" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C164" s="70" t="s">
+        <v>541</v>
+      </c>
+      <c r="D164" s="71" t="s">
+        <v>578</v>
+      </c>
+      <c r="E164" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B164" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="C164" s="75" t="s">
-        <v>566</v>
-      </c>
-      <c r="D164" s="76" t="s">
-        <v>570</v>
-      </c>
-      <c r="E164" s="74" t="s">
-        <v>14</v>
-      </c>
-      <c r="F164" s="75" t="s">
-        <v>568</v>
-      </c>
-      <c r="G164" s="74" t="s">
+      <c r="F164" s="70" t="s">
+        <v>542</v>
+      </c>
+      <c r="G164" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="H164" s="74" t="s">
-        <v>534</v>
-      </c>
-      <c r="I164" s="74" t="s">
+      <c r="H164" s="69" t="s">
+        <v>529</v>
+      </c>
+      <c r="I164" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="J164" s="74" t="s">
+      <c r="J164" s="69" t="s">
         <v>13</v>
       </c>
       <c r="K164" s="58"/>
@@ -9064,34 +9129,34 @@
       <c r="Z164" s="58"/>
     </row>
     <row r="165" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="72">
-        <v>15</v>
-      </c>
-      <c r="B165" s="74" t="s">
+      <c r="A165" s="68">
+        <v>7</v>
+      </c>
+      <c r="B165" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="C165" s="75" t="s">
-        <v>569</v>
-      </c>
-      <c r="D165" s="76" t="s">
-        <v>586</v>
-      </c>
-      <c r="E165" s="74" t="s">
+      <c r="C165" s="70" t="s">
+        <v>543</v>
+      </c>
+      <c r="D165" s="69" t="s">
+        <v>579</v>
+      </c>
+      <c r="E165" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="F165" s="75" t="s">
-        <v>571</v>
-      </c>
-      <c r="G165" s="74" t="s">
+      <c r="F165" s="70" t="s">
+        <v>544</v>
+      </c>
+      <c r="G165" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="H165" s="74" t="s">
-        <v>534</v>
-      </c>
-      <c r="I165" s="74" t="s">
+      <c r="H165" s="69" t="s">
+        <v>529</v>
+      </c>
+      <c r="I165" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="J165" s="74" t="s">
+      <c r="J165" s="69" t="s">
         <v>13</v>
       </c>
       <c r="K165" s="58"/>
@@ -9112,34 +9177,34 @@
       <c r="Z165" s="58"/>
     </row>
     <row r="166" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="73">
-        <v>16</v>
-      </c>
-      <c r="B166" s="74" t="s">
+      <c r="A166" s="68">
+        <v>8</v>
+      </c>
+      <c r="B166" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="C166" s="75" t="s">
-        <v>572</v>
-      </c>
-      <c r="D166" s="76" t="s">
-        <v>577</v>
-      </c>
-      <c r="E166" s="74" t="s">
+      <c r="C166" s="70" t="s">
+        <v>545</v>
+      </c>
+      <c r="D166" s="69" t="s">
+        <v>580</v>
+      </c>
+      <c r="E166" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="F166" s="75" t="s">
-        <v>573</v>
-      </c>
-      <c r="G166" s="74" t="s">
+      <c r="F166" s="70" t="s">
+        <v>546</v>
+      </c>
+      <c r="G166" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="H166" s="74" t="s">
-        <v>534</v>
-      </c>
-      <c r="I166" s="74" t="s">
+      <c r="H166" s="69" t="s">
+        <v>529</v>
+      </c>
+      <c r="I166" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="J166" s="74" t="s">
+      <c r="J166" s="69" t="s">
         <v>13</v>
       </c>
       <c r="K166" s="58"/>
@@ -9161,28 +9226,28 @@
     </row>
     <row r="167" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="72">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B167" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C167" s="75" t="s">
-        <v>574</v>
-      </c>
-      <c r="D167" s="76" t="s">
-        <v>579</v>
+        <v>547</v>
+      </c>
+      <c r="D167" s="74" t="s">
+        <v>550</v>
       </c>
       <c r="E167" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F167" s="75" t="s">
-        <v>575</v>
+        <v>548</v>
       </c>
       <c r="G167" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H167" s="74" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="I167" s="74" t="s">
         <v>12</v>
@@ -9209,28 +9274,28 @@
     </row>
     <row r="168" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="73">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B168" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C168" s="75" t="s">
-        <v>576</v>
-      </c>
-      <c r="D168" s="77" t="s">
-        <v>580</v>
+        <v>549</v>
+      </c>
+      <c r="D168" s="74" t="s">
+        <v>553</v>
       </c>
       <c r="E168" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F168" s="75" t="s">
-        <v>578</v>
+        <v>551</v>
       </c>
       <c r="G168" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H168" s="74" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="I168" s="74" t="s">
         <v>12</v>
@@ -9256,43 +9321,77 @@
       <c r="Z168" s="58"/>
     </row>
     <row r="169" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="86" t="s">
-        <v>609</v>
-      </c>
-      <c r="B169" s="86"/>
-      <c r="C169" s="86"/>
-      <c r="D169" s="86"/>
-      <c r="E169" s="86"/>
-      <c r="F169" s="86"/>
-      <c r="G169" s="86"/>
-      <c r="H169" s="86"/>
-      <c r="I169" s="86"/>
-      <c r="J169" s="86"/>
+      <c r="A169" s="72">
+        <v>11</v>
+      </c>
+      <c r="B169" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C169" s="75" t="s">
+        <v>552</v>
+      </c>
+      <c r="D169" s="74" t="s">
+        <v>556</v>
+      </c>
+      <c r="E169" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F169" s="75" t="s">
+        <v>554</v>
+      </c>
+      <c r="G169" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H169" s="74" t="s">
+        <v>529</v>
+      </c>
+      <c r="I169" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J169" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="K169" s="58"/>
+      <c r="L169" s="58"/>
+      <c r="M169" s="58"/>
+      <c r="N169" s="58"/>
+      <c r="O169" s="58"/>
+      <c r="P169" s="58"/>
+      <c r="Q169" s="58"/>
+      <c r="R169" s="58"/>
+      <c r="S169" s="58"/>
+      <c r="T169" s="58"/>
+      <c r="U169" s="58"/>
+      <c r="V169" s="58"/>
+      <c r="W169" s="58"/>
+      <c r="X169" s="58"/>
+      <c r="Y169" s="58"/>
+      <c r="Z169" s="58"/>
     </row>
     <row r="170" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="73">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B170" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C170" s="75" t="s">
-        <v>595</v>
-      </c>
-      <c r="D170" s="77" t="s">
-        <v>597</v>
+        <v>555</v>
+      </c>
+      <c r="D170" s="74" t="s">
+        <v>559</v>
       </c>
       <c r="E170" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F170" s="75" t="s">
-        <v>596</v>
+        <v>557</v>
       </c>
       <c r="G170" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H170" s="74" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="I170" s="74" t="s">
         <v>12</v>
@@ -9300,31 +9399,47 @@
       <c r="J170" s="74" t="s">
         <v>13</v>
       </c>
+      <c r="K170" s="58"/>
+      <c r="L170" s="58"/>
+      <c r="M170" s="58"/>
+      <c r="N170" s="58"/>
+      <c r="O170" s="58"/>
+      <c r="P170" s="58"/>
+      <c r="Q170" s="58"/>
+      <c r="R170" s="58"/>
+      <c r="S170" s="58"/>
+      <c r="T170" s="58"/>
+      <c r="U170" s="58"/>
+      <c r="V170" s="58"/>
+      <c r="W170" s="58"/>
+      <c r="X170" s="58"/>
+      <c r="Y170" s="58"/>
+      <c r="Z170" s="58"/>
     </row>
     <row r="171" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="73">
-        <v>2</v>
+      <c r="A171" s="72">
+        <v>13</v>
       </c>
       <c r="B171" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C171" s="75" t="s">
-        <v>603</v>
-      </c>
-      <c r="D171" s="77" t="s">
-        <v>604</v>
+        <v>558</v>
+      </c>
+      <c r="D171" s="74" t="s">
+        <v>562</v>
       </c>
       <c r="E171" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F171" s="75" t="s">
-        <v>601</v>
+        <v>560</v>
       </c>
       <c r="G171" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H171" s="74" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="I171" s="74" t="s">
         <v>12</v>
@@ -9332,31 +9447,47 @@
       <c r="J171" s="74" t="s">
         <v>13</v>
       </c>
+      <c r="K171" s="58"/>
+      <c r="L171" s="58"/>
+      <c r="M171" s="58"/>
+      <c r="N171" s="58"/>
+      <c r="O171" s="58"/>
+      <c r="P171" s="58"/>
+      <c r="Q171" s="58"/>
+      <c r="R171" s="58"/>
+      <c r="S171" s="58"/>
+      <c r="T171" s="58"/>
+      <c r="U171" s="58"/>
+      <c r="V171" s="58"/>
+      <c r="W171" s="58"/>
+      <c r="X171" s="58"/>
+      <c r="Y171" s="58"/>
+      <c r="Z171" s="58"/>
     </row>
     <row r="172" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="73">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B172" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C172" s="75" t="s">
-        <v>607</v>
-      </c>
-      <c r="D172" s="81" t="s">
-        <v>608</v>
+        <v>561</v>
+      </c>
+      <c r="D172" s="76" t="s">
+        <v>565</v>
       </c>
       <c r="E172" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F172" s="75" t="s">
-        <v>606</v>
+        <v>563</v>
       </c>
       <c r="G172" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H172" s="74" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="I172" s="74" t="s">
         <v>12</v>
@@ -9364,31 +9495,47 @@
       <c r="J172" s="74" t="s">
         <v>13</v>
       </c>
+      <c r="K172" s="58"/>
+      <c r="L172" s="58"/>
+      <c r="M172" s="58"/>
+      <c r="N172" s="58"/>
+      <c r="O172" s="58"/>
+      <c r="P172" s="58"/>
+      <c r="Q172" s="58"/>
+      <c r="R172" s="58"/>
+      <c r="S172" s="58"/>
+      <c r="T172" s="58"/>
+      <c r="U172" s="58"/>
+      <c r="V172" s="58"/>
+      <c r="W172" s="58"/>
+      <c r="X172" s="58"/>
+      <c r="Y172" s="58"/>
+      <c r="Z172" s="58"/>
     </row>
     <row r="173" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A173" s="73">
-        <v>4</v>
+      <c r="A173" s="72">
+        <v>15</v>
       </c>
       <c r="B173" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="C173" s="79" t="s">
-        <v>611</v>
-      </c>
-      <c r="D173" s="64" t="s">
-        <v>612</v>
-      </c>
-      <c r="E173" s="80" t="s">
+      <c r="C173" s="75" t="s">
+        <v>564</v>
+      </c>
+      <c r="D173" s="76" t="s">
+        <v>581</v>
+      </c>
+      <c r="E173" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F173" s="75" t="s">
-        <v>610</v>
+        <v>566</v>
       </c>
       <c r="G173" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H173" s="74" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="I173" s="74" t="s">
         <v>12</v>
@@ -9396,31 +9543,47 @@
       <c r="J173" s="74" t="s">
         <v>13</v>
       </c>
+      <c r="K173" s="58"/>
+      <c r="L173" s="58"/>
+      <c r="M173" s="58"/>
+      <c r="N173" s="58"/>
+      <c r="O173" s="58"/>
+      <c r="P173" s="58"/>
+      <c r="Q173" s="58"/>
+      <c r="R173" s="58"/>
+      <c r="S173" s="58"/>
+      <c r="T173" s="58"/>
+      <c r="U173" s="58"/>
+      <c r="V173" s="58"/>
+      <c r="W173" s="58"/>
+      <c r="X173" s="58"/>
+      <c r="Y173" s="58"/>
+      <c r="Z173" s="58"/>
     </row>
     <row r="174" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="73">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B174" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="C174" s="79" t="s">
-        <v>617</v>
-      </c>
-      <c r="D174" s="83" t="s">
-        <v>618</v>
-      </c>
-      <c r="E174" s="80" t="s">
+      <c r="C174" s="75" t="s">
+        <v>567</v>
+      </c>
+      <c r="D174" s="76" t="s">
+        <v>572</v>
+      </c>
+      <c r="E174" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F174" s="75" t="s">
-        <v>616</v>
+        <v>568</v>
       </c>
       <c r="G174" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H174" s="74" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="I174" s="74" t="s">
         <v>12</v>
@@ -9428,31 +9591,47 @@
       <c r="J174" s="74" t="s">
         <v>13</v>
       </c>
+      <c r="K174" s="58"/>
+      <c r="L174" s="58"/>
+      <c r="M174" s="58"/>
+      <c r="N174" s="58"/>
+      <c r="O174" s="58"/>
+      <c r="P174" s="58"/>
+      <c r="Q174" s="58"/>
+      <c r="R174" s="58"/>
+      <c r="S174" s="58"/>
+      <c r="T174" s="58"/>
+      <c r="U174" s="58"/>
+      <c r="V174" s="58"/>
+      <c r="W174" s="58"/>
+      <c r="X174" s="58"/>
+      <c r="Y174" s="58"/>
+      <c r="Z174" s="58"/>
     </row>
     <row r="175" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A175" s="73">
-        <v>6</v>
+      <c r="A175" s="72">
+        <v>17</v>
       </c>
       <c r="B175" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C175" s="75" t="s">
-        <v>619</v>
-      </c>
-      <c r="D175" s="77" t="s">
-        <v>621</v>
+        <v>569</v>
+      </c>
+      <c r="D175" s="76" t="s">
+        <v>574</v>
       </c>
       <c r="E175" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F175" s="75" t="s">
-        <v>620</v>
+        <v>570</v>
       </c>
       <c r="G175" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H175" s="74" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="I175" s="74" t="s">
         <v>12</v>
@@ -9460,31 +9639,47 @@
       <c r="J175" s="74" t="s">
         <v>13</v>
       </c>
+      <c r="K175" s="58"/>
+      <c r="L175" s="58"/>
+      <c r="M175" s="58"/>
+      <c r="N175" s="58"/>
+      <c r="O175" s="58"/>
+      <c r="P175" s="58"/>
+      <c r="Q175" s="58"/>
+      <c r="R175" s="58"/>
+      <c r="S175" s="58"/>
+      <c r="T175" s="58"/>
+      <c r="U175" s="58"/>
+      <c r="V175" s="58"/>
+      <c r="W175" s="58"/>
+      <c r="X175" s="58"/>
+      <c r="Y175" s="58"/>
+      <c r="Z175" s="58"/>
     </row>
     <row r="176" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="73">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B176" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C176" s="75" t="s">
-        <v>627</v>
-      </c>
-      <c r="D176" s="83" t="s">
-        <v>626</v>
+        <v>571</v>
+      </c>
+      <c r="D176" s="77" t="s">
+        <v>575</v>
       </c>
       <c r="E176" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F176" s="75" t="s">
-        <v>624</v>
+        <v>573</v>
       </c>
       <c r="G176" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H176" s="74" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="I176" s="74" t="s">
         <v>12</v>
@@ -9492,14 +9687,315 @@
       <c r="J176" s="74" t="s">
         <v>13</v>
       </c>
+      <c r="K176" s="58"/>
+      <c r="L176" s="58"/>
+      <c r="M176" s="58"/>
+      <c r="N176" s="58"/>
+      <c r="O176" s="58"/>
+      <c r="P176" s="58"/>
+      <c r="Q176" s="58"/>
+      <c r="R176" s="58"/>
+      <c r="S176" s="58"/>
+      <c r="T176" s="58"/>
+      <c r="U176" s="58"/>
+      <c r="V176" s="58"/>
+      <c r="W176" s="58"/>
+      <c r="X176" s="58"/>
+      <c r="Y176" s="58"/>
+      <c r="Z176" s="58"/>
+    </row>
+    <row r="177" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="86" t="s">
+        <v>604</v>
+      </c>
+      <c r="B177" s="86"/>
+      <c r="C177" s="86"/>
+      <c r="D177" s="86"/>
+      <c r="E177" s="86"/>
+      <c r="F177" s="86"/>
+      <c r="G177" s="86"/>
+      <c r="H177" s="86"/>
+      <c r="I177" s="86"/>
+      <c r="J177" s="86"/>
+    </row>
+    <row r="178" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A178" s="73">
+        <v>1</v>
+      </c>
+      <c r="B178" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C178" s="75" t="s">
+        <v>590</v>
+      </c>
+      <c r="D178" s="77" t="s">
+        <v>592</v>
+      </c>
+      <c r="E178" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F178" s="75" t="s">
+        <v>591</v>
+      </c>
+      <c r="G178" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H178" s="74" t="s">
+        <v>529</v>
+      </c>
+      <c r="I178" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J178" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A179" s="73">
+        <v>2</v>
+      </c>
+      <c r="B179" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C179" s="75" t="s">
+        <v>598</v>
+      </c>
+      <c r="D179" s="77" t="s">
+        <v>599</v>
+      </c>
+      <c r="E179" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F179" s="75" t="s">
+        <v>596</v>
+      </c>
+      <c r="G179" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H179" s="74" t="s">
+        <v>529</v>
+      </c>
+      <c r="I179" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J179" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="73">
+        <v>3</v>
+      </c>
+      <c r="B180" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C180" s="75" t="s">
+        <v>602</v>
+      </c>
+      <c r="D180" s="81" t="s">
+        <v>603</v>
+      </c>
+      <c r="E180" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F180" s="75" t="s">
+        <v>601</v>
+      </c>
+      <c r="G180" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H180" s="74" t="s">
+        <v>529</v>
+      </c>
+      <c r="I180" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J180" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A181" s="73">
+        <v>4</v>
+      </c>
+      <c r="B181" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C181" s="79" t="s">
+        <v>606</v>
+      </c>
+      <c r="D181" s="64" t="s">
+        <v>607</v>
+      </c>
+      <c r="E181" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="F181" s="75" t="s">
+        <v>605</v>
+      </c>
+      <c r="G181" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H181" s="74" t="s">
+        <v>529</v>
+      </c>
+      <c r="I181" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J181" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A182" s="73">
+        <v>5</v>
+      </c>
+      <c r="B182" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C182" s="79" t="s">
+        <v>612</v>
+      </c>
+      <c r="D182" s="83" t="s">
+        <v>613</v>
+      </c>
+      <c r="E182" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="F182" s="75" t="s">
+        <v>611</v>
+      </c>
+      <c r="G182" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H182" s="74" t="s">
+        <v>529</v>
+      </c>
+      <c r="I182" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J182" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A183" s="73">
+        <v>6</v>
+      </c>
+      <c r="B183" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C183" s="75" t="s">
+        <v>614</v>
+      </c>
+      <c r="D183" s="77" t="s">
+        <v>616</v>
+      </c>
+      <c r="E183" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F183" s="75" t="s">
+        <v>615</v>
+      </c>
+      <c r="G183" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H183" s="74" t="s">
+        <v>529</v>
+      </c>
+      <c r="I183" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J183" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="73">
+        <v>7</v>
+      </c>
+      <c r="B184" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C184" s="75" t="s">
+        <v>622</v>
+      </c>
+      <c r="D184" s="83" t="s">
+        <v>621</v>
+      </c>
+      <c r="E184" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F184" s="75" t="s">
+        <v>619</v>
+      </c>
+      <c r="G184" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H184" s="74" t="s">
+        <v>529</v>
+      </c>
+      <c r="I184" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J184" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A185" s="86" t="s">
+        <v>604</v>
+      </c>
+      <c r="B185" s="86"/>
+      <c r="C185" s="86"/>
+      <c r="D185" s="86"/>
+      <c r="E185" s="86"/>
+      <c r="F185" s="86"/>
+      <c r="G185" s="86"/>
+      <c r="H185" s="86"/>
+      <c r="I185" s="86"/>
+      <c r="J185" s="86"/>
+    </row>
+    <row r="186" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A186" s="73">
+        <v>1</v>
+      </c>
+      <c r="B186" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C186" s="75" t="s">
+        <v>636</v>
+      </c>
+      <c r="D186" s="77" t="s">
+        <v>639</v>
+      </c>
+      <c r="E186" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F186" s="75" t="s">
+        <v>637</v>
+      </c>
+      <c r="G186" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H186" s="74" t="s">
+        <v>638</v>
+      </c>
+      <c r="I186" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J186" s="74" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A169:J169"/>
-    <mergeCell ref="A150:J150"/>
-    <mergeCell ref="A147:J147"/>
-    <mergeCell ref="A125:J125"/>
-    <mergeCell ref="A136:J136"/>
+  <mergeCells count="15">
+    <mergeCell ref="A185:J185"/>
+    <mergeCell ref="A177:J177"/>
+    <mergeCell ref="A158:J158"/>
+    <mergeCell ref="A155:J155"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="A144:J144"/>
     <mergeCell ref="A117:J117"/>
     <mergeCell ref="A115:J115"/>
     <mergeCell ref="A113:J113"/>
@@ -9606,7 +10102,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:X175"/>
+  <dimension ref="A1:X184"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -9691,16 +10187,16 @@
         <v>337</v>
       </c>
       <c r="U1" s="31" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="V1" s="31" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="W1" s="31" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="X1" s="31" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -10761,7 +11257,7 @@
         <v>29</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>22</v>
@@ -11111,7 +11607,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="D22" s="39" t="s">
         <v>95</v>
@@ -16745,7 +17241,7 @@
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A100" s="48" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="B100" s="51" t="s">
         <v>22</v>
@@ -17485,7 +17981,7 @@
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A110" s="48" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B110" s="48" t="s">
         <v>22</v>
@@ -17707,7 +18203,7 @@
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113" s="48" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B113" s="48" t="s">
         <v>22</v>
@@ -17781,7 +18277,7 @@
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="48" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B114" s="48" t="s">
         <v>22</v>
@@ -17855,7 +18351,7 @@
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A115" s="48" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B115" s="48" t="s">
         <v>22</v>
@@ -17929,7 +18425,7 @@
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" s="48" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B116" s="48" t="s">
         <v>22</v>
@@ -18003,7 +18499,7 @@
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A117" s="48" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B117" s="48" t="s">
         <v>22</v>
@@ -18077,7 +18573,7 @@
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118" s="48" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B118" s="48" t="s">
         <v>22</v>
@@ -18151,7 +18647,7 @@
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A119" s="48" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B119" s="48" t="s">
         <v>22</v>
@@ -18225,7 +18721,7 @@
     </row>
     <row r="120" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A120" s="48" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B120" s="48" t="s">
         <v>22</v>
@@ -18299,13 +18795,13 @@
     </row>
     <row r="121" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A121" s="62" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B121" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C121" s="36" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D121" s="48" t="s">
         <v>22</v>
@@ -18314,22 +18810,22 @@
         <v>22</v>
       </c>
       <c r="F121" s="48" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="G121" s="49" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="H121" s="48" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="I121" s="48" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="J121" s="36" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="K121" s="48" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="L121" s="48" t="s">
         <v>22</v>
@@ -18373,7 +18869,7 @@
     </row>
     <row r="122" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A122" s="48" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B122" s="48" t="s">
         <v>22</v>
@@ -18447,13 +18943,13 @@
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A123" s="48" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B123" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C123" s="36" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D123" s="48" t="s">
         <v>22</v>
@@ -18462,22 +18958,22 @@
         <v>22</v>
       </c>
       <c r="F123" s="48" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="G123" s="49" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="H123" s="48" t="s">
         <v>37</v>
       </c>
       <c r="I123" s="48" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="J123" s="36" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="K123" s="48" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="L123" s="48" t="s">
         <v>22</v>
@@ -18521,13 +19017,13 @@
     </row>
     <row r="124" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A124" s="48" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B124" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C124" s="36" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="D124" s="48" t="s">
         <v>22</v>
@@ -18536,22 +19032,22 @@
         <v>22</v>
       </c>
       <c r="F124" s="48" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="G124" s="49" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="H124" s="48" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="I124" s="48" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="J124" s="36" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="K124" s="48" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="L124" s="48" t="s">
         <v>22</v>
@@ -18595,13 +19091,13 @@
     </row>
     <row r="125" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A125" s="48" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B125" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C125" s="36" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D125" s="48" t="s">
         <v>22</v>
@@ -18613,19 +19109,19 @@
         <v>29</v>
       </c>
       <c r="G125" s="49" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="H125" s="48" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="I125" s="48" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="J125" s="36" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="K125" s="48" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="L125" s="48" t="s">
         <v>22</v>
@@ -18669,13 +19165,13 @@
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A126" s="48" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B126" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C126" s="36" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="D126" s="48" t="s">
         <v>22</v>
@@ -18684,22 +19180,22 @@
         <v>22</v>
       </c>
       <c r="F126" s="48" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="G126" s="49" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="H126" s="48" t="s">
         <v>38</v>
       </c>
       <c r="I126" s="48" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="J126" s="36" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="K126" s="48" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="L126" s="48" t="s">
         <v>22</v>
@@ -18743,7 +19239,7 @@
     </row>
     <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A127" s="48" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B127" s="48" t="s">
         <v>22</v>
@@ -18817,7 +19313,7 @@
     </row>
     <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A128" s="48" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B128" s="48" t="s">
         <v>22</v>
@@ -18891,13 +19387,13 @@
     </row>
     <row r="129" spans="1:24" ht="27" x14ac:dyDescent="0.3">
       <c r="A129" s="48" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B129" s="48" t="s">
         <v>22</v>
       </c>
       <c r="C129" s="36" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D129" s="48" t="s">
         <v>22</v>
@@ -18909,19 +19405,19 @@
         <v>29</v>
       </c>
       <c r="G129" s="49" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="H129" s="48" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="I129" s="48" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="J129" s="36" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="K129" s="48" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="L129" s="48" t="s">
         <v>22</v>
@@ -18965,7 +19461,7 @@
     </row>
     <row r="130" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A130" s="48" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B130" s="48" t="s">
         <v>22</v>
@@ -19039,7 +19535,7 @@
     </row>
     <row r="131" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A131" s="48" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B131" s="48" t="s">
         <v>22</v>
@@ -19113,7 +19609,7 @@
     </row>
     <row r="132" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A132" s="48" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B132" s="48" t="s">
         <v>22</v>
@@ -19187,7 +19683,7 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A133" s="48" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B133" s="48" t="s">
         <v>22</v>
@@ -19247,13 +19743,13 @@
         <v>22</v>
       </c>
       <c r="U133" s="48" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="V133" s="48" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="W133" s="48" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="X133" s="48" t="s">
         <v>22</v>
@@ -19261,7 +19757,7 @@
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A134" s="48" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B134" s="48" t="s">
         <v>22</v>
@@ -19321,13 +19817,13 @@
         <v>22</v>
       </c>
       <c r="U134" s="48" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="V134" s="48" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="W134" s="48" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="X134" s="48" t="s">
         <v>22</v>
@@ -19335,7 +19831,7 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A135" s="48" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B135" s="48" t="s">
         <v>22</v>
@@ -19395,13 +19891,13 @@
         <v>22</v>
       </c>
       <c r="U135" s="48" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="V135" s="48" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="W135" s="48" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="X135" s="48" t="s">
         <v>22</v>
@@ -19409,7 +19905,7 @@
     </row>
     <row r="136" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A136" s="48" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B136" s="48" t="s">
         <v>22</v>
@@ -19469,13 +19965,13 @@
         <v>22</v>
       </c>
       <c r="U136" s="48" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="V136" s="48" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="W136" s="48" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="X136" s="48" t="s">
         <v>22</v>
@@ -19483,7 +19979,7 @@
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A137" s="48" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B137" s="48" t="s">
         <v>22</v>
@@ -19543,13 +20039,13 @@
         <v>22</v>
       </c>
       <c r="U137" s="48" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="V137" s="48" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="W137" s="48" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="X137" s="48" t="s">
         <v>22</v>
@@ -19557,7 +20053,7 @@
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A138" s="48" t="s">
-        <v>435</v>
+        <v>397</v>
       </c>
       <c r="B138" s="48" t="s">
         <v>22</v>
@@ -19617,13 +20113,13 @@
         <v>22</v>
       </c>
       <c r="U138" s="48" t="s">
-        <v>22</v>
+        <v>475</v>
       </c>
       <c r="V138" s="48" t="s">
-        <v>22</v>
+        <v>475</v>
       </c>
       <c r="W138" s="48" t="s">
-        <v>22</v>
+        <v>475</v>
       </c>
       <c r="X138" s="48" t="s">
         <v>22</v>
@@ -19631,7 +20127,7 @@
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A139" s="48" t="s">
-        <v>439</v>
+        <v>650</v>
       </c>
       <c r="B139" s="48" t="s">
         <v>22</v>
@@ -19691,13 +20187,13 @@
         <v>22</v>
       </c>
       <c r="U139" s="48" t="s">
-        <v>22</v>
+        <v>475</v>
       </c>
       <c r="V139" s="48" t="s">
-        <v>22</v>
+        <v>475</v>
       </c>
       <c r="W139" s="48" t="s">
-        <v>22</v>
+        <v>475</v>
       </c>
       <c r="X139" s="48" t="s">
         <v>22</v>
@@ -19705,7 +20201,7 @@
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A140" s="48" t="s">
-        <v>442</v>
+        <v>653</v>
       </c>
       <c r="B140" s="48" t="s">
         <v>22</v>
@@ -19765,13 +20261,13 @@
         <v>22</v>
       </c>
       <c r="U140" s="48" t="s">
-        <v>22</v>
+        <v>475</v>
       </c>
       <c r="V140" s="48" t="s">
-        <v>22</v>
+        <v>475</v>
       </c>
       <c r="W140" s="48" t="s">
-        <v>22</v>
+        <v>475</v>
       </c>
       <c r="X140" s="48" t="s">
         <v>22</v>
@@ -19779,7 +20275,7 @@
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A141" s="48" t="s">
-        <v>444</v>
+        <v>654</v>
       </c>
       <c r="B141" s="48" t="s">
         <v>22</v>
@@ -19839,13 +20335,13 @@
         <v>22</v>
       </c>
       <c r="U141" s="48" t="s">
-        <v>525</v>
+        <v>475</v>
       </c>
       <c r="V141" s="48" t="s">
-        <v>525</v>
+        <v>475</v>
       </c>
       <c r="W141" s="48" t="s">
-        <v>525</v>
+        <v>475</v>
       </c>
       <c r="X141" s="48" t="s">
         <v>22</v>
@@ -19853,7 +20349,7 @@
     </row>
     <row r="142" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A142" s="48" t="s">
-        <v>447</v>
+        <v>658</v>
       </c>
       <c r="B142" s="48" t="s">
         <v>22</v>
@@ -19913,13 +20409,13 @@
         <v>22</v>
       </c>
       <c r="U142" s="48" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="V142" s="48" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="W142" s="48" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="X142" s="48" t="s">
         <v>22</v>
@@ -19927,7 +20423,7 @@
     </row>
     <row r="143" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A143" s="48" t="s">
-        <v>450</v>
+        <v>660</v>
       </c>
       <c r="B143" s="48" t="s">
         <v>22</v>
@@ -19987,13 +20483,13 @@
         <v>22</v>
       </c>
       <c r="U143" s="48" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="V143" s="48" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="W143" s="48" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="X143" s="48" t="s">
         <v>22</v>
@@ -20001,7 +20497,7 @@
     </row>
     <row r="144" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A144" s="48" t="s">
-        <v>453</v>
+        <v>663</v>
       </c>
       <c r="B144" s="48" t="s">
         <v>22</v>
@@ -20061,13 +20557,13 @@
         <v>22</v>
       </c>
       <c r="U144" s="48" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="V144" s="48" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="W144" s="48" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="X144" s="48" t="s">
         <v>22</v>
@@ -20075,7 +20571,7 @@
     </row>
     <row r="145" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A145" s="48" t="s">
-        <v>456</v>
+        <v>665</v>
       </c>
       <c r="B145" s="48" t="s">
         <v>22</v>
@@ -20135,21 +20631,21 @@
         <v>22</v>
       </c>
       <c r="U145" s="48" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="V145" s="48" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="W145" s="48" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="X145" s="48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="146" spans="1:24" ht="66.599999999999994" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A146" s="48" t="s">
-        <v>459</v>
+        <v>430</v>
       </c>
       <c r="B146" s="48" t="s">
         <v>22</v>
@@ -20209,21 +20705,21 @@
         <v>22</v>
       </c>
       <c r="U146" s="48" t="s">
-        <v>481</v>
+        <v>22</v>
       </c>
       <c r="V146" s="48" t="s">
-        <v>481</v>
+        <v>22</v>
       </c>
       <c r="W146" s="48" t="s">
-        <v>481</v>
+        <v>22</v>
       </c>
       <c r="X146" s="48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="147" spans="1:24" ht="53.4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A147" s="48" t="s">
-        <v>462</v>
+        <v>434</v>
       </c>
       <c r="B147" s="48" t="s">
         <v>22</v>
@@ -20283,13 +20779,13 @@
         <v>22</v>
       </c>
       <c r="U147" s="48" t="s">
-        <v>482</v>
+        <v>22</v>
       </c>
       <c r="V147" s="48" t="s">
-        <v>482</v>
+        <v>22</v>
       </c>
       <c r="W147" s="48" t="s">
-        <v>482</v>
+        <v>22</v>
       </c>
       <c r="X147" s="48" t="s">
         <v>22</v>
@@ -20297,7 +20793,7 @@
     </row>
     <row r="148" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A148" s="48" t="s">
-        <v>503</v>
+        <v>437</v>
       </c>
       <c r="B148" s="48" t="s">
         <v>22</v>
@@ -20369,9 +20865,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="149" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A149" s="48" t="s">
-        <v>638</v>
+        <v>439</v>
       </c>
       <c r="B149" s="48" t="s">
         <v>22</v>
@@ -20431,21 +20927,21 @@
         <v>22</v>
       </c>
       <c r="U149" s="48" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="V149" s="48" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="W149" s="48" t="s">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="X149" s="48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="150" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="67" t="s">
-        <v>533</v>
+    <row r="150" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A150" s="48" t="s">
+        <v>442</v>
       </c>
       <c r="B150" s="48" t="s">
         <v>22</v>
@@ -20505,21 +21001,21 @@
         <v>22</v>
       </c>
       <c r="U150" s="48" t="s">
-        <v>22</v>
+        <v>472</v>
       </c>
       <c r="V150" s="48" t="s">
-        <v>22</v>
+        <v>472</v>
       </c>
       <c r="W150" s="48" t="s">
-        <v>22</v>
+        <v>472</v>
       </c>
       <c r="X150" s="48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="151" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="70" t="s">
-        <v>537</v>
+    <row r="151" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A151" s="48" t="s">
+        <v>445</v>
       </c>
       <c r="B151" s="48" t="s">
         <v>22</v>
@@ -20579,21 +21075,21 @@
         <v>22</v>
       </c>
       <c r="U151" s="48" t="s">
-        <v>22</v>
+        <v>473</v>
       </c>
       <c r="V151" s="48" t="s">
-        <v>22</v>
+        <v>473</v>
       </c>
       <c r="W151" s="48" t="s">
-        <v>22</v>
+        <v>473</v>
       </c>
       <c r="X151" s="48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="152" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="67" t="s">
-        <v>540</v>
+    <row r="152" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A152" s="48" t="s">
+        <v>448</v>
       </c>
       <c r="B152" s="48" t="s">
         <v>22</v>
@@ -20653,21 +21149,21 @@
         <v>22</v>
       </c>
       <c r="U152" s="48" t="s">
-        <v>22</v>
+        <v>474</v>
       </c>
       <c r="V152" s="48" t="s">
-        <v>22</v>
+        <v>474</v>
       </c>
       <c r="W152" s="48" t="s">
-        <v>22</v>
+        <v>474</v>
       </c>
       <c r="X152" s="48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="153" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="70" t="s">
-        <v>543</v>
+    <row r="153" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A153" s="48" t="s">
+        <v>451</v>
       </c>
       <c r="B153" s="48" t="s">
         <v>22</v>
@@ -20727,21 +21223,21 @@
         <v>22</v>
       </c>
       <c r="U153" s="48" t="s">
-        <v>22</v>
+        <v>475</v>
       </c>
       <c r="V153" s="48" t="s">
-        <v>22</v>
+        <v>475</v>
       </c>
       <c r="W153" s="48" t="s">
-        <v>22</v>
+        <v>475</v>
       </c>
       <c r="X153" s="48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="154" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="67" t="s">
-        <v>545</v>
+    <row r="154" spans="1:24" ht="66.599999999999994" x14ac:dyDescent="0.3">
+      <c r="A154" s="48" t="s">
+        <v>454</v>
       </c>
       <c r="B154" s="48" t="s">
         <v>22</v>
@@ -20801,21 +21297,21 @@
         <v>22</v>
       </c>
       <c r="U154" s="48" t="s">
-        <v>22</v>
+        <v>476</v>
       </c>
       <c r="V154" s="48" t="s">
-        <v>22</v>
+        <v>476</v>
       </c>
       <c r="W154" s="48" t="s">
-        <v>22</v>
+        <v>476</v>
       </c>
       <c r="X154" s="48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="155" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="70" t="s">
-        <v>547</v>
+    <row r="155" spans="1:24" ht="53.4" x14ac:dyDescent="0.3">
+      <c r="A155" s="48" t="s">
+        <v>457</v>
       </c>
       <c r="B155" s="48" t="s">
         <v>22</v>
@@ -20875,21 +21371,21 @@
         <v>22</v>
       </c>
       <c r="U155" s="48" t="s">
-        <v>22</v>
+        <v>477</v>
       </c>
       <c r="V155" s="48" t="s">
-        <v>22</v>
+        <v>477</v>
       </c>
       <c r="W155" s="48" t="s">
-        <v>22</v>
+        <v>477</v>
       </c>
       <c r="X155" s="48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="156" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="67" t="s">
-        <v>549</v>
+    <row r="156" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A156" s="48" t="s">
+        <v>498</v>
       </c>
       <c r="B156" s="48" t="s">
         <v>22</v>
@@ -20962,8 +21458,8 @@
       </c>
     </row>
     <row r="157" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="70" t="s">
-        <v>551</v>
+      <c r="A157" s="48" t="s">
+        <v>633</v>
       </c>
       <c r="B157" s="48" t="s">
         <v>22</v>
@@ -21037,7 +21533,7 @@
     </row>
     <row r="158" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="67" t="s">
-        <v>553</v>
+        <v>528</v>
       </c>
       <c r="B158" s="48" t="s">
         <v>22</v>
@@ -21111,7 +21607,7 @@
     </row>
     <row r="159" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="70" t="s">
-        <v>556</v>
+        <v>532</v>
       </c>
       <c r="B159" s="48" t="s">
         <v>22</v>
@@ -21185,7 +21681,7 @@
     </row>
     <row r="160" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="67" t="s">
-        <v>559</v>
+        <v>535</v>
       </c>
       <c r="B160" s="48" t="s">
         <v>22</v>
@@ -21259,7 +21755,7 @@
     </row>
     <row r="161" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="70" t="s">
-        <v>562</v>
+        <v>538</v>
       </c>
       <c r="B161" s="48" t="s">
         <v>22</v>
@@ -21333,7 +21829,7 @@
     </row>
     <row r="162" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="67" t="s">
-        <v>565</v>
+        <v>540</v>
       </c>
       <c r="B162" s="48" t="s">
         <v>22</v>
@@ -21407,7 +21903,7 @@
     </row>
     <row r="163" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="70" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="B163" s="48" t="s">
         <v>22</v>
@@ -21481,7 +21977,7 @@
     </row>
     <row r="164" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="67" t="s">
-        <v>571</v>
+        <v>544</v>
       </c>
       <c r="B164" s="48" t="s">
         <v>22</v>
@@ -21554,8 +22050,8 @@
       </c>
     </row>
     <row r="165" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="67" t="s">
-        <v>573</v>
+      <c r="A165" s="70" t="s">
+        <v>546</v>
       </c>
       <c r="B165" s="48" t="s">
         <v>22</v>
@@ -21629,7 +22125,7 @@
     </row>
     <row r="166" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="67" t="s">
-        <v>575</v>
+        <v>548</v>
       </c>
       <c r="B166" s="48" t="s">
         <v>22</v>
@@ -21701,621 +22197,1287 @@
         <v>22</v>
       </c>
     </row>
-    <row r="167" spans="1:24" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="67" t="s">
-        <v>578</v>
+    <row r="167" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="70" t="s">
+        <v>551</v>
       </c>
       <c r="B167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X167" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="168" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="67" t="s">
+        <v>554</v>
+      </c>
+      <c r="B168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X168" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="169" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="70" t="s">
+        <v>557</v>
+      </c>
+      <c r="B169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X169" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="170" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="67" t="s">
+        <v>560</v>
+      </c>
+      <c r="B170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X170" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="171" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="70" t="s">
+        <v>563</v>
+      </c>
+      <c r="B171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X171" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="172" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="67" t="s">
+        <v>566</v>
+      </c>
+      <c r="B172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X172" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="173" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="67" t="s">
+        <v>568</v>
+      </c>
+      <c r="B173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X173" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="174" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="67" t="s">
+        <v>570</v>
+      </c>
+      <c r="B174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X174" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="175" spans="1:24" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="67" t="s">
+        <v>573</v>
+      </c>
+      <c r="B175" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="C167" s="36" t="s">
-        <v>470</v>
-      </c>
-      <c r="D167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F167" s="48" t="s">
-        <v>471</v>
-      </c>
-      <c r="G167" s="49" t="s">
-        <v>472</v>
-      </c>
-      <c r="H167" s="48" t="s">
-        <v>473</v>
-      </c>
-      <c r="I167" s="48" t="s">
-        <v>490</v>
-      </c>
-      <c r="J167" s="36" t="s">
-        <v>491</v>
-      </c>
-      <c r="K167" s="48" t="s">
-        <v>492</v>
-      </c>
-      <c r="L167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X167" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="168" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="82"/>
-      <c r="B168" s="48"/>
-      <c r="C168" s="36"/>
-      <c r="D168" s="48"/>
-      <c r="E168" s="48"/>
-      <c r="F168" s="48"/>
-      <c r="G168" s="49"/>
-      <c r="H168" s="48"/>
-      <c r="I168" s="48"/>
-      <c r="J168" s="36"/>
-      <c r="K168" s="48"/>
-      <c r="L168" s="48"/>
-      <c r="M168" s="48"/>
-      <c r="N168" s="48"/>
-      <c r="O168" s="48"/>
-      <c r="P168" s="48"/>
-      <c r="Q168" s="48"/>
-      <c r="R168" s="48"/>
-      <c r="S168" s="48"/>
-      <c r="T168" s="48"/>
-      <c r="U168" s="48"/>
-      <c r="V168" s="48"/>
-      <c r="W168" s="48"/>
-      <c r="X168" s="48"/>
-    </row>
-    <row r="169" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="75" t="s">
+      <c r="C175" s="36" t="s">
+        <v>465</v>
+      </c>
+      <c r="D175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F175" s="48" t="s">
+        <v>466</v>
+      </c>
+      <c r="G175" s="49" t="s">
+        <v>467</v>
+      </c>
+      <c r="H175" s="48" t="s">
+        <v>468</v>
+      </c>
+      <c r="I175" s="48" t="s">
+        <v>485</v>
+      </c>
+      <c r="J175" s="36" t="s">
+        <v>486</v>
+      </c>
+      <c r="K175" s="48" t="s">
+        <v>487</v>
+      </c>
+      <c r="L175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X175" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="176" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="82"/>
+      <c r="B176" s="48"/>
+      <c r="C176" s="36"/>
+      <c r="D176" s="48"/>
+      <c r="E176" s="48"/>
+      <c r="F176" s="48"/>
+      <c r="G176" s="49"/>
+      <c r="H176" s="48"/>
+      <c r="I176" s="48"/>
+      <c r="J176" s="36"/>
+      <c r="K176" s="48"/>
+      <c r="L176" s="48"/>
+      <c r="M176" s="48"/>
+      <c r="N176" s="48"/>
+      <c r="O176" s="48"/>
+      <c r="P176" s="48"/>
+      <c r="Q176" s="48"/>
+      <c r="R176" s="48"/>
+      <c r="S176" s="48"/>
+      <c r="T176" s="48"/>
+      <c r="U176" s="48"/>
+      <c r="V176" s="48"/>
+      <c r="W176" s="48"/>
+      <c r="X176" s="48"/>
+    </row>
+    <row r="177" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="75" t="s">
+        <v>591</v>
+      </c>
+      <c r="B177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S177" s="49" t="s">
+        <v>593</v>
+      </c>
+      <c r="T177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V177" s="48" t="s">
+        <v>609</v>
+      </c>
+      <c r="W177" s="36" t="s">
+        <v>595</v>
+      </c>
+      <c r="X177" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="178" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A178" s="75" t="s">
         <v>596</v>
       </c>
-      <c r="B169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S169" s="49" t="s">
-        <v>598</v>
-      </c>
-      <c r="T169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V169" s="48" t="s">
-        <v>614</v>
-      </c>
-      <c r="W169" s="36" t="s">
-        <v>600</v>
-      </c>
-      <c r="X169" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="170" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="75" t="s">
+      <c r="B178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S178" s="49" t="s">
+        <v>597</v>
+      </c>
+      <c r="T178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W178" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X178" s="78" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="179" spans="1:24" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A179" s="75" t="s">
         <v>601</v>
       </c>
-      <c r="B170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S170" s="49" t="s">
-        <v>602</v>
-      </c>
-      <c r="T170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W170" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X170" s="78" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="171" spans="1:24" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="75" t="s">
-        <v>606</v>
-      </c>
-      <c r="B171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S171" s="49" t="s">
-        <v>602</v>
-      </c>
-      <c r="T171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W171" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X171" s="84" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="172" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A172" s="75" t="s">
+      <c r="B179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S179" s="49" t="s">
+        <v>597</v>
+      </c>
+      <c r="T179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V179" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W179" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X179" s="84" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="180" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="75" t="s">
+        <v>605</v>
+      </c>
+      <c r="B180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S180" s="49" t="s">
+        <v>593</v>
+      </c>
+      <c r="T180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V180" s="48" t="s">
         <v>610</v>
       </c>
-      <c r="B172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S172" s="49" t="s">
-        <v>598</v>
-      </c>
-      <c r="T172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V172" s="48" t="s">
+      <c r="W180" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X180" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="181" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A181" s="75" t="s">
+        <v>611</v>
+      </c>
+      <c r="B181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S181" s="49" t="s">
+        <v>597</v>
+      </c>
+      <c r="T181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W181" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X181" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="182" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A182" s="75" t="s">
         <v>615</v>
       </c>
-      <c r="W172" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X172" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="173" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A173" s="75" t="s">
-        <v>616</v>
-      </c>
-      <c r="B173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S173" s="49" t="s">
-        <v>602</v>
-      </c>
-      <c r="T173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W173" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X173" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="174" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A174" s="75" t="s">
+      <c r="B182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S182" s="49" t="s">
+        <v>597</v>
+      </c>
+      <c r="T182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W182" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X182" s="85" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="183" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A183" s="75" t="s">
+        <v>619</v>
+      </c>
+      <c r="B183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S183" s="49" t="s">
         <v>620</v>
       </c>
-      <c r="B174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S174" s="49" t="s">
-        <v>602</v>
-      </c>
-      <c r="T174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W174" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X174" s="85" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="175" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A175" s="75" t="s">
-        <v>624</v>
-      </c>
-      <c r="B175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S175" s="49" t="s">
-        <v>625</v>
-      </c>
-      <c r="T175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W175" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X175" s="48" t="s">
+      <c r="T183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W183" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X183" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="184" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="75" t="s">
+        <v>637</v>
+      </c>
+      <c r="B184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W184" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X184" s="48" t="s">
         <v>22</v>
       </c>
     </row>
@@ -22442,13 +23604,13 @@
     <hyperlink ref="G121" r:id="rId14" xr:uid="{009DD950-489A-4511-9EE8-3302596C4B91}"/>
     <hyperlink ref="G126" r:id="rId15" xr:uid="{FEC9AB2B-6FD0-4D08-96BB-5634F117BFB0}"/>
     <hyperlink ref="D136" r:id="rId16" xr:uid="{EAE526E7-10C0-4EC9-846A-D81343ACBEC4}"/>
-    <hyperlink ref="G167" r:id="rId17" xr:uid="{0A52F660-ABF2-41CF-BD4C-5E55458D590D}"/>
-    <hyperlink ref="S169" r:id="rId18" xr:uid="{13FB8A07-5562-4AAB-9E83-934C01965617}"/>
-    <hyperlink ref="S171" r:id="rId19" xr:uid="{23F160B7-D3CD-415D-B0D6-1EECB7AFE96F}"/>
-    <hyperlink ref="S172" r:id="rId20" xr:uid="{7206C778-989C-4587-83FA-C09C20DA42BD}"/>
-    <hyperlink ref="S173" r:id="rId21" xr:uid="{3B0D666D-626C-490D-A9B6-B9643B9EDF8A}"/>
-    <hyperlink ref="X170" r:id="rId22" tooltip="pink real heaven" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{7AB2CC85-055B-4B62-B758-A407CA7BD409}"/>
-    <hyperlink ref="X174" r:id="rId23" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{E6426F17-2EE7-4F4A-80B0-E58B87C35EDA}"/>
+    <hyperlink ref="G175" r:id="rId17" xr:uid="{0A52F660-ABF2-41CF-BD4C-5E55458D590D}"/>
+    <hyperlink ref="S177" r:id="rId18" xr:uid="{13FB8A07-5562-4AAB-9E83-934C01965617}"/>
+    <hyperlink ref="S179" r:id="rId19" xr:uid="{23F160B7-D3CD-415D-B0D6-1EECB7AFE96F}"/>
+    <hyperlink ref="S180" r:id="rId20" xr:uid="{7206C778-989C-4587-83FA-C09C20DA42BD}"/>
+    <hyperlink ref="S181" r:id="rId21" xr:uid="{3B0D666D-626C-490D-A9B6-B9643B9EDF8A}"/>
+    <hyperlink ref="X178" r:id="rId22" tooltip="pink real heaven" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{7AB2CC85-055B-4B62-B758-A407CA7BD409}"/>
+    <hyperlink ref="X182" r:id="rId23" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{E6426F17-2EE7-4F4A-80B0-E58B87C35EDA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId24"/>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\Zlaata1042026\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CC2AD9-EA94-42A6-8F3C-FD5183498F98}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA54FDAD-456A-457E-85E4-4C7864CE654B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6326" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6425" uniqueCount="725">
   <si>
     <t>S.No</t>
   </si>
@@ -2174,6 +2174,33 @@
   </si>
   <si>
     <t>Verify that zlaata India and Boss lady  Influencer Banner  is available in the Home Page</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SB_11</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SB_11</t>
+  </si>
+  <si>
+    <t>Verify that the Related Queries display in both zlaata Indai and Boss lady</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SB_12</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SB_13</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SB_12</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SB_13</t>
+  </si>
+  <si>
+    <t>Verify that the close button in both brand search bars is working properly</t>
+  </si>
+  <si>
+    <t>Verify that Recent Searches are displayed correctly in both brand search bars</t>
   </si>
 </sst>
 </file>
@@ -3713,7 +3740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z204"/>
+  <dimension ref="A1:Z207"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
@@ -9281,44 +9308,76 @@
       <c r="W164" s="58"/>
       <c r="X164" s="58"/>
     </row>
-    <row r="165" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A165" s="92" t="s">
-        <v>497</v>
-      </c>
-      <c r="B165" s="92"/>
-      <c r="C165" s="92"/>
-      <c r="D165" s="92"/>
-      <c r="E165" s="92"/>
-      <c r="F165" s="92"/>
-      <c r="G165" s="92"/>
-      <c r="H165" s="92"/>
-      <c r="I165" s="92"/>
-      <c r="J165" s="92"/>
-    </row>
-    <row r="166" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="25">
+        <v>11</v>
+      </c>
+      <c r="B165" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C165" s="48" t="s">
+        <v>716</v>
+      </c>
+      <c r="D165" s="48" t="s">
+        <v>718</v>
+      </c>
+      <c r="E165" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F165" s="48" t="s">
+        <v>717</v>
+      </c>
+      <c r="G165" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H165" s="48" t="s">
+        <v>429</v>
+      </c>
+      <c r="I165" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J165" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K165" s="58"/>
+      <c r="L165" s="58"/>
+      <c r="M165" s="58"/>
+      <c r="N165" s="58"/>
+      <c r="O165" s="58"/>
+      <c r="P165" s="58"/>
+      <c r="Q165" s="58"/>
+      <c r="R165" s="58"/>
+      <c r="S165" s="58"/>
+      <c r="T165" s="58"/>
+      <c r="U165" s="58"/>
+      <c r="V165" s="58"/>
+      <c r="W165" s="58"/>
+      <c r="X165" s="58"/>
+    </row>
+    <row r="166" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="25">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B166" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C166" s="48" t="s">
-        <v>498</v>
-      </c>
-      <c r="D166" s="24" t="s">
-        <v>499</v>
+        <v>719</v>
+      </c>
+      <c r="D166" s="48" t="s">
+        <v>723</v>
       </c>
       <c r="E166" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F166" s="48" t="s">
-        <v>496</v>
+        <v>721</v>
       </c>
       <c r="G166" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H166" s="48" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="I166" s="48" t="s">
         <v>12</v>
@@ -9326,31 +9385,45 @@
       <c r="J166" s="48" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="167" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="K166" s="58"/>
+      <c r="L166" s="58"/>
+      <c r="M166" s="58"/>
+      <c r="N166" s="58"/>
+      <c r="O166" s="58"/>
+      <c r="P166" s="58"/>
+      <c r="Q166" s="58"/>
+      <c r="R166" s="58"/>
+      <c r="S166" s="58"/>
+      <c r="T166" s="58"/>
+      <c r="U166" s="58"/>
+      <c r="V166" s="58"/>
+      <c r="W166" s="58"/>
+      <c r="X166" s="58"/>
+    </row>
+    <row r="167" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="25">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B167" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C167" s="48" t="s">
-        <v>629</v>
-      </c>
-      <c r="D167" s="24" t="s">
-        <v>630</v>
+        <v>720</v>
+      </c>
+      <c r="D167" s="48" t="s">
+        <v>724</v>
       </c>
       <c r="E167" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F167" s="48" t="s">
-        <v>631</v>
+        <v>722</v>
       </c>
       <c r="G167" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H167" s="48" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="I167" s="48" t="s">
         <v>12</v>
@@ -9358,10 +9431,24 @@
       <c r="J167" s="48" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="168" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K167" s="58"/>
+      <c r="L167" s="58"/>
+      <c r="M167" s="58"/>
+      <c r="N167" s="58"/>
+      <c r="O167" s="58"/>
+      <c r="P167" s="58"/>
+      <c r="Q167" s="58"/>
+      <c r="R167" s="58"/>
+      <c r="S167" s="58"/>
+      <c r="T167" s="58"/>
+      <c r="U167" s="58"/>
+      <c r="V167" s="58"/>
+      <c r="W167" s="58"/>
+      <c r="X167" s="58"/>
+    </row>
+    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A168" s="92" t="s">
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="B168" s="92"/>
       <c r="C168" s="92"/>
@@ -9373,179 +9460,113 @@
       <c r="I168" s="92"/>
       <c r="J168" s="92"/>
     </row>
-    <row r="169" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="65">
+    <row r="169" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A169" s="25">
         <v>1</v>
       </c>
-      <c r="B169" s="66" t="s">
+      <c r="B169" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="C169" s="67" t="s">
+      <c r="C169" s="48" t="s">
+        <v>498</v>
+      </c>
+      <c r="D169" s="24" t="s">
+        <v>499</v>
+      </c>
+      <c r="E169" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F169" s="48" t="s">
+        <v>496</v>
+      </c>
+      <c r="G169" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H169" s="48" t="s">
+        <v>369</v>
+      </c>
+      <c r="I169" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J169" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A170" s="25">
+        <v>2</v>
+      </c>
+      <c r="B170" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C170" s="48" t="s">
+        <v>629</v>
+      </c>
+      <c r="D170" s="24" t="s">
+        <v>630</v>
+      </c>
+      <c r="E170" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F170" s="48" t="s">
+        <v>631</v>
+      </c>
+      <c r="G170" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H170" s="48" t="s">
+        <v>369</v>
+      </c>
+      <c r="I170" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J170" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="171" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="92" t="s">
+        <v>523</v>
+      </c>
+      <c r="B171" s="92"/>
+      <c r="C171" s="92"/>
+      <c r="D171" s="92"/>
+      <c r="E171" s="92"/>
+      <c r="F171" s="92"/>
+      <c r="G171" s="92"/>
+      <c r="H171" s="92"/>
+      <c r="I171" s="92"/>
+      <c r="J171" s="92"/>
+    </row>
+    <row r="172" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="65">
+        <v>1</v>
+      </c>
+      <c r="B172" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="C172" s="67" t="s">
         <v>524</v>
       </c>
-      <c r="D169" s="66" t="s">
+      <c r="D172" s="66" t="s">
         <v>525</v>
       </c>
-      <c r="E169" s="66" t="s">
+      <c r="E172" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F169" s="67" t="s">
+      <c r="F172" s="67" t="s">
         <v>526</v>
       </c>
-      <c r="G169" s="66" t="s">
+      <c r="G172" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="H169" s="66" t="s">
+      <c r="H172" s="66" t="s">
         <v>527</v>
       </c>
-      <c r="I169" s="66" t="s">
+      <c r="I172" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="J169" s="66" t="s">
-        <v>13</v>
-      </c>
-      <c r="K169" s="58"/>
-      <c r="L169" s="58"/>
-      <c r="M169" s="58"/>
-      <c r="N169" s="58"/>
-      <c r="O169" s="58"/>
-      <c r="P169" s="58"/>
-      <c r="Q169" s="58"/>
-      <c r="R169" s="58"/>
-      <c r="S169" s="58"/>
-      <c r="T169" s="58"/>
-      <c r="U169" s="58"/>
-      <c r="V169" s="58"/>
-      <c r="W169" s="58"/>
-      <c r="X169" s="58"/>
-      <c r="Y169" s="58"/>
-      <c r="Z169" s="58"/>
-    </row>
-    <row r="170" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="68">
-        <v>2</v>
-      </c>
-      <c r="B170" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="C170" s="70" t="s">
-        <v>528</v>
-      </c>
-      <c r="D170" s="69" t="s">
-        <v>529</v>
-      </c>
-      <c r="E170" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="F170" s="70" t="s">
-        <v>530</v>
-      </c>
-      <c r="G170" s="69" t="s">
-        <v>11</v>
-      </c>
-      <c r="H170" s="69" t="s">
-        <v>527</v>
-      </c>
-      <c r="I170" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="J170" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="K170" s="58"/>
-      <c r="L170" s="58"/>
-      <c r="M170" s="58"/>
-      <c r="N170" s="58"/>
-      <c r="O170" s="58"/>
-      <c r="P170" s="58"/>
-      <c r="Q170" s="58"/>
-      <c r="R170" s="58"/>
-      <c r="S170" s="58"/>
-      <c r="T170" s="58"/>
-      <c r="U170" s="58"/>
-      <c r="V170" s="58"/>
-      <c r="W170" s="58"/>
-      <c r="X170" s="58"/>
-      <c r="Y170" s="58"/>
-      <c r="Z170" s="58"/>
-    </row>
-    <row r="171" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="68">
-        <v>3</v>
-      </c>
-      <c r="B171" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="C171" s="70" t="s">
-        <v>531</v>
-      </c>
-      <c r="D171" s="71" t="s">
-        <v>532</v>
-      </c>
-      <c r="E171" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="F171" s="70" t="s">
-        <v>533</v>
-      </c>
-      <c r="G171" s="69" t="s">
-        <v>11</v>
-      </c>
-      <c r="H171" s="69" t="s">
-        <v>527</v>
-      </c>
-      <c r="I171" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="J171" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="K171" s="58"/>
-      <c r="L171" s="58"/>
-      <c r="M171" s="58"/>
-      <c r="N171" s="58"/>
-      <c r="O171" s="58"/>
-      <c r="P171" s="58"/>
-      <c r="Q171" s="58"/>
-      <c r="R171" s="58"/>
-      <c r="S171" s="58"/>
-      <c r="T171" s="58"/>
-      <c r="U171" s="58"/>
-      <c r="V171" s="58"/>
-      <c r="W171" s="58"/>
-      <c r="X171" s="58"/>
-      <c r="Y171" s="58"/>
-      <c r="Z171" s="58"/>
-    </row>
-    <row r="172" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="68">
-        <v>4</v>
-      </c>
-      <c r="B172" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="C172" s="70" t="s">
-        <v>534</v>
-      </c>
-      <c r="D172" s="69" t="s">
-        <v>535</v>
-      </c>
-      <c r="E172" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="F172" s="70" t="s">
-        <v>536</v>
-      </c>
-      <c r="G172" s="69" t="s">
-        <v>11</v>
-      </c>
-      <c r="H172" s="69" t="s">
-        <v>527</v>
-      </c>
-      <c r="I172" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="J172" s="69" t="s">
+      <c r="J172" s="66" t="s">
         <v>13</v>
       </c>
       <c r="K172" s="58"/>
@@ -9567,22 +9588,22 @@
     </row>
     <row r="173" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B173" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C173" s="70" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="D173" s="69" t="s">
-        <v>575</v>
+        <v>529</v>
       </c>
       <c r="E173" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F173" s="70" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="G173" s="69" t="s">
         <v>11</v>
@@ -9615,22 +9636,22 @@
     </row>
     <row r="174" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B174" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C174" s="70" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="D174" s="71" t="s">
-        <v>576</v>
+        <v>532</v>
       </c>
       <c r="E174" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F174" s="70" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="G174" s="69" t="s">
         <v>11</v>
@@ -9663,22 +9684,22 @@
     </row>
     <row r="175" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="68">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B175" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C175" s="70" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D175" s="69" t="s">
-        <v>577</v>
+        <v>535</v>
       </c>
       <c r="E175" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F175" s="70" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G175" s="69" t="s">
         <v>11</v>
@@ -9711,22 +9732,22 @@
     </row>
     <row r="176" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="68">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B176" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C176" s="70" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="D176" s="69" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="E176" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F176" s="70" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="G176" s="69" t="s">
         <v>11</v>
@@ -9758,34 +9779,34 @@
       <c r="Z176" s="58"/>
     </row>
     <row r="177" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="72">
-        <v>9</v>
-      </c>
-      <c r="B177" s="74" t="s">
+      <c r="A177" s="68">
+        <v>6</v>
+      </c>
+      <c r="B177" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="C177" s="75" t="s">
-        <v>545</v>
-      </c>
-      <c r="D177" s="74" t="s">
-        <v>548</v>
-      </c>
-      <c r="E177" s="74" t="s">
+      <c r="C177" s="70" t="s">
+        <v>539</v>
+      </c>
+      <c r="D177" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="E177" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="F177" s="75" t="s">
-        <v>546</v>
-      </c>
-      <c r="G177" s="74" t="s">
+      <c r="F177" s="70" t="s">
+        <v>540</v>
+      </c>
+      <c r="G177" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="H177" s="74" t="s">
+      <c r="H177" s="69" t="s">
         <v>527</v>
       </c>
-      <c r="I177" s="74" t="s">
+      <c r="I177" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="J177" s="74" t="s">
+      <c r="J177" s="69" t="s">
         <v>13</v>
       </c>
       <c r="K177" s="58"/>
@@ -9806,34 +9827,34 @@
       <c r="Z177" s="58"/>
     </row>
     <row r="178" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="73">
+      <c r="A178" s="68">
+        <v>7</v>
+      </c>
+      <c r="B178" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="B178" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="C178" s="75" t="s">
-        <v>547</v>
-      </c>
-      <c r="D178" s="74" t="s">
-        <v>551</v>
-      </c>
-      <c r="E178" s="74" t="s">
+      <c r="C178" s="70" t="s">
+        <v>541</v>
+      </c>
+      <c r="D178" s="69" t="s">
+        <v>577</v>
+      </c>
+      <c r="E178" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="F178" s="75" t="s">
-        <v>549</v>
-      </c>
-      <c r="G178" s="74" t="s">
+      <c r="F178" s="70" t="s">
+        <v>542</v>
+      </c>
+      <c r="G178" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="H178" s="74" t="s">
+      <c r="H178" s="69" t="s">
         <v>527</v>
       </c>
-      <c r="I178" s="74" t="s">
+      <c r="I178" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="J178" s="74" t="s">
+      <c r="J178" s="69" t="s">
         <v>13</v>
       </c>
       <c r="K178" s="58"/>
@@ -9854,34 +9875,34 @@
       <c r="Z178" s="58"/>
     </row>
     <row r="179" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="72">
+      <c r="A179" s="68">
+        <v>8</v>
+      </c>
+      <c r="B179" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C179" s="70" t="s">
+        <v>543</v>
+      </c>
+      <c r="D179" s="69" t="s">
+        <v>578</v>
+      </c>
+      <c r="E179" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F179" s="70" t="s">
+        <v>544</v>
+      </c>
+      <c r="G179" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="B179" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="C179" s="75" t="s">
-        <v>550</v>
-      </c>
-      <c r="D179" s="74" t="s">
-        <v>554</v>
-      </c>
-      <c r="E179" s="74" t="s">
-        <v>14</v>
-      </c>
-      <c r="F179" s="75" t="s">
-        <v>552</v>
-      </c>
-      <c r="G179" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="H179" s="74" t="s">
+      <c r="H179" s="69" t="s">
         <v>527</v>
       </c>
-      <c r="I179" s="74" t="s">
+      <c r="I179" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="J179" s="74" t="s">
+      <c r="J179" s="69" t="s">
         <v>13</v>
       </c>
       <c r="K179" s="58"/>
@@ -9902,23 +9923,23 @@
       <c r="Z179" s="58"/>
     </row>
     <row r="180" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="73">
-        <v>12</v>
+      <c r="A180" s="72">
+        <v>9</v>
       </c>
       <c r="B180" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C180" s="75" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="D180" s="74" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="E180" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F180" s="75" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="G180" s="74" t="s">
         <v>11</v>
@@ -9950,23 +9971,23 @@
       <c r="Z180" s="58"/>
     </row>
     <row r="181" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="72">
-        <v>13</v>
+      <c r="A181" s="73">
+        <v>10</v>
       </c>
       <c r="B181" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C181" s="75" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="D181" s="74" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="E181" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F181" s="75" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="G181" s="74" t="s">
         <v>11</v>
@@ -9998,23 +10019,23 @@
       <c r="Z181" s="58"/>
     </row>
     <row r="182" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="73">
-        <v>14</v>
+      <c r="A182" s="72">
+        <v>11</v>
       </c>
       <c r="B182" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C182" s="75" t="s">
-        <v>559</v>
-      </c>
-      <c r="D182" s="76" t="s">
-        <v>563</v>
+        <v>550</v>
+      </c>
+      <c r="D182" s="74" t="s">
+        <v>554</v>
       </c>
       <c r="E182" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F182" s="75" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="G182" s="74" t="s">
         <v>11</v>
@@ -10046,23 +10067,23 @@
       <c r="Z182" s="58"/>
     </row>
     <row r="183" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="72">
-        <v>15</v>
+      <c r="A183" s="73">
+        <v>12</v>
       </c>
       <c r="B183" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C183" s="75" t="s">
-        <v>562</v>
-      </c>
-      <c r="D183" s="76" t="s">
-        <v>579</v>
+        <v>553</v>
+      </c>
+      <c r="D183" s="74" t="s">
+        <v>557</v>
       </c>
       <c r="E183" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F183" s="75" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="G183" s="74" t="s">
         <v>11</v>
@@ -10094,23 +10115,23 @@
       <c r="Z183" s="58"/>
     </row>
     <row r="184" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="73">
-        <v>16</v>
+      <c r="A184" s="72">
+        <v>13</v>
       </c>
       <c r="B184" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C184" s="75" t="s">
-        <v>565</v>
-      </c>
-      <c r="D184" s="76" t="s">
-        <v>570</v>
+        <v>556</v>
+      </c>
+      <c r="D184" s="74" t="s">
+        <v>560</v>
       </c>
       <c r="E184" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F184" s="75" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="G184" s="74" t="s">
         <v>11</v>
@@ -10142,23 +10163,23 @@
       <c r="Z184" s="58"/>
     </row>
     <row r="185" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="72">
-        <v>17</v>
+      <c r="A185" s="73">
+        <v>14</v>
       </c>
       <c r="B185" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C185" s="75" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="D185" s="76" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="E185" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F185" s="75" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="G185" s="74" t="s">
         <v>11</v>
@@ -10190,23 +10211,23 @@
       <c r="Z185" s="58"/>
     </row>
     <row r="186" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="73">
-        <v>18</v>
+      <c r="A186" s="72">
+        <v>15</v>
       </c>
       <c r="B186" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C186" s="75" t="s">
-        <v>569</v>
-      </c>
-      <c r="D186" s="77" t="s">
-        <v>573</v>
+        <v>562</v>
+      </c>
+      <c r="D186" s="76" t="s">
+        <v>579</v>
       </c>
       <c r="E186" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F186" s="75" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="G186" s="74" t="s">
         <v>11</v>
@@ -10238,37 +10259,71 @@
       <c r="Z186" s="58"/>
     </row>
     <row r="187" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="92" t="s">
-        <v>602</v>
-      </c>
-      <c r="B187" s="92"/>
-      <c r="C187" s="92"/>
-      <c r="D187" s="92"/>
-      <c r="E187" s="92"/>
-      <c r="F187" s="92"/>
-      <c r="G187" s="92"/>
-      <c r="H187" s="92"/>
-      <c r="I187" s="92"/>
-      <c r="J187" s="92"/>
+      <c r="A187" s="73">
+        <v>16</v>
+      </c>
+      <c r="B187" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C187" s="75" t="s">
+        <v>565</v>
+      </c>
+      <c r="D187" s="76" t="s">
+        <v>570</v>
+      </c>
+      <c r="E187" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F187" s="75" t="s">
+        <v>566</v>
+      </c>
+      <c r="G187" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H187" s="74" t="s">
+        <v>527</v>
+      </c>
+      <c r="I187" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J187" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="K187" s="58"/>
+      <c r="L187" s="58"/>
+      <c r="M187" s="58"/>
+      <c r="N187" s="58"/>
+      <c r="O187" s="58"/>
+      <c r="P187" s="58"/>
+      <c r="Q187" s="58"/>
+      <c r="R187" s="58"/>
+      <c r="S187" s="58"/>
+      <c r="T187" s="58"/>
+      <c r="U187" s="58"/>
+      <c r="V187" s="58"/>
+      <c r="W187" s="58"/>
+      <c r="X187" s="58"/>
+      <c r="Y187" s="58"/>
+      <c r="Z187" s="58"/>
     </row>
     <row r="188" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="73">
-        <v>1</v>
+      <c r="A188" s="72">
+        <v>17</v>
       </c>
       <c r="B188" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C188" s="75" t="s">
-        <v>588</v>
-      </c>
-      <c r="D188" s="77" t="s">
-        <v>590</v>
+        <v>567</v>
+      </c>
+      <c r="D188" s="76" t="s">
+        <v>572</v>
       </c>
       <c r="E188" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F188" s="75" t="s">
-        <v>589</v>
+        <v>568</v>
       </c>
       <c r="G188" s="74" t="s">
         <v>11</v>
@@ -10282,25 +10337,41 @@
       <c r="J188" s="74" t="s">
         <v>13</v>
       </c>
+      <c r="K188" s="58"/>
+      <c r="L188" s="58"/>
+      <c r="M188" s="58"/>
+      <c r="N188" s="58"/>
+      <c r="O188" s="58"/>
+      <c r="P188" s="58"/>
+      <c r="Q188" s="58"/>
+      <c r="R188" s="58"/>
+      <c r="S188" s="58"/>
+      <c r="T188" s="58"/>
+      <c r="U188" s="58"/>
+      <c r="V188" s="58"/>
+      <c r="W188" s="58"/>
+      <c r="X188" s="58"/>
+      <c r="Y188" s="58"/>
+      <c r="Z188" s="58"/>
     </row>
     <row r="189" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="73">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B189" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C189" s="75" t="s">
-        <v>596</v>
+        <v>569</v>
       </c>
       <c r="D189" s="77" t="s">
-        <v>597</v>
+        <v>573</v>
       </c>
       <c r="E189" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F189" s="75" t="s">
-        <v>594</v>
+        <v>571</v>
       </c>
       <c r="G189" s="74" t="s">
         <v>11</v>
@@ -10314,57 +10385,55 @@
       <c r="J189" s="74" t="s">
         <v>13</v>
       </c>
+      <c r="K189" s="58"/>
+      <c r="L189" s="58"/>
+      <c r="M189" s="58"/>
+      <c r="N189" s="58"/>
+      <c r="O189" s="58"/>
+      <c r="P189" s="58"/>
+      <c r="Q189" s="58"/>
+      <c r="R189" s="58"/>
+      <c r="S189" s="58"/>
+      <c r="T189" s="58"/>
+      <c r="U189" s="58"/>
+      <c r="V189" s="58"/>
+      <c r="W189" s="58"/>
+      <c r="X189" s="58"/>
+      <c r="Y189" s="58"/>
+      <c r="Z189" s="58"/>
     </row>
     <row r="190" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="73">
-        <v>3</v>
-      </c>
-      <c r="B190" s="74" t="s">
-        <v>10</v>
-      </c>
-      <c r="C190" s="75" t="s">
-        <v>600</v>
-      </c>
-      <c r="D190" s="81" t="s">
-        <v>601</v>
-      </c>
-      <c r="E190" s="74" t="s">
-        <v>14</v>
-      </c>
-      <c r="F190" s="75" t="s">
-        <v>599</v>
-      </c>
-      <c r="G190" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="H190" s="74" t="s">
-        <v>527</v>
-      </c>
-      <c r="I190" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="J190" s="74" t="s">
-        <v>13</v>
-      </c>
+      <c r="A190" s="92" t="s">
+        <v>602</v>
+      </c>
+      <c r="B190" s="92"/>
+      <c r="C190" s="92"/>
+      <c r="D190" s="92"/>
+      <c r="E190" s="92"/>
+      <c r="F190" s="92"/>
+      <c r="G190" s="92"/>
+      <c r="H190" s="92"/>
+      <c r="I190" s="92"/>
+      <c r="J190" s="92"/>
     </row>
     <row r="191" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B191" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="C191" s="79" t="s">
-        <v>604</v>
-      </c>
-      <c r="D191" s="64" t="s">
-        <v>605</v>
-      </c>
-      <c r="E191" s="80" t="s">
+      <c r="C191" s="75" t="s">
+        <v>588</v>
+      </c>
+      <c r="D191" s="77" t="s">
+        <v>590</v>
+      </c>
+      <c r="E191" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F191" s="75" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="G191" s="74" t="s">
         <v>11</v>
@@ -10381,22 +10450,22 @@
     </row>
     <row r="192" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B192" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="C192" s="79" t="s">
-        <v>610</v>
-      </c>
-      <c r="D192" s="83" t="s">
-        <v>611</v>
-      </c>
-      <c r="E192" s="80" t="s">
+      <c r="C192" s="75" t="s">
+        <v>596</v>
+      </c>
+      <c r="D192" s="77" t="s">
+        <v>597</v>
+      </c>
+      <c r="E192" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F192" s="75" t="s">
-        <v>609</v>
+        <v>594</v>
       </c>
       <c r="G192" s="74" t="s">
         <v>11</v>
@@ -10413,22 +10482,22 @@
     </row>
     <row r="193" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="73">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B193" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C193" s="75" t="s">
-        <v>612</v>
-      </c>
-      <c r="D193" s="77" t="s">
-        <v>614</v>
+        <v>600</v>
+      </c>
+      <c r="D193" s="81" t="s">
+        <v>601</v>
       </c>
       <c r="E193" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F193" s="75" t="s">
-        <v>613</v>
+        <v>599</v>
       </c>
       <c r="G193" s="74" t="s">
         <v>11</v>
@@ -10445,22 +10514,22 @@
     </row>
     <row r="194" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B194" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="C194" s="75" t="s">
-        <v>620</v>
-      </c>
-      <c r="D194" s="83" t="s">
-        <v>619</v>
-      </c>
-      <c r="E194" s="74" t="s">
+      <c r="C194" s="79" t="s">
+        <v>604</v>
+      </c>
+      <c r="D194" s="64" t="s">
+        <v>605</v>
+      </c>
+      <c r="E194" s="80" t="s">
         <v>14</v>
       </c>
       <c r="F194" s="75" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="G194" s="74" t="s">
         <v>11</v>
@@ -10476,43 +10545,61 @@
       </c>
     </row>
     <row r="195" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="92" t="s">
-        <v>602</v>
-      </c>
-      <c r="B195" s="92"/>
-      <c r="C195" s="92"/>
-      <c r="D195" s="92"/>
-      <c r="E195" s="92"/>
-      <c r="F195" s="92"/>
-      <c r="G195" s="92"/>
-      <c r="H195" s="92"/>
-      <c r="I195" s="92"/>
-      <c r="J195" s="92"/>
+      <c r="A195" s="73">
+        <v>5</v>
+      </c>
+      <c r="B195" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C195" s="79" t="s">
+        <v>610</v>
+      </c>
+      <c r="D195" s="83" t="s">
+        <v>611</v>
+      </c>
+      <c r="E195" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="F195" s="75" t="s">
+        <v>609</v>
+      </c>
+      <c r="G195" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H195" s="74" t="s">
+        <v>527</v>
+      </c>
+      <c r="I195" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J195" s="74" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="196" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="73">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B196" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C196" s="75" t="s">
-        <v>634</v>
+        <v>612</v>
       </c>
       <c r="D196" s="77" t="s">
-        <v>637</v>
+        <v>614</v>
       </c>
       <c r="E196" s="74" t="s">
         <v>14</v>
       </c>
       <c r="F196" s="75" t="s">
-        <v>635</v>
+        <v>613</v>
       </c>
       <c r="G196" s="74" t="s">
         <v>11</v>
       </c>
       <c r="H196" s="74" t="s">
-        <v>636</v>
+        <v>527</v>
       </c>
       <c r="I196" s="74" t="s">
         <v>12</v>
@@ -10522,229 +10609,211 @@
       </c>
     </row>
     <row r="197" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="91" t="s">
+      <c r="A197" s="73">
+        <v>7</v>
+      </c>
+      <c r="B197" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C197" s="75" t="s">
+        <v>620</v>
+      </c>
+      <c r="D197" s="83" t="s">
+        <v>619</v>
+      </c>
+      <c r="E197" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F197" s="75" t="s">
+        <v>617</v>
+      </c>
+      <c r="G197" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H197" s="74" t="s">
+        <v>527</v>
+      </c>
+      <c r="I197" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J197" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="92" t="s">
+        <v>602</v>
+      </c>
+      <c r="B198" s="92"/>
+      <c r="C198" s="92"/>
+      <c r="D198" s="92"/>
+      <c r="E198" s="92"/>
+      <c r="F198" s="92"/>
+      <c r="G198" s="92"/>
+      <c r="H198" s="92"/>
+      <c r="I198" s="92"/>
+      <c r="J198" s="92"/>
+    </row>
+    <row r="199" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="73">
+        <v>1</v>
+      </c>
+      <c r="B199" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C199" s="75" t="s">
+        <v>634</v>
+      </c>
+      <c r="D199" s="77" t="s">
+        <v>637</v>
+      </c>
+      <c r="E199" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F199" s="75" t="s">
+        <v>635</v>
+      </c>
+      <c r="G199" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H199" s="74" t="s">
+        <v>636</v>
+      </c>
+      <c r="I199" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J199" s="74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="91" t="s">
         <v>665</v>
       </c>
-      <c r="B197" s="91"/>
-      <c r="C197" s="91"/>
-      <c r="D197" s="91"/>
-      <c r="E197" s="91"/>
-      <c r="F197" s="91"/>
-      <c r="G197" s="91"/>
-      <c r="H197" s="91"/>
-      <c r="I197" s="91"/>
-      <c r="J197" s="91"/>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A198" s="88">
+      <c r="B200" s="91"/>
+      <c r="C200" s="91"/>
+      <c r="D200" s="91"/>
+      <c r="E200" s="91"/>
+      <c r="F200" s="91"/>
+      <c r="G200" s="91"/>
+      <c r="H200" s="91"/>
+      <c r="I200" s="91"/>
+      <c r="J200" s="91"/>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" s="88">
         <v>1</v>
       </c>
-      <c r="B198" s="88" t="s">
+      <c r="B201" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="C198" s="89" t="s">
+      <c r="C201" s="89" t="s">
         <v>666</v>
       </c>
-      <c r="D198" s="45" t="s">
+      <c r="D201" s="45" t="s">
         <v>667</v>
       </c>
-      <c r="E198" s="51" t="s">
+      <c r="E201" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="F198" s="89" t="s">
+      <c r="F201" s="89" t="s">
         <v>668</v>
       </c>
-      <c r="G198" s="51" t="s">
+      <c r="G201" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="H198" s="51" t="s">
+      <c r="H201" s="51" t="s">
         <v>636</v>
       </c>
-      <c r="I198" s="51" t="s">
+      <c r="I201" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="J198" s="90" t="s">
+      <c r="J201" s="90" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A199" s="86">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202" s="86">
         <v>2</v>
       </c>
-      <c r="B199" s="86" t="s">
+      <c r="B202" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="C199" s="87" t="s">
+      <c r="C202" s="87" t="s">
         <v>669</v>
       </c>
-      <c r="D199" s="6" t="s">
+      <c r="D202" s="6" t="s">
         <v>671</v>
       </c>
-      <c r="E199" s="48" t="s">
+      <c r="E202" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F199" s="87" t="s">
+      <c r="F202" s="87" t="s">
         <v>670</v>
       </c>
-      <c r="G199" s="48" t="s">
+      <c r="G202" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H199" s="48" t="s">
+      <c r="H202" s="48" t="s">
         <v>636</v>
       </c>
-      <c r="I199" s="48" t="s">
+      <c r="I202" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J199" s="48" t="s">
+      <c r="J202" s="48" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A200" s="86">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203" s="86">
         <v>3</v>
       </c>
-      <c r="B200" s="86" t="s">
+      <c r="B203" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="C200" s="87" t="s">
+      <c r="C203" s="87" t="s">
         <v>673</v>
       </c>
-      <c r="D200" s="6" t="s">
+      <c r="D203" s="6" t="s">
         <v>674</v>
       </c>
-      <c r="E200" s="48" t="s">
+      <c r="E203" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F200" s="87" t="s">
+      <c r="F203" s="87" t="s">
         <v>672</v>
       </c>
-      <c r="G200" s="48" t="s">
+      <c r="G203" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H200" s="48" t="s">
+      <c r="H203" s="48" t="s">
         <v>636</v>
       </c>
-      <c r="I200" s="48" t="s">
+      <c r="I203" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J200" s="48" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A201" s="28">
-        <v>4</v>
-      </c>
-      <c r="B201" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C201" s="28" t="s">
-        <v>682</v>
-      </c>
-      <c r="D201" s="28" t="s">
-        <v>683</v>
-      </c>
-      <c r="E201" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="F201" s="28" t="s">
-        <v>684</v>
-      </c>
-      <c r="G201" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="H201" s="28" t="s">
-        <v>636</v>
-      </c>
-      <c r="I201" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="J201" s="28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A202" s="28">
-        <v>5</v>
-      </c>
-      <c r="B202" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C202" s="28" t="s">
-        <v>685</v>
-      </c>
-      <c r="D202" s="28" t="s">
-        <v>713</v>
-      </c>
-      <c r="E202" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="F202" s="28" t="s">
-        <v>686</v>
-      </c>
-      <c r="G202" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="H202" s="28" t="s">
-        <v>636</v>
-      </c>
-      <c r="I202" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="J202" s="28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A203" s="28">
-        <v>6</v>
-      </c>
-      <c r="B203" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C203" s="28" t="s">
-        <v>687</v>
-      </c>
-      <c r="D203" s="28" t="s">
-        <v>688</v>
-      </c>
-      <c r="E203" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="F203" s="28" t="s">
-        <v>689</v>
-      </c>
-      <c r="G203" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="H203" s="28" t="s">
-        <v>636</v>
-      </c>
-      <c r="I203" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="J203" s="28" t="s">
+      <c r="J203" s="48" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B204" s="28" t="s">
         <v>10</v>
       </c>
       <c r="C204" s="28" t="s">
-        <v>712</v>
+        <v>682</v>
       </c>
       <c r="D204" s="28" t="s">
-        <v>711</v>
+        <v>683</v>
       </c>
       <c r="E204" s="28" t="s">
         <v>14</v>
       </c>
       <c r="F204" s="28" t="s">
-        <v>710</v>
+        <v>684</v>
       </c>
       <c r="G204" s="28" t="s">
         <v>11</v>
@@ -10756,6 +10825,102 @@
         <v>12</v>
       </c>
       <c r="J204" s="28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205" s="28">
+        <v>5</v>
+      </c>
+      <c r="B205" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C205" s="28" t="s">
+        <v>685</v>
+      </c>
+      <c r="D205" s="28" t="s">
+        <v>713</v>
+      </c>
+      <c r="E205" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F205" s="28" t="s">
+        <v>686</v>
+      </c>
+      <c r="G205" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H205" s="28" t="s">
+        <v>636</v>
+      </c>
+      <c r="I205" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="J205" s="28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" s="28">
+        <v>6</v>
+      </c>
+      <c r="B206" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C206" s="28" t="s">
+        <v>687</v>
+      </c>
+      <c r="D206" s="28" t="s">
+        <v>688</v>
+      </c>
+      <c r="E206" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F206" s="28" t="s">
+        <v>689</v>
+      </c>
+      <c r="G206" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H206" s="28" t="s">
+        <v>636</v>
+      </c>
+      <c r="I206" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="J206" s="28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207" s="28">
+        <v>7</v>
+      </c>
+      <c r="B207" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C207" s="28" t="s">
+        <v>712</v>
+      </c>
+      <c r="D207" s="28" t="s">
+        <v>711</v>
+      </c>
+      <c r="E207" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F207" s="28" t="s">
+        <v>710</v>
+      </c>
+      <c r="G207" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H207" s="28" t="s">
+        <v>636</v>
+      </c>
+      <c r="I207" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="J207" s="28" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10766,15 +10931,15 @@
     <mergeCell ref="A59:J59"/>
     <mergeCell ref="A70:J70"/>
     <mergeCell ref="A82:J82"/>
-    <mergeCell ref="A197:J197"/>
+    <mergeCell ref="A200:J200"/>
     <mergeCell ref="A125:J125"/>
     <mergeCell ref="A123:J123"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A110:J110"/>
-    <mergeCell ref="A195:J195"/>
-    <mergeCell ref="A187:J187"/>
+    <mergeCell ref="A198:J198"/>
+    <mergeCell ref="A190:J190"/>
+    <mergeCell ref="A171:J171"/>
     <mergeCell ref="A168:J168"/>
-    <mergeCell ref="A165:J165"/>
     <mergeCell ref="A143:J143"/>
     <mergeCell ref="A154:J154"/>
   </mergeCells>
@@ -10874,7 +11039,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:X198"/>
+  <dimension ref="A1:X201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -22665,1191 +22830,1191 @@
     </row>
     <row r="163" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A163" s="48" t="s">
+        <v>717</v>
+      </c>
+      <c r="B163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W163" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X163" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="164" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A164" s="48" t="s">
+        <v>721</v>
+      </c>
+      <c r="B164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W164" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X164" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="165" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A165" s="48" t="s">
+        <v>722</v>
+      </c>
+      <c r="B165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W165" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X165" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="166" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A166" s="48" t="s">
         <v>496</v>
       </c>
-      <c r="B163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W163" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X163" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="164" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="48" t="s">
+      <c r="B166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W166" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X166" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="167" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="48" t="s">
         <v>631</v>
       </c>
-      <c r="B164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W164" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X164" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="165" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="67" t="s">
+      <c r="B167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W167" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X167" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="168" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="67" t="s">
         <v>526</v>
       </c>
-      <c r="B165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W165" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X165" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="166" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="70" t="s">
+      <c r="B168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W168" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X168" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="169" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="70" t="s">
         <v>530</v>
       </c>
-      <c r="B166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W166" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X166" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="167" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="67" t="s">
+      <c r="B169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W169" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X169" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="170" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="67" t="s">
         <v>533</v>
       </c>
-      <c r="B167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W167" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X167" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="168" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="70" t="s">
+      <c r="B170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W170" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X170" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="171" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="B168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W168" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X168" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="169" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="67" t="s">
+      <c r="B171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W171" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X171" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="172" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="67" t="s">
         <v>538</v>
       </c>
-      <c r="B169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W169" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X169" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="170" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="70" t="s">
+      <c r="B172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W172" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X172" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="173" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="70" t="s">
         <v>540</v>
       </c>
-      <c r="B170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W170" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X170" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="171" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="67" t="s">
+      <c r="B173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W173" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X173" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="174" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="67" t="s">
         <v>542</v>
       </c>
-      <c r="B171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W171" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X171" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="172" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="70" t="s">
+      <c r="B174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W174" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X174" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="175" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="70" t="s">
         <v>544</v>
       </c>
-      <c r="B172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W172" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X172" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="173" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="67" t="s">
+      <c r="B175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W175" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X175" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="176" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="67" t="s">
         <v>546</v>
       </c>
-      <c r="B173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W173" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X173" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="174" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="70" t="s">
+      <c r="B176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W176" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X176" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="177" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="70" t="s">
         <v>549</v>
       </c>
-      <c r="B174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W174" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X174" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="175" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="67" t="s">
+      <c r="B177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W177" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X177" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="178" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="67" t="s">
         <v>552</v>
       </c>
-      <c r="B175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W175" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X175" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="176" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="70" t="s">
+      <c r="B178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W178" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X178" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="179" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="70" t="s">
         <v>555</v>
-      </c>
-      <c r="B176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W176" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X176" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="177" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="67" t="s">
-        <v>558</v>
-      </c>
-      <c r="B177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W177" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X177" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="178" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="70" t="s">
-        <v>561</v>
-      </c>
-      <c r="B178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W178" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X178" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="179" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="67" t="s">
-        <v>564</v>
       </c>
       <c r="B179" s="48" t="s">
         <v>22</v>
@@ -23923,360 +24088,408 @@
     </row>
     <row r="180" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="67" t="s">
+        <v>558</v>
+      </c>
+      <c r="B180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W180" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X180" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="181" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="70" t="s">
+        <v>561</v>
+      </c>
+      <c r="B181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W181" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X181" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="182" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="67" t="s">
+        <v>564</v>
+      </c>
+      <c r="B182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W182" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X182" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="183" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="67" t="s">
         <v>566</v>
       </c>
-      <c r="B180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W180" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X180" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="181" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="67" t="s">
+      <c r="B183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W183" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X183" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="184" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="67" t="s">
         <v>568</v>
       </c>
-      <c r="B181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W181" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X181" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="182" spans="1:24" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="67" t="s">
+      <c r="B184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W184" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X184" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="185" spans="1:24" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="67" t="s">
         <v>571</v>
       </c>
-      <c r="B182" s="48" t="s">
+      <c r="B185" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="C182" s="36" t="s">
+      <c r="C185" s="36" t="s">
         <v>463</v>
       </c>
-      <c r="D182" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E182" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F182" s="48" t="s">
+      <c r="D185" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E185" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F185" s="48" t="s">
         <v>464</v>
       </c>
-      <c r="G182" s="49" t="s">
+      <c r="G185" s="49" t="s">
         <v>465</v>
       </c>
-      <c r="H182" s="48" t="s">
+      <c r="H185" s="48" t="s">
         <v>466</v>
       </c>
-      <c r="I182" s="48" t="s">
+      <c r="I185" s="48" t="s">
         <v>483</v>
       </c>
-      <c r="J182" s="36" t="s">
+      <c r="J185" s="36" t="s">
         <v>484</v>
       </c>
-      <c r="K182" s="48" t="s">
+      <c r="K185" s="48" t="s">
         <v>485</v>
       </c>
-      <c r="L182" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M182" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N182" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O182" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P182" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q182" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R182" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S182" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T182" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U182" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V182" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W182" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="X182" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="183" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="82"/>
-      <c r="B183" s="48"/>
-      <c r="C183" s="36"/>
-      <c r="D183" s="48"/>
-      <c r="E183" s="48"/>
-      <c r="F183" s="48"/>
-      <c r="G183" s="49"/>
-      <c r="H183" s="48"/>
-      <c r="I183" s="48"/>
-      <c r="J183" s="36"/>
-      <c r="K183" s="48"/>
-      <c r="L183" s="48"/>
-      <c r="M183" s="48"/>
-      <c r="N183" s="48"/>
-      <c r="O183" s="48"/>
-      <c r="P183" s="48"/>
-      <c r="Q183" s="48"/>
-      <c r="R183" s="48"/>
-      <c r="S183" s="48"/>
-      <c r="T183" s="48"/>
-      <c r="U183" s="48"/>
-      <c r="V183" s="48"/>
-      <c r="W183" s="48"/>
-      <c r="X183" s="48"/>
-    </row>
-    <row r="184" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="75" t="s">
-        <v>589</v>
-      </c>
-      <c r="B184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S184" s="49" t="s">
-        <v>591</v>
-      </c>
-      <c r="T184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U184" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V184" s="48" t="s">
-        <v>607</v>
-      </c>
-      <c r="W184" s="36" t="s">
-        <v>593</v>
-      </c>
-      <c r="X184" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="185" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="75" t="s">
-        <v>594</v>
-      </c>
-      <c r="B185" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C185" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D185" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E185" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F185" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G185" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H185" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I185" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J185" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K185" s="48" t="s">
-        <v>22</v>
-      </c>
       <c r="L185" s="48" t="s">
         <v>22</v>
       </c>
@@ -24298,8 +24511,8 @@
       <c r="R185" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="S185" s="49" t="s">
-        <v>595</v>
+      <c r="S185" s="48" t="s">
+        <v>22</v>
       </c>
       <c r="T185" s="48" t="s">
         <v>22</v>
@@ -24310,90 +24523,42 @@
       <c r="V185" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="W185" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X185" s="78" t="s">
-        <v>615</v>
+      <c r="W185" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="X185" s="48" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="186" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="75" t="s">
-        <v>599</v>
-      </c>
-      <c r="B186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S186" s="49" t="s">
-        <v>595</v>
-      </c>
-      <c r="T186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V186" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W186" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X186" s="84" t="s">
-        <v>616</v>
-      </c>
+      <c r="A186" s="82"/>
+      <c r="B186" s="48"/>
+      <c r="C186" s="36"/>
+      <c r="D186" s="48"/>
+      <c r="E186" s="48"/>
+      <c r="F186" s="48"/>
+      <c r="G186" s="49"/>
+      <c r="H186" s="48"/>
+      <c r="I186" s="48"/>
+      <c r="J186" s="36"/>
+      <c r="K186" s="48"/>
+      <c r="L186" s="48"/>
+      <c r="M186" s="48"/>
+      <c r="N186" s="48"/>
+      <c r="O186" s="48"/>
+      <c r="P186" s="48"/>
+      <c r="Q186" s="48"/>
+      <c r="R186" s="48"/>
+      <c r="S186" s="48"/>
+      <c r="T186" s="48"/>
+      <c r="U186" s="48"/>
+      <c r="V186" s="48"/>
+      <c r="W186" s="48"/>
+      <c r="X186" s="48"/>
     </row>
     <row r="187" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="75" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="B187" s="48" t="s">
         <v>22</v>
@@ -24456,10 +24621,10 @@
         <v>22</v>
       </c>
       <c r="V187" s="48" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="W187" s="36" t="s">
-        <v>22</v>
+        <v>593</v>
       </c>
       <c r="X187" s="48" t="s">
         <v>22</v>
@@ -24467,7 +24632,7 @@
     </row>
     <row r="188" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="75" t="s">
-        <v>609</v>
+        <v>594</v>
       </c>
       <c r="B188" s="48" t="s">
         <v>22</v>
@@ -24535,13 +24700,13 @@
       <c r="W188" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="X188" s="48" t="s">
-        <v>22</v>
+      <c r="X188" s="78" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="189" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="75" t="s">
-        <v>613</v>
+        <v>599</v>
       </c>
       <c r="B189" s="48" t="s">
         <v>22</v>
@@ -24609,13 +24774,13 @@
       <c r="W189" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="X189" s="85" t="s">
-        <v>615</v>
+      <c r="X189" s="84" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="190" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="75" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="B190" s="48" t="s">
         <v>22</v>
@@ -24669,7 +24834,7 @@
         <v>22</v>
       </c>
       <c r="S190" s="49" t="s">
-        <v>618</v>
+        <v>591</v>
       </c>
       <c r="T190" s="48" t="s">
         <v>22</v>
@@ -24678,7 +24843,7 @@
         <v>22</v>
       </c>
       <c r="V190" s="48" t="s">
-        <v>22</v>
+        <v>608</v>
       </c>
       <c r="W190" s="36" t="s">
         <v>22</v>
@@ -24689,7 +24854,7 @@
     </row>
     <row r="191" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="75" t="s">
-        <v>635</v>
+        <v>609</v>
       </c>
       <c r="B191" s="48" t="s">
         <v>22</v>
@@ -24742,8 +24907,8 @@
       <c r="R191" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="S191" s="48" t="s">
-        <v>22</v>
+      <c r="S191" s="49" t="s">
+        <v>595</v>
       </c>
       <c r="T191" s="48" t="s">
         <v>22</v>
@@ -24763,7 +24928,7 @@
     </row>
     <row r="192" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="75" t="s">
-        <v>668</v>
+        <v>613</v>
       </c>
       <c r="B192" s="48" t="s">
         <v>22</v>
@@ -24816,8 +24981,8 @@
       <c r="R192" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="S192" s="48" t="s">
-        <v>22</v>
+      <c r="S192" s="49" t="s">
+        <v>595</v>
       </c>
       <c r="T192" s="48" t="s">
         <v>22</v>
@@ -24831,13 +24996,13 @@
       <c r="W192" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="X192" s="48" t="s">
-        <v>22</v>
+      <c r="X192" s="85" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="193" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="75" t="s">
-        <v>670</v>
+        <v>617</v>
       </c>
       <c r="B193" s="48" t="s">
         <v>22</v>
@@ -24890,8 +25055,8 @@
       <c r="R193" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="S193" s="48" t="s">
-        <v>22</v>
+      <c r="S193" s="49" t="s">
+        <v>618</v>
       </c>
       <c r="T193" s="48" t="s">
         <v>22</v>
@@ -24911,7 +25076,7 @@
     </row>
     <row r="194" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="75" t="s">
-        <v>672</v>
+        <v>635</v>
       </c>
       <c r="B194" s="48" t="s">
         <v>22</v>
@@ -24985,7 +25150,7 @@
     </row>
     <row r="195" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="75" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="B195" s="48" t="s">
         <v>22</v>
@@ -25059,7 +25224,7 @@
     </row>
     <row r="196" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="75" t="s">
-        <v>686</v>
+        <v>670</v>
       </c>
       <c r="B196" s="48" t="s">
         <v>22</v>
@@ -25133,7 +25298,7 @@
     </row>
     <row r="197" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="75" t="s">
-        <v>689</v>
+        <v>672</v>
       </c>
       <c r="B197" s="48" t="s">
         <v>22</v>
@@ -25207,75 +25372,297 @@
     </row>
     <row r="198" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="75" t="s">
+        <v>684</v>
+      </c>
+      <c r="B198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V198" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W198" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X198" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="199" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="75" t="s">
+        <v>686</v>
+      </c>
+      <c r="B199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V199" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W199" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X199" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="200" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="75" t="s">
+        <v>689</v>
+      </c>
+      <c r="B200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V200" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W200" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X200" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="201" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="75" t="s">
         <v>710</v>
       </c>
-      <c r="B198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V198" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="W198" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="X198" s="48" t="s">
+      <c r="B201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V201" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W201" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X201" s="48" t="s">
         <v>22</v>
       </c>
     </row>
@@ -25402,13 +25789,13 @@
     <hyperlink ref="G126" r:id="rId14" xr:uid="{009DD950-489A-4511-9EE8-3302596C4B91}"/>
     <hyperlink ref="G131" r:id="rId15" xr:uid="{FEC9AB2B-6FD0-4D08-96BB-5634F117BFB0}"/>
     <hyperlink ref="D141" r:id="rId16" xr:uid="{EAE526E7-10C0-4EC9-846A-D81343ACBEC4}"/>
-    <hyperlink ref="G182" r:id="rId17" xr:uid="{0A52F660-ABF2-41CF-BD4C-5E55458D590D}"/>
-    <hyperlink ref="S184" r:id="rId18" xr:uid="{13FB8A07-5562-4AAB-9E83-934C01965617}"/>
-    <hyperlink ref="S186" r:id="rId19" xr:uid="{23F160B7-D3CD-415D-B0D6-1EECB7AFE96F}"/>
-    <hyperlink ref="S187" r:id="rId20" xr:uid="{7206C778-989C-4587-83FA-C09C20DA42BD}"/>
-    <hyperlink ref="S188" r:id="rId21" xr:uid="{3B0D666D-626C-490D-A9B6-B9643B9EDF8A}"/>
-    <hyperlink ref="X185" r:id="rId22" tooltip="pink real heaven" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{7AB2CC85-055B-4B62-B758-A407CA7BD409}"/>
-    <hyperlink ref="X189" r:id="rId23" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{E6426F17-2EE7-4F4A-80B0-E58B87C35EDA}"/>
+    <hyperlink ref="G185" r:id="rId17" xr:uid="{0A52F660-ABF2-41CF-BD4C-5E55458D590D}"/>
+    <hyperlink ref="S187" r:id="rId18" xr:uid="{13FB8A07-5562-4AAB-9E83-934C01965617}"/>
+    <hyperlink ref="S189" r:id="rId19" xr:uid="{23F160B7-D3CD-415D-B0D6-1EECB7AFE96F}"/>
+    <hyperlink ref="S190" r:id="rId20" xr:uid="{7206C778-989C-4587-83FA-C09C20DA42BD}"/>
+    <hyperlink ref="S191" r:id="rId21" xr:uid="{3B0D666D-626C-490D-A9B6-B9643B9EDF8A}"/>
+    <hyperlink ref="X188" r:id="rId22" tooltip="pink real heaven" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{7AB2CC85-055B-4B62-B758-A407CA7BD409}"/>
+    <hyperlink ref="X192" r:id="rId23" display="https://qa.zlta.testingserver8.com/product-detail/pink-real-heaven" xr:uid="{E6426F17-2EE7-4F4A-80B0-E58B87C35EDA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId24"/>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\Zlaata06042026\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\ZlaataNew19072026\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6D6DDC-C41C-4F63-98CC-E68AB8963119}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A487A85F-B99F-4D71-8E71-22E4C1D513C8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6491" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6921" uniqueCount="771">
   <si>
     <t>S.No</t>
   </si>
@@ -2219,6 +2219,126 @@
   </si>
   <si>
     <t>Verify that the user is able to click on a color dot for a product on the product listing page</t>
+  </si>
+  <si>
+    <t>Before Login</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_BL_01</t>
+  </si>
+  <si>
+    <t>Verify login popup appears when guest user clicks Wishlist icon from header section</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_BL_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_BL_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_BL_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_BL_04</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_BL_05</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_BL_06</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_BL_02</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_BL_03</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_BL_04</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_BL_05</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_BL_06</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_BL_07</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_BL_07</t>
+  </si>
+  <si>
+    <t>Verify login popup appears when guest user clicks Profile icon in header</t>
+  </si>
+  <si>
+    <t>Verify login popup appears when guest user clicks Wishlist icon on product listing page</t>
+  </si>
+  <si>
+    <t>Verify login popup appears when guest user clicks Wishlist icon on product details page</t>
+  </si>
+  <si>
+    <t>Verify login popup appears when guest user clicks Move to Wishlist icon on cart page</t>
+  </si>
+  <si>
+    <t>Verify login popup appears when guest user clicks View Coupons on cart page</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_BL_08</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_BL_09</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_BL_10</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_BL_11</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_BL_12</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_BL_08</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_BL_09</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_BL_10</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_BL_11</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_BL_12</t>
+  </si>
+  <si>
+    <t>Verify login popup appears when guest user clicks Apply button in coupon section on cart page</t>
+  </si>
+  <si>
+    <t>Verify validation message appears when guest user clicks Gift Card Amount section on cart page</t>
+  </si>
+  <si>
+    <t>Verify validation message appears when guest user clicks Threads on cart page</t>
+  </si>
+  <si>
+    <t>Verify login popup appears when guest user clicks Place Order button on cart page</t>
+  </si>
+  <si>
+    <t>Verify login popup appears when guest user clicks Threads action buttons</t>
+  </si>
+  <si>
+    <t>Verify login popup appears when guest user clicks Game icon</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_BL_1</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_BL_1</t>
+  </si>
+  <si>
+    <t>Verify login popup appears when guest user clicks Profile icon in the Landing Page</t>
   </si>
 </sst>
 </file>
@@ -2685,7 +2805,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2917,26 +3037,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2955,6 +3064,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3758,7 +3888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z209"/>
+  <dimension ref="A1:Z223"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
@@ -4509,18 +4639,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="98" t="s">
+      <c r="A24" s="95" t="s">
         <v>155</v>
       </c>
-      <c r="B24" s="99"/>
-      <c r="C24" s="99"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="99"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="99"/>
-      <c r="J24" s="100"/>
+      <c r="B24" s="96"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="96"/>
+      <c r="E24" s="96"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="96"/>
+      <c r="H24" s="96"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="97"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
@@ -4907,18 +5037,18 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="101" t="s">
+      <c r="A37" s="98" t="s">
         <v>170</v>
       </c>
-      <c r="B37" s="102"/>
-      <c r="C37" s="102"/>
-      <c r="D37" s="102"/>
-      <c r="E37" s="102"/>
-      <c r="F37" s="102"/>
-      <c r="G37" s="102"/>
-      <c r="H37" s="102"/>
-      <c r="I37" s="102"/>
-      <c r="J37" s="103"/>
+      <c r="B37" s="99"/>
+      <c r="C37" s="99"/>
+      <c r="D37" s="99"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="99"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="99"/>
+      <c r="J37" s="100"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
@@ -5593,18 +5723,18 @@
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="98" t="s">
+      <c r="A59" s="95" t="s">
         <v>234</v>
       </c>
-      <c r="B59" s="99"/>
-      <c r="C59" s="99"/>
-      <c r="D59" s="99"/>
-      <c r="E59" s="99"/>
-      <c r="F59" s="99"/>
-      <c r="G59" s="99"/>
-      <c r="H59" s="99"/>
-      <c r="I59" s="99"/>
-      <c r="J59" s="100"/>
+      <c r="B59" s="96"/>
+      <c r="C59" s="96"/>
+      <c r="D59" s="96"/>
+      <c r="E59" s="96"/>
+      <c r="F59" s="96"/>
+      <c r="G59" s="96"/>
+      <c r="H59" s="96"/>
+      <c r="I59" s="96"/>
+      <c r="J59" s="97"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="25">
@@ -5927,18 +6057,18 @@
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="101" t="s">
+      <c r="A70" s="98" t="s">
         <v>236</v>
       </c>
-      <c r="B70" s="102"/>
-      <c r="C70" s="102"/>
-      <c r="D70" s="102"/>
-      <c r="E70" s="102"/>
-      <c r="F70" s="102"/>
-      <c r="G70" s="102"/>
-      <c r="H70" s="102"/>
-      <c r="I70" s="102"/>
-      <c r="J70" s="103"/>
+      <c r="B70" s="99"/>
+      <c r="C70" s="99"/>
+      <c r="D70" s="99"/>
+      <c r="E70" s="99"/>
+      <c r="F70" s="99"/>
+      <c r="G70" s="99"/>
+      <c r="H70" s="99"/>
+      <c r="I70" s="99"/>
+      <c r="J70" s="100"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="25">
@@ -6357,18 +6487,18 @@
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="101" t="s">
+      <c r="A84" s="98" t="s">
         <v>334</v>
       </c>
-      <c r="B84" s="102"/>
-      <c r="C84" s="102"/>
-      <c r="D84" s="102"/>
-      <c r="E84" s="102"/>
-      <c r="F84" s="102"/>
-      <c r="G84" s="102"/>
-      <c r="H84" s="102"/>
-      <c r="I84" s="102"/>
-      <c r="J84" s="103"/>
+      <c r="B84" s="99"/>
+      <c r="C84" s="99"/>
+      <c r="D84" s="99"/>
+      <c r="E84" s="99"/>
+      <c r="F84" s="99"/>
+      <c r="G84" s="99"/>
+      <c r="H84" s="99"/>
+      <c r="I84" s="99"/>
+      <c r="J84" s="100"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="25">
@@ -7235,18 +7365,18 @@
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="93" t="s">
+      <c r="A112" s="101" t="s">
         <v>364</v>
       </c>
-      <c r="B112" s="93"/>
-      <c r="C112" s="93"/>
-      <c r="D112" s="93"/>
-      <c r="E112" s="93"/>
-      <c r="F112" s="93"/>
-      <c r="G112" s="93"/>
-      <c r="H112" s="93"/>
-      <c r="I112" s="93"/>
-      <c r="J112" s="93"/>
+      <c r="B112" s="101"/>
+      <c r="C112" s="101"/>
+      <c r="D112" s="101"/>
+      <c r="E112" s="101"/>
+      <c r="F112" s="101"/>
+      <c r="G112" s="101"/>
+      <c r="H112" s="101"/>
+      <c r="I112" s="101"/>
+      <c r="J112" s="101"/>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" s="25">
@@ -7569,18 +7699,18 @@
       </c>
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A123" s="92" t="s">
+      <c r="A123" s="102" t="s">
         <v>366</v>
       </c>
-      <c r="B123" s="92"/>
-      <c r="C123" s="92"/>
-      <c r="D123" s="92"/>
-      <c r="E123" s="92"/>
-      <c r="F123" s="92"/>
-      <c r="G123" s="92"/>
-      <c r="H123" s="92"/>
-      <c r="I123" s="92"/>
-      <c r="J123" s="92"/>
+      <c r="B123" s="102"/>
+      <c r="C123" s="102"/>
+      <c r="D123" s="102"/>
+      <c r="E123" s="102"/>
+      <c r="F123" s="102"/>
+      <c r="G123" s="102"/>
+      <c r="H123" s="102"/>
+      <c r="I123" s="102"/>
+      <c r="J123" s="102"/>
     </row>
     <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" s="25">
@@ -7615,18 +7745,18 @@
       </c>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="92" t="s">
+      <c r="A125" s="102" t="s">
         <v>371</v>
       </c>
-      <c r="B125" s="92"/>
-      <c r="C125" s="92"/>
-      <c r="D125" s="92"/>
-      <c r="E125" s="92"/>
-      <c r="F125" s="92"/>
-      <c r="G125" s="92"/>
-      <c r="H125" s="92"/>
-      <c r="I125" s="92"/>
-      <c r="J125" s="92"/>
+      <c r="B125" s="102"/>
+      <c r="C125" s="102"/>
+      <c r="D125" s="102"/>
+      <c r="E125" s="102"/>
+      <c r="F125" s="102"/>
+      <c r="G125" s="102"/>
+      <c r="H125" s="102"/>
+      <c r="I125" s="102"/>
+      <c r="J125" s="102"/>
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126" s="25">
@@ -7661,18 +7791,18 @@
       </c>
     </row>
     <row r="127" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="92" t="s">
+      <c r="A127" s="102" t="s">
         <v>384</v>
       </c>
-      <c r="B127" s="92"/>
-      <c r="C127" s="92"/>
-      <c r="D127" s="92"/>
-      <c r="E127" s="92"/>
-      <c r="F127" s="92"/>
-      <c r="G127" s="92"/>
-      <c r="H127" s="92"/>
-      <c r="I127" s="92"/>
-      <c r="J127" s="92"/>
+      <c r="B127" s="102"/>
+      <c r="C127" s="102"/>
+      <c r="D127" s="102"/>
+      <c r="E127" s="102"/>
+      <c r="F127" s="102"/>
+      <c r="G127" s="102"/>
+      <c r="H127" s="102"/>
+      <c r="I127" s="102"/>
+      <c r="J127" s="102"/>
     </row>
     <row r="128" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="25">
@@ -8457,18 +8587,18 @@
       <c r="X144" s="58"/>
     </row>
     <row r="145" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="92" t="s">
+      <c r="A145" s="102" t="s">
         <v>396</v>
       </c>
-      <c r="B145" s="92"/>
-      <c r="C145" s="92"/>
-      <c r="D145" s="94"/>
-      <c r="E145" s="94"/>
-      <c r="F145" s="94"/>
-      <c r="G145" s="94"/>
-      <c r="H145" s="94"/>
-      <c r="I145" s="94"/>
-      <c r="J145" s="94"/>
+      <c r="B145" s="102"/>
+      <c r="C145" s="102"/>
+      <c r="D145" s="103"/>
+      <c r="E145" s="103"/>
+      <c r="F145" s="103"/>
+      <c r="G145" s="103"/>
+      <c r="H145" s="103"/>
+      <c r="I145" s="103"/>
+      <c r="J145" s="103"/>
     </row>
     <row r="146" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="59">
@@ -8931,18 +9061,18 @@
       <c r="X155" s="58"/>
     </row>
     <row r="156" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="95" t="s">
+      <c r="A156" s="104" t="s">
         <v>425</v>
       </c>
-      <c r="B156" s="96"/>
-      <c r="C156" s="96"/>
-      <c r="D156" s="96"/>
-      <c r="E156" s="96"/>
-      <c r="F156" s="96"/>
-      <c r="G156" s="96"/>
-      <c r="H156" s="96"/>
-      <c r="I156" s="96"/>
-      <c r="J156" s="97"/>
+      <c r="B156" s="105"/>
+      <c r="C156" s="105"/>
+      <c r="D156" s="105"/>
+      <c r="E156" s="105"/>
+      <c r="F156" s="105"/>
+      <c r="G156" s="105"/>
+      <c r="H156" s="105"/>
+      <c r="I156" s="105"/>
+      <c r="J156" s="106"/>
     </row>
     <row r="157" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="25">
@@ -9529,18 +9659,18 @@
       <c r="X169" s="58"/>
     </row>
     <row r="170" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A170" s="92" t="s">
+      <c r="A170" s="102" t="s">
         <v>497</v>
       </c>
-      <c r="B170" s="92"/>
-      <c r="C170" s="92"/>
-      <c r="D170" s="92"/>
-      <c r="E170" s="92"/>
-      <c r="F170" s="92"/>
-      <c r="G170" s="92"/>
-      <c r="H170" s="92"/>
-      <c r="I170" s="92"/>
-      <c r="J170" s="92"/>
+      <c r="B170" s="102"/>
+      <c r="C170" s="102"/>
+      <c r="D170" s="102"/>
+      <c r="E170" s="102"/>
+      <c r="F170" s="102"/>
+      <c r="G170" s="102"/>
+      <c r="H170" s="102"/>
+      <c r="I170" s="102"/>
+      <c r="J170" s="102"/>
     </row>
     <row r="171" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A171" s="25">
@@ -9607,18 +9737,18 @@
       </c>
     </row>
     <row r="173" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="92" t="s">
+      <c r="A173" s="102" t="s">
         <v>523</v>
       </c>
-      <c r="B173" s="92"/>
-      <c r="C173" s="92"/>
-      <c r="D173" s="92"/>
-      <c r="E173" s="92"/>
-      <c r="F173" s="92"/>
-      <c r="G173" s="92"/>
-      <c r="H173" s="92"/>
-      <c r="I173" s="92"/>
-      <c r="J173" s="92"/>
+      <c r="B173" s="102"/>
+      <c r="C173" s="102"/>
+      <c r="D173" s="102"/>
+      <c r="E173" s="102"/>
+      <c r="F173" s="102"/>
+      <c r="G173" s="102"/>
+      <c r="H173" s="102"/>
+      <c r="I173" s="102"/>
+      <c r="J173" s="102"/>
     </row>
     <row r="174" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="65">
@@ -10485,18 +10615,18 @@
       <c r="Z191" s="58"/>
     </row>
     <row r="192" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="92" t="s">
+      <c r="A192" s="102" t="s">
         <v>602</v>
       </c>
-      <c r="B192" s="92"/>
-      <c r="C192" s="92"/>
-      <c r="D192" s="92"/>
-      <c r="E192" s="92"/>
-      <c r="F192" s="92"/>
-      <c r="G192" s="92"/>
-      <c r="H192" s="92"/>
-      <c r="I192" s="92"/>
-      <c r="J192" s="92"/>
+      <c r="B192" s="102"/>
+      <c r="C192" s="102"/>
+      <c r="D192" s="102"/>
+      <c r="E192" s="102"/>
+      <c r="F192" s="102"/>
+      <c r="G192" s="102"/>
+      <c r="H192" s="102"/>
+      <c r="I192" s="102"/>
+      <c r="J192" s="102"/>
     </row>
     <row r="193" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="73">
@@ -10723,18 +10853,18 @@
       </c>
     </row>
     <row r="200" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="92" t="s">
+      <c r="A200" s="102" t="s">
         <v>602</v>
       </c>
-      <c r="B200" s="92"/>
-      <c r="C200" s="92"/>
-      <c r="D200" s="92"/>
-      <c r="E200" s="92"/>
-      <c r="F200" s="92"/>
-      <c r="G200" s="92"/>
-      <c r="H200" s="92"/>
-      <c r="I200" s="92"/>
-      <c r="J200" s="92"/>
+      <c r="B200" s="102"/>
+      <c r="C200" s="102"/>
+      <c r="D200" s="102"/>
+      <c r="E200" s="102"/>
+      <c r="F200" s="102"/>
+      <c r="G200" s="102"/>
+      <c r="H200" s="102"/>
+      <c r="I200" s="102"/>
+      <c r="J200" s="102"/>
     </row>
     <row r="201" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="73">
@@ -10769,18 +10899,18 @@
       </c>
     </row>
     <row r="202" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="91" t="s">
+      <c r="A202" s="107" t="s">
         <v>665</v>
       </c>
-      <c r="B202" s="91"/>
-      <c r="C202" s="91"/>
-      <c r="D202" s="91"/>
-      <c r="E202" s="91"/>
-      <c r="F202" s="91"/>
-      <c r="G202" s="91"/>
-      <c r="H202" s="91"/>
-      <c r="I202" s="91"/>
-      <c r="J202" s="91"/>
+      <c r="B202" s="107"/>
+      <c r="C202" s="107"/>
+      <c r="D202" s="107"/>
+      <c r="E202" s="107"/>
+      <c r="F202" s="107"/>
+      <c r="G202" s="107"/>
+      <c r="H202" s="107"/>
+      <c r="I202" s="107"/>
+      <c r="J202" s="107"/>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="88">
@@ -10974,7 +11104,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="28">
         <v>7</v>
       </c>
@@ -11006,13 +11136,439 @@
         <v>13</v>
       </c>
     </row>
+    <row r="210" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="107" t="s">
+        <v>731</v>
+      </c>
+      <c r="B210" s="107"/>
+      <c r="C210" s="107"/>
+      <c r="D210" s="107"/>
+      <c r="E210" s="107"/>
+      <c r="F210" s="107"/>
+      <c r="G210" s="107"/>
+      <c r="H210" s="107"/>
+      <c r="I210" s="107"/>
+      <c r="J210" s="107"/>
+    </row>
+    <row r="211" spans="1:10" s="92" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="91">
+        <v>1</v>
+      </c>
+      <c r="B211" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C211" s="89" t="s">
+        <v>769</v>
+      </c>
+      <c r="D211" s="94" t="s">
+        <v>770</v>
+      </c>
+      <c r="E211" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F211" s="89" t="s">
+        <v>768</v>
+      </c>
+      <c r="G211" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H211" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="I211" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J211" s="90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="93">
+        <v>2</v>
+      </c>
+      <c r="B212" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C212" s="89" t="s">
+        <v>732</v>
+      </c>
+      <c r="D212" s="45" t="s">
+        <v>747</v>
+      </c>
+      <c r="E212" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F212" s="89" t="s">
+        <v>734</v>
+      </c>
+      <c r="G212" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H212" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="I212" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J212" s="90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="91">
+        <v>3</v>
+      </c>
+      <c r="B213" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C213" s="89" t="s">
+        <v>735</v>
+      </c>
+      <c r="D213" s="45" t="s">
+        <v>733</v>
+      </c>
+      <c r="E213" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F213" s="89" t="s">
+        <v>740</v>
+      </c>
+      <c r="G213" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H213" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="I213" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J213" s="90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="93">
+        <v>4</v>
+      </c>
+      <c r="B214" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C214" s="89" t="s">
+        <v>736</v>
+      </c>
+      <c r="D214" s="45" t="s">
+        <v>748</v>
+      </c>
+      <c r="E214" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F214" s="89" t="s">
+        <v>741</v>
+      </c>
+      <c r="G214" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H214" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="I214" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J214" s="90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="91">
+        <v>5</v>
+      </c>
+      <c r="B215" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C215" s="89" t="s">
+        <v>737</v>
+      </c>
+      <c r="D215" s="45" t="s">
+        <v>749</v>
+      </c>
+      <c r="E215" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F215" s="89" t="s">
+        <v>742</v>
+      </c>
+      <c r="G215" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H215" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="I215" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J215" s="90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="93">
+        <v>6</v>
+      </c>
+      <c r="B216" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C216" s="89" t="s">
+        <v>738</v>
+      </c>
+      <c r="D216" s="45" t="s">
+        <v>750</v>
+      </c>
+      <c r="E216" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F216" s="89" t="s">
+        <v>743</v>
+      </c>
+      <c r="G216" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H216" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="I216" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J216" s="90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="91">
+        <v>7</v>
+      </c>
+      <c r="B217" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C217" s="89" t="s">
+        <v>739</v>
+      </c>
+      <c r="D217" s="45" t="s">
+        <v>751</v>
+      </c>
+      <c r="E217" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F217" s="89" t="s">
+        <v>744</v>
+      </c>
+      <c r="G217" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H217" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="I217" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J217" s="90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="93">
+        <v>8</v>
+      </c>
+      <c r="B218" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C218" s="89" t="s">
+        <v>745</v>
+      </c>
+      <c r="D218" s="45" t="s">
+        <v>762</v>
+      </c>
+      <c r="E218" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F218" s="89" t="s">
+        <v>746</v>
+      </c>
+      <c r="G218" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H218" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="I218" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J218" s="90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="91">
+        <v>9</v>
+      </c>
+      <c r="B219" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C219" s="89" t="s">
+        <v>752</v>
+      </c>
+      <c r="D219" s="45" t="s">
+        <v>767</v>
+      </c>
+      <c r="E219" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F219" s="89" t="s">
+        <v>757</v>
+      </c>
+      <c r="G219" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H219" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="I219" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J219" s="90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="93">
+        <v>10</v>
+      </c>
+      <c r="B220" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C220" s="89" t="s">
+        <v>753</v>
+      </c>
+      <c r="D220" s="45" t="s">
+        <v>766</v>
+      </c>
+      <c r="E220" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F220" s="89" t="s">
+        <v>758</v>
+      </c>
+      <c r="G220" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H220" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="I220" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J220" s="90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="91">
+        <v>11</v>
+      </c>
+      <c r="B221" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C221" s="89" t="s">
+        <v>754</v>
+      </c>
+      <c r="D221" s="45" t="s">
+        <v>765</v>
+      </c>
+      <c r="E221" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F221" s="89" t="s">
+        <v>759</v>
+      </c>
+      <c r="G221" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H221" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="I221" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J221" s="90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="93">
+        <v>12</v>
+      </c>
+      <c r="B222" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C222" s="89" t="s">
+        <v>755</v>
+      </c>
+      <c r="D222" s="45" t="s">
+        <v>764</v>
+      </c>
+      <c r="E222" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F222" s="89" t="s">
+        <v>760</v>
+      </c>
+      <c r="G222" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H222" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="I222" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J222" s="90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A223" s="91">
+        <v>13</v>
+      </c>
+      <c r="B223" s="88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C223" s="89" t="s">
+        <v>756</v>
+      </c>
+      <c r="D223" s="45" t="s">
+        <v>763</v>
+      </c>
+      <c r="E223" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F223" s="89" t="s">
+        <v>761</v>
+      </c>
+      <c r="G223" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H223" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="I223" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J223" s="90" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A59:J59"/>
-    <mergeCell ref="A70:J70"/>
-    <mergeCell ref="A84:J84"/>
+  <mergeCells count="17">
+    <mergeCell ref="A210:J210"/>
     <mergeCell ref="A202:J202"/>
     <mergeCell ref="A127:J127"/>
     <mergeCell ref="A125:J125"/>
@@ -11024,6 +11580,11 @@
     <mergeCell ref="A170:J170"/>
     <mergeCell ref="A145:J145"/>
     <mergeCell ref="A156:J156"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A59:J59"/>
+    <mergeCell ref="A70:J70"/>
+    <mergeCell ref="A84:J84"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -11121,7 +11682,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:X203"/>
+  <dimension ref="A1:X216"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -25893,6 +26454,968 @@
         <v>22</v>
       </c>
       <c r="X203" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="204" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A204" s="89" t="s">
+        <v>768</v>
+      </c>
+      <c r="B204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V204" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W204" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X204" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="205" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A205" s="89" t="s">
+        <v>734</v>
+      </c>
+      <c r="B205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V205" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W205" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X205" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="206" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A206" s="89" t="s">
+        <v>740</v>
+      </c>
+      <c r="B206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V206" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W206" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X206" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="207" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A207" s="89" t="s">
+        <v>741</v>
+      </c>
+      <c r="B207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V207" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W207" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X207" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="208" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A208" s="89" t="s">
+        <v>742</v>
+      </c>
+      <c r="B208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V208" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W208" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X208" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="209" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A209" s="89" t="s">
+        <v>743</v>
+      </c>
+      <c r="B209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V209" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W209" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X209" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="210" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A210" s="89" t="s">
+        <v>744</v>
+      </c>
+      <c r="B210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V210" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W210" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X210" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="211" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A211" s="89" t="s">
+        <v>746</v>
+      </c>
+      <c r="B211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V211" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W211" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X211" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="212" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A212" s="89" t="s">
+        <v>757</v>
+      </c>
+      <c r="B212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V212" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W212" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X212" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="213" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A213" s="89" t="s">
+        <v>758</v>
+      </c>
+      <c r="B213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V213" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W213" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X213" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="214" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A214" s="89" t="s">
+        <v>759</v>
+      </c>
+      <c r="B214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V214" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W214" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X214" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="215" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A215" s="89" t="s">
+        <v>760</v>
+      </c>
+      <c r="B215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V215" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W215" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X215" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="216" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A216" s="87" t="s">
+        <v>761</v>
+      </c>
+      <c r="B216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V216" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="W216" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X216" s="48" t="s">
         <v>22</v>
       </c>
     </row>
